--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03F4823-18DA-497B-8C2D-E59295BB8615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0730580-511F-41E7-811B-D29AFA2B5C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="3180" windowWidth="21600" windowHeight="12645" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="22" r:id="rId1"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10129" uniqueCount="2351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10134" uniqueCount="2354">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -10975,6 +10975,15 @@
   </si>
   <si>
     <t>Ratio (%)</t>
+  </si>
+  <si>
+    <t>upri_typ_nm</t>
+  </si>
+  <si>
+    <t>単価区分名</t>
+  </si>
+  <si>
+    <t>Unit price type name</t>
   </si>
 </sst>
 </file>
@@ -13069,6 +13078,45 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="230" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="3" xfId="230" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="229" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -13122,6 +13170,102 @@
     </xf>
     <xf numFmtId="168" fontId="53" fillId="0" borderId="24" xfId="229" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="29" borderId="42" xfId="228" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13193,15 +13337,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13209,132 +13344,6 @@
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="3" xfId="230" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="242">
@@ -14765,130 +14774,130 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:47">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="66" t="s">
         <v>390</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="56"/>
-      <c r="AJ3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="68"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="69"/>
+      <c r="AJ3" s="70" t="s">
         <v>391</v>
       </c>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="58" t="s">
+      <c r="AK3" s="70"/>
+      <c r="AL3" s="70"/>
+      <c r="AM3" s="70"/>
+      <c r="AN3" s="70"/>
+      <c r="AO3" s="70"/>
+      <c r="AP3" s="71" t="s">
         <v>392</v>
       </c>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="60"/>
+      <c r="AQ3" s="72"/>
+      <c r="AR3" s="72"/>
+      <c r="AS3" s="72"/>
+      <c r="AT3" s="72"/>
+      <c r="AU3" s="73"/>
     </row>
     <row r="4" spans="2:47">
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="55"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="56"/>
-      <c r="AJ4" s="57"/>
-      <c r="AK4" s="57"/>
-      <c r="AL4" s="57"/>
-      <c r="AM4" s="57"/>
-      <c r="AN4" s="57"/>
-      <c r="AO4" s="57"/>
-      <c r="AP4" s="58"/>
-      <c r="AQ4" s="59"/>
-      <c r="AR4" s="59"/>
-      <c r="AS4" s="59"/>
-      <c r="AT4" s="59"/>
-      <c r="AU4" s="60"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="AD4" s="68"/>
+      <c r="AE4" s="68"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="69"/>
+      <c r="AJ4" s="70"/>
+      <c r="AK4" s="70"/>
+      <c r="AL4" s="70"/>
+      <c r="AM4" s="70"/>
+      <c r="AN4" s="70"/>
+      <c r="AO4" s="70"/>
+      <c r="AP4" s="71"/>
+      <c r="AQ4" s="72"/>
+      <c r="AR4" s="72"/>
+      <c r="AS4" s="72"/>
+      <c r="AT4" s="72"/>
+      <c r="AU4" s="73"/>
     </row>
     <row r="5" spans="2:47">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="AD5" s="61"/>
-      <c r="AE5" s="62"/>
-      <c r="AF5" s="62"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="63"/>
-      <c r="AJ5" s="64" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="AD5" s="74"/>
+      <c r="AE5" s="75"/>
+      <c r="AF5" s="75"/>
+      <c r="AG5" s="75"/>
+      <c r="AH5" s="75"/>
+      <c r="AI5" s="76"/>
+      <c r="AJ5" s="77" t="s">
         <v>1841</v>
       </c>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="64"/>
-      <c r="AM5" s="64"/>
-      <c r="AN5" s="64"/>
-      <c r="AO5" s="64"/>
-      <c r="AP5" s="65" t="s">
+      <c r="AK5" s="77"/>
+      <c r="AL5" s="77"/>
+      <c r="AM5" s="77"/>
+      <c r="AN5" s="77"/>
+      <c r="AO5" s="77"/>
+      <c r="AP5" s="78" t="s">
         <v>2337</v>
       </c>
-      <c r="AQ5" s="66"/>
-      <c r="AR5" s="66"/>
-      <c r="AS5" s="66"/>
-      <c r="AT5" s="66"/>
-      <c r="AU5" s="67"/>
+      <c r="AQ5" s="79"/>
+      <c r="AR5" s="79"/>
+      <c r="AS5" s="79"/>
+      <c r="AT5" s="79"/>
+      <c r="AU5" s="80"/>
     </row>
     <row r="6" spans="2:47">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="AD6" s="62"/>
-      <c r="AE6" s="62"/>
-      <c r="AF6" s="62"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
-      <c r="AL6" s="64"/>
-      <c r="AM6" s="64"/>
-      <c r="AN6" s="64"/>
-      <c r="AO6" s="64"/>
-      <c r="AP6" s="68"/>
-      <c r="AQ6" s="66"/>
-      <c r="AR6" s="66"/>
-      <c r="AS6" s="66"/>
-      <c r="AT6" s="66"/>
-      <c r="AU6" s="67"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="75"/>
+      <c r="AG6" s="75"/>
+      <c r="AH6" s="75"/>
+      <c r="AI6" s="76"/>
+      <c r="AJ6" s="77"/>
+      <c r="AK6" s="77"/>
+      <c r="AL6" s="77"/>
+      <c r="AM6" s="77"/>
+      <c r="AN6" s="77"/>
+      <c r="AO6" s="77"/>
+      <c r="AP6" s="81"/>
+      <c r="AQ6" s="79"/>
+      <c r="AR6" s="79"/>
+      <c r="AS6" s="79"/>
+      <c r="AT6" s="79"/>
+      <c r="AU6" s="80"/>
     </row>
     <row r="7" spans="2:47" ht="24">
       <c r="B7" s="33" t="s">
@@ -14910,122 +14919,122 @@
       </c>
     </row>
     <row r="15" spans="2:47">
-      <c r="M15" s="51" t="s">
+      <c r="M15" s="64" t="s">
         <v>393</v>
       </c>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="52"/>
-      <c r="R15" s="52"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="52"/>
-      <c r="U15" s="52"/>
-      <c r="V15" s="52"/>
-      <c r="W15" s="52"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="52"/>
-      <c r="Z15" s="52"/>
-      <c r="AA15" s="52"/>
-      <c r="AB15" s="52"/>
-      <c r="AC15" s="52"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="52"/>
-      <c r="AF15" s="52"/>
-      <c r="AG15" s="52"/>
-      <c r="AH15" s="52"/>
-      <c r="AI15" s="52"/>
-      <c r="AJ15" s="52"/>
-      <c r="AK15" s="52"/>
-      <c r="AL15" s="52"/>
-      <c r="AM15" s="52"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="65"/>
+      <c r="AF15" s="65"/>
+      <c r="AG15" s="65"/>
+      <c r="AH15" s="65"/>
+      <c r="AI15" s="65"/>
+      <c r="AJ15" s="65"/>
+      <c r="AK15" s="65"/>
+      <c r="AL15" s="65"/>
+      <c r="AM15" s="65"/>
     </row>
     <row r="16" spans="2:47">
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="52"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="52"/>
-      <c r="U16" s="52"/>
-      <c r="V16" s="52"/>
-      <c r="W16" s="52"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="52"/>
-      <c r="Z16" s="52"/>
-      <c r="AA16" s="52"/>
-      <c r="AB16" s="52"/>
-      <c r="AC16" s="52"/>
-      <c r="AD16" s="52"/>
-      <c r="AE16" s="52"/>
-      <c r="AF16" s="52"/>
-      <c r="AG16" s="52"/>
-      <c r="AH16" s="52"/>
-      <c r="AI16" s="52"/>
-      <c r="AJ16" s="52"/>
-      <c r="AK16" s="52"/>
-      <c r="AL16" s="52"/>
-      <c r="AM16" s="52"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="65"/>
+      <c r="U16" s="65"/>
+      <c r="V16" s="65"/>
+      <c r="W16" s="65"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="65"/>
+      <c r="Z16" s="65"/>
+      <c r="AA16" s="65"/>
+      <c r="AB16" s="65"/>
+      <c r="AC16" s="65"/>
+      <c r="AD16" s="65"/>
+      <c r="AE16" s="65"/>
+      <c r="AF16" s="65"/>
+      <c r="AG16" s="65"/>
+      <c r="AH16" s="65"/>
+      <c r="AI16" s="65"/>
+      <c r="AJ16" s="65"/>
+      <c r="AK16" s="65"/>
+      <c r="AL16" s="65"/>
+      <c r="AM16" s="65"/>
     </row>
     <row r="17" spans="13:39">
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="52"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="52"/>
-      <c r="W17" s="52"/>
-      <c r="X17" s="52"/>
-      <c r="Y17" s="52"/>
-      <c r="Z17" s="52"/>
-      <c r="AA17" s="52"/>
-      <c r="AB17" s="52"/>
-      <c r="AC17" s="52"/>
-      <c r="AD17" s="52"/>
-      <c r="AE17" s="52"/>
-      <c r="AF17" s="52"/>
-      <c r="AG17" s="52"/>
-      <c r="AH17" s="52"/>
-      <c r="AI17" s="52"/>
-      <c r="AJ17" s="52"/>
-      <c r="AK17" s="52"/>
-      <c r="AL17" s="52"/>
-      <c r="AM17" s="52"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="65"/>
+      <c r="Z17" s="65"/>
+      <c r="AA17" s="65"/>
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="65"/>
+      <c r="AD17" s="65"/>
+      <c r="AE17" s="65"/>
+      <c r="AF17" s="65"/>
+      <c r="AG17" s="65"/>
+      <c r="AH17" s="65"/>
+      <c r="AI17" s="65"/>
+      <c r="AJ17" s="65"/>
+      <c r="AK17" s="65"/>
+      <c r="AL17" s="65"/>
+      <c r="AM17" s="65"/>
     </row>
     <row r="18" spans="13:39">
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="52"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="52"/>
-      <c r="U18" s="52"/>
-      <c r="V18" s="52"/>
-      <c r="W18" s="52"/>
-      <c r="X18" s="52"/>
-      <c r="Y18" s="52"/>
-      <c r="Z18" s="52"/>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="52"/>
-      <c r="AC18" s="52"/>
-      <c r="AD18" s="52"/>
-      <c r="AE18" s="52"/>
-      <c r="AF18" s="52"/>
-      <c r="AG18" s="52"/>
-      <c r="AH18" s="52"/>
-      <c r="AI18" s="52"/>
-      <c r="AJ18" s="52"/>
-      <c r="AK18" s="52"/>
-      <c r="AL18" s="52"/>
-      <c r="AM18" s="52"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
+      <c r="Z18" s="65"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="65"/>
+      <c r="AD18" s="65"/>
+      <c r="AE18" s="65"/>
+      <c r="AF18" s="65"/>
+      <c r="AG18" s="65"/>
+      <c r="AH18" s="65"/>
+      <c r="AI18" s="65"/>
+      <c r="AJ18" s="65"/>
+      <c r="AK18" s="65"/>
+      <c r="AL18" s="65"/>
+      <c r="AM18" s="65"/>
     </row>
     <row r="26" spans="13:39" ht="15.75" customHeight="1"/>
     <row r="27" spans="13:39" ht="15.75" customHeight="1"/>
@@ -15065,126 +15074,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="34" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="73" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
-      <c r="AH1" s="74"/>
-      <c r="AI1" s="74"/>
-      <c r="AJ1" s="74"/>
-      <c r="AK1" s="74"/>
-      <c r="AL1" s="74"/>
-      <c r="AM1" s="74"/>
-      <c r="AN1" s="74"/>
-      <c r="AO1" s="74"/>
-      <c r="AP1" s="74"/>
-      <c r="AQ1" s="74"/>
-      <c r="AR1" s="74"/>
-      <c r="AS1" s="74"/>
-      <c r="AT1" s="74"/>
-      <c r="AU1" s="74"/>
-      <c r="AV1" s="74"/>
-      <c r="AW1" s="74"/>
-      <c r="AX1" s="75"/>
-      <c r="AY1" s="69" t="s">
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="119"/>
+      <c r="AJ1" s="119"/>
+      <c r="AK1" s="119"/>
+      <c r="AL1" s="119"/>
+      <c r="AM1" s="119"/>
+      <c r="AN1" s="119"/>
+      <c r="AO1" s="119"/>
+      <c r="AP1" s="119"/>
+      <c r="AQ1" s="119"/>
+      <c r="AR1" s="119"/>
+      <c r="AS1" s="119"/>
+      <c r="AT1" s="119"/>
+      <c r="AU1" s="119"/>
+      <c r="AV1" s="119"/>
+      <c r="AW1" s="119"/>
+      <c r="AX1" s="120"/>
+      <c r="AY1" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="69"/>
-      <c r="BA1" s="69"/>
-      <c r="BB1" s="69"/>
-      <c r="BC1" s="70"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="114"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" s="34" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="77"/>
-      <c r="AD2" s="77"/>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="77"/>
-      <c r="AJ2" s="77"/>
-      <c r="AK2" s="77"/>
-      <c r="AL2" s="77"/>
-      <c r="AM2" s="77"/>
-      <c r="AN2" s="77"/>
-      <c r="AO2" s="77"/>
-      <c r="AP2" s="77"/>
-      <c r="AQ2" s="77"/>
-      <c r="AR2" s="77"/>
-      <c r="AS2" s="77"/>
-      <c r="AT2" s="77"/>
-      <c r="AU2" s="77"/>
-      <c r="AV2" s="77"/>
-      <c r="AW2" s="77"/>
-      <c r="AX2" s="78"/>
-      <c r="AY2" s="71" t="s">
+      <c r="A2" s="132"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="122"/>
+      <c r="AA2" s="122"/>
+      <c r="AB2" s="122"/>
+      <c r="AC2" s="122"/>
+      <c r="AD2" s="122"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="122"/>
+      <c r="AG2" s="122"/>
+      <c r="AH2" s="122"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
+      <c r="AK2" s="122"/>
+      <c r="AL2" s="122"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="122"/>
+      <c r="AO2" s="122"/>
+      <c r="AP2" s="122"/>
+      <c r="AQ2" s="122"/>
+      <c r="AR2" s="122"/>
+      <c r="AS2" s="122"/>
+      <c r="AT2" s="122"/>
+      <c r="AU2" s="122"/>
+      <c r="AV2" s="122"/>
+      <c r="AW2" s="122"/>
+      <c r="AX2" s="123"/>
+      <c r="AY2" s="116" t="s">
         <v>1841</v>
       </c>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71"/>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="72"/>
+      <c r="AZ2" s="116"/>
+      <c r="BA2" s="116"/>
+      <c r="BB2" s="116"/>
+      <c r="BC2" s="117"/>
     </row>
     <row r="3" spans="1:55" s="34" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A3" s="35"/>
@@ -15236,1934 +15245,1951 @@
       <c r="A4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="79" t="s">
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="89"/>
-      <c r="T4" s="89"/>
-      <c r="U4" s="89"/>
-      <c r="V4" s="89"/>
-      <c r="W4" s="89"/>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
-      <c r="AB4" s="89"/>
-      <c r="AC4" s="89"/>
-      <c r="AD4" s="89"/>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="90"/>
-      <c r="AL4" s="90"/>
-      <c r="AM4" s="90"/>
-      <c r="AN4" s="91"/>
-      <c r="AO4" s="82" t="s">
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="134"/>
+      <c r="O4" s="134"/>
+      <c r="P4" s="134"/>
+      <c r="Q4" s="134"/>
+      <c r="R4" s="134"/>
+      <c r="S4" s="134"/>
+      <c r="T4" s="134"/>
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="134"/>
+      <c r="X4" s="134"/>
+      <c r="Y4" s="134"/>
+      <c r="Z4" s="134"/>
+      <c r="AA4" s="134"/>
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="134"/>
+      <c r="AD4" s="134"/>
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="134"/>
+      <c r="AG4" s="134"/>
+      <c r="AH4" s="134"/>
+      <c r="AI4" s="134"/>
+      <c r="AJ4" s="134"/>
+      <c r="AK4" s="135"/>
+      <c r="AL4" s="135"/>
+      <c r="AM4" s="135"/>
+      <c r="AN4" s="136"/>
+      <c r="AO4" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="AP4" s="83"/>
-      <c r="AQ4" s="83"/>
-      <c r="AR4" s="83"/>
-      <c r="AS4" s="83"/>
-      <c r="AT4" s="83"/>
-      <c r="AU4" s="83"/>
-      <c r="AV4" s="83"/>
-      <c r="AW4" s="83"/>
-      <c r="AX4" s="83"/>
-      <c r="AY4" s="83"/>
-      <c r="AZ4" s="83"/>
-      <c r="BA4" s="83"/>
-      <c r="BB4" s="83"/>
-      <c r="BC4" s="84"/>
+      <c r="AP4" s="128"/>
+      <c r="AQ4" s="128"/>
+      <c r="AR4" s="128"/>
+      <c r="AS4" s="128"/>
+      <c r="AT4" s="128"/>
+      <c r="AU4" s="128"/>
+      <c r="AV4" s="128"/>
+      <c r="AW4" s="128"/>
+      <c r="AX4" s="128"/>
+      <c r="AY4" s="128"/>
+      <c r="AZ4" s="128"/>
+      <c r="BA4" s="128"/>
+      <c r="BB4" s="128"/>
+      <c r="BC4" s="129"/>
     </row>
     <row r="5" spans="1:55" ht="15" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>1803</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="117" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="115"/>
-      <c r="S5" s="115"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="115"/>
-      <c r="W5" s="115"/>
-      <c r="X5" s="115"/>
-      <c r="Y5" s="115"/>
-      <c r="Z5" s="115"/>
-      <c r="AA5" s="115"/>
-      <c r="AB5" s="115"/>
-      <c r="AC5" s="115"/>
-      <c r="AD5" s="115"/>
-      <c r="AE5" s="115"/>
-      <c r="AF5" s="115"/>
-      <c r="AG5" s="115"/>
-      <c r="AH5" s="115"/>
-      <c r="AI5" s="115"/>
-      <c r="AJ5" s="115"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="121"/>
-      <c r="AO5" s="114"/>
-      <c r="AP5" s="115"/>
-      <c r="AQ5" s="115"/>
-      <c r="AR5" s="115"/>
-      <c r="AS5" s="115"/>
-      <c r="AT5" s="115"/>
-      <c r="AU5" s="115"/>
-      <c r="AV5" s="115"/>
-      <c r="AW5" s="115"/>
-      <c r="AX5" s="115"/>
-      <c r="AY5" s="115"/>
-      <c r="AZ5" s="115"/>
-      <c r="BA5" s="115"/>
-      <c r="BB5" s="115"/>
-      <c r="BC5" s="116"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94"/>
+      <c r="V5" s="94"/>
+      <c r="W5" s="94"/>
+      <c r="X5" s="94"/>
+      <c r="Y5" s="94"/>
+      <c r="Z5" s="94"/>
+      <c r="AA5" s="94"/>
+      <c r="AB5" s="94"/>
+      <c r="AC5" s="94"/>
+      <c r="AD5" s="94"/>
+      <c r="AE5" s="94"/>
+      <c r="AF5" s="94"/>
+      <c r="AG5" s="94"/>
+      <c r="AH5" s="94"/>
+      <c r="AI5" s="94"/>
+      <c r="AJ5" s="94"/>
+      <c r="AK5" s="95"/>
+      <c r="AL5" s="95"/>
+      <c r="AM5" s="95"/>
+      <c r="AN5" s="96"/>
+      <c r="AO5" s="110"/>
+      <c r="AP5" s="94"/>
+      <c r="AQ5" s="94"/>
+      <c r="AR5" s="94"/>
+      <c r="AS5" s="94"/>
+      <c r="AT5" s="94"/>
+      <c r="AU5" s="94"/>
+      <c r="AV5" s="94"/>
+      <c r="AW5" s="94"/>
+      <c r="AX5" s="94"/>
+      <c r="AY5" s="94"/>
+      <c r="AZ5" s="94"/>
+      <c r="BA5" s="94"/>
+      <c r="BB5" s="94"/>
+      <c r="BC5" s="111"/>
     </row>
     <row r="6" spans="1:55" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
         <v>2334</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="124" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="99" t="s">
         <v>2335</v>
       </c>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="125"/>
-      <c r="M6" s="125"/>
-      <c r="N6" s="125"/>
-      <c r="O6" s="125"/>
-      <c r="P6" s="125"/>
-      <c r="Q6" s="125"/>
-      <c r="R6" s="125"/>
-      <c r="S6" s="125"/>
-      <c r="T6" s="125"/>
-      <c r="U6" s="125"/>
-      <c r="V6" s="125"/>
-      <c r="W6" s="125"/>
-      <c r="X6" s="125"/>
-      <c r="Y6" s="125"/>
-      <c r="Z6" s="125"/>
-      <c r="AA6" s="125"/>
-      <c r="AB6" s="125"/>
-      <c r="AC6" s="125"/>
-      <c r="AD6" s="125"/>
-      <c r="AE6" s="125"/>
-      <c r="AF6" s="125"/>
-      <c r="AG6" s="125"/>
-      <c r="AH6" s="125"/>
-      <c r="AI6" s="125"/>
-      <c r="AJ6" s="125"/>
-      <c r="AK6" s="125"/>
-      <c r="AL6" s="125"/>
-      <c r="AM6" s="125"/>
-      <c r="AN6" s="126"/>
-      <c r="AO6" s="95" t="s">
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="100"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="100"/>
+      <c r="S6" s="100"/>
+      <c r="T6" s="100"/>
+      <c r="U6" s="100"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
+      <c r="X6" s="100"/>
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="100"/>
+      <c r="AA6" s="100"/>
+      <c r="AB6" s="100"/>
+      <c r="AC6" s="100"/>
+      <c r="AD6" s="100"/>
+      <c r="AE6" s="100"/>
+      <c r="AF6" s="100"/>
+      <c r="AG6" s="100"/>
+      <c r="AH6" s="100"/>
+      <c r="AI6" s="100"/>
+      <c r="AJ6" s="100"/>
+      <c r="AK6" s="100"/>
+      <c r="AL6" s="100"/>
+      <c r="AM6" s="100"/>
+      <c r="AN6" s="101"/>
+      <c r="AO6" s="137" t="s">
         <v>2336</v>
       </c>
-      <c r="AP6" s="96"/>
-      <c r="AQ6" s="96"/>
-      <c r="AR6" s="96"/>
-      <c r="AS6" s="96"/>
-      <c r="AT6" s="96"/>
-      <c r="AU6" s="96"/>
-      <c r="AV6" s="96"/>
-      <c r="AW6" s="96"/>
-      <c r="AX6" s="96"/>
-      <c r="AY6" s="96"/>
-      <c r="AZ6" s="96"/>
-      <c r="BA6" s="96"/>
-      <c r="BB6" s="96"/>
-      <c r="BC6" s="97"/>
+      <c r="AP6" s="138"/>
+      <c r="AQ6" s="138"/>
+      <c r="AR6" s="138"/>
+      <c r="AS6" s="138"/>
+      <c r="AT6" s="138"/>
+      <c r="AU6" s="138"/>
+      <c r="AV6" s="138"/>
+      <c r="AW6" s="138"/>
+      <c r="AX6" s="138"/>
+      <c r="AY6" s="138"/>
+      <c r="AZ6" s="138"/>
+      <c r="BA6" s="138"/>
+      <c r="BB6" s="138"/>
+      <c r="BC6" s="139"/>
     </row>
     <row r="7" spans="1:55" ht="15" customHeight="1">
       <c r="A7" s="40"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="99"/>
-      <c r="U7" s="99"/>
-      <c r="V7" s="99"/>
-      <c r="W7" s="99"/>
-      <c r="X7" s="99"/>
-      <c r="Y7" s="99"/>
-      <c r="Z7" s="99"/>
-      <c r="AA7" s="99"/>
-      <c r="AB7" s="99"/>
-      <c r="AC7" s="99"/>
-      <c r="AD7" s="99"/>
-      <c r="AE7" s="99"/>
-      <c r="AF7" s="99"/>
-      <c r="AG7" s="99"/>
-      <c r="AH7" s="99"/>
-      <c r="AI7" s="99"/>
-      <c r="AJ7" s="99"/>
-      <c r="AK7" s="101"/>
-      <c r="AL7" s="101"/>
-      <c r="AM7" s="101"/>
-      <c r="AN7" s="102"/>
-      <c r="AO7" s="98"/>
-      <c r="AP7" s="99"/>
-      <c r="AQ7" s="99"/>
-      <c r="AR7" s="99"/>
-      <c r="AS7" s="99"/>
-      <c r="AT7" s="99"/>
-      <c r="AU7" s="99"/>
-      <c r="AV7" s="99"/>
-      <c r="AW7" s="99"/>
-      <c r="AX7" s="99"/>
-      <c r="AY7" s="99"/>
-      <c r="AZ7" s="99"/>
-      <c r="BA7" s="99"/>
-      <c r="BB7" s="99"/>
-      <c r="BC7" s="100"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="83"/>
+      <c r="X7" s="83"/>
+      <c r="Y7" s="83"/>
+      <c r="Z7" s="83"/>
+      <c r="AA7" s="83"/>
+      <c r="AB7" s="83"/>
+      <c r="AC7" s="83"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="83"/>
+      <c r="AF7" s="83"/>
+      <c r="AG7" s="83"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="83"/>
+      <c r="AJ7" s="83"/>
+      <c r="AK7" s="86"/>
+      <c r="AL7" s="86"/>
+      <c r="AM7" s="86"/>
+      <c r="AN7" s="87"/>
+      <c r="AO7" s="82"/>
+      <c r="AP7" s="83"/>
+      <c r="AQ7" s="83"/>
+      <c r="AR7" s="83"/>
+      <c r="AS7" s="83"/>
+      <c r="AT7" s="83"/>
+      <c r="AU7" s="83"/>
+      <c r="AV7" s="83"/>
+      <c r="AW7" s="83"/>
+      <c r="AX7" s="83"/>
+      <c r="AY7" s="83"/>
+      <c r="AZ7" s="83"/>
+      <c r="BA7" s="83"/>
+      <c r="BB7" s="83"/>
+      <c r="BC7" s="84"/>
     </row>
     <row r="8" spans="1:55" ht="15" customHeight="1">
       <c r="A8" s="40"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99"/>
-      <c r="M8" s="99"/>
-      <c r="N8" s="99"/>
-      <c r="O8" s="99"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="99"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="99"/>
-      <c r="U8" s="99"/>
-      <c r="V8" s="99"/>
-      <c r="W8" s="99"/>
-      <c r="X8" s="99"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
-      <c r="AA8" s="99"/>
-      <c r="AB8" s="99"/>
-      <c r="AC8" s="99"/>
-      <c r="AD8" s="99"/>
-      <c r="AE8" s="99"/>
-      <c r="AF8" s="99"/>
-      <c r="AG8" s="99"/>
-      <c r="AH8" s="99"/>
-      <c r="AI8" s="99"/>
-      <c r="AJ8" s="99"/>
-      <c r="AK8" s="101"/>
-      <c r="AL8" s="101"/>
-      <c r="AM8" s="101"/>
-      <c r="AN8" s="102"/>
-      <c r="AO8" s="98"/>
-      <c r="AP8" s="99"/>
-      <c r="AQ8" s="99"/>
-      <c r="AR8" s="99"/>
-      <c r="AS8" s="99"/>
-      <c r="AT8" s="99"/>
-      <c r="AU8" s="99"/>
-      <c r="AV8" s="99"/>
-      <c r="AW8" s="99"/>
-      <c r="AX8" s="99"/>
-      <c r="AY8" s="99"/>
-      <c r="AZ8" s="99"/>
-      <c r="BA8" s="99"/>
-      <c r="BB8" s="99"/>
-      <c r="BC8" s="100"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="83"/>
+      <c r="V8" s="83"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="83"/>
+      <c r="Y8" s="83"/>
+      <c r="Z8" s="83"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="83"/>
+      <c r="AC8" s="83"/>
+      <c r="AD8" s="83"/>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="83"/>
+      <c r="AG8" s="83"/>
+      <c r="AH8" s="83"/>
+      <c r="AI8" s="83"/>
+      <c r="AJ8" s="83"/>
+      <c r="AK8" s="86"/>
+      <c r="AL8" s="86"/>
+      <c r="AM8" s="86"/>
+      <c r="AN8" s="87"/>
+      <c r="AO8" s="82"/>
+      <c r="AP8" s="83"/>
+      <c r="AQ8" s="83"/>
+      <c r="AR8" s="83"/>
+      <c r="AS8" s="83"/>
+      <c r="AT8" s="83"/>
+      <c r="AU8" s="83"/>
+      <c r="AV8" s="83"/>
+      <c r="AW8" s="83"/>
+      <c r="AX8" s="83"/>
+      <c r="AY8" s="83"/>
+      <c r="AZ8" s="83"/>
+      <c r="BA8" s="83"/>
+      <c r="BB8" s="83"/>
+      <c r="BC8" s="84"/>
     </row>
     <row r="9" spans="1:55" ht="15" customHeight="1">
       <c r="A9" s="40"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="99"/>
-      <c r="T9" s="99"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
-      <c r="AA9" s="99"/>
-      <c r="AB9" s="99"/>
-      <c r="AC9" s="99"/>
-      <c r="AD9" s="99"/>
-      <c r="AE9" s="99"/>
-      <c r="AF9" s="99"/>
-      <c r="AG9" s="99"/>
-      <c r="AH9" s="99"/>
-      <c r="AI9" s="99"/>
-      <c r="AJ9" s="99"/>
-      <c r="AK9" s="101"/>
-      <c r="AL9" s="101"/>
-      <c r="AM9" s="101"/>
-      <c r="AN9" s="102"/>
-      <c r="AO9" s="98"/>
-      <c r="AP9" s="99"/>
-      <c r="AQ9" s="99"/>
-      <c r="AR9" s="99"/>
-      <c r="AS9" s="99"/>
-      <c r="AT9" s="99"/>
-      <c r="AU9" s="99"/>
-      <c r="AV9" s="99"/>
-      <c r="AW9" s="99"/>
-      <c r="AX9" s="99"/>
-      <c r="AY9" s="99"/>
-      <c r="AZ9" s="99"/>
-      <c r="BA9" s="99"/>
-      <c r="BB9" s="99"/>
-      <c r="BC9" s="100"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="86"/>
+      <c r="AL9" s="86"/>
+      <c r="AM9" s="86"/>
+      <c r="AN9" s="87"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="83"/>
+      <c r="AQ9" s="83"/>
+      <c r="AR9" s="83"/>
+      <c r="AS9" s="83"/>
+      <c r="AT9" s="83"/>
+      <c r="AU9" s="83"/>
+      <c r="AV9" s="83"/>
+      <c r="AW9" s="83"/>
+      <c r="AX9" s="83"/>
+      <c r="AY9" s="83"/>
+      <c r="AZ9" s="83"/>
+      <c r="BA9" s="83"/>
+      <c r="BB9" s="83"/>
+      <c r="BC9" s="84"/>
     </row>
     <row r="10" spans="1:55" ht="15" customHeight="1">
       <c r="A10" s="40"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="99"/>
-      <c r="K10" s="99"/>
-      <c r="L10" s="99"/>
-      <c r="M10" s="99"/>
-      <c r="N10" s="99"/>
-      <c r="O10" s="99"/>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="99"/>
-      <c r="R10" s="99"/>
-      <c r="S10" s="99"/>
-      <c r="T10" s="99"/>
-      <c r="U10" s="99"/>
-      <c r="V10" s="99"/>
-      <c r="W10" s="99"/>
-      <c r="X10" s="99"/>
-      <c r="Y10" s="99"/>
-      <c r="Z10" s="99"/>
-      <c r="AA10" s="99"/>
-      <c r="AB10" s="99"/>
-      <c r="AC10" s="99"/>
-      <c r="AD10" s="99"/>
-      <c r="AE10" s="99"/>
-      <c r="AF10" s="99"/>
-      <c r="AG10" s="99"/>
-      <c r="AH10" s="99"/>
-      <c r="AI10" s="99"/>
-      <c r="AJ10" s="99"/>
-      <c r="AK10" s="101"/>
-      <c r="AL10" s="101"/>
-      <c r="AM10" s="101"/>
-      <c r="AN10" s="102"/>
-      <c r="AO10" s="98"/>
-      <c r="AP10" s="99"/>
-      <c r="AQ10" s="99"/>
-      <c r="AR10" s="99"/>
-      <c r="AS10" s="99"/>
-      <c r="AT10" s="99"/>
-      <c r="AU10" s="99"/>
-      <c r="AV10" s="99"/>
-      <c r="AW10" s="99"/>
-      <c r="AX10" s="99"/>
-      <c r="AY10" s="99"/>
-      <c r="AZ10" s="99"/>
-      <c r="BA10" s="99"/>
-      <c r="BB10" s="99"/>
-      <c r="BC10" s="100"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="83"/>
+      <c r="V10" s="83"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="83"/>
+      <c r="Y10" s="83"/>
+      <c r="Z10" s="83"/>
+      <c r="AA10" s="83"/>
+      <c r="AB10" s="83"/>
+      <c r="AC10" s="83"/>
+      <c r="AD10" s="83"/>
+      <c r="AE10" s="83"/>
+      <c r="AF10" s="83"/>
+      <c r="AG10" s="83"/>
+      <c r="AH10" s="83"/>
+      <c r="AI10" s="83"/>
+      <c r="AJ10" s="83"/>
+      <c r="AK10" s="86"/>
+      <c r="AL10" s="86"/>
+      <c r="AM10" s="86"/>
+      <c r="AN10" s="87"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="83"/>
+      <c r="AQ10" s="83"/>
+      <c r="AR10" s="83"/>
+      <c r="AS10" s="83"/>
+      <c r="AT10" s="83"/>
+      <c r="AU10" s="83"/>
+      <c r="AV10" s="83"/>
+      <c r="AW10" s="83"/>
+      <c r="AX10" s="83"/>
+      <c r="AY10" s="83"/>
+      <c r="AZ10" s="83"/>
+      <c r="BA10" s="83"/>
+      <c r="BB10" s="83"/>
+      <c r="BC10" s="84"/>
     </row>
     <row r="11" spans="1:55" ht="15" customHeight="1">
       <c r="A11" s="40"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="99"/>
-      <c r="T11" s="99"/>
-      <c r="U11" s="99"/>
-      <c r="V11" s="99"/>
-      <c r="W11" s="99"/>
-      <c r="X11" s="99"/>
-      <c r="Y11" s="99"/>
-      <c r="Z11" s="99"/>
-      <c r="AA11" s="99"/>
-      <c r="AB11" s="99"/>
-      <c r="AC11" s="99"/>
-      <c r="AD11" s="99"/>
-      <c r="AE11" s="99"/>
-      <c r="AF11" s="99"/>
-      <c r="AG11" s="99"/>
-      <c r="AH11" s="99"/>
-      <c r="AI11" s="99"/>
-      <c r="AJ11" s="99"/>
-      <c r="AK11" s="101"/>
-      <c r="AL11" s="101"/>
-      <c r="AM11" s="101"/>
-      <c r="AN11" s="102"/>
-      <c r="AO11" s="98"/>
-      <c r="AP11" s="99"/>
-      <c r="AQ11" s="99"/>
-      <c r="AR11" s="99"/>
-      <c r="AS11" s="99"/>
-      <c r="AT11" s="99"/>
-      <c r="AU11" s="99"/>
-      <c r="AV11" s="99"/>
-      <c r="AW11" s="99"/>
-      <c r="AX11" s="99"/>
-      <c r="AY11" s="99"/>
-      <c r="AZ11" s="99"/>
-      <c r="BA11" s="99"/>
-      <c r="BB11" s="99"/>
-      <c r="BC11" s="100"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="83"/>
+      <c r="T11" s="83"/>
+      <c r="U11" s="83"/>
+      <c r="V11" s="83"/>
+      <c r="W11" s="83"/>
+      <c r="X11" s="83"/>
+      <c r="Y11" s="83"/>
+      <c r="Z11" s="83"/>
+      <c r="AA11" s="83"/>
+      <c r="AB11" s="83"/>
+      <c r="AC11" s="83"/>
+      <c r="AD11" s="83"/>
+      <c r="AE11" s="83"/>
+      <c r="AF11" s="83"/>
+      <c r="AG11" s="83"/>
+      <c r="AH11" s="83"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="83"/>
+      <c r="AK11" s="86"/>
+      <c r="AL11" s="86"/>
+      <c r="AM11" s="86"/>
+      <c r="AN11" s="87"/>
+      <c r="AO11" s="82"/>
+      <c r="AP11" s="83"/>
+      <c r="AQ11" s="83"/>
+      <c r="AR11" s="83"/>
+      <c r="AS11" s="83"/>
+      <c r="AT11" s="83"/>
+      <c r="AU11" s="83"/>
+      <c r="AV11" s="83"/>
+      <c r="AW11" s="83"/>
+      <c r="AX11" s="83"/>
+      <c r="AY11" s="83"/>
+      <c r="AZ11" s="83"/>
+      <c r="BA11" s="83"/>
+      <c r="BB11" s="83"/>
+      <c r="BC11" s="84"/>
     </row>
     <row r="12" spans="1:55" ht="15" customHeight="1">
       <c r="A12" s="40"/>
-      <c r="B12" s="92"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="99"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="99"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="99"/>
-      <c r="R12" s="99"/>
-      <c r="S12" s="99"/>
-      <c r="T12" s="99"/>
-      <c r="U12" s="99"/>
-      <c r="V12" s="99"/>
-      <c r="W12" s="99"/>
-      <c r="X12" s="99"/>
-      <c r="Y12" s="99"/>
-      <c r="Z12" s="99"/>
-      <c r="AA12" s="99"/>
-      <c r="AB12" s="99"/>
-      <c r="AC12" s="99"/>
-      <c r="AD12" s="99"/>
-      <c r="AE12" s="99"/>
-      <c r="AF12" s="99"/>
-      <c r="AG12" s="99"/>
-      <c r="AH12" s="99"/>
-      <c r="AI12" s="99"/>
-      <c r="AJ12" s="99"/>
-      <c r="AK12" s="101"/>
-      <c r="AL12" s="101"/>
-      <c r="AM12" s="101"/>
-      <c r="AN12" s="102"/>
-      <c r="AO12" s="98"/>
-      <c r="AP12" s="99"/>
-      <c r="AQ12" s="99"/>
-      <c r="AR12" s="99"/>
-      <c r="AS12" s="99"/>
-      <c r="AT12" s="99"/>
-      <c r="AU12" s="99"/>
-      <c r="AV12" s="99"/>
-      <c r="AW12" s="99"/>
-      <c r="AX12" s="99"/>
-      <c r="AY12" s="99"/>
-      <c r="AZ12" s="99"/>
-      <c r="BA12" s="99"/>
-      <c r="BB12" s="99"/>
-      <c r="BC12" s="100"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="83"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="83"/>
+      <c r="U12" s="83"/>
+      <c r="V12" s="83"/>
+      <c r="W12" s="83"/>
+      <c r="X12" s="83"/>
+      <c r="Y12" s="83"/>
+      <c r="Z12" s="83"/>
+      <c r="AA12" s="83"/>
+      <c r="AB12" s="83"/>
+      <c r="AC12" s="83"/>
+      <c r="AD12" s="83"/>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="83"/>
+      <c r="AG12" s="83"/>
+      <c r="AH12" s="83"/>
+      <c r="AI12" s="83"/>
+      <c r="AJ12" s="83"/>
+      <c r="AK12" s="86"/>
+      <c r="AL12" s="86"/>
+      <c r="AM12" s="86"/>
+      <c r="AN12" s="87"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="83"/>
+      <c r="AQ12" s="83"/>
+      <c r="AR12" s="83"/>
+      <c r="AS12" s="83"/>
+      <c r="AT12" s="83"/>
+      <c r="AU12" s="83"/>
+      <c r="AV12" s="83"/>
+      <c r="AW12" s="83"/>
+      <c r="AX12" s="83"/>
+      <c r="AY12" s="83"/>
+      <c r="AZ12" s="83"/>
+      <c r="BA12" s="83"/>
+      <c r="BB12" s="83"/>
+      <c r="BC12" s="84"/>
     </row>
     <row r="13" spans="1:55" ht="15" customHeight="1">
       <c r="A13" s="40"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="99"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="99"/>
-      <c r="S13" s="99"/>
-      <c r="T13" s="99"/>
-      <c r="U13" s="99"/>
-      <c r="V13" s="99"/>
-      <c r="W13" s="99"/>
-      <c r="X13" s="99"/>
-      <c r="Y13" s="99"/>
-      <c r="Z13" s="99"/>
-      <c r="AA13" s="99"/>
-      <c r="AB13" s="99"/>
-      <c r="AC13" s="99"/>
-      <c r="AD13" s="99"/>
-      <c r="AE13" s="99"/>
-      <c r="AF13" s="99"/>
-      <c r="AG13" s="99"/>
-      <c r="AH13" s="99"/>
-      <c r="AI13" s="99"/>
-      <c r="AJ13" s="99"/>
-      <c r="AK13" s="101"/>
-      <c r="AL13" s="101"/>
-      <c r="AM13" s="101"/>
-      <c r="AN13" s="102"/>
-      <c r="AO13" s="98"/>
-      <c r="AP13" s="99"/>
-      <c r="AQ13" s="99"/>
-      <c r="AR13" s="99"/>
-      <c r="AS13" s="99"/>
-      <c r="AT13" s="99"/>
-      <c r="AU13" s="99"/>
-      <c r="AV13" s="99"/>
-      <c r="AW13" s="99"/>
-      <c r="AX13" s="99"/>
-      <c r="AY13" s="99"/>
-      <c r="AZ13" s="99"/>
-      <c r="BA13" s="99"/>
-      <c r="BB13" s="99"/>
-      <c r="BC13" s="100"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="83"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="83"/>
+      <c r="Y13" s="83"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="83"/>
+      <c r="AB13" s="83"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="83"/>
+      <c r="AE13" s="83"/>
+      <c r="AF13" s="83"/>
+      <c r="AG13" s="83"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="83"/>
+      <c r="AK13" s="86"/>
+      <c r="AL13" s="86"/>
+      <c r="AM13" s="86"/>
+      <c r="AN13" s="87"/>
+      <c r="AO13" s="82"/>
+      <c r="AP13" s="83"/>
+      <c r="AQ13" s="83"/>
+      <c r="AR13" s="83"/>
+      <c r="AS13" s="83"/>
+      <c r="AT13" s="83"/>
+      <c r="AU13" s="83"/>
+      <c r="AV13" s="83"/>
+      <c r="AW13" s="83"/>
+      <c r="AX13" s="83"/>
+      <c r="AY13" s="83"/>
+      <c r="AZ13" s="83"/>
+      <c r="BA13" s="83"/>
+      <c r="BB13" s="83"/>
+      <c r="BC13" s="84"/>
     </row>
     <row r="14" spans="1:55" ht="15" customHeight="1">
       <c r="A14" s="40"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="99"/>
-      <c r="O14" s="99"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="99"/>
-      <c r="R14" s="99"/>
-      <c r="S14" s="99"/>
-      <c r="T14" s="99"/>
-      <c r="U14" s="99"/>
-      <c r="V14" s="99"/>
-      <c r="W14" s="99"/>
-      <c r="X14" s="99"/>
-      <c r="Y14" s="99"/>
-      <c r="Z14" s="99"/>
-      <c r="AA14" s="99"/>
-      <c r="AB14" s="99"/>
-      <c r="AC14" s="99"/>
-      <c r="AD14" s="99"/>
-      <c r="AE14" s="99"/>
-      <c r="AF14" s="99"/>
-      <c r="AG14" s="99"/>
-      <c r="AH14" s="99"/>
-      <c r="AI14" s="99"/>
-      <c r="AJ14" s="99"/>
-      <c r="AK14" s="101"/>
-      <c r="AL14" s="101"/>
-      <c r="AM14" s="101"/>
-      <c r="AN14" s="102"/>
-      <c r="AO14" s="98"/>
-      <c r="AP14" s="99"/>
-      <c r="AQ14" s="99"/>
-      <c r="AR14" s="99"/>
-      <c r="AS14" s="99"/>
-      <c r="AT14" s="99"/>
-      <c r="AU14" s="99"/>
-      <c r="AV14" s="99"/>
-      <c r="AW14" s="99"/>
-      <c r="AX14" s="99"/>
-      <c r="AY14" s="99"/>
-      <c r="AZ14" s="99"/>
-      <c r="BA14" s="99"/>
-      <c r="BB14" s="99"/>
-      <c r="BC14" s="100"/>
+      <c r="B14" s="85"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="83"/>
+      <c r="U14" s="83"/>
+      <c r="V14" s="83"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="83"/>
+      <c r="Y14" s="83"/>
+      <c r="Z14" s="83"/>
+      <c r="AA14" s="83"/>
+      <c r="AB14" s="83"/>
+      <c r="AC14" s="83"/>
+      <c r="AD14" s="83"/>
+      <c r="AE14" s="83"/>
+      <c r="AF14" s="83"/>
+      <c r="AG14" s="83"/>
+      <c r="AH14" s="83"/>
+      <c r="AI14" s="83"/>
+      <c r="AJ14" s="83"/>
+      <c r="AK14" s="86"/>
+      <c r="AL14" s="86"/>
+      <c r="AM14" s="86"/>
+      <c r="AN14" s="87"/>
+      <c r="AO14" s="82"/>
+      <c r="AP14" s="83"/>
+      <c r="AQ14" s="83"/>
+      <c r="AR14" s="83"/>
+      <c r="AS14" s="83"/>
+      <c r="AT14" s="83"/>
+      <c r="AU14" s="83"/>
+      <c r="AV14" s="83"/>
+      <c r="AW14" s="83"/>
+      <c r="AX14" s="83"/>
+      <c r="AY14" s="83"/>
+      <c r="AZ14" s="83"/>
+      <c r="BA14" s="83"/>
+      <c r="BB14" s="83"/>
+      <c r="BC14" s="84"/>
     </row>
     <row r="15" spans="1:55" ht="15" customHeight="1">
       <c r="A15" s="40"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="99"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="99"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="99"/>
-      <c r="T15" s="99"/>
-      <c r="U15" s="99"/>
-      <c r="V15" s="99"/>
-      <c r="W15" s="99"/>
-      <c r="X15" s="99"/>
-      <c r="Y15" s="99"/>
-      <c r="Z15" s="99"/>
-      <c r="AA15" s="99"/>
-      <c r="AB15" s="99"/>
-      <c r="AC15" s="99"/>
-      <c r="AD15" s="99"/>
-      <c r="AE15" s="99"/>
-      <c r="AF15" s="99"/>
-      <c r="AG15" s="99"/>
-      <c r="AH15" s="99"/>
-      <c r="AI15" s="99"/>
-      <c r="AJ15" s="99"/>
-      <c r="AK15" s="101"/>
-      <c r="AL15" s="101"/>
-      <c r="AM15" s="101"/>
-      <c r="AN15" s="102"/>
-      <c r="AO15" s="98"/>
-      <c r="AP15" s="99"/>
-      <c r="AQ15" s="99"/>
-      <c r="AR15" s="99"/>
-      <c r="AS15" s="99"/>
-      <c r="AT15" s="99"/>
-      <c r="AU15" s="99"/>
-      <c r="AV15" s="99"/>
-      <c r="AW15" s="99"/>
-      <c r="AX15" s="99"/>
-      <c r="AY15" s="99"/>
-      <c r="AZ15" s="99"/>
-      <c r="BA15" s="99"/>
-      <c r="BB15" s="99"/>
-      <c r="BC15" s="100"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="83"/>
+      <c r="T15" s="83"/>
+      <c r="U15" s="83"/>
+      <c r="V15" s="83"/>
+      <c r="W15" s="83"/>
+      <c r="X15" s="83"/>
+      <c r="Y15" s="83"/>
+      <c r="Z15" s="83"/>
+      <c r="AA15" s="83"/>
+      <c r="AB15" s="83"/>
+      <c r="AC15" s="83"/>
+      <c r="AD15" s="83"/>
+      <c r="AE15" s="83"/>
+      <c r="AF15" s="83"/>
+      <c r="AG15" s="83"/>
+      <c r="AH15" s="83"/>
+      <c r="AI15" s="83"/>
+      <c r="AJ15" s="83"/>
+      <c r="AK15" s="86"/>
+      <c r="AL15" s="86"/>
+      <c r="AM15" s="86"/>
+      <c r="AN15" s="87"/>
+      <c r="AO15" s="82"/>
+      <c r="AP15" s="83"/>
+      <c r="AQ15" s="83"/>
+      <c r="AR15" s="83"/>
+      <c r="AS15" s="83"/>
+      <c r="AT15" s="83"/>
+      <c r="AU15" s="83"/>
+      <c r="AV15" s="83"/>
+      <c r="AW15" s="83"/>
+      <c r="AX15" s="83"/>
+      <c r="AY15" s="83"/>
+      <c r="AZ15" s="83"/>
+      <c r="BA15" s="83"/>
+      <c r="BB15" s="83"/>
+      <c r="BC15" s="84"/>
     </row>
     <row r="16" spans="1:55" ht="15" customHeight="1">
       <c r="A16" s="40"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="99"/>
-      <c r="O16" s="99"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="99"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="99"/>
-      <c r="V16" s="99"/>
-      <c r="W16" s="99"/>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="99"/>
-      <c r="Z16" s="99"/>
-      <c r="AA16" s="99"/>
-      <c r="AB16" s="99"/>
-      <c r="AC16" s="99"/>
-      <c r="AD16" s="99"/>
-      <c r="AE16" s="99"/>
-      <c r="AF16" s="99"/>
-      <c r="AG16" s="99"/>
-      <c r="AH16" s="99"/>
-      <c r="AI16" s="99"/>
-      <c r="AJ16" s="99"/>
-      <c r="AK16" s="101"/>
-      <c r="AL16" s="101"/>
-      <c r="AM16" s="101"/>
-      <c r="AN16" s="102"/>
-      <c r="AO16" s="98"/>
-      <c r="AP16" s="99"/>
-      <c r="AQ16" s="99"/>
-      <c r="AR16" s="99"/>
-      <c r="AS16" s="99"/>
-      <c r="AT16" s="99"/>
-      <c r="AU16" s="99"/>
-      <c r="AV16" s="99"/>
-      <c r="AW16" s="99"/>
-      <c r="AX16" s="99"/>
-      <c r="AY16" s="99"/>
-      <c r="AZ16" s="99"/>
-      <c r="BA16" s="99"/>
-      <c r="BB16" s="99"/>
-      <c r="BC16" s="100"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="83"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="83"/>
+      <c r="S16" s="83"/>
+      <c r="T16" s="83"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="83"/>
+      <c r="W16" s="83"/>
+      <c r="X16" s="83"/>
+      <c r="Y16" s="83"/>
+      <c r="Z16" s="83"/>
+      <c r="AA16" s="83"/>
+      <c r="AB16" s="83"/>
+      <c r="AC16" s="83"/>
+      <c r="AD16" s="83"/>
+      <c r="AE16" s="83"/>
+      <c r="AF16" s="83"/>
+      <c r="AG16" s="83"/>
+      <c r="AH16" s="83"/>
+      <c r="AI16" s="83"/>
+      <c r="AJ16" s="83"/>
+      <c r="AK16" s="86"/>
+      <c r="AL16" s="86"/>
+      <c r="AM16" s="86"/>
+      <c r="AN16" s="87"/>
+      <c r="AO16" s="82"/>
+      <c r="AP16" s="83"/>
+      <c r="AQ16" s="83"/>
+      <c r="AR16" s="83"/>
+      <c r="AS16" s="83"/>
+      <c r="AT16" s="83"/>
+      <c r="AU16" s="83"/>
+      <c r="AV16" s="83"/>
+      <c r="AW16" s="83"/>
+      <c r="AX16" s="83"/>
+      <c r="AY16" s="83"/>
+      <c r="AZ16" s="83"/>
+      <c r="BA16" s="83"/>
+      <c r="BB16" s="83"/>
+      <c r="BC16" s="84"/>
     </row>
     <row r="17" spans="1:55" ht="15" customHeight="1">
       <c r="A17" s="40"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="99"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="99"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="99"/>
-      <c r="R17" s="99"/>
-      <c r="S17" s="99"/>
-      <c r="T17" s="99"/>
-      <c r="U17" s="99"/>
-      <c r="V17" s="99"/>
-      <c r="W17" s="99"/>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="99"/>
-      <c r="Z17" s="99"/>
-      <c r="AA17" s="99"/>
-      <c r="AB17" s="99"/>
-      <c r="AC17" s="99"/>
-      <c r="AD17" s="99"/>
-      <c r="AE17" s="99"/>
-      <c r="AF17" s="99"/>
-      <c r="AG17" s="99"/>
-      <c r="AH17" s="99"/>
-      <c r="AI17" s="99"/>
-      <c r="AJ17" s="99"/>
-      <c r="AK17" s="101"/>
-      <c r="AL17" s="101"/>
-      <c r="AM17" s="101"/>
-      <c r="AN17" s="102"/>
-      <c r="AO17" s="98"/>
-      <c r="AP17" s="99"/>
-      <c r="AQ17" s="99"/>
-      <c r="AR17" s="99"/>
-      <c r="AS17" s="99"/>
-      <c r="AT17" s="99"/>
-      <c r="AU17" s="99"/>
-      <c r="AV17" s="99"/>
-      <c r="AW17" s="99"/>
-      <c r="AX17" s="99"/>
-      <c r="AY17" s="99"/>
-      <c r="AZ17" s="99"/>
-      <c r="BA17" s="99"/>
-      <c r="BB17" s="99"/>
-      <c r="BC17" s="100"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="83"/>
+      <c r="N17" s="83"/>
+      <c r="O17" s="83"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="83"/>
+      <c r="R17" s="83"/>
+      <c r="S17" s="83"/>
+      <c r="T17" s="83"/>
+      <c r="U17" s="83"/>
+      <c r="V17" s="83"/>
+      <c r="W17" s="83"/>
+      <c r="X17" s="83"/>
+      <c r="Y17" s="83"/>
+      <c r="Z17" s="83"/>
+      <c r="AA17" s="83"/>
+      <c r="AB17" s="83"/>
+      <c r="AC17" s="83"/>
+      <c r="AD17" s="83"/>
+      <c r="AE17" s="83"/>
+      <c r="AF17" s="83"/>
+      <c r="AG17" s="83"/>
+      <c r="AH17" s="83"/>
+      <c r="AI17" s="83"/>
+      <c r="AJ17" s="83"/>
+      <c r="AK17" s="86"/>
+      <c r="AL17" s="86"/>
+      <c r="AM17" s="86"/>
+      <c r="AN17" s="87"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="83"/>
+      <c r="AQ17" s="83"/>
+      <c r="AR17" s="83"/>
+      <c r="AS17" s="83"/>
+      <c r="AT17" s="83"/>
+      <c r="AU17" s="83"/>
+      <c r="AV17" s="83"/>
+      <c r="AW17" s="83"/>
+      <c r="AX17" s="83"/>
+      <c r="AY17" s="83"/>
+      <c r="AZ17" s="83"/>
+      <c r="BA17" s="83"/>
+      <c r="BB17" s="83"/>
+      <c r="BC17" s="84"/>
     </row>
     <row r="18" spans="1:55" ht="15" customHeight="1">
       <c r="A18" s="40"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="99"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="99"/>
-      <c r="R18" s="99"/>
-      <c r="S18" s="99"/>
-      <c r="T18" s="99"/>
-      <c r="U18" s="99"/>
-      <c r="V18" s="99"/>
-      <c r="W18" s="99"/>
-      <c r="X18" s="99"/>
-      <c r="Y18" s="99"/>
-      <c r="Z18" s="99"/>
-      <c r="AA18" s="99"/>
-      <c r="AB18" s="99"/>
-      <c r="AC18" s="99"/>
-      <c r="AD18" s="99"/>
-      <c r="AE18" s="99"/>
-      <c r="AF18" s="99"/>
-      <c r="AG18" s="99"/>
-      <c r="AH18" s="99"/>
-      <c r="AI18" s="99"/>
-      <c r="AJ18" s="99"/>
-      <c r="AK18" s="101"/>
-      <c r="AL18" s="101"/>
-      <c r="AM18" s="101"/>
-      <c r="AN18" s="102"/>
-      <c r="AO18" s="98"/>
-      <c r="AP18" s="99"/>
-      <c r="AQ18" s="99"/>
-      <c r="AR18" s="99"/>
-      <c r="AS18" s="99"/>
-      <c r="AT18" s="99"/>
-      <c r="AU18" s="99"/>
-      <c r="AV18" s="99"/>
-      <c r="AW18" s="99"/>
-      <c r="AX18" s="99"/>
-      <c r="AY18" s="99"/>
-      <c r="AZ18" s="99"/>
-      <c r="BA18" s="99"/>
-      <c r="BB18" s="99"/>
-      <c r="BC18" s="100"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="83"/>
+      <c r="N18" s="83"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="83"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="83"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="83"/>
+      <c r="Y18" s="83"/>
+      <c r="Z18" s="83"/>
+      <c r="AA18" s="83"/>
+      <c r="AB18" s="83"/>
+      <c r="AC18" s="83"/>
+      <c r="AD18" s="83"/>
+      <c r="AE18" s="83"/>
+      <c r="AF18" s="83"/>
+      <c r="AG18" s="83"/>
+      <c r="AH18" s="83"/>
+      <c r="AI18" s="83"/>
+      <c r="AJ18" s="83"/>
+      <c r="AK18" s="86"/>
+      <c r="AL18" s="86"/>
+      <c r="AM18" s="86"/>
+      <c r="AN18" s="87"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="83"/>
+      <c r="AQ18" s="83"/>
+      <c r="AR18" s="83"/>
+      <c r="AS18" s="83"/>
+      <c r="AT18" s="83"/>
+      <c r="AU18" s="83"/>
+      <c r="AV18" s="83"/>
+      <c r="AW18" s="83"/>
+      <c r="AX18" s="83"/>
+      <c r="AY18" s="83"/>
+      <c r="AZ18" s="83"/>
+      <c r="BA18" s="83"/>
+      <c r="BB18" s="83"/>
+      <c r="BC18" s="84"/>
     </row>
     <row r="19" spans="1:55" ht="15" customHeight="1">
       <c r="A19" s="40"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="99"/>
-      <c r="S19" s="99"/>
-      <c r="T19" s="99"/>
-      <c r="U19" s="99"/>
-      <c r="V19" s="99"/>
-      <c r="W19" s="99"/>
-      <c r="X19" s="99"/>
-      <c r="Y19" s="99"/>
-      <c r="Z19" s="99"/>
-      <c r="AA19" s="99"/>
-      <c r="AB19" s="99"/>
-      <c r="AC19" s="99"/>
-      <c r="AD19" s="99"/>
-      <c r="AE19" s="99"/>
-      <c r="AF19" s="99"/>
-      <c r="AG19" s="99"/>
-      <c r="AH19" s="99"/>
-      <c r="AI19" s="99"/>
-      <c r="AJ19" s="99"/>
-      <c r="AK19" s="101"/>
-      <c r="AL19" s="101"/>
-      <c r="AM19" s="101"/>
-      <c r="AN19" s="102"/>
-      <c r="AO19" s="98"/>
-      <c r="AP19" s="99"/>
-      <c r="AQ19" s="99"/>
-      <c r="AR19" s="99"/>
-      <c r="AS19" s="99"/>
-      <c r="AT19" s="99"/>
-      <c r="AU19" s="99"/>
-      <c r="AV19" s="99"/>
-      <c r="AW19" s="99"/>
-      <c r="AX19" s="99"/>
-      <c r="AY19" s="99"/>
-      <c r="AZ19" s="99"/>
-      <c r="BA19" s="99"/>
-      <c r="BB19" s="99"/>
-      <c r="BC19" s="100"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="83"/>
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="83"/>
+      <c r="W19" s="83"/>
+      <c r="X19" s="83"/>
+      <c r="Y19" s="83"/>
+      <c r="Z19" s="83"/>
+      <c r="AA19" s="83"/>
+      <c r="AB19" s="83"/>
+      <c r="AC19" s="83"/>
+      <c r="AD19" s="83"/>
+      <c r="AE19" s="83"/>
+      <c r="AF19" s="83"/>
+      <c r="AG19" s="83"/>
+      <c r="AH19" s="83"/>
+      <c r="AI19" s="83"/>
+      <c r="AJ19" s="83"/>
+      <c r="AK19" s="86"/>
+      <c r="AL19" s="86"/>
+      <c r="AM19" s="86"/>
+      <c r="AN19" s="87"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="83"/>
+      <c r="AQ19" s="83"/>
+      <c r="AR19" s="83"/>
+      <c r="AS19" s="83"/>
+      <c r="AT19" s="83"/>
+      <c r="AU19" s="83"/>
+      <c r="AV19" s="83"/>
+      <c r="AW19" s="83"/>
+      <c r="AX19" s="83"/>
+      <c r="AY19" s="83"/>
+      <c r="AZ19" s="83"/>
+      <c r="BA19" s="83"/>
+      <c r="BB19" s="83"/>
+      <c r="BC19" s="84"/>
     </row>
     <row r="20" spans="1:55" ht="15" customHeight="1">
       <c r="A20" s="40"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="99"/>
-      <c r="K20" s="99"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="99"/>
-      <c r="N20" s="99"/>
-      <c r="O20" s="99"/>
-      <c r="P20" s="99"/>
-      <c r="Q20" s="99"/>
-      <c r="R20" s="99"/>
-      <c r="S20" s="99"/>
-      <c r="T20" s="99"/>
-      <c r="U20" s="99"/>
-      <c r="V20" s="99"/>
-      <c r="W20" s="99"/>
-      <c r="X20" s="99"/>
-      <c r="Y20" s="99"/>
-      <c r="Z20" s="99"/>
-      <c r="AA20" s="99"/>
-      <c r="AB20" s="99"/>
-      <c r="AC20" s="99"/>
-      <c r="AD20" s="99"/>
-      <c r="AE20" s="99"/>
-      <c r="AF20" s="99"/>
-      <c r="AG20" s="99"/>
-      <c r="AH20" s="99"/>
-      <c r="AI20" s="99"/>
-      <c r="AJ20" s="99"/>
-      <c r="AK20" s="101"/>
-      <c r="AL20" s="101"/>
-      <c r="AM20" s="101"/>
-      <c r="AN20" s="102"/>
-      <c r="AO20" s="98"/>
-      <c r="AP20" s="99"/>
-      <c r="AQ20" s="99"/>
-      <c r="AR20" s="99"/>
-      <c r="AS20" s="99"/>
-      <c r="AT20" s="99"/>
-      <c r="AU20" s="99"/>
-      <c r="AV20" s="99"/>
-      <c r="AW20" s="99"/>
-      <c r="AX20" s="99"/>
-      <c r="AY20" s="99"/>
-      <c r="AZ20" s="99"/>
-      <c r="BA20" s="99"/>
-      <c r="BB20" s="99"/>
-      <c r="BC20" s="100"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="83"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="86"/>
+      <c r="AL20" s="86"/>
+      <c r="AM20" s="86"/>
+      <c r="AN20" s="87"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="84"/>
     </row>
     <row r="21" spans="1:55" ht="15" customHeight="1">
       <c r="A21" s="40"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="99"/>
-      <c r="Q21" s="99"/>
-      <c r="R21" s="99"/>
-      <c r="S21" s="99"/>
-      <c r="T21" s="99"/>
-      <c r="U21" s="99"/>
-      <c r="V21" s="99"/>
-      <c r="W21" s="99"/>
-      <c r="X21" s="99"/>
-      <c r="Y21" s="99"/>
-      <c r="Z21" s="99"/>
-      <c r="AA21" s="99"/>
-      <c r="AB21" s="99"/>
-      <c r="AC21" s="99"/>
-      <c r="AD21" s="99"/>
-      <c r="AE21" s="99"/>
-      <c r="AF21" s="99"/>
-      <c r="AG21" s="99"/>
-      <c r="AH21" s="99"/>
-      <c r="AI21" s="99"/>
-      <c r="AJ21" s="99"/>
-      <c r="AK21" s="101"/>
-      <c r="AL21" s="101"/>
-      <c r="AM21" s="101"/>
-      <c r="AN21" s="102"/>
-      <c r="AO21" s="98"/>
-      <c r="AP21" s="99"/>
-      <c r="AQ21" s="99"/>
-      <c r="AR21" s="99"/>
-      <c r="AS21" s="99"/>
-      <c r="AT21" s="99"/>
-      <c r="AU21" s="99"/>
-      <c r="AV21" s="99"/>
-      <c r="AW21" s="99"/>
-      <c r="AX21" s="99"/>
-      <c r="AY21" s="99"/>
-      <c r="AZ21" s="99"/>
-      <c r="BA21" s="99"/>
-      <c r="BB21" s="99"/>
-      <c r="BC21" s="100"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="83"/>
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="83"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="83"/>
+      <c r="Y21" s="83"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="83"/>
+      <c r="AB21" s="83"/>
+      <c r="AC21" s="83"/>
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="83"/>
+      <c r="AF21" s="83"/>
+      <c r="AG21" s="83"/>
+      <c r="AH21" s="83"/>
+      <c r="AI21" s="83"/>
+      <c r="AJ21" s="83"/>
+      <c r="AK21" s="86"/>
+      <c r="AL21" s="86"/>
+      <c r="AM21" s="86"/>
+      <c r="AN21" s="87"/>
+      <c r="AO21" s="82"/>
+      <c r="AP21" s="83"/>
+      <c r="AQ21" s="83"/>
+      <c r="AR21" s="83"/>
+      <c r="AS21" s="83"/>
+      <c r="AT21" s="83"/>
+      <c r="AU21" s="83"/>
+      <c r="AV21" s="83"/>
+      <c r="AW21" s="83"/>
+      <c r="AX21" s="83"/>
+      <c r="AY21" s="83"/>
+      <c r="AZ21" s="83"/>
+      <c r="BA21" s="83"/>
+      <c r="BB21" s="83"/>
+      <c r="BC21" s="84"/>
     </row>
     <row r="22" spans="1:55" ht="15" customHeight="1">
       <c r="A22" s="40"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="99"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="99"/>
-      <c r="N22" s="99"/>
-      <c r="O22" s="99"/>
-      <c r="P22" s="99"/>
-      <c r="Q22" s="99"/>
-      <c r="R22" s="99"/>
-      <c r="S22" s="99"/>
-      <c r="T22" s="99"/>
-      <c r="U22" s="99"/>
-      <c r="V22" s="99"/>
-      <c r="W22" s="99"/>
-      <c r="X22" s="99"/>
-      <c r="Y22" s="99"/>
-      <c r="Z22" s="99"/>
-      <c r="AA22" s="99"/>
-      <c r="AB22" s="99"/>
-      <c r="AC22" s="99"/>
-      <c r="AD22" s="99"/>
-      <c r="AE22" s="99"/>
-      <c r="AF22" s="99"/>
-      <c r="AG22" s="99"/>
-      <c r="AH22" s="99"/>
-      <c r="AI22" s="99"/>
-      <c r="AJ22" s="99"/>
-      <c r="AK22" s="101"/>
-      <c r="AL22" s="101"/>
-      <c r="AM22" s="101"/>
-      <c r="AN22" s="102"/>
-      <c r="AO22" s="98"/>
-      <c r="AP22" s="99"/>
-      <c r="AQ22" s="99"/>
-      <c r="AR22" s="99"/>
-      <c r="AS22" s="99"/>
-      <c r="AT22" s="99"/>
-      <c r="AU22" s="99"/>
-      <c r="AV22" s="99"/>
-      <c r="AW22" s="99"/>
-      <c r="AX22" s="99"/>
-      <c r="AY22" s="99"/>
-      <c r="AZ22" s="99"/>
-      <c r="BA22" s="99"/>
-      <c r="BB22" s="99"/>
-      <c r="BC22" s="100"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="83"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="83"/>
+      <c r="T22" s="83"/>
+      <c r="U22" s="83"/>
+      <c r="V22" s="83"/>
+      <c r="W22" s="83"/>
+      <c r="X22" s="83"/>
+      <c r="Y22" s="83"/>
+      <c r="Z22" s="83"/>
+      <c r="AA22" s="83"/>
+      <c r="AB22" s="83"/>
+      <c r="AC22" s="83"/>
+      <c r="AD22" s="83"/>
+      <c r="AE22" s="83"/>
+      <c r="AF22" s="83"/>
+      <c r="AG22" s="83"/>
+      <c r="AH22" s="83"/>
+      <c r="AI22" s="83"/>
+      <c r="AJ22" s="83"/>
+      <c r="AK22" s="86"/>
+      <c r="AL22" s="86"/>
+      <c r="AM22" s="86"/>
+      <c r="AN22" s="87"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="83"/>
+      <c r="AQ22" s="83"/>
+      <c r="AR22" s="83"/>
+      <c r="AS22" s="83"/>
+      <c r="AT22" s="83"/>
+      <c r="AU22" s="83"/>
+      <c r="AV22" s="83"/>
+      <c r="AW22" s="83"/>
+      <c r="AX22" s="83"/>
+      <c r="AY22" s="83"/>
+      <c r="AZ22" s="83"/>
+      <c r="BA22" s="83"/>
+      <c r="BB22" s="83"/>
+      <c r="BC22" s="84"/>
     </row>
     <row r="23" spans="1:55" ht="15" customHeight="1">
       <c r="A23" s="41"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="99"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="99"/>
-      <c r="O23" s="99"/>
-      <c r="P23" s="99"/>
-      <c r="Q23" s="99"/>
-      <c r="R23" s="99"/>
-      <c r="S23" s="99"/>
-      <c r="T23" s="99"/>
-      <c r="U23" s="99"/>
-      <c r="V23" s="99"/>
-      <c r="W23" s="99"/>
-      <c r="X23" s="99"/>
-      <c r="Y23" s="99"/>
-      <c r="Z23" s="99"/>
-      <c r="AA23" s="99"/>
-      <c r="AB23" s="99"/>
-      <c r="AC23" s="99"/>
-      <c r="AD23" s="99"/>
-      <c r="AE23" s="99"/>
-      <c r="AF23" s="99"/>
-      <c r="AG23" s="99"/>
-      <c r="AH23" s="99"/>
-      <c r="AI23" s="99"/>
-      <c r="AJ23" s="99"/>
-      <c r="AK23" s="101"/>
-      <c r="AL23" s="101"/>
-      <c r="AM23" s="101"/>
-      <c r="AN23" s="102"/>
-      <c r="AO23" s="98"/>
-      <c r="AP23" s="99"/>
-      <c r="AQ23" s="99"/>
-      <c r="AR23" s="99"/>
-      <c r="AS23" s="99"/>
-      <c r="AT23" s="99"/>
-      <c r="AU23" s="99"/>
-      <c r="AV23" s="99"/>
-      <c r="AW23" s="99"/>
-      <c r="AX23" s="99"/>
-      <c r="AY23" s="99"/>
-      <c r="AZ23" s="99"/>
-      <c r="BA23" s="99"/>
-      <c r="BB23" s="99"/>
-      <c r="BC23" s="100"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="83"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="83"/>
+      <c r="W23" s="83"/>
+      <c r="X23" s="83"/>
+      <c r="Y23" s="83"/>
+      <c r="Z23" s="83"/>
+      <c r="AA23" s="83"/>
+      <c r="AB23" s="83"/>
+      <c r="AC23" s="83"/>
+      <c r="AD23" s="83"/>
+      <c r="AE23" s="83"/>
+      <c r="AF23" s="83"/>
+      <c r="AG23" s="83"/>
+      <c r="AH23" s="83"/>
+      <c r="AI23" s="83"/>
+      <c r="AJ23" s="83"/>
+      <c r="AK23" s="86"/>
+      <c r="AL23" s="86"/>
+      <c r="AM23" s="86"/>
+      <c r="AN23" s="87"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="83"/>
+      <c r="AQ23" s="83"/>
+      <c r="AR23" s="83"/>
+      <c r="AS23" s="83"/>
+      <c r="AT23" s="83"/>
+      <c r="AU23" s="83"/>
+      <c r="AV23" s="83"/>
+      <c r="AW23" s="83"/>
+      <c r="AX23" s="83"/>
+      <c r="AY23" s="83"/>
+      <c r="AZ23" s="83"/>
+      <c r="BA23" s="83"/>
+      <c r="BB23" s="83"/>
+      <c r="BC23" s="84"/>
     </row>
     <row r="24" spans="1:55" ht="15" customHeight="1">
       <c r="A24" s="41"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="99"/>
-      <c r="N24" s="99"/>
-      <c r="O24" s="99"/>
-      <c r="P24" s="99"/>
-      <c r="Q24" s="99"/>
-      <c r="R24" s="99"/>
-      <c r="S24" s="99"/>
-      <c r="T24" s="99"/>
-      <c r="U24" s="99"/>
-      <c r="V24" s="99"/>
-      <c r="W24" s="99"/>
-      <c r="X24" s="99"/>
-      <c r="Y24" s="99"/>
-      <c r="Z24" s="99"/>
-      <c r="AA24" s="99"/>
-      <c r="AB24" s="99"/>
-      <c r="AC24" s="99"/>
-      <c r="AD24" s="99"/>
-      <c r="AE24" s="99"/>
-      <c r="AF24" s="99"/>
-      <c r="AG24" s="99"/>
-      <c r="AH24" s="99"/>
-      <c r="AI24" s="99"/>
-      <c r="AJ24" s="99"/>
-      <c r="AK24" s="101"/>
-      <c r="AL24" s="101"/>
-      <c r="AM24" s="101"/>
-      <c r="AN24" s="102"/>
-      <c r="AO24" s="98"/>
-      <c r="AP24" s="99"/>
-      <c r="AQ24" s="99"/>
-      <c r="AR24" s="99"/>
-      <c r="AS24" s="99"/>
-      <c r="AT24" s="99"/>
-      <c r="AU24" s="99"/>
-      <c r="AV24" s="99"/>
-      <c r="AW24" s="99"/>
-      <c r="AX24" s="99"/>
-      <c r="AY24" s="99"/>
-      <c r="AZ24" s="99"/>
-      <c r="BA24" s="99"/>
-      <c r="BB24" s="99"/>
-      <c r="BC24" s="100"/>
+      <c r="B24" s="85"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="83"/>
+      <c r="S24" s="83"/>
+      <c r="T24" s="83"/>
+      <c r="U24" s="83"/>
+      <c r="V24" s="83"/>
+      <c r="W24" s="83"/>
+      <c r="X24" s="83"/>
+      <c r="Y24" s="83"/>
+      <c r="Z24" s="83"/>
+      <c r="AA24" s="83"/>
+      <c r="AB24" s="83"/>
+      <c r="AC24" s="83"/>
+      <c r="AD24" s="83"/>
+      <c r="AE24" s="83"/>
+      <c r="AF24" s="83"/>
+      <c r="AG24" s="83"/>
+      <c r="AH24" s="83"/>
+      <c r="AI24" s="83"/>
+      <c r="AJ24" s="83"/>
+      <c r="AK24" s="86"/>
+      <c r="AL24" s="86"/>
+      <c r="AM24" s="86"/>
+      <c r="AN24" s="87"/>
+      <c r="AO24" s="82"/>
+      <c r="AP24" s="83"/>
+      <c r="AQ24" s="83"/>
+      <c r="AR24" s="83"/>
+      <c r="AS24" s="83"/>
+      <c r="AT24" s="83"/>
+      <c r="AU24" s="83"/>
+      <c r="AV24" s="83"/>
+      <c r="AW24" s="83"/>
+      <c r="AX24" s="83"/>
+      <c r="AY24" s="83"/>
+      <c r="AZ24" s="83"/>
+      <c r="BA24" s="83"/>
+      <c r="BB24" s="83"/>
+      <c r="BC24" s="84"/>
     </row>
     <row r="25" spans="1:55" ht="15" customHeight="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="99"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="99"/>
-      <c r="V25" s="99"/>
-      <c r="W25" s="99"/>
-      <c r="X25" s="99"/>
-      <c r="Y25" s="99"/>
-      <c r="Z25" s="99"/>
-      <c r="AA25" s="99"/>
-      <c r="AB25" s="99"/>
-      <c r="AC25" s="99"/>
-      <c r="AD25" s="99"/>
-      <c r="AE25" s="99"/>
-      <c r="AF25" s="99"/>
-      <c r="AG25" s="99"/>
-      <c r="AH25" s="99"/>
-      <c r="AI25" s="99"/>
-      <c r="AJ25" s="99"/>
-      <c r="AK25" s="101"/>
-      <c r="AL25" s="101"/>
-      <c r="AM25" s="101"/>
-      <c r="AN25" s="102"/>
-      <c r="AO25" s="98"/>
-      <c r="AP25" s="99"/>
-      <c r="AQ25" s="99"/>
-      <c r="AR25" s="99"/>
-      <c r="AS25" s="99"/>
-      <c r="AT25" s="99"/>
-      <c r="AU25" s="99"/>
-      <c r="AV25" s="99"/>
-      <c r="AW25" s="99"/>
-      <c r="AX25" s="99"/>
-      <c r="AY25" s="99"/>
-      <c r="AZ25" s="99"/>
-      <c r="BA25" s="99"/>
-      <c r="BB25" s="99"/>
-      <c r="BC25" s="100"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="83"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="83"/>
+      <c r="T25" s="83"/>
+      <c r="U25" s="83"/>
+      <c r="V25" s="83"/>
+      <c r="W25" s="83"/>
+      <c r="X25" s="83"/>
+      <c r="Y25" s="83"/>
+      <c r="Z25" s="83"/>
+      <c r="AA25" s="83"/>
+      <c r="AB25" s="83"/>
+      <c r="AC25" s="83"/>
+      <c r="AD25" s="83"/>
+      <c r="AE25" s="83"/>
+      <c r="AF25" s="83"/>
+      <c r="AG25" s="83"/>
+      <c r="AH25" s="83"/>
+      <c r="AI25" s="83"/>
+      <c r="AJ25" s="83"/>
+      <c r="AK25" s="86"/>
+      <c r="AL25" s="86"/>
+      <c r="AM25" s="86"/>
+      <c r="AN25" s="87"/>
+      <c r="AO25" s="82"/>
+      <c r="AP25" s="83"/>
+      <c r="AQ25" s="83"/>
+      <c r="AR25" s="83"/>
+      <c r="AS25" s="83"/>
+      <c r="AT25" s="83"/>
+      <c r="AU25" s="83"/>
+      <c r="AV25" s="83"/>
+      <c r="AW25" s="83"/>
+      <c r="AX25" s="83"/>
+      <c r="AY25" s="83"/>
+      <c r="AZ25" s="83"/>
+      <c r="BA25" s="83"/>
+      <c r="BB25" s="83"/>
+      <c r="BC25" s="84"/>
     </row>
     <row r="26" spans="1:55" ht="15" customHeight="1">
       <c r="A26" s="40"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="99"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="99"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="99"/>
-      <c r="AB26" s="99"/>
-      <c r="AC26" s="99"/>
-      <c r="AD26" s="99"/>
-      <c r="AE26" s="99"/>
-      <c r="AF26" s="99"/>
-      <c r="AG26" s="99"/>
-      <c r="AH26" s="99"/>
-      <c r="AI26" s="99"/>
-      <c r="AJ26" s="99"/>
-      <c r="AK26" s="101"/>
-      <c r="AL26" s="101"/>
-      <c r="AM26" s="101"/>
-      <c r="AN26" s="102"/>
-      <c r="AO26" s="98"/>
-      <c r="AP26" s="99"/>
-      <c r="AQ26" s="99"/>
-      <c r="AR26" s="99"/>
-      <c r="AS26" s="99"/>
-      <c r="AT26" s="99"/>
-      <c r="AU26" s="99"/>
-      <c r="AV26" s="99"/>
-      <c r="AW26" s="99"/>
-      <c r="AX26" s="99"/>
-      <c r="AY26" s="99"/>
-      <c r="AZ26" s="99"/>
-      <c r="BA26" s="99"/>
-      <c r="BB26" s="99"/>
-      <c r="BC26" s="100"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="83"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="83"/>
+      <c r="S26" s="83"/>
+      <c r="T26" s="83"/>
+      <c r="U26" s="83"/>
+      <c r="V26" s="83"/>
+      <c r="W26" s="83"/>
+      <c r="X26" s="83"/>
+      <c r="Y26" s="83"/>
+      <c r="Z26" s="83"/>
+      <c r="AA26" s="83"/>
+      <c r="AB26" s="83"/>
+      <c r="AC26" s="83"/>
+      <c r="AD26" s="83"/>
+      <c r="AE26" s="83"/>
+      <c r="AF26" s="83"/>
+      <c r="AG26" s="83"/>
+      <c r="AH26" s="83"/>
+      <c r="AI26" s="83"/>
+      <c r="AJ26" s="83"/>
+      <c r="AK26" s="86"/>
+      <c r="AL26" s="86"/>
+      <c r="AM26" s="86"/>
+      <c r="AN26" s="87"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="83"/>
+      <c r="AQ26" s="83"/>
+      <c r="AR26" s="83"/>
+      <c r="AS26" s="83"/>
+      <c r="AT26" s="83"/>
+      <c r="AU26" s="83"/>
+      <c r="AV26" s="83"/>
+      <c r="AW26" s="83"/>
+      <c r="AX26" s="83"/>
+      <c r="AY26" s="83"/>
+      <c r="AZ26" s="83"/>
+      <c r="BA26" s="83"/>
+      <c r="BB26" s="83"/>
+      <c r="BC26" s="84"/>
     </row>
     <row r="27" spans="1:55" ht="15" customHeight="1">
       <c r="A27" s="40"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="92"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="99"/>
-      <c r="O27" s="99"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="99"/>
-      <c r="R27" s="99"/>
-      <c r="S27" s="99"/>
-      <c r="T27" s="99"/>
-      <c r="U27" s="99"/>
-      <c r="V27" s="99"/>
-      <c r="W27" s="99"/>
-      <c r="X27" s="99"/>
-      <c r="Y27" s="99"/>
-      <c r="Z27" s="99"/>
-      <c r="AA27" s="99"/>
-      <c r="AB27" s="99"/>
-      <c r="AC27" s="99"/>
-      <c r="AD27" s="99"/>
-      <c r="AE27" s="99"/>
-      <c r="AF27" s="99"/>
-      <c r="AG27" s="99"/>
-      <c r="AH27" s="99"/>
-      <c r="AI27" s="99"/>
-      <c r="AJ27" s="99"/>
-      <c r="AK27" s="101"/>
-      <c r="AL27" s="101"/>
-      <c r="AM27" s="101"/>
-      <c r="AN27" s="102"/>
-      <c r="AO27" s="98"/>
-      <c r="AP27" s="99"/>
-      <c r="AQ27" s="99"/>
-      <c r="AR27" s="99"/>
-      <c r="AS27" s="99"/>
-      <c r="AT27" s="99"/>
-      <c r="AU27" s="99"/>
-      <c r="AV27" s="99"/>
-      <c r="AW27" s="99"/>
-      <c r="AX27" s="99"/>
-      <c r="AY27" s="99"/>
-      <c r="AZ27" s="99"/>
-      <c r="BA27" s="99"/>
-      <c r="BB27" s="99"/>
-      <c r="BC27" s="100"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="83"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="83"/>
+      <c r="O27" s="83"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="83"/>
+      <c r="S27" s="83"/>
+      <c r="T27" s="83"/>
+      <c r="U27" s="83"/>
+      <c r="V27" s="83"/>
+      <c r="W27" s="83"/>
+      <c r="X27" s="83"/>
+      <c r="Y27" s="83"/>
+      <c r="Z27" s="83"/>
+      <c r="AA27" s="83"/>
+      <c r="AB27" s="83"/>
+      <c r="AC27" s="83"/>
+      <c r="AD27" s="83"/>
+      <c r="AE27" s="83"/>
+      <c r="AF27" s="83"/>
+      <c r="AG27" s="83"/>
+      <c r="AH27" s="83"/>
+      <c r="AI27" s="83"/>
+      <c r="AJ27" s="83"/>
+      <c r="AK27" s="86"/>
+      <c r="AL27" s="86"/>
+      <c r="AM27" s="86"/>
+      <c r="AN27" s="87"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="83"/>
+      <c r="AQ27" s="83"/>
+      <c r="AR27" s="83"/>
+      <c r="AS27" s="83"/>
+      <c r="AT27" s="83"/>
+      <c r="AU27" s="83"/>
+      <c r="AV27" s="83"/>
+      <c r="AW27" s="83"/>
+      <c r="AX27" s="83"/>
+      <c r="AY27" s="83"/>
+      <c r="AZ27" s="83"/>
+      <c r="BA27" s="83"/>
+      <c r="BB27" s="83"/>
+      <c r="BC27" s="84"/>
     </row>
     <row r="28" spans="1:55" ht="15" customHeight="1">
       <c r="A28" s="40"/>
-      <c r="B28" s="92"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="99"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="99"/>
-      <c r="R28" s="99"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="99"/>
-      <c r="V28" s="99"/>
-      <c r="W28" s="99"/>
-      <c r="X28" s="99"/>
-      <c r="Y28" s="99"/>
-      <c r="Z28" s="99"/>
-      <c r="AA28" s="99"/>
-      <c r="AB28" s="99"/>
-      <c r="AC28" s="99"/>
-      <c r="AD28" s="99"/>
-      <c r="AE28" s="99"/>
-      <c r="AF28" s="99"/>
-      <c r="AG28" s="99"/>
-      <c r="AH28" s="99"/>
-      <c r="AI28" s="99"/>
-      <c r="AJ28" s="99"/>
-      <c r="AK28" s="101"/>
-      <c r="AL28" s="101"/>
-      <c r="AM28" s="101"/>
-      <c r="AN28" s="102"/>
-      <c r="AO28" s="98"/>
-      <c r="AP28" s="99"/>
-      <c r="AQ28" s="99"/>
-      <c r="AR28" s="99"/>
-      <c r="AS28" s="99"/>
-      <c r="AT28" s="99"/>
-      <c r="AU28" s="99"/>
-      <c r="AV28" s="99"/>
-      <c r="AW28" s="99"/>
-      <c r="AX28" s="99"/>
-      <c r="AY28" s="99"/>
-      <c r="AZ28" s="99"/>
-      <c r="BA28" s="99"/>
-      <c r="BB28" s="99"/>
-      <c r="BC28" s="100"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="83"/>
+      <c r="T28" s="83"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="83"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="83"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="83"/>
+      <c r="AB28" s="83"/>
+      <c r="AC28" s="83"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="83"/>
+      <c r="AF28" s="83"/>
+      <c r="AG28" s="83"/>
+      <c r="AH28" s="83"/>
+      <c r="AI28" s="83"/>
+      <c r="AJ28" s="83"/>
+      <c r="AK28" s="86"/>
+      <c r="AL28" s="86"/>
+      <c r="AM28" s="86"/>
+      <c r="AN28" s="87"/>
+      <c r="AO28" s="82"/>
+      <c r="AP28" s="83"/>
+      <c r="AQ28" s="83"/>
+      <c r="AR28" s="83"/>
+      <c r="AS28" s="83"/>
+      <c r="AT28" s="83"/>
+      <c r="AU28" s="83"/>
+      <c r="AV28" s="83"/>
+      <c r="AW28" s="83"/>
+      <c r="AX28" s="83"/>
+      <c r="AY28" s="83"/>
+      <c r="AZ28" s="83"/>
+      <c r="BA28" s="83"/>
+      <c r="BB28" s="83"/>
+      <c r="BC28" s="84"/>
     </row>
     <row r="29" spans="1:55" ht="15" customHeight="1">
       <c r="A29" s="40"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="99"/>
-      <c r="K29" s="99"/>
-      <c r="L29" s="99"/>
-      <c r="M29" s="99"/>
-      <c r="N29" s="99"/>
-      <c r="O29" s="99"/>
-      <c r="P29" s="99"/>
-      <c r="Q29" s="99"/>
-      <c r="R29" s="99"/>
-      <c r="S29" s="99"/>
-      <c r="T29" s="99"/>
-      <c r="U29" s="99"/>
-      <c r="V29" s="99"/>
-      <c r="W29" s="99"/>
-      <c r="X29" s="99"/>
-      <c r="Y29" s="99"/>
-      <c r="Z29" s="99"/>
-      <c r="AA29" s="99"/>
-      <c r="AB29" s="99"/>
-      <c r="AC29" s="99"/>
-      <c r="AD29" s="99"/>
-      <c r="AE29" s="99"/>
-      <c r="AF29" s="99"/>
-      <c r="AG29" s="99"/>
-      <c r="AH29" s="99"/>
-      <c r="AI29" s="99"/>
-      <c r="AJ29" s="99"/>
-      <c r="AK29" s="101"/>
-      <c r="AL29" s="101"/>
-      <c r="AM29" s="101"/>
-      <c r="AN29" s="102"/>
-      <c r="AO29" s="98"/>
-      <c r="AP29" s="99"/>
-      <c r="AQ29" s="99"/>
-      <c r="AR29" s="99"/>
-      <c r="AS29" s="99"/>
-      <c r="AT29" s="99"/>
-      <c r="AU29" s="99"/>
-      <c r="AV29" s="99"/>
-      <c r="AW29" s="99"/>
-      <c r="AX29" s="99"/>
-      <c r="AY29" s="99"/>
-      <c r="AZ29" s="99"/>
-      <c r="BA29" s="99"/>
-      <c r="BB29" s="99"/>
-      <c r="BC29" s="100"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="83"/>
+      <c r="O29" s="83"/>
+      <c r="P29" s="83"/>
+      <c r="Q29" s="83"/>
+      <c r="R29" s="83"/>
+      <c r="S29" s="83"/>
+      <c r="T29" s="83"/>
+      <c r="U29" s="83"/>
+      <c r="V29" s="83"/>
+      <c r="W29" s="83"/>
+      <c r="X29" s="83"/>
+      <c r="Y29" s="83"/>
+      <c r="Z29" s="83"/>
+      <c r="AA29" s="83"/>
+      <c r="AB29" s="83"/>
+      <c r="AC29" s="83"/>
+      <c r="AD29" s="83"/>
+      <c r="AE29" s="83"/>
+      <c r="AF29" s="83"/>
+      <c r="AG29" s="83"/>
+      <c r="AH29" s="83"/>
+      <c r="AI29" s="83"/>
+      <c r="AJ29" s="83"/>
+      <c r="AK29" s="86"/>
+      <c r="AL29" s="86"/>
+      <c r="AM29" s="86"/>
+      <c r="AN29" s="87"/>
+      <c r="AO29" s="82"/>
+      <c r="AP29" s="83"/>
+      <c r="AQ29" s="83"/>
+      <c r="AR29" s="83"/>
+      <c r="AS29" s="83"/>
+      <c r="AT29" s="83"/>
+      <c r="AU29" s="83"/>
+      <c r="AV29" s="83"/>
+      <c r="AW29" s="83"/>
+      <c r="AX29" s="83"/>
+      <c r="AY29" s="83"/>
+      <c r="AZ29" s="83"/>
+      <c r="BA29" s="83"/>
+      <c r="BB29" s="83"/>
+      <c r="BC29" s="84"/>
     </row>
     <row r="30" spans="1:55" ht="15" customHeight="1">
       <c r="A30" s="40"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="99"/>
-      <c r="R30" s="99"/>
-      <c r="S30" s="99"/>
-      <c r="T30" s="99"/>
-      <c r="U30" s="99"/>
-      <c r="V30" s="99"/>
-      <c r="W30" s="99"/>
-      <c r="X30" s="99"/>
-      <c r="Y30" s="99"/>
-      <c r="Z30" s="99"/>
-      <c r="AA30" s="99"/>
-      <c r="AB30" s="99"/>
-      <c r="AC30" s="99"/>
-      <c r="AD30" s="99"/>
-      <c r="AE30" s="99"/>
-      <c r="AF30" s="99"/>
-      <c r="AG30" s="99"/>
-      <c r="AH30" s="99"/>
-      <c r="AI30" s="99"/>
-      <c r="AJ30" s="99"/>
-      <c r="AK30" s="101"/>
-      <c r="AL30" s="101"/>
-      <c r="AM30" s="101"/>
-      <c r="AN30" s="102"/>
-      <c r="AO30" s="98"/>
-      <c r="AP30" s="99"/>
-      <c r="AQ30" s="99"/>
-      <c r="AR30" s="99"/>
-      <c r="AS30" s="99"/>
-      <c r="AT30" s="99"/>
-      <c r="AU30" s="99"/>
-      <c r="AV30" s="99"/>
-      <c r="AW30" s="99"/>
-      <c r="AX30" s="99"/>
-      <c r="AY30" s="99"/>
-      <c r="AZ30" s="99"/>
-      <c r="BA30" s="99"/>
-      <c r="BB30" s="99"/>
-      <c r="BC30" s="100"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="83"/>
+      <c r="O30" s="83"/>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="83"/>
+      <c r="R30" s="83"/>
+      <c r="S30" s="83"/>
+      <c r="T30" s="83"/>
+      <c r="U30" s="83"/>
+      <c r="V30" s="83"/>
+      <c r="W30" s="83"/>
+      <c r="X30" s="83"/>
+      <c r="Y30" s="83"/>
+      <c r="Z30" s="83"/>
+      <c r="AA30" s="83"/>
+      <c r="AB30" s="83"/>
+      <c r="AC30" s="83"/>
+      <c r="AD30" s="83"/>
+      <c r="AE30" s="83"/>
+      <c r="AF30" s="83"/>
+      <c r="AG30" s="83"/>
+      <c r="AH30" s="83"/>
+      <c r="AI30" s="83"/>
+      <c r="AJ30" s="83"/>
+      <c r="AK30" s="86"/>
+      <c r="AL30" s="86"/>
+      <c r="AM30" s="86"/>
+      <c r="AN30" s="87"/>
+      <c r="AO30" s="82"/>
+      <c r="AP30" s="83"/>
+      <c r="AQ30" s="83"/>
+      <c r="AR30" s="83"/>
+      <c r="AS30" s="83"/>
+      <c r="AT30" s="83"/>
+      <c r="AU30" s="83"/>
+      <c r="AV30" s="83"/>
+      <c r="AW30" s="83"/>
+      <c r="AX30" s="83"/>
+      <c r="AY30" s="83"/>
+      <c r="AZ30" s="83"/>
+      <c r="BA30" s="83"/>
+      <c r="BB30" s="83"/>
+      <c r="BC30" s="84"/>
     </row>
     <row r="31" spans="1:55" ht="15" customHeight="1">
       <c r="A31" s="40"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="99"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="99"/>
-      <c r="R31" s="99"/>
-      <c r="S31" s="99"/>
-      <c r="T31" s="99"/>
-      <c r="U31" s="99"/>
-      <c r="V31" s="99"/>
-      <c r="W31" s="99"/>
-      <c r="X31" s="99"/>
-      <c r="Y31" s="99"/>
-      <c r="Z31" s="99"/>
-      <c r="AA31" s="99"/>
-      <c r="AB31" s="99"/>
-      <c r="AC31" s="99"/>
-      <c r="AD31" s="99"/>
-      <c r="AE31" s="99"/>
-      <c r="AF31" s="99"/>
-      <c r="AG31" s="99"/>
-      <c r="AH31" s="99"/>
-      <c r="AI31" s="99"/>
-      <c r="AJ31" s="99"/>
-      <c r="AK31" s="101"/>
-      <c r="AL31" s="101"/>
-      <c r="AM31" s="101"/>
-      <c r="AN31" s="102"/>
-      <c r="AO31" s="98"/>
-      <c r="AP31" s="99"/>
-      <c r="AQ31" s="99"/>
-      <c r="AR31" s="99"/>
-      <c r="AS31" s="99"/>
-      <c r="AT31" s="99"/>
-      <c r="AU31" s="99"/>
-      <c r="AV31" s="99"/>
-      <c r="AW31" s="99"/>
-      <c r="AX31" s="99"/>
-      <c r="AY31" s="99"/>
-      <c r="AZ31" s="99"/>
-      <c r="BA31" s="99"/>
-      <c r="BB31" s="99"/>
-      <c r="BC31" s="100"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
+      <c r="M31" s="83"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="83"/>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="83"/>
+      <c r="R31" s="83"/>
+      <c r="S31" s="83"/>
+      <c r="T31" s="83"/>
+      <c r="U31" s="83"/>
+      <c r="V31" s="83"/>
+      <c r="W31" s="83"/>
+      <c r="X31" s="83"/>
+      <c r="Y31" s="83"/>
+      <c r="Z31" s="83"/>
+      <c r="AA31" s="83"/>
+      <c r="AB31" s="83"/>
+      <c r="AC31" s="83"/>
+      <c r="AD31" s="83"/>
+      <c r="AE31" s="83"/>
+      <c r="AF31" s="83"/>
+      <c r="AG31" s="83"/>
+      <c r="AH31" s="83"/>
+      <c r="AI31" s="83"/>
+      <c r="AJ31" s="83"/>
+      <c r="AK31" s="86"/>
+      <c r="AL31" s="86"/>
+      <c r="AM31" s="86"/>
+      <c r="AN31" s="87"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="83"/>
+      <c r="AQ31" s="83"/>
+      <c r="AR31" s="83"/>
+      <c r="AS31" s="83"/>
+      <c r="AT31" s="83"/>
+      <c r="AU31" s="83"/>
+      <c r="AV31" s="83"/>
+      <c r="AW31" s="83"/>
+      <c r="AX31" s="83"/>
+      <c r="AY31" s="83"/>
+      <c r="AZ31" s="83"/>
+      <c r="BA31" s="83"/>
+      <c r="BB31" s="83"/>
+      <c r="BC31" s="84"/>
     </row>
     <row r="32" spans="1:55" ht="15" customHeight="1">
       <c r="A32" s="40"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="92"/>
-      <c r="J32" s="99"/>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
-      <c r="M32" s="99"/>
-      <c r="N32" s="99"/>
-      <c r="O32" s="99"/>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="99"/>
-      <c r="R32" s="99"/>
-      <c r="S32" s="99"/>
-      <c r="T32" s="99"/>
-      <c r="U32" s="99"/>
-      <c r="V32" s="99"/>
-      <c r="W32" s="99"/>
-      <c r="X32" s="99"/>
-      <c r="Y32" s="99"/>
-      <c r="Z32" s="99"/>
-      <c r="AA32" s="99"/>
-      <c r="AB32" s="99"/>
-      <c r="AC32" s="99"/>
-      <c r="AD32" s="99"/>
-      <c r="AE32" s="99"/>
-      <c r="AF32" s="99"/>
-      <c r="AG32" s="99"/>
-      <c r="AH32" s="99"/>
-      <c r="AI32" s="99"/>
-      <c r="AJ32" s="99"/>
-      <c r="AK32" s="101"/>
-      <c r="AL32" s="101"/>
-      <c r="AM32" s="101"/>
-      <c r="AN32" s="102"/>
-      <c r="AO32" s="98"/>
-      <c r="AP32" s="99"/>
-      <c r="AQ32" s="99"/>
-      <c r="AR32" s="99"/>
-      <c r="AS32" s="99"/>
-      <c r="AT32" s="99"/>
-      <c r="AU32" s="99"/>
-      <c r="AV32" s="99"/>
-      <c r="AW32" s="99"/>
-      <c r="AX32" s="99"/>
-      <c r="AY32" s="99"/>
-      <c r="AZ32" s="99"/>
-      <c r="BA32" s="99"/>
-      <c r="BB32" s="99"/>
-      <c r="BC32" s="100"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83"/>
+      <c r="M32" s="83"/>
+      <c r="N32" s="83"/>
+      <c r="O32" s="83"/>
+      <c r="P32" s="83"/>
+      <c r="Q32" s="83"/>
+      <c r="R32" s="83"/>
+      <c r="S32" s="83"/>
+      <c r="T32" s="83"/>
+      <c r="U32" s="83"/>
+      <c r="V32" s="83"/>
+      <c r="W32" s="83"/>
+      <c r="X32" s="83"/>
+      <c r="Y32" s="83"/>
+      <c r="Z32" s="83"/>
+      <c r="AA32" s="83"/>
+      <c r="AB32" s="83"/>
+      <c r="AC32" s="83"/>
+      <c r="AD32" s="83"/>
+      <c r="AE32" s="83"/>
+      <c r="AF32" s="83"/>
+      <c r="AG32" s="83"/>
+      <c r="AH32" s="83"/>
+      <c r="AI32" s="83"/>
+      <c r="AJ32" s="83"/>
+      <c r="AK32" s="86"/>
+      <c r="AL32" s="86"/>
+      <c r="AM32" s="86"/>
+      <c r="AN32" s="87"/>
+      <c r="AO32" s="82"/>
+      <c r="AP32" s="83"/>
+      <c r="AQ32" s="83"/>
+      <c r="AR32" s="83"/>
+      <c r="AS32" s="83"/>
+      <c r="AT32" s="83"/>
+      <c r="AU32" s="83"/>
+      <c r="AV32" s="83"/>
+      <c r="AW32" s="83"/>
+      <c r="AX32" s="83"/>
+      <c r="AY32" s="83"/>
+      <c r="AZ32" s="83"/>
+      <c r="BA32" s="83"/>
+      <c r="BB32" s="83"/>
+      <c r="BC32" s="84"/>
     </row>
     <row r="33" spans="1:55" ht="15" customHeight="1">
       <c r="A33" s="40"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="92"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
-      <c r="M33" s="99"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="99"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="99"/>
-      <c r="R33" s="99"/>
-      <c r="S33" s="99"/>
-      <c r="T33" s="99"/>
-      <c r="U33" s="99"/>
-      <c r="V33" s="99"/>
-      <c r="W33" s="99"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="99"/>
-      <c r="Z33" s="99"/>
-      <c r="AA33" s="99"/>
-      <c r="AB33" s="99"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="99"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="99"/>
-      <c r="AG33" s="99"/>
-      <c r="AH33" s="99"/>
-      <c r="AI33" s="99"/>
-      <c r="AJ33" s="99"/>
-      <c r="AK33" s="101"/>
-      <c r="AL33" s="101"/>
-      <c r="AM33" s="101"/>
-      <c r="AN33" s="102"/>
-      <c r="AO33" s="98"/>
-      <c r="AP33" s="99"/>
-      <c r="AQ33" s="99"/>
-      <c r="AR33" s="99"/>
-      <c r="AS33" s="99"/>
-      <c r="AT33" s="99"/>
-      <c r="AU33" s="99"/>
-      <c r="AV33" s="99"/>
-      <c r="AW33" s="99"/>
-      <c r="AX33" s="99"/>
-      <c r="AY33" s="99"/>
-      <c r="AZ33" s="99"/>
-      <c r="BA33" s="99"/>
-      <c r="BB33" s="99"/>
-      <c r="BC33" s="100"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="83"/>
+      <c r="M33" s="83"/>
+      <c r="N33" s="83"/>
+      <c r="O33" s="83"/>
+      <c r="P33" s="83"/>
+      <c r="Q33" s="83"/>
+      <c r="R33" s="83"/>
+      <c r="S33" s="83"/>
+      <c r="T33" s="83"/>
+      <c r="U33" s="83"/>
+      <c r="V33" s="83"/>
+      <c r="W33" s="83"/>
+      <c r="X33" s="83"/>
+      <c r="Y33" s="83"/>
+      <c r="Z33" s="83"/>
+      <c r="AA33" s="83"/>
+      <c r="AB33" s="83"/>
+      <c r="AC33" s="83"/>
+      <c r="AD33" s="83"/>
+      <c r="AE33" s="83"/>
+      <c r="AF33" s="83"/>
+      <c r="AG33" s="83"/>
+      <c r="AH33" s="83"/>
+      <c r="AI33" s="83"/>
+      <c r="AJ33" s="83"/>
+      <c r="AK33" s="86"/>
+      <c r="AL33" s="86"/>
+      <c r="AM33" s="86"/>
+      <c r="AN33" s="87"/>
+      <c r="AO33" s="82"/>
+      <c r="AP33" s="83"/>
+      <c r="AQ33" s="83"/>
+      <c r="AR33" s="83"/>
+      <c r="AS33" s="83"/>
+      <c r="AT33" s="83"/>
+      <c r="AU33" s="83"/>
+      <c r="AV33" s="83"/>
+      <c r="AW33" s="83"/>
+      <c r="AX33" s="83"/>
+      <c r="AY33" s="83"/>
+      <c r="AZ33" s="83"/>
+      <c r="BA33" s="83"/>
+      <c r="BB33" s="83"/>
+      <c r="BC33" s="84"/>
     </row>
     <row r="34" spans="1:55" ht="15" customHeight="1">
       <c r="A34" s="40"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="99"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="99"/>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="99"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="99"/>
-      <c r="R34" s="99"/>
-      <c r="S34" s="99"/>
-      <c r="T34" s="99"/>
-      <c r="U34" s="99"/>
-      <c r="V34" s="99"/>
-      <c r="W34" s="99"/>
-      <c r="X34" s="99"/>
-      <c r="Y34" s="99"/>
-      <c r="Z34" s="99"/>
-      <c r="AA34" s="99"/>
-      <c r="AB34" s="99"/>
-      <c r="AC34" s="99"/>
-      <c r="AD34" s="99"/>
-      <c r="AE34" s="99"/>
-      <c r="AF34" s="99"/>
-      <c r="AG34" s="99"/>
-      <c r="AH34" s="99"/>
-      <c r="AI34" s="99"/>
-      <c r="AJ34" s="99"/>
-      <c r="AK34" s="101"/>
-      <c r="AL34" s="101"/>
-      <c r="AM34" s="101"/>
-      <c r="AN34" s="102"/>
-      <c r="AO34" s="98"/>
-      <c r="AP34" s="99"/>
-      <c r="AQ34" s="99"/>
-      <c r="AR34" s="99"/>
-      <c r="AS34" s="99"/>
-      <c r="AT34" s="99"/>
-      <c r="AU34" s="99"/>
-      <c r="AV34" s="99"/>
-      <c r="AW34" s="99"/>
-      <c r="AX34" s="99"/>
-      <c r="AY34" s="99"/>
-      <c r="AZ34" s="99"/>
-      <c r="BA34" s="99"/>
-      <c r="BB34" s="99"/>
-      <c r="BC34" s="100"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
+      <c r="L34" s="83"/>
+      <c r="M34" s="83"/>
+      <c r="N34" s="83"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="83"/>
+      <c r="Q34" s="83"/>
+      <c r="R34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="83"/>
+      <c r="V34" s="83"/>
+      <c r="W34" s="83"/>
+      <c r="X34" s="83"/>
+      <c r="Y34" s="83"/>
+      <c r="Z34" s="83"/>
+      <c r="AA34" s="83"/>
+      <c r="AB34" s="83"/>
+      <c r="AC34" s="83"/>
+      <c r="AD34" s="83"/>
+      <c r="AE34" s="83"/>
+      <c r="AF34" s="83"/>
+      <c r="AG34" s="83"/>
+      <c r="AH34" s="83"/>
+      <c r="AI34" s="83"/>
+      <c r="AJ34" s="83"/>
+      <c r="AK34" s="86"/>
+      <c r="AL34" s="86"/>
+      <c r="AM34" s="86"/>
+      <c r="AN34" s="87"/>
+      <c r="AO34" s="82"/>
+      <c r="AP34" s="83"/>
+      <c r="AQ34" s="83"/>
+      <c r="AR34" s="83"/>
+      <c r="AS34" s="83"/>
+      <c r="AT34" s="83"/>
+      <c r="AU34" s="83"/>
+      <c r="AV34" s="83"/>
+      <c r="AW34" s="83"/>
+      <c r="AX34" s="83"/>
+      <c r="AY34" s="83"/>
+      <c r="AZ34" s="83"/>
+      <c r="BA34" s="83"/>
+      <c r="BB34" s="83"/>
+      <c r="BC34" s="84"/>
     </row>
     <row r="35" spans="1:55" ht="15" customHeight="1">
       <c r="A35" s="40"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="99"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="99"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="99"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="99"/>
-      <c r="R35" s="99"/>
-      <c r="S35" s="99"/>
-      <c r="T35" s="99"/>
-      <c r="U35" s="99"/>
-      <c r="V35" s="99"/>
-      <c r="W35" s="99"/>
-      <c r="X35" s="99"/>
-      <c r="Y35" s="99"/>
-      <c r="Z35" s="99"/>
-      <c r="AA35" s="99"/>
-      <c r="AB35" s="99"/>
-      <c r="AC35" s="99"/>
-      <c r="AD35" s="99"/>
-      <c r="AE35" s="99"/>
-      <c r="AF35" s="99"/>
-      <c r="AG35" s="99"/>
-      <c r="AH35" s="99"/>
-      <c r="AI35" s="99"/>
-      <c r="AJ35" s="99"/>
-      <c r="AK35" s="101"/>
-      <c r="AL35" s="101"/>
-      <c r="AM35" s="101"/>
-      <c r="AN35" s="102"/>
-      <c r="AO35" s="98"/>
-      <c r="AP35" s="99"/>
-      <c r="AQ35" s="99"/>
-      <c r="AR35" s="99"/>
-      <c r="AS35" s="99"/>
-      <c r="AT35" s="99"/>
-      <c r="AU35" s="99"/>
-      <c r="AV35" s="99"/>
-      <c r="AW35" s="99"/>
-      <c r="AX35" s="99"/>
-      <c r="AY35" s="99"/>
-      <c r="AZ35" s="99"/>
-      <c r="BA35" s="99"/>
-      <c r="BB35" s="99"/>
-      <c r="BC35" s="100"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="83"/>
+      <c r="N35" s="83"/>
+      <c r="O35" s="83"/>
+      <c r="P35" s="83"/>
+      <c r="Q35" s="83"/>
+      <c r="R35" s="83"/>
+      <c r="S35" s="83"/>
+      <c r="T35" s="83"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+      <c r="Z35" s="83"/>
+      <c r="AA35" s="83"/>
+      <c r="AB35" s="83"/>
+      <c r="AC35" s="83"/>
+      <c r="AD35" s="83"/>
+      <c r="AE35" s="83"/>
+      <c r="AF35" s="83"/>
+      <c r="AG35" s="83"/>
+      <c r="AH35" s="83"/>
+      <c r="AI35" s="83"/>
+      <c r="AJ35" s="83"/>
+      <c r="AK35" s="86"/>
+      <c r="AL35" s="86"/>
+      <c r="AM35" s="86"/>
+      <c r="AN35" s="87"/>
+      <c r="AO35" s="82"/>
+      <c r="AP35" s="83"/>
+      <c r="AQ35" s="83"/>
+      <c r="AR35" s="83"/>
+      <c r="AS35" s="83"/>
+      <c r="AT35" s="83"/>
+      <c r="AU35" s="83"/>
+      <c r="AV35" s="83"/>
+      <c r="AW35" s="83"/>
+      <c r="AX35" s="83"/>
+      <c r="AY35" s="83"/>
+      <c r="AZ35" s="83"/>
+      <c r="BA35" s="83"/>
+      <c r="BB35" s="83"/>
+      <c r="BC35" s="84"/>
     </row>
     <row r="36" spans="1:55" ht="15" customHeight="1" thickBot="1">
       <c r="A36" s="42"/>
-      <c r="B36" s="109"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="112"/>
-      <c r="H36" s="113"/>
-      <c r="I36" s="109"/>
-      <c r="J36" s="107"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="107"/>
-      <c r="N36" s="107"/>
-      <c r="O36" s="107"/>
-      <c r="P36" s="107"/>
-      <c r="Q36" s="107"/>
-      <c r="R36" s="107"/>
-      <c r="S36" s="107"/>
-      <c r="T36" s="107"/>
-      <c r="U36" s="107"/>
-      <c r="V36" s="107"/>
-      <c r="W36" s="107"/>
-      <c r="X36" s="107"/>
-      <c r="Y36" s="107"/>
-      <c r="Z36" s="107"/>
-      <c r="AA36" s="107"/>
-      <c r="AB36" s="107"/>
-      <c r="AC36" s="107"/>
-      <c r="AD36" s="107"/>
-      <c r="AE36" s="107"/>
-      <c r="AF36" s="107"/>
-      <c r="AG36" s="107"/>
-      <c r="AH36" s="107"/>
-      <c r="AI36" s="107"/>
-      <c r="AJ36" s="107"/>
-      <c r="AK36" s="110"/>
-      <c r="AL36" s="110"/>
-      <c r="AM36" s="110"/>
-      <c r="AN36" s="111"/>
-      <c r="AO36" s="106"/>
-      <c r="AP36" s="107"/>
-      <c r="AQ36" s="107"/>
-      <c r="AR36" s="107"/>
-      <c r="AS36" s="107"/>
-      <c r="AT36" s="107"/>
-      <c r="AU36" s="107"/>
-      <c r="AV36" s="107"/>
-      <c r="AW36" s="107"/>
-      <c r="AX36" s="107"/>
-      <c r="AY36" s="107"/>
-      <c r="AZ36" s="107"/>
-      <c r="BA36" s="107"/>
-      <c r="BB36" s="107"/>
-      <c r="BC36" s="108"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="103"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
+      <c r="P36" s="103"/>
+      <c r="Q36" s="103"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="103"/>
+      <c r="T36" s="103"/>
+      <c r="U36" s="103"/>
+      <c r="V36" s="103"/>
+      <c r="W36" s="103"/>
+      <c r="X36" s="103"/>
+      <c r="Y36" s="103"/>
+      <c r="Z36" s="103"/>
+      <c r="AA36" s="103"/>
+      <c r="AB36" s="103"/>
+      <c r="AC36" s="103"/>
+      <c r="AD36" s="103"/>
+      <c r="AE36" s="103"/>
+      <c r="AF36" s="103"/>
+      <c r="AG36" s="103"/>
+      <c r="AH36" s="103"/>
+      <c r="AI36" s="103"/>
+      <c r="AJ36" s="103"/>
+      <c r="AK36" s="106"/>
+      <c r="AL36" s="106"/>
+      <c r="AM36" s="106"/>
+      <c r="AN36" s="107"/>
+      <c r="AO36" s="102"/>
+      <c r="AP36" s="103"/>
+      <c r="AQ36" s="103"/>
+      <c r="AR36" s="103"/>
+      <c r="AS36" s="103"/>
+      <c r="AT36" s="103"/>
+      <c r="AU36" s="103"/>
+      <c r="AV36" s="103"/>
+      <c r="AW36" s="103"/>
+      <c r="AX36" s="103"/>
+      <c r="AY36" s="103"/>
+      <c r="AZ36" s="103"/>
+      <c r="BA36" s="103"/>
+      <c r="BB36" s="103"/>
+      <c r="BC36" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="AO24:BC24"/>
-    <mergeCell ref="I24:AN24"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I28:AN28"/>
-    <mergeCell ref="AO27:BC27"/>
-    <mergeCell ref="AO28:BC28"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I29:AN29"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:AN25"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="AO23:BC23"/>
-    <mergeCell ref="I23:AN23"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="AO13:BC13"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="I12:AN12"/>
-    <mergeCell ref="I11:AN11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="AO19:BC19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:AN21"/>
-    <mergeCell ref="AO21:BC21"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:AN20"/>
-    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="AY2:BC2"/>
+    <mergeCell ref="I1:AX2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="AO4:BC4"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I4:AN4"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="AO6:BC6"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="AO29:BC29"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="AO14:BC14"/>
+    <mergeCell ref="AO9:BC9"/>
+    <mergeCell ref="AO8:BC8"/>
+    <mergeCell ref="I10:AN10"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:AN14"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:AN32"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="AO36:BC36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AO35:BC35"/>
+    <mergeCell ref="I35:AN35"/>
+    <mergeCell ref="I36:AN36"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="I33:AN33"/>
+    <mergeCell ref="AO5:BC5"/>
+    <mergeCell ref="AO34:BC34"/>
+    <mergeCell ref="I34:AN34"/>
+    <mergeCell ref="AO33:BC33"/>
+    <mergeCell ref="I27:AN27"/>
+    <mergeCell ref="AO7:BC7"/>
+    <mergeCell ref="AO32:BC32"/>
+    <mergeCell ref="AO26:BC26"/>
+    <mergeCell ref="AO22:BC22"/>
+    <mergeCell ref="AO30:BC30"/>
+    <mergeCell ref="AO31:BC31"/>
+    <mergeCell ref="I26:AN26"/>
+    <mergeCell ref="I30:AN30"/>
+    <mergeCell ref="I31:AN31"/>
+    <mergeCell ref="AO25:BC25"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I9:AN9"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="I5:AN5"/>
@@ -17188,54 +17214,37 @@
     <mergeCell ref="AO16:BC16"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="I19:AN19"/>
-    <mergeCell ref="AO36:BC36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="AO35:BC35"/>
-    <mergeCell ref="I35:AN35"/>
-    <mergeCell ref="I36:AN36"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="I33:AN33"/>
-    <mergeCell ref="AO5:BC5"/>
-    <mergeCell ref="AO34:BC34"/>
-    <mergeCell ref="I34:AN34"/>
-    <mergeCell ref="AO33:BC33"/>
-    <mergeCell ref="I27:AN27"/>
-    <mergeCell ref="AO7:BC7"/>
-    <mergeCell ref="AO32:BC32"/>
-    <mergeCell ref="AO26:BC26"/>
-    <mergeCell ref="AO22:BC22"/>
-    <mergeCell ref="AO30:BC30"/>
-    <mergeCell ref="AO31:BC31"/>
-    <mergeCell ref="I26:AN26"/>
-    <mergeCell ref="I30:AN30"/>
-    <mergeCell ref="I31:AN31"/>
-    <mergeCell ref="AO25:BC25"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I9:AN9"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="AY2:BC2"/>
-    <mergeCell ref="I1:AX2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="AO4:BC4"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I4:AN4"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="AO6:BC6"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="AO29:BC29"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="AO14:BC14"/>
-    <mergeCell ref="AO9:BC9"/>
-    <mergeCell ref="AO8:BC8"/>
-    <mergeCell ref="I10:AN10"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:AN14"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:AN32"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="AO23:BC23"/>
+    <mergeCell ref="I23:AN23"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="I11:AN11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="AO19:BC19"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:AN21"/>
+    <mergeCell ref="AO21:BC21"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:AN20"/>
+    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="AO24:BC24"/>
+    <mergeCell ref="I24:AN24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I28:AN28"/>
+    <mergeCell ref="AO27:BC27"/>
+    <mergeCell ref="AO28:BC28"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I29:AN29"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:AN25"/>
   </mergeCells>
   <phoneticPr fontId="36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -17293,17 +17302,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
       <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:11">
@@ -17354,15 +17363,15 @@
       <c r="K6" s="47"/>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="B7" s="127"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
       <c r="K7" s="47"/>
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1">
@@ -17452,17 +17461,17 @@
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="127" t="s">
+      <c r="B15" s="58" t="s">
         <v>1839</v>
       </c>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="129"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
       <c r="K15" s="46"/>
     </row>
     <row r="16" spans="1:11" ht="36">
@@ -17590,17 +17599,17 @@
     </row>
     <row r="22" spans="1:11" ht="12" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="127" t="s">
+      <c r="B22" s="58" t="s">
         <v>1805</v>
       </c>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="128"/>
-      <c r="J22" s="129"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="60"/>
       <c r="K22" s="46"/>
     </row>
     <row r="23" spans="1:11" ht="36">
@@ -17730,17 +17739,17 @@
     </row>
     <row r="29" spans="1:11" ht="12" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="127" t="s">
+      <c r="B29" s="58" t="s">
         <v>1806</v>
       </c>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="129"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="60"/>
       <c r="K29" s="46"/>
     </row>
     <row r="30" spans="1:11" ht="36">
@@ -17870,17 +17879,17 @@
     </row>
     <row r="36" spans="1:11" ht="12" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="127" t="s">
+      <c r="B36" s="58" t="s">
         <v>1808</v>
       </c>
-      <c r="C36" s="128"/>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="128"/>
-      <c r="H36" s="128"/>
-      <c r="I36" s="128"/>
-      <c r="J36" s="129"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="60"/>
       <c r="K36" s="46"/>
     </row>
     <row r="37" spans="1:11" ht="36">
@@ -18010,17 +18019,17 @@
     </row>
     <row r="43" spans="1:11" s="25" customFormat="1" ht="12" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="127" t="s">
+      <c r="B43" s="58" t="s">
         <v>1810</v>
       </c>
-      <c r="C43" s="128"/>
-      <c r="D43" s="128"/>
-      <c r="E43" s="128"/>
-      <c r="F43" s="128"/>
-      <c r="G43" s="128"/>
-      <c r="H43" s="128"/>
-      <c r="I43" s="128"/>
-      <c r="J43" s="129"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="60"/>
       <c r="K43" s="48"/>
     </row>
     <row r="44" spans="1:11" s="25" customFormat="1" ht="36">
@@ -18125,17 +18134,17 @@
     </row>
     <row r="49" spans="1:11" ht="48" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="127" t="s">
+      <c r="B49" s="58" t="s">
         <v>1811</v>
       </c>
-      <c r="C49" s="128"/>
-      <c r="D49" s="128"/>
-      <c r="E49" s="128"/>
-      <c r="F49" s="128"/>
-      <c r="G49" s="128"/>
-      <c r="H49" s="128"/>
-      <c r="I49" s="128"/>
-      <c r="J49" s="129"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="60"/>
       <c r="K49" s="46"/>
     </row>
     <row r="50" spans="1:11">
@@ -18280,17 +18289,17 @@
     </row>
     <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="127" t="s">
+      <c r="B57" s="58" t="s">
         <v>1813</v>
       </c>
-      <c r="C57" s="128"/>
-      <c r="D57" s="128"/>
-      <c r="E57" s="128"/>
-      <c r="F57" s="128"/>
-      <c r="G57" s="128"/>
-      <c r="H57" s="128"/>
-      <c r="I57" s="128"/>
-      <c r="J57" s="129"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="60"/>
       <c r="K57" s="46"/>
     </row>
     <row r="58" spans="1:11" ht="36">
@@ -18395,17 +18404,17 @@
     </row>
     <row r="63" spans="1:11" ht="24" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="127" t="s">
+      <c r="B63" s="58" t="s">
         <v>1815</v>
       </c>
-      <c r="C63" s="128"/>
-      <c r="D63" s="128"/>
-      <c r="E63" s="128"/>
-      <c r="F63" s="128"/>
-      <c r="G63" s="128"/>
-      <c r="H63" s="128"/>
-      <c r="I63" s="128"/>
-      <c r="J63" s="129"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59"/>
+      <c r="J63" s="60"/>
       <c r="K63" s="46"/>
     </row>
     <row r="64" spans="1:11" ht="36">
@@ -18510,17 +18519,17 @@
     </row>
     <row r="69" spans="1:11" ht="24" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="127" t="s">
+      <c r="B69" s="58" t="s">
         <v>1817</v>
       </c>
-      <c r="C69" s="128"/>
-      <c r="D69" s="128"/>
-      <c r="E69" s="128"/>
-      <c r="F69" s="128"/>
-      <c r="G69" s="128"/>
-      <c r="H69" s="128"/>
-      <c r="I69" s="128"/>
-      <c r="J69" s="129"/>
+      <c r="C69" s="59"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="59"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="59"/>
+      <c r="J69" s="60"/>
       <c r="K69" s="46"/>
     </row>
     <row r="70" spans="1:11" ht="36">
@@ -18625,17 +18634,17 @@
     </row>
     <row r="75" spans="1:11" ht="12" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="127" t="s">
+      <c r="B75" s="58" t="s">
         <v>1818</v>
       </c>
-      <c r="C75" s="128"/>
-      <c r="D75" s="128"/>
-      <c r="E75" s="128"/>
-      <c r="F75" s="128"/>
-      <c r="G75" s="128"/>
-      <c r="H75" s="128"/>
-      <c r="I75" s="128"/>
-      <c r="J75" s="129"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="60"/>
       <c r="K75" s="46"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -19201,17 +19210,17 @@
     </row>
     <row r="101" spans="1:11" ht="12" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="127" t="s">
+      <c r="B101" s="58" t="s">
         <v>1819</v>
       </c>
-      <c r="C101" s="128"/>
-      <c r="D101" s="128"/>
-      <c r="E101" s="128"/>
-      <c r="F101" s="128"/>
-      <c r="G101" s="128"/>
-      <c r="H101" s="128"/>
-      <c r="I101" s="128"/>
-      <c r="J101" s="129"/>
+      <c r="C101" s="59"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="59"/>
+      <c r="F101" s="59"/>
+      <c r="G101" s="59"/>
+      <c r="H101" s="59"/>
+      <c r="I101" s="59"/>
+      <c r="J101" s="60"/>
       <c r="K101" s="46"/>
     </row>
     <row r="102" spans="1:11" ht="12" customHeight="1">
@@ -19730,17 +19739,17 @@
     </row>
     <row r="125" spans="1:11" ht="12" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="127" t="s">
+      <c r="B125" s="58" t="s">
         <v>1820</v>
       </c>
-      <c r="C125" s="128"/>
-      <c r="D125" s="128"/>
-      <c r="E125" s="128"/>
-      <c r="F125" s="128"/>
-      <c r="G125" s="128"/>
-      <c r="H125" s="128"/>
-      <c r="I125" s="128"/>
-      <c r="J125" s="129"/>
+      <c r="C125" s="59"/>
+      <c r="D125" s="59"/>
+      <c r="E125" s="59"/>
+      <c r="F125" s="59"/>
+      <c r="G125" s="59"/>
+      <c r="H125" s="59"/>
+      <c r="I125" s="59"/>
+      <c r="J125" s="60"/>
       <c r="K125" s="46"/>
     </row>
     <row r="126" spans="1:11" ht="36">
@@ -20259,17 +20268,17 @@
     </row>
     <row r="149" spans="1:11" ht="12" customHeight="1">
       <c r="A149" s="1"/>
-      <c r="B149" s="127" t="s">
+      <c r="B149" s="58" t="s">
         <v>1822</v>
       </c>
-      <c r="C149" s="128"/>
-      <c r="D149" s="128"/>
-      <c r="E149" s="128"/>
-      <c r="F149" s="128"/>
-      <c r="G149" s="128"/>
-      <c r="H149" s="128"/>
-      <c r="I149" s="128"/>
-      <c r="J149" s="129"/>
+      <c r="C149" s="59"/>
+      <c r="D149" s="59"/>
+      <c r="E149" s="59"/>
+      <c r="F149" s="59"/>
+      <c r="G149" s="59"/>
+      <c r="H149" s="59"/>
+      <c r="I149" s="59"/>
+      <c r="J149" s="60"/>
       <c r="K149" s="46"/>
     </row>
     <row r="150" spans="1:11" ht="36">
@@ -20512,17 +20521,17 @@
     </row>
     <row r="161" spans="1:11" ht="24" customHeight="1">
       <c r="A161" s="1"/>
-      <c r="B161" s="127" t="s">
+      <c r="B161" s="58" t="s">
         <v>1824</v>
       </c>
-      <c r="C161" s="128"/>
-      <c r="D161" s="128"/>
-      <c r="E161" s="128"/>
-      <c r="F161" s="128"/>
-      <c r="G161" s="128"/>
-      <c r="H161" s="128"/>
-      <c r="I161" s="128"/>
-      <c r="J161" s="129"/>
+      <c r="C161" s="59"/>
+      <c r="D161" s="59"/>
+      <c r="E161" s="59"/>
+      <c r="F161" s="59"/>
+      <c r="G161" s="59"/>
+      <c r="H161" s="59"/>
+      <c r="I161" s="59"/>
+      <c r="J161" s="60"/>
       <c r="K161" s="46"/>
     </row>
     <row r="162" spans="1:11">
@@ -20694,17 +20703,17 @@
     </row>
     <row r="170" spans="1:11" ht="12" customHeight="1">
       <c r="A170" s="1"/>
-      <c r="B170" s="127" t="s">
+      <c r="B170" s="58" t="s">
         <v>1818</v>
       </c>
-      <c r="C170" s="128"/>
-      <c r="D170" s="128"/>
-      <c r="E170" s="128"/>
-      <c r="F170" s="128"/>
-      <c r="G170" s="128"/>
-      <c r="H170" s="128"/>
-      <c r="I170" s="128"/>
-      <c r="J170" s="129"/>
+      <c r="C170" s="59"/>
+      <c r="D170" s="59"/>
+      <c r="E170" s="59"/>
+      <c r="F170" s="59"/>
+      <c r="G170" s="59"/>
+      <c r="H170" s="59"/>
+      <c r="I170" s="59"/>
+      <c r="J170" s="60"/>
       <c r="K170" s="46"/>
     </row>
     <row r="171" spans="1:11" ht="36">
@@ -21382,17 +21391,17 @@
     </row>
     <row r="202" spans="1:11" ht="24" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="127" t="s">
+      <c r="B202" s="58" t="s">
         <v>1827</v>
       </c>
-      <c r="C202" s="128"/>
-      <c r="D202" s="128"/>
-      <c r="E202" s="128"/>
-      <c r="F202" s="128"/>
-      <c r="G202" s="128"/>
-      <c r="H202" s="128"/>
-      <c r="I202" s="128"/>
-      <c r="J202" s="129"/>
+      <c r="C202" s="59"/>
+      <c r="D202" s="59"/>
+      <c r="E202" s="59"/>
+      <c r="F202" s="59"/>
+      <c r="G202" s="59"/>
+      <c r="H202" s="59"/>
+      <c r="I202" s="59"/>
+      <c r="J202" s="60"/>
       <c r="K202" s="46"/>
     </row>
     <row r="203" spans="1:11" ht="12" customHeight="1">
@@ -30558,17 +30567,17 @@
     </row>
     <row r="620" spans="1:11" ht="24" customHeight="1">
       <c r="A620" s="1"/>
-      <c r="B620" s="127" t="s">
+      <c r="B620" s="58" t="s">
         <v>1829</v>
       </c>
-      <c r="C620" s="128"/>
-      <c r="D620" s="128"/>
-      <c r="E620" s="128"/>
-      <c r="F620" s="128"/>
-      <c r="G620" s="128"/>
-      <c r="H620" s="128"/>
-      <c r="I620" s="128"/>
-      <c r="J620" s="129"/>
+      <c r="C620" s="59"/>
+      <c r="D620" s="59"/>
+      <c r="E620" s="59"/>
+      <c r="F620" s="59"/>
+      <c r="G620" s="59"/>
+      <c r="H620" s="59"/>
+      <c r="I620" s="59"/>
+      <c r="J620" s="60"/>
       <c r="K620" s="46"/>
     </row>
     <row r="621" spans="1:11" ht="12" customHeight="1">
@@ -39756,17 +39765,17 @@
     </row>
     <row r="1039" spans="1:11" ht="24" customHeight="1">
       <c r="A1039" s="1"/>
-      <c r="B1039" s="127" t="s">
+      <c r="B1039" s="58" t="s">
         <v>1831</v>
       </c>
-      <c r="C1039" s="128"/>
-      <c r="D1039" s="128"/>
-      <c r="E1039" s="128"/>
-      <c r="F1039" s="128"/>
-      <c r="G1039" s="128"/>
-      <c r="H1039" s="128"/>
-      <c r="I1039" s="128"/>
-      <c r="J1039" s="129"/>
+      <c r="C1039" s="59"/>
+      <c r="D1039" s="59"/>
+      <c r="E1039" s="59"/>
+      <c r="F1039" s="59"/>
+      <c r="G1039" s="59"/>
+      <c r="H1039" s="59"/>
+      <c r="I1039" s="59"/>
+      <c r="J1039" s="60"/>
       <c r="K1039" s="46"/>
     </row>
     <row r="1040" spans="1:11" ht="12" customHeight="1">
@@ -48995,6 +49004,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B101:J101"/>
+    <mergeCell ref="B125:J125"/>
+    <mergeCell ref="B202:J202"/>
+    <mergeCell ref="B620:J620"/>
+    <mergeCell ref="B1039:J1039"/>
+    <mergeCell ref="B170:J170"/>
+    <mergeCell ref="B161:J161"/>
+    <mergeCell ref="B149:J149"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B15:J15"/>
@@ -49007,14 +49024,6 @@
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B36:J36"/>
     <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B101:J101"/>
-    <mergeCell ref="B125:J125"/>
-    <mergeCell ref="B202:J202"/>
-    <mergeCell ref="B620:J620"/>
-    <mergeCell ref="B1039:J1039"/>
-    <mergeCell ref="B170:J170"/>
-    <mergeCell ref="B161:J161"/>
-    <mergeCell ref="B149:J149"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -49073,17 +49082,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
       <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11">
@@ -49142,7 +49151,7 @@
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K620"/>
+  <dimension ref="A1:K621"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="9" customWidth="1"/>
@@ -49185,17 +49194,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
       <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:11">
@@ -49239,15 +49248,15 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
       <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:11">
@@ -49329,17 +49338,17 @@
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="127" t="s">
+      <c r="B14" s="58" t="s">
         <v>1832</v>
       </c>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="129"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="60"/>
       <c r="K14" s="46"/>
     </row>
     <row r="15" spans="1:11" ht="36">
@@ -49708,17 +49717,17 @@
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="58" t="s">
         <v>1833</v>
       </c>
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="131"/>
-      <c r="G32" s="131"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
-      <c r="J32" s="132"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="63"/>
       <c r="K32" s="46"/>
     </row>
     <row r="33" spans="1:11" ht="24">
@@ -49928,7 +49937,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="60">
+    <row r="42" spans="1:11" ht="48">
       <c r="B42" s="6" t="s">
         <v>102</v>
       </c>
@@ -50100,17 +50109,17 @@
     </row>
     <row r="50" spans="1:11" ht="12" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="127" t="s">
+      <c r="B50" s="58" t="s">
         <v>1835</v>
       </c>
-      <c r="C50" s="131"/>
-      <c r="D50" s="131"/>
-      <c r="E50" s="131"/>
-      <c r="F50" s="131"/>
-      <c r="G50" s="131"/>
-      <c r="H50" s="131"/>
-      <c r="I50" s="131"/>
-      <c r="J50" s="132"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="J50" s="63"/>
       <c r="K50" s="46"/>
     </row>
     <row r="51" spans="1:11" ht="36">
@@ -51272,17 +51281,17 @@
     </row>
     <row r="102" spans="1:11" ht="24" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="127" t="s">
+      <c r="B102" s="58" t="s">
         <v>1840</v>
       </c>
-      <c r="C102" s="128"/>
-      <c r="D102" s="128"/>
-      <c r="E102" s="128"/>
-      <c r="F102" s="128"/>
-      <c r="G102" s="128"/>
-      <c r="H102" s="128"/>
-      <c r="I102" s="128"/>
-      <c r="J102" s="129"/>
+      <c r="C102" s="59"/>
+      <c r="D102" s="59"/>
+      <c r="E102" s="59"/>
+      <c r="F102" s="59"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="59"/>
+      <c r="I102" s="59"/>
+      <c r="J102" s="60"/>
       <c r="K102" s="46"/>
     </row>
     <row r="103" spans="1:11" ht="36">
@@ -52089,17 +52098,17 @@
     </row>
     <row r="139" spans="1:11" ht="24" customHeight="1">
       <c r="A139" s="1"/>
-      <c r="B139" s="127" t="s">
+      <c r="B139" s="58" t="s">
         <v>1838</v>
       </c>
-      <c r="C139" s="128"/>
-      <c r="D139" s="128"/>
-      <c r="E139" s="128"/>
-      <c r="F139" s="128"/>
-      <c r="G139" s="128"/>
-      <c r="H139" s="128"/>
-      <c r="I139" s="128"/>
-      <c r="J139" s="129"/>
+      <c r="C139" s="59"/>
+      <c r="D139" s="59"/>
+      <c r="E139" s="59"/>
+      <c r="F139" s="59"/>
+      <c r="G139" s="59"/>
+      <c r="H139" s="59"/>
+      <c r="I139" s="59"/>
+      <c r="J139" s="60"/>
       <c r="K139" s="46"/>
     </row>
     <row r="140" spans="1:11" ht="24">
@@ -57001,7 +57010,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="353" spans="1:11" ht="60">
+    <row r="353" spans="1:11" ht="48">
       <c r="A353" s="1"/>
       <c r="B353" s="6" t="s">
         <v>37</v>
@@ -63083,95 +63092,118 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="617" spans="1:11" s="139" customFormat="1">
-      <c r="A617" s="133"/>
-      <c r="B617" s="134" t="s">
-        <v>37</v>
-      </c>
-      <c r="C617" s="134" t="s">
+    <row r="617" spans="1:11" s="57" customFormat="1">
+      <c r="A617" s="51"/>
+      <c r="B617" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C617" s="52" t="s">
         <v>2339</v>
       </c>
-      <c r="D617" s="134" t="s">
+      <c r="D617" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="E617" s="134"/>
-      <c r="F617" s="134"/>
-      <c r="G617" s="135" t="s">
+      <c r="E617" s="52"/>
+      <c r="F617" s="52"/>
+      <c r="G617" s="53" t="s">
         <v>2343</v>
       </c>
-      <c r="H617" s="136"/>
-      <c r="I617" s="136"/>
-      <c r="J617" s="137"/>
-      <c r="K617" s="138" t="s">
+      <c r="H617" s="54"/>
+      <c r="I617" s="54"/>
+      <c r="J617" s="55"/>
+      <c r="K617" s="56" t="s">
         <v>2347</v>
       </c>
     </row>
-    <row r="618" spans="1:11" s="139" customFormat="1">
-      <c r="A618" s="133"/>
-      <c r="B618" s="134" t="s">
-        <v>37</v>
-      </c>
-      <c r="C618" s="134" t="s">
+    <row r="618" spans="1:11" s="57" customFormat="1">
+      <c r="A618" s="51"/>
+      <c r="B618" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C618" s="52" t="s">
         <v>2340</v>
       </c>
-      <c r="D618" s="134" t="s">
+      <c r="D618" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="E618" s="134"/>
-      <c r="F618" s="134"/>
-      <c r="G618" s="135" t="s">
+      <c r="E618" s="52"/>
+      <c r="F618" s="52"/>
+      <c r="G618" s="53" t="s">
         <v>2344</v>
       </c>
-      <c r="H618" s="136"/>
-      <c r="I618" s="136"/>
-      <c r="J618" s="137"/>
-      <c r="K618" s="138" t="s">
+      <c r="H618" s="54"/>
+      <c r="I618" s="54"/>
+      <c r="J618" s="55"/>
+      <c r="K618" s="56" t="s">
         <v>2348</v>
       </c>
     </row>
-    <row r="619" spans="1:11" s="139" customFormat="1">
-      <c r="A619" s="133"/>
-      <c r="B619" s="134" t="s">
-        <v>37</v>
-      </c>
-      <c r="C619" s="134" t="s">
+    <row r="619" spans="1:11" s="57" customFormat="1">
+      <c r="A619" s="51"/>
+      <c r="B619" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C619" s="52" t="s">
         <v>2341</v>
       </c>
-      <c r="D619" s="134" t="s">
+      <c r="D619" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="E619" s="134"/>
-      <c r="F619" s="134"/>
-      <c r="G619" s="135" t="s">
+      <c r="E619" s="52"/>
+      <c r="F619" s="52"/>
+      <c r="G619" s="53" t="s">
         <v>2345</v>
       </c>
-      <c r="H619" s="136"/>
-      <c r="I619" s="136"/>
-      <c r="J619" s="137"/>
-      <c r="K619" s="138" t="s">
+      <c r="H619" s="54"/>
+      <c r="I619" s="54"/>
+      <c r="J619" s="55"/>
+      <c r="K619" s="56" t="s">
         <v>2349</v>
       </c>
     </row>
-    <row r="620" spans="1:11" s="139" customFormat="1">
-      <c r="A620" s="133"/>
-      <c r="B620" s="134" t="s">
-        <v>37</v>
-      </c>
-      <c r="C620" s="134" t="s">
+    <row r="620" spans="1:11" s="57" customFormat="1">
+      <c r="A620" s="51"/>
+      <c r="B620" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C620" s="52" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D620" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E620" s="52"/>
+      <c r="F620" s="52"/>
+      <c r="G620" s="53" t="s">
+        <v>2352</v>
+      </c>
+      <c r="H620" s="54"/>
+      <c r="I620" s="54"/>
+      <c r="J620" s="55"/>
+      <c r="K620" s="56" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="621" spans="1:11" s="57" customFormat="1">
+      <c r="A621" s="51"/>
+      <c r="B621" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C621" s="52" t="s">
         <v>2342</v>
       </c>
-      <c r="D620" s="134" t="s">
+      <c r="D621" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="E620" s="134"/>
-      <c r="F620" s="134"/>
-      <c r="G620" s="135" t="s">
+      <c r="E621" s="52"/>
+      <c r="F621" s="52"/>
+      <c r="G621" s="53" t="s">
         <v>2346</v>
       </c>
-      <c r="H620" s="136"/>
-      <c r="I620" s="136"/>
-      <c r="J620" s="137"/>
-      <c r="K620" s="138" t="s">
+      <c r="H621" s="54"/>
+      <c r="I621" s="54"/>
+      <c r="J621" s="55"/>
+      <c r="K621" s="56" t="s">
         <v>2350</v>
       </c>
     </row>

--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0730580-511F-41E7-811B-D29AFA2B5C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B7F650-5C82-4CB8-A681-9A9F50552EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10134" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10142" uniqueCount="2358">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -10984,6 +10984,18 @@
   </si>
   <si>
     <t>Unit price type name</t>
+  </si>
+  <si>
+    <t>trd_cur_dscnt_amt</t>
+  </si>
+  <si>
+    <t>trd_cur_amt</t>
+  </si>
+  <si>
+    <t>値引</t>
+  </si>
+  <si>
+    <t>金額（値引き後）</t>
   </si>
 </sst>
 </file>
@@ -49151,7 +49163,7 @@
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K621"/>
+  <dimension ref="A1:K623"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="9" customWidth="1"/>
@@ -61557,7 +61569,7 @@
         <v>37</v>
       </c>
       <c r="C550" s="6" t="s">
-        <v>1570</v>
+        <v>801</v>
       </c>
       <c r="D550" s="6" t="s">
         <v>151</v>
@@ -63206,6 +63218,48 @@
       <c r="K621" s="56" t="s">
         <v>2350</v>
       </c>
+    </row>
+    <row r="622" spans="1:11" s="57" customFormat="1">
+      <c r="A622" s="51"/>
+      <c r="B622" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C622" s="52" t="s">
+        <v>2354</v>
+      </c>
+      <c r="D622" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E622" s="52"/>
+      <c r="F622" s="52"/>
+      <c r="G622" s="53" t="s">
+        <v>2356</v>
+      </c>
+      <c r="H622" s="54"/>
+      <c r="I622" s="54"/>
+      <c r="J622" s="55"/>
+      <c r="K622" s="56"/>
+    </row>
+    <row r="623" spans="1:11" s="57" customFormat="1">
+      <c r="A623" s="51"/>
+      <c r="B623" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C623" s="52" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D623" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E623" s="52"/>
+      <c r="F623" s="52"/>
+      <c r="G623" s="53" t="s">
+        <v>2357</v>
+      </c>
+      <c r="H623" s="54"/>
+      <c r="I623" s="54"/>
+      <c r="J623" s="55"/>
+      <c r="K623" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B7F650-5C82-4CB8-A681-9A9F50552EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06E6743-F4BA-450A-91BB-5F08EBA24287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="22" r:id="rId1"/>
@@ -19,7 +19,18 @@
     <sheet name="非通信" sheetId="3" r:id="rId4"/>
     <sheet name="入力補助画面用カラム名クラス" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06E6743-F4BA-450A-91BB-5F08EBA24287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB31AB43-C438-4883-B9CA-DA44082A9EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="22" r:id="rId1"/>
@@ -647,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10142" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10183" uniqueCount="2377">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -11007,6 +11007,81 @@
   </si>
   <si>
     <t>金額（値引き後）</t>
+  </si>
+  <si>
+    <t>取引</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MAM_TRD</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>取引情報を取引マスタから取得する&lt;br&gt;
+引数の取引パタン区分を指定した場合は、対応する取引情報を取得する&lt;br&gt;
+引数の機能ＩＤを指定した場合は、取引パタン区分を取引パタン制御情報から抽出し、抽出した取引パタン区分に対応する取引情報を取得する&lt;br&gt;
+引数の機能IDは、引数の取引パタン区分が未指定か「null」の場合に有効</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chk_msg:"MAUAL0046"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引パタン区分</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>func_id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>機能ＩＤ</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Function ID</t>
+  </si>
+  <si>
+    <t>trd_cd</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引ＣＤ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Transaction cd.</t>
+  </si>
+  <si>
+    <t>trd_nm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引名</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Transaction name</t>
+  </si>
+  <si>
+    <t>trd_ptn_typ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SloTrd</t>
+  </si>
+  <si>
+    <t>売上部門CD</t>
+  </si>
+  <si>
+    <t>Sale Department cd.</t>
   </si>
 </sst>
 </file>
@@ -11021,7 +11096,7 @@
     <numFmt numFmtId="167" formatCode="0.00_)"/>
     <numFmt numFmtId="168" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
-  <fonts count="62">
+  <fonts count="63">
     <font>
       <sz val="9"/>
       <name val="ＭＳ ゴシック"/>
@@ -11439,8 +11514,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11630,6 +11712,12 @@
       <patternFill patternType="solid">
         <fgColor indexed="65"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -12959,7 +13047,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -13194,102 +13282,6 @@
     <xf numFmtId="168" fontId="53" fillId="0" borderId="24" xfId="229" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="59" fillId="29" borderId="42" xfId="228" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -13360,6 +13352,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13367,6 +13368,114 @@
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="242">
@@ -15097,126 +15206,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="34" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="118" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
-      <c r="AM1" s="119"/>
-      <c r="AN1" s="119"/>
-      <c r="AO1" s="119"/>
-      <c r="AP1" s="119"/>
-      <c r="AQ1" s="119"/>
-      <c r="AR1" s="119"/>
-      <c r="AS1" s="119"/>
-      <c r="AT1" s="119"/>
-      <c r="AU1" s="119"/>
-      <c r="AV1" s="119"/>
-      <c r="AW1" s="119"/>
-      <c r="AX1" s="120"/>
-      <c r="AY1" s="114" t="s">
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
+      <c r="Z1" s="87"/>
+      <c r="AA1" s="87"/>
+      <c r="AB1" s="87"/>
+      <c r="AC1" s="87"/>
+      <c r="AD1" s="87"/>
+      <c r="AE1" s="87"/>
+      <c r="AF1" s="87"/>
+      <c r="AG1" s="87"/>
+      <c r="AH1" s="87"/>
+      <c r="AI1" s="87"/>
+      <c r="AJ1" s="87"/>
+      <c r="AK1" s="87"/>
+      <c r="AL1" s="87"/>
+      <c r="AM1" s="87"/>
+      <c r="AN1" s="87"/>
+      <c r="AO1" s="87"/>
+      <c r="AP1" s="87"/>
+      <c r="AQ1" s="87"/>
+      <c r="AR1" s="87"/>
+      <c r="AS1" s="87"/>
+      <c r="AT1" s="87"/>
+      <c r="AU1" s="87"/>
+      <c r="AV1" s="87"/>
+      <c r="AW1" s="87"/>
+      <c r="AX1" s="88"/>
+      <c r="AY1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="114"/>
-      <c r="BC1" s="115"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="82"/>
+      <c r="BB1" s="82"/>
+      <c r="BC1" s="83"/>
     </row>
     <row r="2" spans="1:55" s="34" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
-      <c r="AH2" s="122"/>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="122"/>
-      <c r="AO2" s="122"/>
-      <c r="AP2" s="122"/>
-      <c r="AQ2" s="122"/>
-      <c r="AR2" s="122"/>
-      <c r="AS2" s="122"/>
-      <c r="AT2" s="122"/>
-      <c r="AU2" s="122"/>
-      <c r="AV2" s="122"/>
-      <c r="AW2" s="122"/>
-      <c r="AX2" s="123"/>
-      <c r="AY2" s="116" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="90"/>
+      <c r="R2" s="90"/>
+      <c r="S2" s="90"/>
+      <c r="T2" s="90"/>
+      <c r="U2" s="90"/>
+      <c r="V2" s="90"/>
+      <c r="W2" s="90"/>
+      <c r="X2" s="90"/>
+      <c r="Y2" s="90"/>
+      <c r="Z2" s="90"/>
+      <c r="AA2" s="90"/>
+      <c r="AB2" s="90"/>
+      <c r="AC2" s="90"/>
+      <c r="AD2" s="90"/>
+      <c r="AE2" s="90"/>
+      <c r="AF2" s="90"/>
+      <c r="AG2" s="90"/>
+      <c r="AH2" s="90"/>
+      <c r="AI2" s="90"/>
+      <c r="AJ2" s="90"/>
+      <c r="AK2" s="90"/>
+      <c r="AL2" s="90"/>
+      <c r="AM2" s="90"/>
+      <c r="AN2" s="90"/>
+      <c r="AO2" s="90"/>
+      <c r="AP2" s="90"/>
+      <c r="AQ2" s="90"/>
+      <c r="AR2" s="90"/>
+      <c r="AS2" s="90"/>
+      <c r="AT2" s="90"/>
+      <c r="AU2" s="90"/>
+      <c r="AV2" s="90"/>
+      <c r="AW2" s="90"/>
+      <c r="AX2" s="91"/>
+      <c r="AY2" s="84" t="s">
         <v>1841</v>
       </c>
-      <c r="AZ2" s="116"/>
-      <c r="BA2" s="116"/>
-      <c r="BB2" s="116"/>
-      <c r="BC2" s="117"/>
+      <c r="AZ2" s="84"/>
+      <c r="BA2" s="84"/>
+      <c r="BB2" s="84"/>
+      <c r="BC2" s="85"/>
     </row>
     <row r="3" spans="1:55" s="34" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A3" s="35"/>
@@ -15268,1903 +15377,1982 @@
       <c r="A4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="124" t="s">
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="134"/>
-      <c r="O4" s="134"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="134"/>
-      <c r="R4" s="134"/>
-      <c r="S4" s="134"/>
-      <c r="T4" s="134"/>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="134"/>
-      <c r="X4" s="134"/>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="134"/>
-      <c r="AA4" s="134"/>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="134"/>
-      <c r="AD4" s="134"/>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="134"/>
-      <c r="AG4" s="134"/>
-      <c r="AH4" s="134"/>
-      <c r="AI4" s="134"/>
-      <c r="AJ4" s="134"/>
-      <c r="AK4" s="135"/>
-      <c r="AL4" s="135"/>
-      <c r="AM4" s="135"/>
-      <c r="AN4" s="136"/>
-      <c r="AO4" s="127" t="s">
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="102"/>
+      <c r="V4" s="102"/>
+      <c r="W4" s="102"/>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="102"/>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="102"/>
+      <c r="AB4" s="102"/>
+      <c r="AC4" s="102"/>
+      <c r="AD4" s="102"/>
+      <c r="AE4" s="102"/>
+      <c r="AF4" s="102"/>
+      <c r="AG4" s="102"/>
+      <c r="AH4" s="102"/>
+      <c r="AI4" s="102"/>
+      <c r="AJ4" s="102"/>
+      <c r="AK4" s="103"/>
+      <c r="AL4" s="103"/>
+      <c r="AM4" s="103"/>
+      <c r="AN4" s="104"/>
+      <c r="AO4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="AP4" s="128"/>
-      <c r="AQ4" s="128"/>
-      <c r="AR4" s="128"/>
-      <c r="AS4" s="128"/>
-      <c r="AT4" s="128"/>
-      <c r="AU4" s="128"/>
-      <c r="AV4" s="128"/>
-      <c r="AW4" s="128"/>
-      <c r="AX4" s="128"/>
-      <c r="AY4" s="128"/>
-      <c r="AZ4" s="128"/>
-      <c r="BA4" s="128"/>
-      <c r="BB4" s="128"/>
-      <c r="BC4" s="129"/>
+      <c r="AP4" s="96"/>
+      <c r="AQ4" s="96"/>
+      <c r="AR4" s="96"/>
+      <c r="AS4" s="96"/>
+      <c r="AT4" s="96"/>
+      <c r="AU4" s="96"/>
+      <c r="AV4" s="96"/>
+      <c r="AW4" s="96"/>
+      <c r="AX4" s="96"/>
+      <c r="AY4" s="96"/>
+      <c r="AZ4" s="96"/>
+      <c r="BA4" s="96"/>
+      <c r="BB4" s="96"/>
+      <c r="BC4" s="97"/>
     </row>
     <row r="5" spans="1:55" ht="15" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>1803</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="93" t="s">
+      <c r="B5" s="130"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
-      <c r="S5" s="94"/>
-      <c r="T5" s="94"/>
-      <c r="U5" s="94"/>
-      <c r="V5" s="94"/>
-      <c r="W5" s="94"/>
-      <c r="X5" s="94"/>
-      <c r="Y5" s="94"/>
-      <c r="Z5" s="94"/>
-      <c r="AA5" s="94"/>
-      <c r="AB5" s="94"/>
-      <c r="AC5" s="94"/>
-      <c r="AD5" s="94"/>
-      <c r="AE5" s="94"/>
-      <c r="AF5" s="94"/>
-      <c r="AG5" s="94"/>
-      <c r="AH5" s="94"/>
-      <c r="AI5" s="94"/>
-      <c r="AJ5" s="94"/>
-      <c r="AK5" s="95"/>
-      <c r="AL5" s="95"/>
-      <c r="AM5" s="95"/>
-      <c r="AN5" s="96"/>
-      <c r="AO5" s="110"/>
-      <c r="AP5" s="94"/>
-      <c r="AQ5" s="94"/>
-      <c r="AR5" s="94"/>
-      <c r="AS5" s="94"/>
-      <c r="AT5" s="94"/>
-      <c r="AU5" s="94"/>
-      <c r="AV5" s="94"/>
-      <c r="AW5" s="94"/>
-      <c r="AX5" s="94"/>
-      <c r="AY5" s="94"/>
-      <c r="AZ5" s="94"/>
-      <c r="BA5" s="94"/>
-      <c r="BB5" s="94"/>
-      <c r="BC5" s="111"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="128"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="128"/>
+      <c r="W5" s="128"/>
+      <c r="X5" s="128"/>
+      <c r="Y5" s="128"/>
+      <c r="Z5" s="128"/>
+      <c r="AA5" s="128"/>
+      <c r="AB5" s="128"/>
+      <c r="AC5" s="128"/>
+      <c r="AD5" s="128"/>
+      <c r="AE5" s="128"/>
+      <c r="AF5" s="128"/>
+      <c r="AG5" s="128"/>
+      <c r="AH5" s="128"/>
+      <c r="AI5" s="128"/>
+      <c r="AJ5" s="128"/>
+      <c r="AK5" s="133"/>
+      <c r="AL5" s="133"/>
+      <c r="AM5" s="133"/>
+      <c r="AN5" s="134"/>
+      <c r="AO5" s="127"/>
+      <c r="AP5" s="128"/>
+      <c r="AQ5" s="128"/>
+      <c r="AR5" s="128"/>
+      <c r="AS5" s="128"/>
+      <c r="AT5" s="128"/>
+      <c r="AU5" s="128"/>
+      <c r="AV5" s="128"/>
+      <c r="AW5" s="128"/>
+      <c r="AX5" s="128"/>
+      <c r="AY5" s="128"/>
+      <c r="AZ5" s="128"/>
+      <c r="BA5" s="128"/>
+      <c r="BB5" s="128"/>
+      <c r="BC5" s="129"/>
     </row>
     <row r="6" spans="1:55" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
         <v>2334</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="99" t="s">
+      <c r="B6" s="105"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="137" t="s">
         <v>2335</v>
       </c>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="100"/>
-      <c r="N6" s="100"/>
-      <c r="O6" s="100"/>
-      <c r="P6" s="100"/>
-      <c r="Q6" s="100"/>
-      <c r="R6" s="100"/>
-      <c r="S6" s="100"/>
-      <c r="T6" s="100"/>
-      <c r="U6" s="100"/>
-      <c r="V6" s="100"/>
-      <c r="W6" s="100"/>
-      <c r="X6" s="100"/>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="100"/>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="100"/>
-      <c r="AC6" s="100"/>
-      <c r="AD6" s="100"/>
-      <c r="AE6" s="100"/>
-      <c r="AF6" s="100"/>
-      <c r="AG6" s="100"/>
-      <c r="AH6" s="100"/>
-      <c r="AI6" s="100"/>
-      <c r="AJ6" s="100"/>
-      <c r="AK6" s="100"/>
-      <c r="AL6" s="100"/>
-      <c r="AM6" s="100"/>
-      <c r="AN6" s="101"/>
-      <c r="AO6" s="137" t="s">
+      <c r="J6" s="138"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="138"/>
+      <c r="N6" s="138"/>
+      <c r="O6" s="138"/>
+      <c r="P6" s="138"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="138"/>
+      <c r="S6" s="138"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="138"/>
+      <c r="V6" s="138"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="138"/>
+      <c r="Y6" s="138"/>
+      <c r="Z6" s="138"/>
+      <c r="AA6" s="138"/>
+      <c r="AB6" s="138"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+      <c r="AE6" s="138"/>
+      <c r="AF6" s="138"/>
+      <c r="AG6" s="138"/>
+      <c r="AH6" s="138"/>
+      <c r="AI6" s="138"/>
+      <c r="AJ6" s="138"/>
+      <c r="AK6" s="138"/>
+      <c r="AL6" s="138"/>
+      <c r="AM6" s="138"/>
+      <c r="AN6" s="139"/>
+      <c r="AO6" s="108" t="s">
         <v>2336</v>
       </c>
-      <c r="AP6" s="138"/>
-      <c r="AQ6" s="138"/>
-      <c r="AR6" s="138"/>
-      <c r="AS6" s="138"/>
-      <c r="AT6" s="138"/>
-      <c r="AU6" s="138"/>
-      <c r="AV6" s="138"/>
-      <c r="AW6" s="138"/>
-      <c r="AX6" s="138"/>
-      <c r="AY6" s="138"/>
-      <c r="AZ6" s="138"/>
-      <c r="BA6" s="138"/>
-      <c r="BB6" s="138"/>
-      <c r="BC6" s="139"/>
+      <c r="AP6" s="109"/>
+      <c r="AQ6" s="109"/>
+      <c r="AR6" s="109"/>
+      <c r="AS6" s="109"/>
+      <c r="AT6" s="109"/>
+      <c r="AU6" s="109"/>
+      <c r="AV6" s="109"/>
+      <c r="AW6" s="109"/>
+      <c r="AX6" s="109"/>
+      <c r="AY6" s="109"/>
+      <c r="AZ6" s="109"/>
+      <c r="BA6" s="109"/>
+      <c r="BB6" s="109"/>
+      <c r="BC6" s="110"/>
     </row>
     <row r="7" spans="1:55" ht="15" customHeight="1">
       <c r="A7" s="40"/>
-      <c r="B7" s="90"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="83"/>
-      <c r="Y7" s="83"/>
-      <c r="Z7" s="83"/>
-      <c r="AA7" s="83"/>
-      <c r="AB7" s="83"/>
-      <c r="AC7" s="83"/>
-      <c r="AD7" s="83"/>
-      <c r="AE7" s="83"/>
-      <c r="AF7" s="83"/>
-      <c r="AG7" s="83"/>
-      <c r="AH7" s="83"/>
-      <c r="AI7" s="83"/>
-      <c r="AJ7" s="83"/>
-      <c r="AK7" s="86"/>
-      <c r="AL7" s="86"/>
-      <c r="AM7" s="86"/>
-      <c r="AN7" s="87"/>
-      <c r="AO7" s="82"/>
-      <c r="AP7" s="83"/>
-      <c r="AQ7" s="83"/>
-      <c r="AR7" s="83"/>
-      <c r="AS7" s="83"/>
-      <c r="AT7" s="83"/>
-      <c r="AU7" s="83"/>
-      <c r="AV7" s="83"/>
-      <c r="AW7" s="83"/>
-      <c r="AX7" s="83"/>
-      <c r="AY7" s="83"/>
-      <c r="AZ7" s="83"/>
-      <c r="BA7" s="83"/>
-      <c r="BB7" s="83"/>
-      <c r="BC7" s="84"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="112"/>
+      <c r="R7" s="112"/>
+      <c r="S7" s="112"/>
+      <c r="T7" s="112"/>
+      <c r="U7" s="112"/>
+      <c r="V7" s="112"/>
+      <c r="W7" s="112"/>
+      <c r="X7" s="112"/>
+      <c r="Y7" s="112"/>
+      <c r="Z7" s="112"/>
+      <c r="AA7" s="112"/>
+      <c r="AB7" s="112"/>
+      <c r="AC7" s="112"/>
+      <c r="AD7" s="112"/>
+      <c r="AE7" s="112"/>
+      <c r="AF7" s="112"/>
+      <c r="AG7" s="112"/>
+      <c r="AH7" s="112"/>
+      <c r="AI7" s="112"/>
+      <c r="AJ7" s="112"/>
+      <c r="AK7" s="114"/>
+      <c r="AL7" s="114"/>
+      <c r="AM7" s="114"/>
+      <c r="AN7" s="115"/>
+      <c r="AO7" s="111"/>
+      <c r="AP7" s="112"/>
+      <c r="AQ7" s="112"/>
+      <c r="AR7" s="112"/>
+      <c r="AS7" s="112"/>
+      <c r="AT7" s="112"/>
+      <c r="AU7" s="112"/>
+      <c r="AV7" s="112"/>
+      <c r="AW7" s="112"/>
+      <c r="AX7" s="112"/>
+      <c r="AY7" s="112"/>
+      <c r="AZ7" s="112"/>
+      <c r="BA7" s="112"/>
+      <c r="BB7" s="112"/>
+      <c r="BC7" s="113"/>
     </row>
     <row r="8" spans="1:55" ht="15" customHeight="1">
       <c r="A8" s="40"/>
-      <c r="B8" s="90"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="83"/>
-      <c r="V8" s="83"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
-      <c r="Y8" s="83"/>
-      <c r="Z8" s="83"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="83"/>
-      <c r="AC8" s="83"/>
-      <c r="AD8" s="83"/>
-      <c r="AE8" s="83"/>
-      <c r="AF8" s="83"/>
-      <c r="AG8" s="83"/>
-      <c r="AH8" s="83"/>
-      <c r="AI8" s="83"/>
-      <c r="AJ8" s="83"/>
-      <c r="AK8" s="86"/>
-      <c r="AL8" s="86"/>
-      <c r="AM8" s="86"/>
-      <c r="AN8" s="87"/>
-      <c r="AO8" s="82"/>
-      <c r="AP8" s="83"/>
-      <c r="AQ8" s="83"/>
-      <c r="AR8" s="83"/>
-      <c r="AS8" s="83"/>
-      <c r="AT8" s="83"/>
-      <c r="AU8" s="83"/>
-      <c r="AV8" s="83"/>
-      <c r="AW8" s="83"/>
-      <c r="AX8" s="83"/>
-      <c r="AY8" s="83"/>
-      <c r="AZ8" s="83"/>
-      <c r="BA8" s="83"/>
-      <c r="BB8" s="83"/>
-      <c r="BC8" s="84"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="112"/>
+      <c r="R8" s="112"/>
+      <c r="S8" s="112"/>
+      <c r="T8" s="112"/>
+      <c r="U8" s="112"/>
+      <c r="V8" s="112"/>
+      <c r="W8" s="112"/>
+      <c r="X8" s="112"/>
+      <c r="Y8" s="112"/>
+      <c r="Z8" s="112"/>
+      <c r="AA8" s="112"/>
+      <c r="AB8" s="112"/>
+      <c r="AC8" s="112"/>
+      <c r="AD8" s="112"/>
+      <c r="AE8" s="112"/>
+      <c r="AF8" s="112"/>
+      <c r="AG8" s="112"/>
+      <c r="AH8" s="112"/>
+      <c r="AI8" s="112"/>
+      <c r="AJ8" s="112"/>
+      <c r="AK8" s="114"/>
+      <c r="AL8" s="114"/>
+      <c r="AM8" s="114"/>
+      <c r="AN8" s="115"/>
+      <c r="AO8" s="111"/>
+      <c r="AP8" s="112"/>
+      <c r="AQ8" s="112"/>
+      <c r="AR8" s="112"/>
+      <c r="AS8" s="112"/>
+      <c r="AT8" s="112"/>
+      <c r="AU8" s="112"/>
+      <c r="AV8" s="112"/>
+      <c r="AW8" s="112"/>
+      <c r="AX8" s="112"/>
+      <c r="AY8" s="112"/>
+      <c r="AZ8" s="112"/>
+      <c r="BA8" s="112"/>
+      <c r="BB8" s="112"/>
+      <c r="BC8" s="113"/>
     </row>
     <row r="9" spans="1:55" ht="15" customHeight="1">
       <c r="A9" s="40"/>
-      <c r="B9" s="90"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="83"/>
-      <c r="U9" s="83"/>
-      <c r="V9" s="83"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="83"/>
-      <c r="Y9" s="83"/>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="83"/>
-      <c r="AD9" s="83"/>
-      <c r="AE9" s="83"/>
-      <c r="AF9" s="83"/>
-      <c r="AG9" s="83"/>
-      <c r="AH9" s="83"/>
-      <c r="AI9" s="83"/>
-      <c r="AJ9" s="83"/>
-      <c r="AK9" s="86"/>
-      <c r="AL9" s="86"/>
-      <c r="AM9" s="86"/>
-      <c r="AN9" s="87"/>
-      <c r="AO9" s="82"/>
-      <c r="AP9" s="83"/>
-      <c r="AQ9" s="83"/>
-      <c r="AR9" s="83"/>
-      <c r="AS9" s="83"/>
-      <c r="AT9" s="83"/>
-      <c r="AU9" s="83"/>
-      <c r="AV9" s="83"/>
-      <c r="AW9" s="83"/>
-      <c r="AX9" s="83"/>
-      <c r="AY9" s="83"/>
-      <c r="AZ9" s="83"/>
-      <c r="BA9" s="83"/>
-      <c r="BB9" s="83"/>
-      <c r="BC9" s="84"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="112"/>
+      <c r="R9" s="112"/>
+      <c r="S9" s="112"/>
+      <c r="T9" s="112"/>
+      <c r="U9" s="112"/>
+      <c r="V9" s="112"/>
+      <c r="W9" s="112"/>
+      <c r="X9" s="112"/>
+      <c r="Y9" s="112"/>
+      <c r="Z9" s="112"/>
+      <c r="AA9" s="112"/>
+      <c r="AB9" s="112"/>
+      <c r="AC9" s="112"/>
+      <c r="AD9" s="112"/>
+      <c r="AE9" s="112"/>
+      <c r="AF9" s="112"/>
+      <c r="AG9" s="112"/>
+      <c r="AH9" s="112"/>
+      <c r="AI9" s="112"/>
+      <c r="AJ9" s="112"/>
+      <c r="AK9" s="114"/>
+      <c r="AL9" s="114"/>
+      <c r="AM9" s="114"/>
+      <c r="AN9" s="115"/>
+      <c r="AO9" s="111"/>
+      <c r="AP9" s="112"/>
+      <c r="AQ9" s="112"/>
+      <c r="AR9" s="112"/>
+      <c r="AS9" s="112"/>
+      <c r="AT9" s="112"/>
+      <c r="AU9" s="112"/>
+      <c r="AV9" s="112"/>
+      <c r="AW9" s="112"/>
+      <c r="AX9" s="112"/>
+      <c r="AY9" s="112"/>
+      <c r="AZ9" s="112"/>
+      <c r="BA9" s="112"/>
+      <c r="BB9" s="112"/>
+      <c r="BC9" s="113"/>
     </row>
     <row r="10" spans="1:55" ht="15" customHeight="1">
       <c r="A10" s="40"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="83"/>
-      <c r="V10" s="83"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="83"/>
-      <c r="Y10" s="83"/>
-      <c r="Z10" s="83"/>
-      <c r="AA10" s="83"/>
-      <c r="AB10" s="83"/>
-      <c r="AC10" s="83"/>
-      <c r="AD10" s="83"/>
-      <c r="AE10" s="83"/>
-      <c r="AF10" s="83"/>
-      <c r="AG10" s="83"/>
-      <c r="AH10" s="83"/>
-      <c r="AI10" s="83"/>
-      <c r="AJ10" s="83"/>
-      <c r="AK10" s="86"/>
-      <c r="AL10" s="86"/>
-      <c r="AM10" s="86"/>
-      <c r="AN10" s="87"/>
-      <c r="AO10" s="82"/>
-      <c r="AP10" s="83"/>
-      <c r="AQ10" s="83"/>
-      <c r="AR10" s="83"/>
-      <c r="AS10" s="83"/>
-      <c r="AT10" s="83"/>
-      <c r="AU10" s="83"/>
-      <c r="AV10" s="83"/>
-      <c r="AW10" s="83"/>
-      <c r="AX10" s="83"/>
-      <c r="AY10" s="83"/>
-      <c r="AZ10" s="83"/>
-      <c r="BA10" s="83"/>
-      <c r="BB10" s="83"/>
-      <c r="BC10" s="84"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="112"/>
+      <c r="R10" s="112"/>
+      <c r="S10" s="112"/>
+      <c r="T10" s="112"/>
+      <c r="U10" s="112"/>
+      <c r="V10" s="112"/>
+      <c r="W10" s="112"/>
+      <c r="X10" s="112"/>
+      <c r="Y10" s="112"/>
+      <c r="Z10" s="112"/>
+      <c r="AA10" s="112"/>
+      <c r="AB10" s="112"/>
+      <c r="AC10" s="112"/>
+      <c r="AD10" s="112"/>
+      <c r="AE10" s="112"/>
+      <c r="AF10" s="112"/>
+      <c r="AG10" s="112"/>
+      <c r="AH10" s="112"/>
+      <c r="AI10" s="112"/>
+      <c r="AJ10" s="112"/>
+      <c r="AK10" s="114"/>
+      <c r="AL10" s="114"/>
+      <c r="AM10" s="114"/>
+      <c r="AN10" s="115"/>
+      <c r="AO10" s="111"/>
+      <c r="AP10" s="112"/>
+      <c r="AQ10" s="112"/>
+      <c r="AR10" s="112"/>
+      <c r="AS10" s="112"/>
+      <c r="AT10" s="112"/>
+      <c r="AU10" s="112"/>
+      <c r="AV10" s="112"/>
+      <c r="AW10" s="112"/>
+      <c r="AX10" s="112"/>
+      <c r="AY10" s="112"/>
+      <c r="AZ10" s="112"/>
+      <c r="BA10" s="112"/>
+      <c r="BB10" s="112"/>
+      <c r="BC10" s="113"/>
     </row>
     <row r="11" spans="1:55" ht="15" customHeight="1">
       <c r="A11" s="40"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="83"/>
-      <c r="S11" s="83"/>
-      <c r="T11" s="83"/>
-      <c r="U11" s="83"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="83"/>
-      <c r="Z11" s="83"/>
-      <c r="AA11" s="83"/>
-      <c r="AB11" s="83"/>
-      <c r="AC11" s="83"/>
-      <c r="AD11" s="83"/>
-      <c r="AE11" s="83"/>
-      <c r="AF11" s="83"/>
-      <c r="AG11" s="83"/>
-      <c r="AH11" s="83"/>
-      <c r="AI11" s="83"/>
-      <c r="AJ11" s="83"/>
-      <c r="AK11" s="86"/>
-      <c r="AL11" s="86"/>
-      <c r="AM11" s="86"/>
-      <c r="AN11" s="87"/>
-      <c r="AO11" s="82"/>
-      <c r="AP11" s="83"/>
-      <c r="AQ11" s="83"/>
-      <c r="AR11" s="83"/>
-      <c r="AS11" s="83"/>
-      <c r="AT11" s="83"/>
-      <c r="AU11" s="83"/>
-      <c r="AV11" s="83"/>
-      <c r="AW11" s="83"/>
-      <c r="AX11" s="83"/>
-      <c r="AY11" s="83"/>
-      <c r="AZ11" s="83"/>
-      <c r="BA11" s="83"/>
-      <c r="BB11" s="83"/>
-      <c r="BC11" s="84"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="112"/>
+      <c r="R11" s="112"/>
+      <c r="S11" s="112"/>
+      <c r="T11" s="112"/>
+      <c r="U11" s="112"/>
+      <c r="V11" s="112"/>
+      <c r="W11" s="112"/>
+      <c r="X11" s="112"/>
+      <c r="Y11" s="112"/>
+      <c r="Z11" s="112"/>
+      <c r="AA11" s="112"/>
+      <c r="AB11" s="112"/>
+      <c r="AC11" s="112"/>
+      <c r="AD11" s="112"/>
+      <c r="AE11" s="112"/>
+      <c r="AF11" s="112"/>
+      <c r="AG11" s="112"/>
+      <c r="AH11" s="112"/>
+      <c r="AI11" s="112"/>
+      <c r="AJ11" s="112"/>
+      <c r="AK11" s="114"/>
+      <c r="AL11" s="114"/>
+      <c r="AM11" s="114"/>
+      <c r="AN11" s="115"/>
+      <c r="AO11" s="111"/>
+      <c r="AP11" s="112"/>
+      <c r="AQ11" s="112"/>
+      <c r="AR11" s="112"/>
+      <c r="AS11" s="112"/>
+      <c r="AT11" s="112"/>
+      <c r="AU11" s="112"/>
+      <c r="AV11" s="112"/>
+      <c r="AW11" s="112"/>
+      <c r="AX11" s="112"/>
+      <c r="AY11" s="112"/>
+      <c r="AZ11" s="112"/>
+      <c r="BA11" s="112"/>
+      <c r="BB11" s="112"/>
+      <c r="BC11" s="113"/>
     </row>
     <row r="12" spans="1:55" ht="15" customHeight="1">
       <c r="A12" s="40"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="83"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="83"/>
-      <c r="T12" s="83"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="83"/>
-      <c r="X12" s="83"/>
-      <c r="Y12" s="83"/>
-      <c r="Z12" s="83"/>
-      <c r="AA12" s="83"/>
-      <c r="AB12" s="83"/>
-      <c r="AC12" s="83"/>
-      <c r="AD12" s="83"/>
-      <c r="AE12" s="83"/>
-      <c r="AF12" s="83"/>
-      <c r="AG12" s="83"/>
-      <c r="AH12" s="83"/>
-      <c r="AI12" s="83"/>
-      <c r="AJ12" s="83"/>
-      <c r="AK12" s="86"/>
-      <c r="AL12" s="86"/>
-      <c r="AM12" s="86"/>
-      <c r="AN12" s="87"/>
-      <c r="AO12" s="82"/>
-      <c r="AP12" s="83"/>
-      <c r="AQ12" s="83"/>
-      <c r="AR12" s="83"/>
-      <c r="AS12" s="83"/>
-      <c r="AT12" s="83"/>
-      <c r="AU12" s="83"/>
-      <c r="AV12" s="83"/>
-      <c r="AW12" s="83"/>
-      <c r="AX12" s="83"/>
-      <c r="AY12" s="83"/>
-      <c r="AZ12" s="83"/>
-      <c r="BA12" s="83"/>
-      <c r="BB12" s="83"/>
-      <c r="BC12" s="84"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="112"/>
+      <c r="R12" s="112"/>
+      <c r="S12" s="112"/>
+      <c r="T12" s="112"/>
+      <c r="U12" s="112"/>
+      <c r="V12" s="112"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="112"/>
+      <c r="Y12" s="112"/>
+      <c r="Z12" s="112"/>
+      <c r="AA12" s="112"/>
+      <c r="AB12" s="112"/>
+      <c r="AC12" s="112"/>
+      <c r="AD12" s="112"/>
+      <c r="AE12" s="112"/>
+      <c r="AF12" s="112"/>
+      <c r="AG12" s="112"/>
+      <c r="AH12" s="112"/>
+      <c r="AI12" s="112"/>
+      <c r="AJ12" s="112"/>
+      <c r="AK12" s="114"/>
+      <c r="AL12" s="114"/>
+      <c r="AM12" s="114"/>
+      <c r="AN12" s="115"/>
+      <c r="AO12" s="111"/>
+      <c r="AP12" s="112"/>
+      <c r="AQ12" s="112"/>
+      <c r="AR12" s="112"/>
+      <c r="AS12" s="112"/>
+      <c r="AT12" s="112"/>
+      <c r="AU12" s="112"/>
+      <c r="AV12" s="112"/>
+      <c r="AW12" s="112"/>
+      <c r="AX12" s="112"/>
+      <c r="AY12" s="112"/>
+      <c r="AZ12" s="112"/>
+      <c r="BA12" s="112"/>
+      <c r="BB12" s="112"/>
+      <c r="BC12" s="113"/>
     </row>
     <row r="13" spans="1:55" ht="15" customHeight="1">
       <c r="A13" s="40"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="83"/>
-      <c r="U13" s="83"/>
-      <c r="V13" s="83"/>
-      <c r="W13" s="83"/>
-      <c r="X13" s="83"/>
-      <c r="Y13" s="83"/>
-      <c r="Z13" s="83"/>
-      <c r="AA13" s="83"/>
-      <c r="AB13" s="83"/>
-      <c r="AC13" s="83"/>
-      <c r="AD13" s="83"/>
-      <c r="AE13" s="83"/>
-      <c r="AF13" s="83"/>
-      <c r="AG13" s="83"/>
-      <c r="AH13" s="83"/>
-      <c r="AI13" s="83"/>
-      <c r="AJ13" s="83"/>
-      <c r="AK13" s="86"/>
-      <c r="AL13" s="86"/>
-      <c r="AM13" s="86"/>
-      <c r="AN13" s="87"/>
-      <c r="AO13" s="82"/>
-      <c r="AP13" s="83"/>
-      <c r="AQ13" s="83"/>
-      <c r="AR13" s="83"/>
-      <c r="AS13" s="83"/>
-      <c r="AT13" s="83"/>
-      <c r="AU13" s="83"/>
-      <c r="AV13" s="83"/>
-      <c r="AW13" s="83"/>
-      <c r="AX13" s="83"/>
-      <c r="AY13" s="83"/>
-      <c r="AZ13" s="83"/>
-      <c r="BA13" s="83"/>
-      <c r="BB13" s="83"/>
-      <c r="BC13" s="84"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="112"/>
+      <c r="Q13" s="112"/>
+      <c r="R13" s="112"/>
+      <c r="S13" s="112"/>
+      <c r="T13" s="112"/>
+      <c r="U13" s="112"/>
+      <c r="V13" s="112"/>
+      <c r="W13" s="112"/>
+      <c r="X13" s="112"/>
+      <c r="Y13" s="112"/>
+      <c r="Z13" s="112"/>
+      <c r="AA13" s="112"/>
+      <c r="AB13" s="112"/>
+      <c r="AC13" s="112"/>
+      <c r="AD13" s="112"/>
+      <c r="AE13" s="112"/>
+      <c r="AF13" s="112"/>
+      <c r="AG13" s="112"/>
+      <c r="AH13" s="112"/>
+      <c r="AI13" s="112"/>
+      <c r="AJ13" s="112"/>
+      <c r="AK13" s="114"/>
+      <c r="AL13" s="114"/>
+      <c r="AM13" s="114"/>
+      <c r="AN13" s="115"/>
+      <c r="AO13" s="111"/>
+      <c r="AP13" s="112"/>
+      <c r="AQ13" s="112"/>
+      <c r="AR13" s="112"/>
+      <c r="AS13" s="112"/>
+      <c r="AT13" s="112"/>
+      <c r="AU13" s="112"/>
+      <c r="AV13" s="112"/>
+      <c r="AW13" s="112"/>
+      <c r="AX13" s="112"/>
+      <c r="AY13" s="112"/>
+      <c r="AZ13" s="112"/>
+      <c r="BA13" s="112"/>
+      <c r="BB13" s="112"/>
+      <c r="BC13" s="113"/>
     </row>
     <row r="14" spans="1:55" ht="15" customHeight="1">
       <c r="A14" s="40"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="83"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="83"/>
-      <c r="U14" s="83"/>
-      <c r="V14" s="83"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="83"/>
-      <c r="Y14" s="83"/>
-      <c r="Z14" s="83"/>
-      <c r="AA14" s="83"/>
-      <c r="AB14" s="83"/>
-      <c r="AC14" s="83"/>
-      <c r="AD14" s="83"/>
-      <c r="AE14" s="83"/>
-      <c r="AF14" s="83"/>
-      <c r="AG14" s="83"/>
-      <c r="AH14" s="83"/>
-      <c r="AI14" s="83"/>
-      <c r="AJ14" s="83"/>
-      <c r="AK14" s="86"/>
-      <c r="AL14" s="86"/>
-      <c r="AM14" s="86"/>
-      <c r="AN14" s="87"/>
-      <c r="AO14" s="82"/>
-      <c r="AP14" s="83"/>
-      <c r="AQ14" s="83"/>
-      <c r="AR14" s="83"/>
-      <c r="AS14" s="83"/>
-      <c r="AT14" s="83"/>
-      <c r="AU14" s="83"/>
-      <c r="AV14" s="83"/>
-      <c r="AW14" s="83"/>
-      <c r="AX14" s="83"/>
-      <c r="AY14" s="83"/>
-      <c r="AZ14" s="83"/>
-      <c r="BA14" s="83"/>
-      <c r="BB14" s="83"/>
-      <c r="BC14" s="84"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="112"/>
+      <c r="R14" s="112"/>
+      <c r="S14" s="112"/>
+      <c r="T14" s="112"/>
+      <c r="U14" s="112"/>
+      <c r="V14" s="112"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="112"/>
+      <c r="Y14" s="112"/>
+      <c r="Z14" s="112"/>
+      <c r="AA14" s="112"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="112"/>
+      <c r="AD14" s="112"/>
+      <c r="AE14" s="112"/>
+      <c r="AF14" s="112"/>
+      <c r="AG14" s="112"/>
+      <c r="AH14" s="112"/>
+      <c r="AI14" s="112"/>
+      <c r="AJ14" s="112"/>
+      <c r="AK14" s="114"/>
+      <c r="AL14" s="114"/>
+      <c r="AM14" s="114"/>
+      <c r="AN14" s="115"/>
+      <c r="AO14" s="111"/>
+      <c r="AP14" s="112"/>
+      <c r="AQ14" s="112"/>
+      <c r="AR14" s="112"/>
+      <c r="AS14" s="112"/>
+      <c r="AT14" s="112"/>
+      <c r="AU14" s="112"/>
+      <c r="AV14" s="112"/>
+      <c r="AW14" s="112"/>
+      <c r="AX14" s="112"/>
+      <c r="AY14" s="112"/>
+      <c r="AZ14" s="112"/>
+      <c r="BA14" s="112"/>
+      <c r="BB14" s="112"/>
+      <c r="BC14" s="113"/>
     </row>
     <row r="15" spans="1:55" ht="15" customHeight="1">
       <c r="A15" s="40"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="83"/>
-      <c r="R15" s="83"/>
-      <c r="S15" s="83"/>
-      <c r="T15" s="83"/>
-      <c r="U15" s="83"/>
-      <c r="V15" s="83"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="83"/>
-      <c r="Y15" s="83"/>
-      <c r="Z15" s="83"/>
-      <c r="AA15" s="83"/>
-      <c r="AB15" s="83"/>
-      <c r="AC15" s="83"/>
-      <c r="AD15" s="83"/>
-      <c r="AE15" s="83"/>
-      <c r="AF15" s="83"/>
-      <c r="AG15" s="83"/>
-      <c r="AH15" s="83"/>
-      <c r="AI15" s="83"/>
-      <c r="AJ15" s="83"/>
-      <c r="AK15" s="86"/>
-      <c r="AL15" s="86"/>
-      <c r="AM15" s="86"/>
-      <c r="AN15" s="87"/>
-      <c r="AO15" s="82"/>
-      <c r="AP15" s="83"/>
-      <c r="AQ15" s="83"/>
-      <c r="AR15" s="83"/>
-      <c r="AS15" s="83"/>
-      <c r="AT15" s="83"/>
-      <c r="AU15" s="83"/>
-      <c r="AV15" s="83"/>
-      <c r="AW15" s="83"/>
-      <c r="AX15" s="83"/>
-      <c r="AY15" s="83"/>
-      <c r="AZ15" s="83"/>
-      <c r="BA15" s="83"/>
-      <c r="BB15" s="83"/>
-      <c r="BC15" s="84"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="106"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="112"/>
+      <c r="S15" s="112"/>
+      <c r="T15" s="112"/>
+      <c r="U15" s="112"/>
+      <c r="V15" s="112"/>
+      <c r="W15" s="112"/>
+      <c r="X15" s="112"/>
+      <c r="Y15" s="112"/>
+      <c r="Z15" s="112"/>
+      <c r="AA15" s="112"/>
+      <c r="AB15" s="112"/>
+      <c r="AC15" s="112"/>
+      <c r="AD15" s="112"/>
+      <c r="AE15" s="112"/>
+      <c r="AF15" s="112"/>
+      <c r="AG15" s="112"/>
+      <c r="AH15" s="112"/>
+      <c r="AI15" s="112"/>
+      <c r="AJ15" s="112"/>
+      <c r="AK15" s="114"/>
+      <c r="AL15" s="114"/>
+      <c r="AM15" s="114"/>
+      <c r="AN15" s="115"/>
+      <c r="AO15" s="111"/>
+      <c r="AP15" s="112"/>
+      <c r="AQ15" s="112"/>
+      <c r="AR15" s="112"/>
+      <c r="AS15" s="112"/>
+      <c r="AT15" s="112"/>
+      <c r="AU15" s="112"/>
+      <c r="AV15" s="112"/>
+      <c r="AW15" s="112"/>
+      <c r="AX15" s="112"/>
+      <c r="AY15" s="112"/>
+      <c r="AZ15" s="112"/>
+      <c r="BA15" s="112"/>
+      <c r="BB15" s="112"/>
+      <c r="BC15" s="113"/>
     </row>
     <row r="16" spans="1:55" ht="15" customHeight="1">
       <c r="A16" s="40"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="83"/>
-      <c r="Q16" s="83"/>
-      <c r="R16" s="83"/>
-      <c r="S16" s="83"/>
-      <c r="T16" s="83"/>
-      <c r="U16" s="83"/>
-      <c r="V16" s="83"/>
-      <c r="W16" s="83"/>
-      <c r="X16" s="83"/>
-      <c r="Y16" s="83"/>
-      <c r="Z16" s="83"/>
-      <c r="AA16" s="83"/>
-      <c r="AB16" s="83"/>
-      <c r="AC16" s="83"/>
-      <c r="AD16" s="83"/>
-      <c r="AE16" s="83"/>
-      <c r="AF16" s="83"/>
-      <c r="AG16" s="83"/>
-      <c r="AH16" s="83"/>
-      <c r="AI16" s="83"/>
-      <c r="AJ16" s="83"/>
-      <c r="AK16" s="86"/>
-      <c r="AL16" s="86"/>
-      <c r="AM16" s="86"/>
-      <c r="AN16" s="87"/>
-      <c r="AO16" s="82"/>
-      <c r="AP16" s="83"/>
-      <c r="AQ16" s="83"/>
-      <c r="AR16" s="83"/>
-      <c r="AS16" s="83"/>
-      <c r="AT16" s="83"/>
-      <c r="AU16" s="83"/>
-      <c r="AV16" s="83"/>
-      <c r="AW16" s="83"/>
-      <c r="AX16" s="83"/>
-      <c r="AY16" s="83"/>
-      <c r="AZ16" s="83"/>
-      <c r="BA16" s="83"/>
-      <c r="BB16" s="83"/>
-      <c r="BC16" s="84"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="112"/>
+      <c r="S16" s="112"/>
+      <c r="T16" s="112"/>
+      <c r="U16" s="112"/>
+      <c r="V16" s="112"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="112"/>
+      <c r="Y16" s="112"/>
+      <c r="Z16" s="112"/>
+      <c r="AA16" s="112"/>
+      <c r="AB16" s="112"/>
+      <c r="AC16" s="112"/>
+      <c r="AD16" s="112"/>
+      <c r="AE16" s="112"/>
+      <c r="AF16" s="112"/>
+      <c r="AG16" s="112"/>
+      <c r="AH16" s="112"/>
+      <c r="AI16" s="112"/>
+      <c r="AJ16" s="112"/>
+      <c r="AK16" s="114"/>
+      <c r="AL16" s="114"/>
+      <c r="AM16" s="114"/>
+      <c r="AN16" s="115"/>
+      <c r="AO16" s="111"/>
+      <c r="AP16" s="112"/>
+      <c r="AQ16" s="112"/>
+      <c r="AR16" s="112"/>
+      <c r="AS16" s="112"/>
+      <c r="AT16" s="112"/>
+      <c r="AU16" s="112"/>
+      <c r="AV16" s="112"/>
+      <c r="AW16" s="112"/>
+      <c r="AX16" s="112"/>
+      <c r="AY16" s="112"/>
+      <c r="AZ16" s="112"/>
+      <c r="BA16" s="112"/>
+      <c r="BB16" s="112"/>
+      <c r="BC16" s="113"/>
     </row>
     <row r="17" spans="1:55" ht="15" customHeight="1">
       <c r="A17" s="40"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="83"/>
-      <c r="Q17" s="83"/>
-      <c r="R17" s="83"/>
-      <c r="S17" s="83"/>
-      <c r="T17" s="83"/>
-      <c r="U17" s="83"/>
-      <c r="V17" s="83"/>
-      <c r="W17" s="83"/>
-      <c r="X17" s="83"/>
-      <c r="Y17" s="83"/>
-      <c r="Z17" s="83"/>
-      <c r="AA17" s="83"/>
-      <c r="AB17" s="83"/>
-      <c r="AC17" s="83"/>
-      <c r="AD17" s="83"/>
-      <c r="AE17" s="83"/>
-      <c r="AF17" s="83"/>
-      <c r="AG17" s="83"/>
-      <c r="AH17" s="83"/>
-      <c r="AI17" s="83"/>
-      <c r="AJ17" s="83"/>
-      <c r="AK17" s="86"/>
-      <c r="AL17" s="86"/>
-      <c r="AM17" s="86"/>
-      <c r="AN17" s="87"/>
-      <c r="AO17" s="82"/>
-      <c r="AP17" s="83"/>
-      <c r="AQ17" s="83"/>
-      <c r="AR17" s="83"/>
-      <c r="AS17" s="83"/>
-      <c r="AT17" s="83"/>
-      <c r="AU17" s="83"/>
-      <c r="AV17" s="83"/>
-      <c r="AW17" s="83"/>
-      <c r="AX17" s="83"/>
-      <c r="AY17" s="83"/>
-      <c r="AZ17" s="83"/>
-      <c r="BA17" s="83"/>
-      <c r="BB17" s="83"/>
-      <c r="BC17" s="84"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="106"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="112"/>
+      <c r="R17" s="112"/>
+      <c r="S17" s="112"/>
+      <c r="T17" s="112"/>
+      <c r="U17" s="112"/>
+      <c r="V17" s="112"/>
+      <c r="W17" s="112"/>
+      <c r="X17" s="112"/>
+      <c r="Y17" s="112"/>
+      <c r="Z17" s="112"/>
+      <c r="AA17" s="112"/>
+      <c r="AB17" s="112"/>
+      <c r="AC17" s="112"/>
+      <c r="AD17" s="112"/>
+      <c r="AE17" s="112"/>
+      <c r="AF17" s="112"/>
+      <c r="AG17" s="112"/>
+      <c r="AH17" s="112"/>
+      <c r="AI17" s="112"/>
+      <c r="AJ17" s="112"/>
+      <c r="AK17" s="114"/>
+      <c r="AL17" s="114"/>
+      <c r="AM17" s="114"/>
+      <c r="AN17" s="115"/>
+      <c r="AO17" s="111"/>
+      <c r="AP17" s="112"/>
+      <c r="AQ17" s="112"/>
+      <c r="AR17" s="112"/>
+      <c r="AS17" s="112"/>
+      <c r="AT17" s="112"/>
+      <c r="AU17" s="112"/>
+      <c r="AV17" s="112"/>
+      <c r="AW17" s="112"/>
+      <c r="AX17" s="112"/>
+      <c r="AY17" s="112"/>
+      <c r="AZ17" s="112"/>
+      <c r="BA17" s="112"/>
+      <c r="BB17" s="112"/>
+      <c r="BC17" s="113"/>
     </row>
     <row r="18" spans="1:55" ht="15" customHeight="1">
       <c r="A18" s="40"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="83"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="83"/>
-      <c r="Q18" s="83"/>
-      <c r="R18" s="83"/>
-      <c r="S18" s="83"/>
-      <c r="T18" s="83"/>
-      <c r="U18" s="83"/>
-      <c r="V18" s="83"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="83"/>
-      <c r="Y18" s="83"/>
-      <c r="Z18" s="83"/>
-      <c r="AA18" s="83"/>
-      <c r="AB18" s="83"/>
-      <c r="AC18" s="83"/>
-      <c r="AD18" s="83"/>
-      <c r="AE18" s="83"/>
-      <c r="AF18" s="83"/>
-      <c r="AG18" s="83"/>
-      <c r="AH18" s="83"/>
-      <c r="AI18" s="83"/>
-      <c r="AJ18" s="83"/>
-      <c r="AK18" s="86"/>
-      <c r="AL18" s="86"/>
-      <c r="AM18" s="86"/>
-      <c r="AN18" s="87"/>
-      <c r="AO18" s="82"/>
-      <c r="AP18" s="83"/>
-      <c r="AQ18" s="83"/>
-      <c r="AR18" s="83"/>
-      <c r="AS18" s="83"/>
-      <c r="AT18" s="83"/>
-      <c r="AU18" s="83"/>
-      <c r="AV18" s="83"/>
-      <c r="AW18" s="83"/>
-      <c r="AX18" s="83"/>
-      <c r="AY18" s="83"/>
-      <c r="AZ18" s="83"/>
-      <c r="BA18" s="83"/>
-      <c r="BB18" s="83"/>
-      <c r="BC18" s="84"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="112"/>
+      <c r="W18" s="112"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="112"/>
+      <c r="AE18" s="112"/>
+      <c r="AF18" s="112"/>
+      <c r="AG18" s="112"/>
+      <c r="AH18" s="112"/>
+      <c r="AI18" s="112"/>
+      <c r="AJ18" s="112"/>
+      <c r="AK18" s="114"/>
+      <c r="AL18" s="114"/>
+      <c r="AM18" s="114"/>
+      <c r="AN18" s="115"/>
+      <c r="AO18" s="111"/>
+      <c r="AP18" s="112"/>
+      <c r="AQ18" s="112"/>
+      <c r="AR18" s="112"/>
+      <c r="AS18" s="112"/>
+      <c r="AT18" s="112"/>
+      <c r="AU18" s="112"/>
+      <c r="AV18" s="112"/>
+      <c r="AW18" s="112"/>
+      <c r="AX18" s="112"/>
+      <c r="AY18" s="112"/>
+      <c r="AZ18" s="112"/>
+      <c r="BA18" s="112"/>
+      <c r="BB18" s="112"/>
+      <c r="BC18" s="113"/>
     </row>
     <row r="19" spans="1:55" ht="15" customHeight="1">
       <c r="A19" s="40"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="83"/>
-      <c r="S19" s="83"/>
-      <c r="T19" s="83"/>
-      <c r="U19" s="83"/>
-      <c r="V19" s="83"/>
-      <c r="W19" s="83"/>
-      <c r="X19" s="83"/>
-      <c r="Y19" s="83"/>
-      <c r="Z19" s="83"/>
-      <c r="AA19" s="83"/>
-      <c r="AB19" s="83"/>
-      <c r="AC19" s="83"/>
-      <c r="AD19" s="83"/>
-      <c r="AE19" s="83"/>
-      <c r="AF19" s="83"/>
-      <c r="AG19" s="83"/>
-      <c r="AH19" s="83"/>
-      <c r="AI19" s="83"/>
-      <c r="AJ19" s="83"/>
-      <c r="AK19" s="86"/>
-      <c r="AL19" s="86"/>
-      <c r="AM19" s="86"/>
-      <c r="AN19" s="87"/>
-      <c r="AO19" s="82"/>
-      <c r="AP19" s="83"/>
-      <c r="AQ19" s="83"/>
-      <c r="AR19" s="83"/>
-      <c r="AS19" s="83"/>
-      <c r="AT19" s="83"/>
-      <c r="AU19" s="83"/>
-      <c r="AV19" s="83"/>
-      <c r="AW19" s="83"/>
-      <c r="AX19" s="83"/>
-      <c r="AY19" s="83"/>
-      <c r="AZ19" s="83"/>
-      <c r="BA19" s="83"/>
-      <c r="BB19" s="83"/>
-      <c r="BC19" s="84"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="112"/>
+      <c r="R19" s="112"/>
+      <c r="S19" s="112"/>
+      <c r="T19" s="112"/>
+      <c r="U19" s="112"/>
+      <c r="V19" s="112"/>
+      <c r="W19" s="112"/>
+      <c r="X19" s="112"/>
+      <c r="Y19" s="112"/>
+      <c r="Z19" s="112"/>
+      <c r="AA19" s="112"/>
+      <c r="AB19" s="112"/>
+      <c r="AC19" s="112"/>
+      <c r="AD19" s="112"/>
+      <c r="AE19" s="112"/>
+      <c r="AF19" s="112"/>
+      <c r="AG19" s="112"/>
+      <c r="AH19" s="112"/>
+      <c r="AI19" s="112"/>
+      <c r="AJ19" s="112"/>
+      <c r="AK19" s="114"/>
+      <c r="AL19" s="114"/>
+      <c r="AM19" s="114"/>
+      <c r="AN19" s="115"/>
+      <c r="AO19" s="111"/>
+      <c r="AP19" s="112"/>
+      <c r="AQ19" s="112"/>
+      <c r="AR19" s="112"/>
+      <c r="AS19" s="112"/>
+      <c r="AT19" s="112"/>
+      <c r="AU19" s="112"/>
+      <c r="AV19" s="112"/>
+      <c r="AW19" s="112"/>
+      <c r="AX19" s="112"/>
+      <c r="AY19" s="112"/>
+      <c r="AZ19" s="112"/>
+      <c r="BA19" s="112"/>
+      <c r="BB19" s="112"/>
+      <c r="BC19" s="113"/>
     </row>
     <row r="20" spans="1:55" ht="15" customHeight="1">
       <c r="A20" s="40"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="83"/>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="83"/>
-      <c r="S20" s="83"/>
-      <c r="T20" s="83"/>
-      <c r="U20" s="83"/>
-      <c r="V20" s="83"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="83"/>
-      <c r="Y20" s="83"/>
-      <c r="Z20" s="83"/>
-      <c r="AA20" s="83"/>
-      <c r="AB20" s="83"/>
-      <c r="AC20" s="83"/>
-      <c r="AD20" s="83"/>
-      <c r="AE20" s="83"/>
-      <c r="AF20" s="83"/>
-      <c r="AG20" s="83"/>
-      <c r="AH20" s="83"/>
-      <c r="AI20" s="83"/>
-      <c r="AJ20" s="83"/>
-      <c r="AK20" s="86"/>
-      <c r="AL20" s="86"/>
-      <c r="AM20" s="86"/>
-      <c r="AN20" s="87"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="83"/>
-      <c r="AQ20" s="83"/>
-      <c r="AR20" s="83"/>
-      <c r="AS20" s="83"/>
-      <c r="AT20" s="83"/>
-      <c r="AU20" s="83"/>
-      <c r="AV20" s="83"/>
-      <c r="AW20" s="83"/>
-      <c r="AX20" s="83"/>
-      <c r="AY20" s="83"/>
-      <c r="AZ20" s="83"/>
-      <c r="BA20" s="83"/>
-      <c r="BB20" s="83"/>
-      <c r="BC20" s="84"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="112"/>
+      <c r="R20" s="112"/>
+      <c r="S20" s="112"/>
+      <c r="T20" s="112"/>
+      <c r="U20" s="112"/>
+      <c r="V20" s="112"/>
+      <c r="W20" s="112"/>
+      <c r="X20" s="112"/>
+      <c r="Y20" s="112"/>
+      <c r="Z20" s="112"/>
+      <c r="AA20" s="112"/>
+      <c r="AB20" s="112"/>
+      <c r="AC20" s="112"/>
+      <c r="AD20" s="112"/>
+      <c r="AE20" s="112"/>
+      <c r="AF20" s="112"/>
+      <c r="AG20" s="112"/>
+      <c r="AH20" s="112"/>
+      <c r="AI20" s="112"/>
+      <c r="AJ20" s="112"/>
+      <c r="AK20" s="114"/>
+      <c r="AL20" s="114"/>
+      <c r="AM20" s="114"/>
+      <c r="AN20" s="115"/>
+      <c r="AO20" s="111"/>
+      <c r="AP20" s="112"/>
+      <c r="AQ20" s="112"/>
+      <c r="AR20" s="112"/>
+      <c r="AS20" s="112"/>
+      <c r="AT20" s="112"/>
+      <c r="AU20" s="112"/>
+      <c r="AV20" s="112"/>
+      <c r="AW20" s="112"/>
+      <c r="AX20" s="112"/>
+      <c r="AY20" s="112"/>
+      <c r="AZ20" s="112"/>
+      <c r="BA20" s="112"/>
+      <c r="BB20" s="112"/>
+      <c r="BC20" s="113"/>
     </row>
     <row r="21" spans="1:55" ht="15" customHeight="1">
       <c r="A21" s="40"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="85"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
-      <c r="S21" s="83"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="83"/>
-      <c r="Y21" s="83"/>
-      <c r="Z21" s="83"/>
-      <c r="AA21" s="83"/>
-      <c r="AB21" s="83"/>
-      <c r="AC21" s="83"/>
-      <c r="AD21" s="83"/>
-      <c r="AE21" s="83"/>
-      <c r="AF21" s="83"/>
-      <c r="AG21" s="83"/>
-      <c r="AH21" s="83"/>
-      <c r="AI21" s="83"/>
-      <c r="AJ21" s="83"/>
-      <c r="AK21" s="86"/>
-      <c r="AL21" s="86"/>
-      <c r="AM21" s="86"/>
-      <c r="AN21" s="87"/>
-      <c r="AO21" s="82"/>
-      <c r="AP21" s="83"/>
-      <c r="AQ21" s="83"/>
-      <c r="AR21" s="83"/>
-      <c r="AS21" s="83"/>
-      <c r="AT21" s="83"/>
-      <c r="AU21" s="83"/>
-      <c r="AV21" s="83"/>
-      <c r="AW21" s="83"/>
-      <c r="AX21" s="83"/>
-      <c r="AY21" s="83"/>
-      <c r="AZ21" s="83"/>
-      <c r="BA21" s="83"/>
-      <c r="BB21" s="83"/>
-      <c r="BC21" s="84"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="112"/>
+      <c r="W21" s="112"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="112"/>
+      <c r="AE21" s="112"/>
+      <c r="AF21" s="112"/>
+      <c r="AG21" s="112"/>
+      <c r="AH21" s="112"/>
+      <c r="AI21" s="112"/>
+      <c r="AJ21" s="112"/>
+      <c r="AK21" s="114"/>
+      <c r="AL21" s="114"/>
+      <c r="AM21" s="114"/>
+      <c r="AN21" s="115"/>
+      <c r="AO21" s="111"/>
+      <c r="AP21" s="112"/>
+      <c r="AQ21" s="112"/>
+      <c r="AR21" s="112"/>
+      <c r="AS21" s="112"/>
+      <c r="AT21" s="112"/>
+      <c r="AU21" s="112"/>
+      <c r="AV21" s="112"/>
+      <c r="AW21" s="112"/>
+      <c r="AX21" s="112"/>
+      <c r="AY21" s="112"/>
+      <c r="AZ21" s="112"/>
+      <c r="BA21" s="112"/>
+      <c r="BB21" s="112"/>
+      <c r="BC21" s="113"/>
     </row>
     <row r="22" spans="1:55" ht="15" customHeight="1">
       <c r="A22" s="40"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="83"/>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="83"/>
-      <c r="S22" s="83"/>
-      <c r="T22" s="83"/>
-      <c r="U22" s="83"/>
-      <c r="V22" s="83"/>
-      <c r="W22" s="83"/>
-      <c r="X22" s="83"/>
-      <c r="Y22" s="83"/>
-      <c r="Z22" s="83"/>
-      <c r="AA22" s="83"/>
-      <c r="AB22" s="83"/>
-      <c r="AC22" s="83"/>
-      <c r="AD22" s="83"/>
-      <c r="AE22" s="83"/>
-      <c r="AF22" s="83"/>
-      <c r="AG22" s="83"/>
-      <c r="AH22" s="83"/>
-      <c r="AI22" s="83"/>
-      <c r="AJ22" s="83"/>
-      <c r="AK22" s="86"/>
-      <c r="AL22" s="86"/>
-      <c r="AM22" s="86"/>
-      <c r="AN22" s="87"/>
-      <c r="AO22" s="82"/>
-      <c r="AP22" s="83"/>
-      <c r="AQ22" s="83"/>
-      <c r="AR22" s="83"/>
-      <c r="AS22" s="83"/>
-      <c r="AT22" s="83"/>
-      <c r="AU22" s="83"/>
-      <c r="AV22" s="83"/>
-      <c r="AW22" s="83"/>
-      <c r="AX22" s="83"/>
-      <c r="AY22" s="83"/>
-      <c r="AZ22" s="83"/>
-      <c r="BA22" s="83"/>
-      <c r="BB22" s="83"/>
-      <c r="BC22" s="84"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="106"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="112"/>
+      <c r="R22" s="112"/>
+      <c r="S22" s="112"/>
+      <c r="T22" s="112"/>
+      <c r="U22" s="112"/>
+      <c r="V22" s="112"/>
+      <c r="W22" s="112"/>
+      <c r="X22" s="112"/>
+      <c r="Y22" s="112"/>
+      <c r="Z22" s="112"/>
+      <c r="AA22" s="112"/>
+      <c r="AB22" s="112"/>
+      <c r="AC22" s="112"/>
+      <c r="AD22" s="112"/>
+      <c r="AE22" s="112"/>
+      <c r="AF22" s="112"/>
+      <c r="AG22" s="112"/>
+      <c r="AH22" s="112"/>
+      <c r="AI22" s="112"/>
+      <c r="AJ22" s="112"/>
+      <c r="AK22" s="114"/>
+      <c r="AL22" s="114"/>
+      <c r="AM22" s="114"/>
+      <c r="AN22" s="115"/>
+      <c r="AO22" s="111"/>
+      <c r="AP22" s="112"/>
+      <c r="AQ22" s="112"/>
+      <c r="AR22" s="112"/>
+      <c r="AS22" s="112"/>
+      <c r="AT22" s="112"/>
+      <c r="AU22" s="112"/>
+      <c r="AV22" s="112"/>
+      <c r="AW22" s="112"/>
+      <c r="AX22" s="112"/>
+      <c r="AY22" s="112"/>
+      <c r="AZ22" s="112"/>
+      <c r="BA22" s="112"/>
+      <c r="BB22" s="112"/>
+      <c r="BC22" s="113"/>
     </row>
     <row r="23" spans="1:55" ht="15" customHeight="1">
       <c r="A23" s="41"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="83"/>
-      <c r="S23" s="83"/>
-      <c r="T23" s="83"/>
-      <c r="U23" s="83"/>
-      <c r="V23" s="83"/>
-      <c r="W23" s="83"/>
-      <c r="X23" s="83"/>
-      <c r="Y23" s="83"/>
-      <c r="Z23" s="83"/>
-      <c r="AA23" s="83"/>
-      <c r="AB23" s="83"/>
-      <c r="AC23" s="83"/>
-      <c r="AD23" s="83"/>
-      <c r="AE23" s="83"/>
-      <c r="AF23" s="83"/>
-      <c r="AG23" s="83"/>
-      <c r="AH23" s="83"/>
-      <c r="AI23" s="83"/>
-      <c r="AJ23" s="83"/>
-      <c r="AK23" s="86"/>
-      <c r="AL23" s="86"/>
-      <c r="AM23" s="86"/>
-      <c r="AN23" s="87"/>
-      <c r="AO23" s="82"/>
-      <c r="AP23" s="83"/>
-      <c r="AQ23" s="83"/>
-      <c r="AR23" s="83"/>
-      <c r="AS23" s="83"/>
-      <c r="AT23" s="83"/>
-      <c r="AU23" s="83"/>
-      <c r="AV23" s="83"/>
-      <c r="AW23" s="83"/>
-      <c r="AX23" s="83"/>
-      <c r="AY23" s="83"/>
-      <c r="AZ23" s="83"/>
-      <c r="BA23" s="83"/>
-      <c r="BB23" s="83"/>
-      <c r="BC23" s="84"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="112"/>
+      <c r="R23" s="112"/>
+      <c r="S23" s="112"/>
+      <c r="T23" s="112"/>
+      <c r="U23" s="112"/>
+      <c r="V23" s="112"/>
+      <c r="W23" s="112"/>
+      <c r="X23" s="112"/>
+      <c r="Y23" s="112"/>
+      <c r="Z23" s="112"/>
+      <c r="AA23" s="112"/>
+      <c r="AB23" s="112"/>
+      <c r="AC23" s="112"/>
+      <c r="AD23" s="112"/>
+      <c r="AE23" s="112"/>
+      <c r="AF23" s="112"/>
+      <c r="AG23" s="112"/>
+      <c r="AH23" s="112"/>
+      <c r="AI23" s="112"/>
+      <c r="AJ23" s="112"/>
+      <c r="AK23" s="114"/>
+      <c r="AL23" s="114"/>
+      <c r="AM23" s="114"/>
+      <c r="AN23" s="115"/>
+      <c r="AO23" s="111"/>
+      <c r="AP23" s="112"/>
+      <c r="AQ23" s="112"/>
+      <c r="AR23" s="112"/>
+      <c r="AS23" s="112"/>
+      <c r="AT23" s="112"/>
+      <c r="AU23" s="112"/>
+      <c r="AV23" s="112"/>
+      <c r="AW23" s="112"/>
+      <c r="AX23" s="112"/>
+      <c r="AY23" s="112"/>
+      <c r="AZ23" s="112"/>
+      <c r="BA23" s="112"/>
+      <c r="BB23" s="112"/>
+      <c r="BC23" s="113"/>
     </row>
     <row r="24" spans="1:55" ht="15" customHeight="1">
       <c r="A24" s="41"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
-      <c r="S24" s="83"/>
-      <c r="T24" s="83"/>
-      <c r="U24" s="83"/>
-      <c r="V24" s="83"/>
-      <c r="W24" s="83"/>
-      <c r="X24" s="83"/>
-      <c r="Y24" s="83"/>
-      <c r="Z24" s="83"/>
-      <c r="AA24" s="83"/>
-      <c r="AB24" s="83"/>
-      <c r="AC24" s="83"/>
-      <c r="AD24" s="83"/>
-      <c r="AE24" s="83"/>
-      <c r="AF24" s="83"/>
-      <c r="AG24" s="83"/>
-      <c r="AH24" s="83"/>
-      <c r="AI24" s="83"/>
-      <c r="AJ24" s="83"/>
-      <c r="AK24" s="86"/>
-      <c r="AL24" s="86"/>
-      <c r="AM24" s="86"/>
-      <c r="AN24" s="87"/>
-      <c r="AO24" s="82"/>
-      <c r="AP24" s="83"/>
-      <c r="AQ24" s="83"/>
-      <c r="AR24" s="83"/>
-      <c r="AS24" s="83"/>
-      <c r="AT24" s="83"/>
-      <c r="AU24" s="83"/>
-      <c r="AV24" s="83"/>
-      <c r="AW24" s="83"/>
-      <c r="AX24" s="83"/>
-      <c r="AY24" s="83"/>
-      <c r="AZ24" s="83"/>
-      <c r="BA24" s="83"/>
-      <c r="BB24" s="83"/>
-      <c r="BC24" s="84"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="112"/>
+      <c r="R24" s="112"/>
+      <c r="S24" s="112"/>
+      <c r="T24" s="112"/>
+      <c r="U24" s="112"/>
+      <c r="V24" s="112"/>
+      <c r="W24" s="112"/>
+      <c r="X24" s="112"/>
+      <c r="Y24" s="112"/>
+      <c r="Z24" s="112"/>
+      <c r="AA24" s="112"/>
+      <c r="AB24" s="112"/>
+      <c r="AC24" s="112"/>
+      <c r="AD24" s="112"/>
+      <c r="AE24" s="112"/>
+      <c r="AF24" s="112"/>
+      <c r="AG24" s="112"/>
+      <c r="AH24" s="112"/>
+      <c r="AI24" s="112"/>
+      <c r="AJ24" s="112"/>
+      <c r="AK24" s="114"/>
+      <c r="AL24" s="114"/>
+      <c r="AM24" s="114"/>
+      <c r="AN24" s="115"/>
+      <c r="AO24" s="111"/>
+      <c r="AP24" s="112"/>
+      <c r="AQ24" s="112"/>
+      <c r="AR24" s="112"/>
+      <c r="AS24" s="112"/>
+      <c r="AT24" s="112"/>
+      <c r="AU24" s="112"/>
+      <c r="AV24" s="112"/>
+      <c r="AW24" s="112"/>
+      <c r="AX24" s="112"/>
+      <c r="AY24" s="112"/>
+      <c r="AZ24" s="112"/>
+      <c r="BA24" s="112"/>
+      <c r="BB24" s="112"/>
+      <c r="BC24" s="113"/>
     </row>
     <row r="25" spans="1:55" ht="15" customHeight="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="83"/>
-      <c r="S25" s="83"/>
-      <c r="T25" s="83"/>
-      <c r="U25" s="83"/>
-      <c r="V25" s="83"/>
-      <c r="W25" s="83"/>
-      <c r="X25" s="83"/>
-      <c r="Y25" s="83"/>
-      <c r="Z25" s="83"/>
-      <c r="AA25" s="83"/>
-      <c r="AB25" s="83"/>
-      <c r="AC25" s="83"/>
-      <c r="AD25" s="83"/>
-      <c r="AE25" s="83"/>
-      <c r="AF25" s="83"/>
-      <c r="AG25" s="83"/>
-      <c r="AH25" s="83"/>
-      <c r="AI25" s="83"/>
-      <c r="AJ25" s="83"/>
-      <c r="AK25" s="86"/>
-      <c r="AL25" s="86"/>
-      <c r="AM25" s="86"/>
-      <c r="AN25" s="87"/>
-      <c r="AO25" s="82"/>
-      <c r="AP25" s="83"/>
-      <c r="AQ25" s="83"/>
-      <c r="AR25" s="83"/>
-      <c r="AS25" s="83"/>
-      <c r="AT25" s="83"/>
-      <c r="AU25" s="83"/>
-      <c r="AV25" s="83"/>
-      <c r="AW25" s="83"/>
-      <c r="AX25" s="83"/>
-      <c r="AY25" s="83"/>
-      <c r="AZ25" s="83"/>
-      <c r="BA25" s="83"/>
-      <c r="BB25" s="83"/>
-      <c r="BC25" s="84"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="112"/>
+      <c r="R25" s="112"/>
+      <c r="S25" s="112"/>
+      <c r="T25" s="112"/>
+      <c r="U25" s="112"/>
+      <c r="V25" s="112"/>
+      <c r="W25" s="112"/>
+      <c r="X25" s="112"/>
+      <c r="Y25" s="112"/>
+      <c r="Z25" s="112"/>
+      <c r="AA25" s="112"/>
+      <c r="AB25" s="112"/>
+      <c r="AC25" s="112"/>
+      <c r="AD25" s="112"/>
+      <c r="AE25" s="112"/>
+      <c r="AF25" s="112"/>
+      <c r="AG25" s="112"/>
+      <c r="AH25" s="112"/>
+      <c r="AI25" s="112"/>
+      <c r="AJ25" s="112"/>
+      <c r="AK25" s="114"/>
+      <c r="AL25" s="114"/>
+      <c r="AM25" s="114"/>
+      <c r="AN25" s="115"/>
+      <c r="AO25" s="111"/>
+      <c r="AP25" s="112"/>
+      <c r="AQ25" s="112"/>
+      <c r="AR25" s="112"/>
+      <c r="AS25" s="112"/>
+      <c r="AT25" s="112"/>
+      <c r="AU25" s="112"/>
+      <c r="AV25" s="112"/>
+      <c r="AW25" s="112"/>
+      <c r="AX25" s="112"/>
+      <c r="AY25" s="112"/>
+      <c r="AZ25" s="112"/>
+      <c r="BA25" s="112"/>
+      <c r="BB25" s="112"/>
+      <c r="BC25" s="113"/>
     </row>
     <row r="26" spans="1:55" ht="15" customHeight="1">
       <c r="A26" s="40"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="83"/>
-      <c r="S26" s="83"/>
-      <c r="T26" s="83"/>
-      <c r="U26" s="83"/>
-      <c r="V26" s="83"/>
-      <c r="W26" s="83"/>
-      <c r="X26" s="83"/>
-      <c r="Y26" s="83"/>
-      <c r="Z26" s="83"/>
-      <c r="AA26" s="83"/>
-      <c r="AB26" s="83"/>
-      <c r="AC26" s="83"/>
-      <c r="AD26" s="83"/>
-      <c r="AE26" s="83"/>
-      <c r="AF26" s="83"/>
-      <c r="AG26" s="83"/>
-      <c r="AH26" s="83"/>
-      <c r="AI26" s="83"/>
-      <c r="AJ26" s="83"/>
-      <c r="AK26" s="86"/>
-      <c r="AL26" s="86"/>
-      <c r="AM26" s="86"/>
-      <c r="AN26" s="87"/>
-      <c r="AO26" s="82"/>
-      <c r="AP26" s="83"/>
-      <c r="AQ26" s="83"/>
-      <c r="AR26" s="83"/>
-      <c r="AS26" s="83"/>
-      <c r="AT26" s="83"/>
-      <c r="AU26" s="83"/>
-      <c r="AV26" s="83"/>
-      <c r="AW26" s="83"/>
-      <c r="AX26" s="83"/>
-      <c r="AY26" s="83"/>
-      <c r="AZ26" s="83"/>
-      <c r="BA26" s="83"/>
-      <c r="BB26" s="83"/>
-      <c r="BC26" s="84"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="112"/>
+      <c r="R26" s="112"/>
+      <c r="S26" s="112"/>
+      <c r="T26" s="112"/>
+      <c r="U26" s="112"/>
+      <c r="V26" s="112"/>
+      <c r="W26" s="112"/>
+      <c r="X26" s="112"/>
+      <c r="Y26" s="112"/>
+      <c r="Z26" s="112"/>
+      <c r="AA26" s="112"/>
+      <c r="AB26" s="112"/>
+      <c r="AC26" s="112"/>
+      <c r="AD26" s="112"/>
+      <c r="AE26" s="112"/>
+      <c r="AF26" s="112"/>
+      <c r="AG26" s="112"/>
+      <c r="AH26" s="112"/>
+      <c r="AI26" s="112"/>
+      <c r="AJ26" s="112"/>
+      <c r="AK26" s="114"/>
+      <c r="AL26" s="114"/>
+      <c r="AM26" s="114"/>
+      <c r="AN26" s="115"/>
+      <c r="AO26" s="111"/>
+      <c r="AP26" s="112"/>
+      <c r="AQ26" s="112"/>
+      <c r="AR26" s="112"/>
+      <c r="AS26" s="112"/>
+      <c r="AT26" s="112"/>
+      <c r="AU26" s="112"/>
+      <c r="AV26" s="112"/>
+      <c r="AW26" s="112"/>
+      <c r="AX26" s="112"/>
+      <c r="AY26" s="112"/>
+      <c r="AZ26" s="112"/>
+      <c r="BA26" s="112"/>
+      <c r="BB26" s="112"/>
+      <c r="BC26" s="113"/>
     </row>
     <row r="27" spans="1:55" ht="15" customHeight="1">
       <c r="A27" s="40"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="83"/>
-      <c r="S27" s="83"/>
-      <c r="T27" s="83"/>
-      <c r="U27" s="83"/>
-      <c r="V27" s="83"/>
-      <c r="W27" s="83"/>
-      <c r="X27" s="83"/>
-      <c r="Y27" s="83"/>
-      <c r="Z27" s="83"/>
-      <c r="AA27" s="83"/>
-      <c r="AB27" s="83"/>
-      <c r="AC27" s="83"/>
-      <c r="AD27" s="83"/>
-      <c r="AE27" s="83"/>
-      <c r="AF27" s="83"/>
-      <c r="AG27" s="83"/>
-      <c r="AH27" s="83"/>
-      <c r="AI27" s="83"/>
-      <c r="AJ27" s="83"/>
-      <c r="AK27" s="86"/>
-      <c r="AL27" s="86"/>
-      <c r="AM27" s="86"/>
-      <c r="AN27" s="87"/>
-      <c r="AO27" s="82"/>
-      <c r="AP27" s="83"/>
-      <c r="AQ27" s="83"/>
-      <c r="AR27" s="83"/>
-      <c r="AS27" s="83"/>
-      <c r="AT27" s="83"/>
-      <c r="AU27" s="83"/>
-      <c r="AV27" s="83"/>
-      <c r="AW27" s="83"/>
-      <c r="AX27" s="83"/>
-      <c r="AY27" s="83"/>
-      <c r="AZ27" s="83"/>
-      <c r="BA27" s="83"/>
-      <c r="BB27" s="83"/>
-      <c r="BC27" s="84"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="107"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="112"/>
+      <c r="R27" s="112"/>
+      <c r="S27" s="112"/>
+      <c r="T27" s="112"/>
+      <c r="U27" s="112"/>
+      <c r="V27" s="112"/>
+      <c r="W27" s="112"/>
+      <c r="X27" s="112"/>
+      <c r="Y27" s="112"/>
+      <c r="Z27" s="112"/>
+      <c r="AA27" s="112"/>
+      <c r="AB27" s="112"/>
+      <c r="AC27" s="112"/>
+      <c r="AD27" s="112"/>
+      <c r="AE27" s="112"/>
+      <c r="AF27" s="112"/>
+      <c r="AG27" s="112"/>
+      <c r="AH27" s="112"/>
+      <c r="AI27" s="112"/>
+      <c r="AJ27" s="112"/>
+      <c r="AK27" s="114"/>
+      <c r="AL27" s="114"/>
+      <c r="AM27" s="114"/>
+      <c r="AN27" s="115"/>
+      <c r="AO27" s="111"/>
+      <c r="AP27" s="112"/>
+      <c r="AQ27" s="112"/>
+      <c r="AR27" s="112"/>
+      <c r="AS27" s="112"/>
+      <c r="AT27" s="112"/>
+      <c r="AU27" s="112"/>
+      <c r="AV27" s="112"/>
+      <c r="AW27" s="112"/>
+      <c r="AX27" s="112"/>
+      <c r="AY27" s="112"/>
+      <c r="AZ27" s="112"/>
+      <c r="BA27" s="112"/>
+      <c r="BB27" s="112"/>
+      <c r="BC27" s="113"/>
     </row>
     <row r="28" spans="1:55" ht="15" customHeight="1">
       <c r="A28" s="40"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-      <c r="R28" s="83"/>
-      <c r="S28" s="83"/>
-      <c r="T28" s="83"/>
-      <c r="U28" s="83"/>
-      <c r="V28" s="83"/>
-      <c r="W28" s="83"/>
-      <c r="X28" s="83"/>
-      <c r="Y28" s="83"/>
-      <c r="Z28" s="83"/>
-      <c r="AA28" s="83"/>
-      <c r="AB28" s="83"/>
-      <c r="AC28" s="83"/>
-      <c r="AD28" s="83"/>
-      <c r="AE28" s="83"/>
-      <c r="AF28" s="83"/>
-      <c r="AG28" s="83"/>
-      <c r="AH28" s="83"/>
-      <c r="AI28" s="83"/>
-      <c r="AJ28" s="83"/>
-      <c r="AK28" s="86"/>
-      <c r="AL28" s="86"/>
-      <c r="AM28" s="86"/>
-      <c r="AN28" s="87"/>
-      <c r="AO28" s="82"/>
-      <c r="AP28" s="83"/>
-      <c r="AQ28" s="83"/>
-      <c r="AR28" s="83"/>
-      <c r="AS28" s="83"/>
-      <c r="AT28" s="83"/>
-      <c r="AU28" s="83"/>
-      <c r="AV28" s="83"/>
-      <c r="AW28" s="83"/>
-      <c r="AX28" s="83"/>
-      <c r="AY28" s="83"/>
-      <c r="AZ28" s="83"/>
-      <c r="BA28" s="83"/>
-      <c r="BB28" s="83"/>
-      <c r="BC28" s="84"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="106"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="106"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="107"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="112"/>
+      <c r="K28" s="112"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="112"/>
+      <c r="R28" s="112"/>
+      <c r="S28" s="112"/>
+      <c r="T28" s="112"/>
+      <c r="U28" s="112"/>
+      <c r="V28" s="112"/>
+      <c r="W28" s="112"/>
+      <c r="X28" s="112"/>
+      <c r="Y28" s="112"/>
+      <c r="Z28" s="112"/>
+      <c r="AA28" s="112"/>
+      <c r="AB28" s="112"/>
+      <c r="AC28" s="112"/>
+      <c r="AD28" s="112"/>
+      <c r="AE28" s="112"/>
+      <c r="AF28" s="112"/>
+      <c r="AG28" s="112"/>
+      <c r="AH28" s="112"/>
+      <c r="AI28" s="112"/>
+      <c r="AJ28" s="112"/>
+      <c r="AK28" s="114"/>
+      <c r="AL28" s="114"/>
+      <c r="AM28" s="114"/>
+      <c r="AN28" s="115"/>
+      <c r="AO28" s="111"/>
+      <c r="AP28" s="112"/>
+      <c r="AQ28" s="112"/>
+      <c r="AR28" s="112"/>
+      <c r="AS28" s="112"/>
+      <c r="AT28" s="112"/>
+      <c r="AU28" s="112"/>
+      <c r="AV28" s="112"/>
+      <c r="AW28" s="112"/>
+      <c r="AX28" s="112"/>
+      <c r="AY28" s="112"/>
+      <c r="AZ28" s="112"/>
+      <c r="BA28" s="112"/>
+      <c r="BB28" s="112"/>
+      <c r="BC28" s="113"/>
     </row>
     <row r="29" spans="1:55" ht="15" customHeight="1">
       <c r="A29" s="40"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="83"/>
-      <c r="R29" s="83"/>
-      <c r="S29" s="83"/>
-      <c r="T29" s="83"/>
-      <c r="U29" s="83"/>
-      <c r="V29" s="83"/>
-      <c r="W29" s="83"/>
-      <c r="X29" s="83"/>
-      <c r="Y29" s="83"/>
-      <c r="Z29" s="83"/>
-      <c r="AA29" s="83"/>
-      <c r="AB29" s="83"/>
-      <c r="AC29" s="83"/>
-      <c r="AD29" s="83"/>
-      <c r="AE29" s="83"/>
-      <c r="AF29" s="83"/>
-      <c r="AG29" s="83"/>
-      <c r="AH29" s="83"/>
-      <c r="AI29" s="83"/>
-      <c r="AJ29" s="83"/>
-      <c r="AK29" s="86"/>
-      <c r="AL29" s="86"/>
-      <c r="AM29" s="86"/>
-      <c r="AN29" s="87"/>
-      <c r="AO29" s="82"/>
-      <c r="AP29" s="83"/>
-      <c r="AQ29" s="83"/>
-      <c r="AR29" s="83"/>
-      <c r="AS29" s="83"/>
-      <c r="AT29" s="83"/>
-      <c r="AU29" s="83"/>
-      <c r="AV29" s="83"/>
-      <c r="AW29" s="83"/>
-      <c r="AX29" s="83"/>
-      <c r="AY29" s="83"/>
-      <c r="AZ29" s="83"/>
-      <c r="BA29" s="83"/>
-      <c r="BB29" s="83"/>
-      <c r="BC29" s="84"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="107"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="112"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="112"/>
+      <c r="R29" s="112"/>
+      <c r="S29" s="112"/>
+      <c r="T29" s="112"/>
+      <c r="U29" s="112"/>
+      <c r="V29" s="112"/>
+      <c r="W29" s="112"/>
+      <c r="X29" s="112"/>
+      <c r="Y29" s="112"/>
+      <c r="Z29" s="112"/>
+      <c r="AA29" s="112"/>
+      <c r="AB29" s="112"/>
+      <c r="AC29" s="112"/>
+      <c r="AD29" s="112"/>
+      <c r="AE29" s="112"/>
+      <c r="AF29" s="112"/>
+      <c r="AG29" s="112"/>
+      <c r="AH29" s="112"/>
+      <c r="AI29" s="112"/>
+      <c r="AJ29" s="112"/>
+      <c r="AK29" s="114"/>
+      <c r="AL29" s="114"/>
+      <c r="AM29" s="114"/>
+      <c r="AN29" s="115"/>
+      <c r="AO29" s="111"/>
+      <c r="AP29" s="112"/>
+      <c r="AQ29" s="112"/>
+      <c r="AR29" s="112"/>
+      <c r="AS29" s="112"/>
+      <c r="AT29" s="112"/>
+      <c r="AU29" s="112"/>
+      <c r="AV29" s="112"/>
+      <c r="AW29" s="112"/>
+      <c r="AX29" s="112"/>
+      <c r="AY29" s="112"/>
+      <c r="AZ29" s="112"/>
+      <c r="BA29" s="112"/>
+      <c r="BB29" s="112"/>
+      <c r="BC29" s="113"/>
     </row>
     <row r="30" spans="1:55" ht="15" customHeight="1">
       <c r="A30" s="40"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="83"/>
-      <c r="R30" s="83"/>
-      <c r="S30" s="83"/>
-      <c r="T30" s="83"/>
-      <c r="U30" s="83"/>
-      <c r="V30" s="83"/>
-      <c r="W30" s="83"/>
-      <c r="X30" s="83"/>
-      <c r="Y30" s="83"/>
-      <c r="Z30" s="83"/>
-      <c r="AA30" s="83"/>
-      <c r="AB30" s="83"/>
-      <c r="AC30" s="83"/>
-      <c r="AD30" s="83"/>
-      <c r="AE30" s="83"/>
-      <c r="AF30" s="83"/>
-      <c r="AG30" s="83"/>
-      <c r="AH30" s="83"/>
-      <c r="AI30" s="83"/>
-      <c r="AJ30" s="83"/>
-      <c r="AK30" s="86"/>
-      <c r="AL30" s="86"/>
-      <c r="AM30" s="86"/>
-      <c r="AN30" s="87"/>
-      <c r="AO30" s="82"/>
-      <c r="AP30" s="83"/>
-      <c r="AQ30" s="83"/>
-      <c r="AR30" s="83"/>
-      <c r="AS30" s="83"/>
-      <c r="AT30" s="83"/>
-      <c r="AU30" s="83"/>
-      <c r="AV30" s="83"/>
-      <c r="AW30" s="83"/>
-      <c r="AX30" s="83"/>
-      <c r="AY30" s="83"/>
-      <c r="AZ30" s="83"/>
-      <c r="BA30" s="83"/>
-      <c r="BB30" s="83"/>
-      <c r="BC30" s="84"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="107"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="112"/>
+      <c r="K30" s="112"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="112"/>
+      <c r="R30" s="112"/>
+      <c r="S30" s="112"/>
+      <c r="T30" s="112"/>
+      <c r="U30" s="112"/>
+      <c r="V30" s="112"/>
+      <c r="W30" s="112"/>
+      <c r="X30" s="112"/>
+      <c r="Y30" s="112"/>
+      <c r="Z30" s="112"/>
+      <c r="AA30" s="112"/>
+      <c r="AB30" s="112"/>
+      <c r="AC30" s="112"/>
+      <c r="AD30" s="112"/>
+      <c r="AE30" s="112"/>
+      <c r="AF30" s="112"/>
+      <c r="AG30" s="112"/>
+      <c r="AH30" s="112"/>
+      <c r="AI30" s="112"/>
+      <c r="AJ30" s="112"/>
+      <c r="AK30" s="114"/>
+      <c r="AL30" s="114"/>
+      <c r="AM30" s="114"/>
+      <c r="AN30" s="115"/>
+      <c r="AO30" s="111"/>
+      <c r="AP30" s="112"/>
+      <c r="AQ30" s="112"/>
+      <c r="AR30" s="112"/>
+      <c r="AS30" s="112"/>
+      <c r="AT30" s="112"/>
+      <c r="AU30" s="112"/>
+      <c r="AV30" s="112"/>
+      <c r="AW30" s="112"/>
+      <c r="AX30" s="112"/>
+      <c r="AY30" s="112"/>
+      <c r="AZ30" s="112"/>
+      <c r="BA30" s="112"/>
+      <c r="BB30" s="112"/>
+      <c r="BC30" s="113"/>
     </row>
     <row r="31" spans="1:55" ht="15" customHeight="1">
       <c r="A31" s="40"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="83"/>
-      <c r="R31" s="83"/>
-      <c r="S31" s="83"/>
-      <c r="T31" s="83"/>
-      <c r="U31" s="83"/>
-      <c r="V31" s="83"/>
-      <c r="W31" s="83"/>
-      <c r="X31" s="83"/>
-      <c r="Y31" s="83"/>
-      <c r="Z31" s="83"/>
-      <c r="AA31" s="83"/>
-      <c r="AB31" s="83"/>
-      <c r="AC31" s="83"/>
-      <c r="AD31" s="83"/>
-      <c r="AE31" s="83"/>
-      <c r="AF31" s="83"/>
-      <c r="AG31" s="83"/>
-      <c r="AH31" s="83"/>
-      <c r="AI31" s="83"/>
-      <c r="AJ31" s="83"/>
-      <c r="AK31" s="86"/>
-      <c r="AL31" s="86"/>
-      <c r="AM31" s="86"/>
-      <c r="AN31" s="87"/>
-      <c r="AO31" s="82"/>
-      <c r="AP31" s="83"/>
-      <c r="AQ31" s="83"/>
-      <c r="AR31" s="83"/>
-      <c r="AS31" s="83"/>
-      <c r="AT31" s="83"/>
-      <c r="AU31" s="83"/>
-      <c r="AV31" s="83"/>
-      <c r="AW31" s="83"/>
-      <c r="AX31" s="83"/>
-      <c r="AY31" s="83"/>
-      <c r="AZ31" s="83"/>
-      <c r="BA31" s="83"/>
-      <c r="BB31" s="83"/>
-      <c r="BC31" s="84"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="106"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="107"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="112"/>
+      <c r="T31" s="112"/>
+      <c r="U31" s="112"/>
+      <c r="V31" s="112"/>
+      <c r="W31" s="112"/>
+      <c r="X31" s="112"/>
+      <c r="Y31" s="112"/>
+      <c r="Z31" s="112"/>
+      <c r="AA31" s="112"/>
+      <c r="AB31" s="112"/>
+      <c r="AC31" s="112"/>
+      <c r="AD31" s="112"/>
+      <c r="AE31" s="112"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="112"/>
+      <c r="AH31" s="112"/>
+      <c r="AI31" s="112"/>
+      <c r="AJ31" s="112"/>
+      <c r="AK31" s="114"/>
+      <c r="AL31" s="114"/>
+      <c r="AM31" s="114"/>
+      <c r="AN31" s="115"/>
+      <c r="AO31" s="111"/>
+      <c r="AP31" s="112"/>
+      <c r="AQ31" s="112"/>
+      <c r="AR31" s="112"/>
+      <c r="AS31" s="112"/>
+      <c r="AT31" s="112"/>
+      <c r="AU31" s="112"/>
+      <c r="AV31" s="112"/>
+      <c r="AW31" s="112"/>
+      <c r="AX31" s="112"/>
+      <c r="AY31" s="112"/>
+      <c r="AZ31" s="112"/>
+      <c r="BA31" s="112"/>
+      <c r="BB31" s="112"/>
+      <c r="BC31" s="113"/>
     </row>
     <row r="32" spans="1:55" ht="15" customHeight="1">
       <c r="A32" s="40"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="83"/>
-      <c r="P32" s="83"/>
-      <c r="Q32" s="83"/>
-      <c r="R32" s="83"/>
-      <c r="S32" s="83"/>
-      <c r="T32" s="83"/>
-      <c r="U32" s="83"/>
-      <c r="V32" s="83"/>
-      <c r="W32" s="83"/>
-      <c r="X32" s="83"/>
-      <c r="Y32" s="83"/>
-      <c r="Z32" s="83"/>
-      <c r="AA32" s="83"/>
-      <c r="AB32" s="83"/>
-      <c r="AC32" s="83"/>
-      <c r="AD32" s="83"/>
-      <c r="AE32" s="83"/>
-      <c r="AF32" s="83"/>
-      <c r="AG32" s="83"/>
-      <c r="AH32" s="83"/>
-      <c r="AI32" s="83"/>
-      <c r="AJ32" s="83"/>
-      <c r="AK32" s="86"/>
-      <c r="AL32" s="86"/>
-      <c r="AM32" s="86"/>
-      <c r="AN32" s="87"/>
-      <c r="AO32" s="82"/>
-      <c r="AP32" s="83"/>
-      <c r="AQ32" s="83"/>
-      <c r="AR32" s="83"/>
-      <c r="AS32" s="83"/>
-      <c r="AT32" s="83"/>
-      <c r="AU32" s="83"/>
-      <c r="AV32" s="83"/>
-      <c r="AW32" s="83"/>
-      <c r="AX32" s="83"/>
-      <c r="AY32" s="83"/>
-      <c r="AZ32" s="83"/>
-      <c r="BA32" s="83"/>
-      <c r="BB32" s="83"/>
-      <c r="BC32" s="84"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="112"/>
+      <c r="K32" s="112"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="112"/>
+      <c r="R32" s="112"/>
+      <c r="S32" s="112"/>
+      <c r="T32" s="112"/>
+      <c r="U32" s="112"/>
+      <c r="V32" s="112"/>
+      <c r="W32" s="112"/>
+      <c r="X32" s="112"/>
+      <c r="Y32" s="112"/>
+      <c r="Z32" s="112"/>
+      <c r="AA32" s="112"/>
+      <c r="AB32" s="112"/>
+      <c r="AC32" s="112"/>
+      <c r="AD32" s="112"/>
+      <c r="AE32" s="112"/>
+      <c r="AF32" s="112"/>
+      <c r="AG32" s="112"/>
+      <c r="AH32" s="112"/>
+      <c r="AI32" s="112"/>
+      <c r="AJ32" s="112"/>
+      <c r="AK32" s="114"/>
+      <c r="AL32" s="114"/>
+      <c r="AM32" s="114"/>
+      <c r="AN32" s="115"/>
+      <c r="AO32" s="111"/>
+      <c r="AP32" s="112"/>
+      <c r="AQ32" s="112"/>
+      <c r="AR32" s="112"/>
+      <c r="AS32" s="112"/>
+      <c r="AT32" s="112"/>
+      <c r="AU32" s="112"/>
+      <c r="AV32" s="112"/>
+      <c r="AW32" s="112"/>
+      <c r="AX32" s="112"/>
+      <c r="AY32" s="112"/>
+      <c r="AZ32" s="112"/>
+      <c r="BA32" s="112"/>
+      <c r="BB32" s="112"/>
+      <c r="BC32" s="113"/>
     </row>
     <row r="33" spans="1:55" ht="15" customHeight="1">
       <c r="A33" s="40"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="83"/>
-      <c r="S33" s="83"/>
-      <c r="T33" s="83"/>
-      <c r="U33" s="83"/>
-      <c r="V33" s="83"/>
-      <c r="W33" s="83"/>
-      <c r="X33" s="83"/>
-      <c r="Y33" s="83"/>
-      <c r="Z33" s="83"/>
-      <c r="AA33" s="83"/>
-      <c r="AB33" s="83"/>
-      <c r="AC33" s="83"/>
-      <c r="AD33" s="83"/>
-      <c r="AE33" s="83"/>
-      <c r="AF33" s="83"/>
-      <c r="AG33" s="83"/>
-      <c r="AH33" s="83"/>
-      <c r="AI33" s="83"/>
-      <c r="AJ33" s="83"/>
-      <c r="AK33" s="86"/>
-      <c r="AL33" s="86"/>
-      <c r="AM33" s="86"/>
-      <c r="AN33" s="87"/>
-      <c r="AO33" s="82"/>
-      <c r="AP33" s="83"/>
-      <c r="AQ33" s="83"/>
-      <c r="AR33" s="83"/>
-      <c r="AS33" s="83"/>
-      <c r="AT33" s="83"/>
-      <c r="AU33" s="83"/>
-      <c r="AV33" s="83"/>
-      <c r="AW33" s="83"/>
-      <c r="AX33" s="83"/>
-      <c r="AY33" s="83"/>
-      <c r="AZ33" s="83"/>
-      <c r="BA33" s="83"/>
-      <c r="BB33" s="83"/>
-      <c r="BC33" s="84"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="106"/>
+      <c r="D33" s="106"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="112"/>
+      <c r="K33" s="112"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="112"/>
+      <c r="R33" s="112"/>
+      <c r="S33" s="112"/>
+      <c r="T33" s="112"/>
+      <c r="U33" s="112"/>
+      <c r="V33" s="112"/>
+      <c r="W33" s="112"/>
+      <c r="X33" s="112"/>
+      <c r="Y33" s="112"/>
+      <c r="Z33" s="112"/>
+      <c r="AA33" s="112"/>
+      <c r="AB33" s="112"/>
+      <c r="AC33" s="112"/>
+      <c r="AD33" s="112"/>
+      <c r="AE33" s="112"/>
+      <c r="AF33" s="112"/>
+      <c r="AG33" s="112"/>
+      <c r="AH33" s="112"/>
+      <c r="AI33" s="112"/>
+      <c r="AJ33" s="112"/>
+      <c r="AK33" s="114"/>
+      <c r="AL33" s="114"/>
+      <c r="AM33" s="114"/>
+      <c r="AN33" s="115"/>
+      <c r="AO33" s="111"/>
+      <c r="AP33" s="112"/>
+      <c r="AQ33" s="112"/>
+      <c r="AR33" s="112"/>
+      <c r="AS33" s="112"/>
+      <c r="AT33" s="112"/>
+      <c r="AU33" s="112"/>
+      <c r="AV33" s="112"/>
+      <c r="AW33" s="112"/>
+      <c r="AX33" s="112"/>
+      <c r="AY33" s="112"/>
+      <c r="AZ33" s="112"/>
+      <c r="BA33" s="112"/>
+      <c r="BB33" s="112"/>
+      <c r="BC33" s="113"/>
     </row>
     <row r="34" spans="1:55" ht="15" customHeight="1">
       <c r="A34" s="40"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="83"/>
-      <c r="P34" s="83"/>
-      <c r="Q34" s="83"/>
-      <c r="R34" s="83"/>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="83"/>
-      <c r="V34" s="83"/>
-      <c r="W34" s="83"/>
-      <c r="X34" s="83"/>
-      <c r="Y34" s="83"/>
-      <c r="Z34" s="83"/>
-      <c r="AA34" s="83"/>
-      <c r="AB34" s="83"/>
-      <c r="AC34" s="83"/>
-      <c r="AD34" s="83"/>
-      <c r="AE34" s="83"/>
-      <c r="AF34" s="83"/>
-      <c r="AG34" s="83"/>
-      <c r="AH34" s="83"/>
-      <c r="AI34" s="83"/>
-      <c r="AJ34" s="83"/>
-      <c r="AK34" s="86"/>
-      <c r="AL34" s="86"/>
-      <c r="AM34" s="86"/>
-      <c r="AN34" s="87"/>
-      <c r="AO34" s="82"/>
-      <c r="AP34" s="83"/>
-      <c r="AQ34" s="83"/>
-      <c r="AR34" s="83"/>
-      <c r="AS34" s="83"/>
-      <c r="AT34" s="83"/>
-      <c r="AU34" s="83"/>
-      <c r="AV34" s="83"/>
-      <c r="AW34" s="83"/>
-      <c r="AX34" s="83"/>
-      <c r="AY34" s="83"/>
-      <c r="AZ34" s="83"/>
-      <c r="BA34" s="83"/>
-      <c r="BB34" s="83"/>
-      <c r="BC34" s="84"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="106"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="107"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="112"/>
+      <c r="K34" s="112"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="112"/>
+      <c r="R34" s="112"/>
+      <c r="S34" s="112"/>
+      <c r="T34" s="112"/>
+      <c r="U34" s="112"/>
+      <c r="V34" s="112"/>
+      <c r="W34" s="112"/>
+      <c r="X34" s="112"/>
+      <c r="Y34" s="112"/>
+      <c r="Z34" s="112"/>
+      <c r="AA34" s="112"/>
+      <c r="AB34" s="112"/>
+      <c r="AC34" s="112"/>
+      <c r="AD34" s="112"/>
+      <c r="AE34" s="112"/>
+      <c r="AF34" s="112"/>
+      <c r="AG34" s="112"/>
+      <c r="AH34" s="112"/>
+      <c r="AI34" s="112"/>
+      <c r="AJ34" s="112"/>
+      <c r="AK34" s="114"/>
+      <c r="AL34" s="114"/>
+      <c r="AM34" s="114"/>
+      <c r="AN34" s="115"/>
+      <c r="AO34" s="111"/>
+      <c r="AP34" s="112"/>
+      <c r="AQ34" s="112"/>
+      <c r="AR34" s="112"/>
+      <c r="AS34" s="112"/>
+      <c r="AT34" s="112"/>
+      <c r="AU34" s="112"/>
+      <c r="AV34" s="112"/>
+      <c r="AW34" s="112"/>
+      <c r="AX34" s="112"/>
+      <c r="AY34" s="112"/>
+      <c r="AZ34" s="112"/>
+      <c r="BA34" s="112"/>
+      <c r="BB34" s="112"/>
+      <c r="BC34" s="113"/>
     </row>
     <row r="35" spans="1:55" ht="15" customHeight="1">
       <c r="A35" s="40"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="83"/>
-      <c r="U35" s="83"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
-      <c r="Y35" s="83"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="83"/>
-      <c r="AC35" s="83"/>
-      <c r="AD35" s="83"/>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="83"/>
-      <c r="AG35" s="83"/>
-      <c r="AH35" s="83"/>
-      <c r="AI35" s="83"/>
-      <c r="AJ35" s="83"/>
-      <c r="AK35" s="86"/>
-      <c r="AL35" s="86"/>
-      <c r="AM35" s="86"/>
-      <c r="AN35" s="87"/>
-      <c r="AO35" s="82"/>
-      <c r="AP35" s="83"/>
-      <c r="AQ35" s="83"/>
-      <c r="AR35" s="83"/>
-      <c r="AS35" s="83"/>
-      <c r="AT35" s="83"/>
-      <c r="AU35" s="83"/>
-      <c r="AV35" s="83"/>
-      <c r="AW35" s="83"/>
-      <c r="AX35" s="83"/>
-      <c r="AY35" s="83"/>
-      <c r="AZ35" s="83"/>
-      <c r="BA35" s="83"/>
-      <c r="BB35" s="83"/>
-      <c r="BC35" s="84"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="106"/>
+      <c r="D35" s="106"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="107"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="112"/>
+      <c r="K35" s="112"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="112"/>
+      <c r="R35" s="112"/>
+      <c r="S35" s="112"/>
+      <c r="T35" s="112"/>
+      <c r="U35" s="112"/>
+      <c r="V35" s="112"/>
+      <c r="W35" s="112"/>
+      <c r="X35" s="112"/>
+      <c r="Y35" s="112"/>
+      <c r="Z35" s="112"/>
+      <c r="AA35" s="112"/>
+      <c r="AB35" s="112"/>
+      <c r="AC35" s="112"/>
+      <c r="AD35" s="112"/>
+      <c r="AE35" s="112"/>
+      <c r="AF35" s="112"/>
+      <c r="AG35" s="112"/>
+      <c r="AH35" s="112"/>
+      <c r="AI35" s="112"/>
+      <c r="AJ35" s="112"/>
+      <c r="AK35" s="114"/>
+      <c r="AL35" s="114"/>
+      <c r="AM35" s="114"/>
+      <c r="AN35" s="115"/>
+      <c r="AO35" s="111"/>
+      <c r="AP35" s="112"/>
+      <c r="AQ35" s="112"/>
+      <c r="AR35" s="112"/>
+      <c r="AS35" s="112"/>
+      <c r="AT35" s="112"/>
+      <c r="AU35" s="112"/>
+      <c r="AV35" s="112"/>
+      <c r="AW35" s="112"/>
+      <c r="AX35" s="112"/>
+      <c r="AY35" s="112"/>
+      <c r="AZ35" s="112"/>
+      <c r="BA35" s="112"/>
+      <c r="BB35" s="112"/>
+      <c r="BC35" s="113"/>
     </row>
     <row r="36" spans="1:55" ht="15" customHeight="1" thickBot="1">
       <c r="A36" s="42"/>
-      <c r="B36" s="105"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="109"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="103"/>
-      <c r="L36" s="103"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="103"/>
-      <c r="P36" s="103"/>
-      <c r="Q36" s="103"/>
-      <c r="R36" s="103"/>
-      <c r="S36" s="103"/>
-      <c r="T36" s="103"/>
-      <c r="U36" s="103"/>
-      <c r="V36" s="103"/>
-      <c r="W36" s="103"/>
-      <c r="X36" s="103"/>
-      <c r="Y36" s="103"/>
-      <c r="Z36" s="103"/>
-      <c r="AA36" s="103"/>
-      <c r="AB36" s="103"/>
-      <c r="AC36" s="103"/>
-      <c r="AD36" s="103"/>
-      <c r="AE36" s="103"/>
-      <c r="AF36" s="103"/>
-      <c r="AG36" s="103"/>
-      <c r="AH36" s="103"/>
-      <c r="AI36" s="103"/>
-      <c r="AJ36" s="103"/>
-      <c r="AK36" s="106"/>
-      <c r="AL36" s="106"/>
-      <c r="AM36" s="106"/>
-      <c r="AN36" s="107"/>
-      <c r="AO36" s="102"/>
-      <c r="AP36" s="103"/>
-      <c r="AQ36" s="103"/>
-      <c r="AR36" s="103"/>
-      <c r="AS36" s="103"/>
-      <c r="AT36" s="103"/>
-      <c r="AU36" s="103"/>
-      <c r="AV36" s="103"/>
-      <c r="AW36" s="103"/>
-      <c r="AX36" s="103"/>
-      <c r="AY36" s="103"/>
-      <c r="AZ36" s="103"/>
-      <c r="BA36" s="103"/>
-      <c r="BB36" s="103"/>
-      <c r="BC36" s="104"/>
+      <c r="B36" s="122"/>
+      <c r="C36" s="125"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="120"/>
+      <c r="N36" s="120"/>
+      <c r="O36" s="120"/>
+      <c r="P36" s="120"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="120"/>
+      <c r="S36" s="120"/>
+      <c r="T36" s="120"/>
+      <c r="U36" s="120"/>
+      <c r="V36" s="120"/>
+      <c r="W36" s="120"/>
+      <c r="X36" s="120"/>
+      <c r="Y36" s="120"/>
+      <c r="Z36" s="120"/>
+      <c r="AA36" s="120"/>
+      <c r="AB36" s="120"/>
+      <c r="AC36" s="120"/>
+      <c r="AD36" s="120"/>
+      <c r="AE36" s="120"/>
+      <c r="AF36" s="120"/>
+      <c r="AG36" s="120"/>
+      <c r="AH36" s="120"/>
+      <c r="AI36" s="120"/>
+      <c r="AJ36" s="120"/>
+      <c r="AK36" s="123"/>
+      <c r="AL36" s="123"/>
+      <c r="AM36" s="123"/>
+      <c r="AN36" s="124"/>
+      <c r="AO36" s="119"/>
+      <c r="AP36" s="120"/>
+      <c r="AQ36" s="120"/>
+      <c r="AR36" s="120"/>
+      <c r="AS36" s="120"/>
+      <c r="AT36" s="120"/>
+      <c r="AU36" s="120"/>
+      <c r="AV36" s="120"/>
+      <c r="AW36" s="120"/>
+      <c r="AX36" s="120"/>
+      <c r="AY36" s="120"/>
+      <c r="AZ36" s="120"/>
+      <c r="BA36" s="120"/>
+      <c r="BB36" s="120"/>
+      <c r="BC36" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="103">
+    <mergeCell ref="AO24:BC24"/>
+    <mergeCell ref="I24:AN24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I28:AN28"/>
+    <mergeCell ref="AO27:BC27"/>
+    <mergeCell ref="AO28:BC28"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I29:AN29"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:AN25"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="AO23:BC23"/>
+    <mergeCell ref="I23:AN23"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="I11:AN11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="AO19:BC19"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:AN21"/>
+    <mergeCell ref="AO21:BC21"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:AN20"/>
+    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I5:AN5"/>
+    <mergeCell ref="I7:AN7"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:AN6"/>
+    <mergeCell ref="I22:AN22"/>
+    <mergeCell ref="I13:AN13"/>
+    <mergeCell ref="AO11:BC11"/>
+    <mergeCell ref="I8:AN8"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="I17:AN17"/>
+    <mergeCell ref="AO17:BC17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="I18:AN18"/>
+    <mergeCell ref="AO18:BC18"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:AN15"/>
+    <mergeCell ref="AO15:BC15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:AN16"/>
+    <mergeCell ref="AO16:BC16"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="I19:AN19"/>
+    <mergeCell ref="AO36:BC36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AO35:BC35"/>
+    <mergeCell ref="I35:AN35"/>
+    <mergeCell ref="I36:AN36"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="I33:AN33"/>
+    <mergeCell ref="AO5:BC5"/>
+    <mergeCell ref="AO34:BC34"/>
+    <mergeCell ref="I34:AN34"/>
+    <mergeCell ref="AO33:BC33"/>
+    <mergeCell ref="I27:AN27"/>
+    <mergeCell ref="AO7:BC7"/>
+    <mergeCell ref="AO32:BC32"/>
+    <mergeCell ref="AO26:BC26"/>
+    <mergeCell ref="AO22:BC22"/>
+    <mergeCell ref="AO30:BC30"/>
+    <mergeCell ref="AO31:BC31"/>
+    <mergeCell ref="I26:AN26"/>
+    <mergeCell ref="I30:AN30"/>
+    <mergeCell ref="I31:AN31"/>
+    <mergeCell ref="AO25:BC25"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I9:AN9"/>
     <mergeCell ref="AY1:BC1"/>
     <mergeCell ref="AY2:BC2"/>
     <mergeCell ref="I1:AX2"/>
@@ -17189,85 +17377,6 @@
     <mergeCell ref="I32:AN32"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="AO36:BC36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="AO35:BC35"/>
-    <mergeCell ref="I35:AN35"/>
-    <mergeCell ref="I36:AN36"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="I33:AN33"/>
-    <mergeCell ref="AO5:BC5"/>
-    <mergeCell ref="AO34:BC34"/>
-    <mergeCell ref="I34:AN34"/>
-    <mergeCell ref="AO33:BC33"/>
-    <mergeCell ref="I27:AN27"/>
-    <mergeCell ref="AO7:BC7"/>
-    <mergeCell ref="AO32:BC32"/>
-    <mergeCell ref="AO26:BC26"/>
-    <mergeCell ref="AO22:BC22"/>
-    <mergeCell ref="AO30:BC30"/>
-    <mergeCell ref="AO31:BC31"/>
-    <mergeCell ref="I26:AN26"/>
-    <mergeCell ref="I30:AN30"/>
-    <mergeCell ref="I31:AN31"/>
-    <mergeCell ref="AO25:BC25"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I9:AN9"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I5:AN5"/>
-    <mergeCell ref="I7:AN7"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:AN6"/>
-    <mergeCell ref="I22:AN22"/>
-    <mergeCell ref="I13:AN13"/>
-    <mergeCell ref="AO11:BC11"/>
-    <mergeCell ref="I8:AN8"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="I17:AN17"/>
-    <mergeCell ref="AO17:BC17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="I18:AN18"/>
-    <mergeCell ref="AO18:BC18"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:AN15"/>
-    <mergeCell ref="AO15:BC15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:AN16"/>
-    <mergeCell ref="AO16:BC16"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I19:AN19"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="AO23:BC23"/>
-    <mergeCell ref="I23:AN23"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="AO13:BC13"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="I12:AN12"/>
-    <mergeCell ref="I11:AN11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="AO19:BC19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:AN21"/>
-    <mergeCell ref="AO21:BC21"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:AN20"/>
-    <mergeCell ref="AO20:BC20"/>
-    <mergeCell ref="AO24:BC24"/>
-    <mergeCell ref="I24:AN24"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I28:AN28"/>
-    <mergeCell ref="AO27:BC27"/>
-    <mergeCell ref="AO28:BC28"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I29:AN29"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:AN25"/>
   </mergeCells>
   <phoneticPr fontId="36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -17282,7 +17391,7 @@
   <sheetPr codeName="Sheet4">
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1458"/>
+  <dimension ref="A1:K1469"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="9" customWidth="1"/>
@@ -48981,7 +49090,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="1457" spans="2:11" ht="12" customHeight="1">
+    <row r="1457" spans="1:11" ht="12" customHeight="1">
       <c r="B1457" s="6" t="s">
         <v>102</v>
       </c>
@@ -49003,7 +49112,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="1458" spans="2:11" ht="12" customHeight="1">
+    <row r="1458" spans="1:11" ht="12" customHeight="1">
       <c r="B1458" s="6" t="s">
         <v>102</v>
       </c>
@@ -49025,16 +49134,216 @@
         <v>2062</v>
       </c>
     </row>
+    <row r="1461" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1461" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1461" s="140" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C1461" s="141"/>
+      <c r="D1461" s="53" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E1461" s="55"/>
+      <c r="F1461" s="52">
+        <v>3</v>
+      </c>
+      <c r="G1461" s="140" t="s">
+        <v>2359</v>
+      </c>
+      <c r="H1461" s="141"/>
+      <c r="I1461" s="140"/>
+      <c r="J1461" s="141"/>
+      <c r="K1461" s="142" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:11" s="143" customFormat="1" ht="57" customHeight="1">
+      <c r="A1462" s="51"/>
+      <c r="B1462" s="144" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C1462" s="145"/>
+      <c r="D1462" s="145"/>
+      <c r="E1462" s="145"/>
+      <c r="F1462" s="145"/>
+      <c r="G1462" s="145"/>
+      <c r="H1462" s="145"/>
+      <c r="I1462" s="145"/>
+      <c r="J1462" s="146"/>
+      <c r="K1462" s="142"/>
+    </row>
+    <row r="1463" spans="1:11" s="143" customFormat="1" ht="42.75">
+      <c r="A1463" s="51"/>
+      <c r="B1463" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1463" s="52" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D1463" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1463" s="52"/>
+      <c r="F1463" s="52"/>
+      <c r="G1463" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1463" s="54"/>
+      <c r="I1463" s="54"/>
+      <c r="J1463" s="55"/>
+      <c r="K1463" s="142" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1464" s="51"/>
+      <c r="B1464" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1464" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="D1464" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1464" s="52"/>
+      <c r="F1464" s="52"/>
+      <c r="G1464" s="53" t="s">
+        <v>2363</v>
+      </c>
+      <c r="H1464" s="54"/>
+      <c r="I1464" s="54"/>
+      <c r="J1464" s="55"/>
+      <c r="K1464" s="142" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1465" s="51"/>
+      <c r="B1465" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1465" s="52" t="s">
+        <v>2364</v>
+      </c>
+      <c r="D1465" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1465" s="52"/>
+      <c r="F1465" s="52"/>
+      <c r="G1465" s="53" t="s">
+        <v>2365</v>
+      </c>
+      <c r="H1465" s="54"/>
+      <c r="I1465" s="54"/>
+      <c r="J1465" s="55"/>
+      <c r="K1465" s="142" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1466" s="51"/>
+      <c r="B1466" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1466" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1466" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1466" s="52"/>
+      <c r="F1466" s="52"/>
+      <c r="G1466" s="53" t="s">
+        <v>2375</v>
+      </c>
+      <c r="H1466" s="54"/>
+      <c r="I1466" s="54"/>
+      <c r="J1466" s="55"/>
+      <c r="K1466" s="142" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1467" s="51"/>
+      <c r="B1467" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1467" s="52" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D1467" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1467" s="52">
+        <v>10</v>
+      </c>
+      <c r="F1467" s="52">
+        <v>10</v>
+      </c>
+      <c r="G1467" s="53" t="s">
+        <v>2368</v>
+      </c>
+      <c r="H1467" s="54"/>
+      <c r="I1467" s="54"/>
+      <c r="J1467" s="55"/>
+      <c r="K1467" s="142" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1468" s="51"/>
+      <c r="B1468" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1468" s="52" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D1468" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1468" s="52">
+        <v>20</v>
+      </c>
+      <c r="F1468" s="52"/>
+      <c r="G1468" s="53" t="s">
+        <v>2371</v>
+      </c>
+      <c r="H1468" s="54"/>
+      <c r="I1468" s="54"/>
+      <c r="J1468" s="55"/>
+      <c r="K1468" s="142" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:11" s="143" customFormat="1" ht="14.25">
+      <c r="A1469" s="51"/>
+      <c r="B1469" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1469" s="52" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D1469" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1469" s="52"/>
+      <c r="F1469" s="52"/>
+      <c r="G1469" s="53" t="s">
+        <v>2363</v>
+      </c>
+      <c r="H1469" s="54"/>
+      <c r="I1469" s="54"/>
+      <c r="J1469" s="55"/>
+      <c r="K1469" s="142" t="s">
+        <v>1925</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B101:J101"/>
-    <mergeCell ref="B125:J125"/>
-    <mergeCell ref="B202:J202"/>
-    <mergeCell ref="B620:J620"/>
-    <mergeCell ref="B1039:J1039"/>
-    <mergeCell ref="B170:J170"/>
-    <mergeCell ref="B161:J161"/>
-    <mergeCell ref="B149:J149"/>
+  <mergeCells count="21">
+    <mergeCell ref="B1462:J1462"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B15:J15"/>
@@ -49047,6 +49356,14 @@
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B36:J36"/>
     <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B101:J101"/>
+    <mergeCell ref="B125:J125"/>
+    <mergeCell ref="B202:J202"/>
+    <mergeCell ref="B620:J620"/>
+    <mergeCell ref="B1039:J1039"/>
+    <mergeCell ref="B170:J170"/>
+    <mergeCell ref="B161:J161"/>
+    <mergeCell ref="B149:J149"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB31AB43-C438-4883-B9CA-DA44082A9EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118A0C4E-518D-4E30-BB48-8F4F6EF105B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="22" r:id="rId1"/>
@@ -647,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10183" uniqueCount="2377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10239" uniqueCount="2399">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -11082,6 +11082,87 @@
   </si>
   <si>
     <t>Sale Department cd.</t>
+  </si>
+  <si>
+    <t>MAM_BP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>chk_msg:"MAUAL0117"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ispnl_mod_id:"MA"</t>
+  </si>
+  <si>
+    <t>ispnl_scr_id:"MAUAP1020"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SloBp</t>
+  </si>
+  <si>
+    <t>取引先名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bp_alt_nm1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引先別名１</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BP alias name 1</t>
+  </si>
+  <si>
+    <t>bp_alt_nm2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引先別名２</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BP alias name 2</t>
+  </si>
+  <si>
+    <t>bp_alt_nm3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引先別名３</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BP alias name 3</t>
+  </si>
+  <si>
+    <t>bp_alt_nm4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引先別名４</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BP alias name 4</t>
+  </si>
+  <si>
+    <t>Sale department cd.</t>
+  </si>
+  <si>
+    <t>引数の検索区分（取引先入力補助検索区分）に対応する取引先情報を、取引先マスタから取得する&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>受注登録用の取引先</t>
   </si>
 </sst>
 </file>
@@ -13047,7 +13128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -13210,6 +13291,30 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="3" xfId="230" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -13217,15 +13322,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="3" xfId="230" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="229" applyFont="1" applyAlignment="1">
@@ -13281,6 +13377,102 @@
     </xf>
     <xf numFmtId="168" fontId="53" fillId="0" borderId="24" xfId="229" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="29" borderId="42" xfId="228" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13352,15 +13544,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13369,112 +13552,19 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14906,130 +14996,130 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:47">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="71" t="s">
         <v>390</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="69"/>
-      <c r="AJ3" s="70" t="s">
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73"/>
+      <c r="AH3" s="73"/>
+      <c r="AI3" s="74"/>
+      <c r="AJ3" s="75" t="s">
         <v>391</v>
       </c>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="71" t="s">
+      <c r="AK3" s="75"/>
+      <c r="AL3" s="75"/>
+      <c r="AM3" s="75"/>
+      <c r="AN3" s="75"/>
+      <c r="AO3" s="75"/>
+      <c r="AP3" s="76" t="s">
         <v>392</v>
       </c>
-      <c r="AQ3" s="72"/>
-      <c r="AR3" s="72"/>
-      <c r="AS3" s="72"/>
-      <c r="AT3" s="72"/>
-      <c r="AU3" s="73"/>
+      <c r="AQ3" s="77"/>
+      <c r="AR3" s="77"/>
+      <c r="AS3" s="77"/>
+      <c r="AT3" s="77"/>
+      <c r="AU3" s="78"/>
     </row>
     <row r="4" spans="2:47">
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="69"/>
-      <c r="AJ4" s="70"/>
-      <c r="AK4" s="70"/>
-      <c r="AL4" s="70"/>
-      <c r="AM4" s="70"/>
-      <c r="AN4" s="70"/>
-      <c r="AO4" s="70"/>
-      <c r="AP4" s="71"/>
-      <c r="AQ4" s="72"/>
-      <c r="AR4" s="72"/>
-      <c r="AS4" s="72"/>
-      <c r="AT4" s="72"/>
-      <c r="AU4" s="73"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="AD4" s="73"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
+      <c r="AI4" s="74"/>
+      <c r="AJ4" s="75"/>
+      <c r="AK4" s="75"/>
+      <c r="AL4" s="75"/>
+      <c r="AM4" s="75"/>
+      <c r="AN4" s="75"/>
+      <c r="AO4" s="75"/>
+      <c r="AP4" s="76"/>
+      <c r="AQ4" s="77"/>
+      <c r="AR4" s="77"/>
+      <c r="AS4" s="77"/>
+      <c r="AT4" s="77"/>
+      <c r="AU4" s="78"/>
     </row>
     <row r="5" spans="2:47">
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="AD5" s="74"/>
-      <c r="AE5" s="75"/>
-      <c r="AF5" s="75"/>
-      <c r="AG5" s="75"/>
-      <c r="AH5" s="75"/>
-      <c r="AI5" s="76"/>
-      <c r="AJ5" s="77" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="AD5" s="79"/>
+      <c r="AE5" s="80"/>
+      <c r="AF5" s="80"/>
+      <c r="AG5" s="80"/>
+      <c r="AH5" s="80"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="82" t="s">
         <v>1841</v>
       </c>
-      <c r="AK5" s="77"/>
-      <c r="AL5" s="77"/>
-      <c r="AM5" s="77"/>
-      <c r="AN5" s="77"/>
-      <c r="AO5" s="77"/>
-      <c r="AP5" s="78" t="s">
+      <c r="AK5" s="82"/>
+      <c r="AL5" s="82"/>
+      <c r="AM5" s="82"/>
+      <c r="AN5" s="82"/>
+      <c r="AO5" s="82"/>
+      <c r="AP5" s="83" t="s">
         <v>2337</v>
       </c>
-      <c r="AQ5" s="79"/>
-      <c r="AR5" s="79"/>
-      <c r="AS5" s="79"/>
-      <c r="AT5" s="79"/>
-      <c r="AU5" s="80"/>
+      <c r="AQ5" s="84"/>
+      <c r="AR5" s="84"/>
+      <c r="AS5" s="84"/>
+      <c r="AT5" s="84"/>
+      <c r="AU5" s="85"/>
     </row>
     <row r="6" spans="2:47">
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="75"/>
-      <c r="AF6" s="75"/>
-      <c r="AG6" s="75"/>
-      <c r="AH6" s="75"/>
-      <c r="AI6" s="76"/>
-      <c r="AJ6" s="77"/>
-      <c r="AK6" s="77"/>
-      <c r="AL6" s="77"/>
-      <c r="AM6" s="77"/>
-      <c r="AN6" s="77"/>
-      <c r="AO6" s="77"/>
-      <c r="AP6" s="81"/>
-      <c r="AQ6" s="79"/>
-      <c r="AR6" s="79"/>
-      <c r="AS6" s="79"/>
-      <c r="AT6" s="79"/>
-      <c r="AU6" s="80"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="AD6" s="80"/>
+      <c r="AE6" s="80"/>
+      <c r="AF6" s="80"/>
+      <c r="AG6" s="80"/>
+      <c r="AH6" s="80"/>
+      <c r="AI6" s="81"/>
+      <c r="AJ6" s="82"/>
+      <c r="AK6" s="82"/>
+      <c r="AL6" s="82"/>
+      <c r="AM6" s="82"/>
+      <c r="AN6" s="82"/>
+      <c r="AO6" s="82"/>
+      <c r="AP6" s="86"/>
+      <c r="AQ6" s="84"/>
+      <c r="AR6" s="84"/>
+      <c r="AS6" s="84"/>
+      <c r="AT6" s="84"/>
+      <c r="AU6" s="85"/>
     </row>
     <row r="7" spans="2:47" ht="24">
       <c r="B7" s="33" t="s">
@@ -15051,122 +15141,122 @@
       </c>
     </row>
     <row r="15" spans="2:47">
-      <c r="M15" s="64" t="s">
+      <c r="M15" s="69" t="s">
         <v>393</v>
       </c>
-      <c r="N15" s="65"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="65"/>
-      <c r="X15" s="65"/>
-      <c r="Y15" s="65"/>
-      <c r="Z15" s="65"/>
-      <c r="AA15" s="65"/>
-      <c r="AB15" s="65"/>
-      <c r="AC15" s="65"/>
-      <c r="AD15" s="65"/>
-      <c r="AE15" s="65"/>
-      <c r="AF15" s="65"/>
-      <c r="AG15" s="65"/>
-      <c r="AH15" s="65"/>
-      <c r="AI15" s="65"/>
-      <c r="AJ15" s="65"/>
-      <c r="AK15" s="65"/>
-      <c r="AL15" s="65"/>
-      <c r="AM15" s="65"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+      <c r="Z15" s="70"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="70"/>
+      <c r="AC15" s="70"/>
+      <c r="AD15" s="70"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+      <c r="AI15" s="70"/>
+      <c r="AJ15" s="70"/>
+      <c r="AK15" s="70"/>
+      <c r="AL15" s="70"/>
+      <c r="AM15" s="70"/>
     </row>
     <row r="16" spans="2:47">
-      <c r="M16" s="65"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="65"/>
-      <c r="P16" s="65"/>
-      <c r="Q16" s="65"/>
-      <c r="R16" s="65"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="65"/>
-      <c r="X16" s="65"/>
-      <c r="Y16" s="65"/>
-      <c r="Z16" s="65"/>
-      <c r="AA16" s="65"/>
-      <c r="AB16" s="65"/>
-      <c r="AC16" s="65"/>
-      <c r="AD16" s="65"/>
-      <c r="AE16" s="65"/>
-      <c r="AF16" s="65"/>
-      <c r="AG16" s="65"/>
-      <c r="AH16" s="65"/>
-      <c r="AI16" s="65"/>
-      <c r="AJ16" s="65"/>
-      <c r="AK16" s="65"/>
-      <c r="AL16" s="65"/>
-      <c r="AM16" s="65"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="70"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="70"/>
+      <c r="Z16" s="70"/>
+      <c r="AA16" s="70"/>
+      <c r="AB16" s="70"/>
+      <c r="AC16" s="70"/>
+      <c r="AD16" s="70"/>
+      <c r="AE16" s="70"/>
+      <c r="AF16" s="70"/>
+      <c r="AG16" s="70"/>
+      <c r="AH16" s="70"/>
+      <c r="AI16" s="70"/>
+      <c r="AJ16" s="70"/>
+      <c r="AK16" s="70"/>
+      <c r="AL16" s="70"/>
+      <c r="AM16" s="70"/>
     </row>
     <row r="17" spans="13:39">
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-      <c r="Z17" s="65"/>
-      <c r="AA17" s="65"/>
-      <c r="AB17" s="65"/>
-      <c r="AC17" s="65"/>
-      <c r="AD17" s="65"/>
-      <c r="AE17" s="65"/>
-      <c r="AF17" s="65"/>
-      <c r="AG17" s="65"/>
-      <c r="AH17" s="65"/>
-      <c r="AI17" s="65"/>
-      <c r="AJ17" s="65"/>
-      <c r="AK17" s="65"/>
-      <c r="AL17" s="65"/>
-      <c r="AM17" s="65"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="70"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="70"/>
+      <c r="AI17" s="70"/>
+      <c r="AJ17" s="70"/>
+      <c r="AK17" s="70"/>
+      <c r="AL17" s="70"/>
+      <c r="AM17" s="70"/>
     </row>
     <row r="18" spans="13:39">
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65"/>
-      <c r="P18" s="65"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="65"/>
-      <c r="AB18" s="65"/>
-      <c r="AC18" s="65"/>
-      <c r="AD18" s="65"/>
-      <c r="AE18" s="65"/>
-      <c r="AF18" s="65"/>
-      <c r="AG18" s="65"/>
-      <c r="AH18" s="65"/>
-      <c r="AI18" s="65"/>
-      <c r="AJ18" s="65"/>
-      <c r="AK18" s="65"/>
-      <c r="AL18" s="65"/>
-      <c r="AM18" s="65"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
+      <c r="V18" s="70"/>
+      <c r="W18" s="70"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="70"/>
+      <c r="AI18" s="70"/>
+      <c r="AJ18" s="70"/>
+      <c r="AK18" s="70"/>
+      <c r="AL18" s="70"/>
+      <c r="AM18" s="70"/>
     </row>
     <row r="26" spans="13:39" ht="15.75" customHeight="1"/>
     <row r="27" spans="13:39" ht="15.75" customHeight="1"/>
@@ -15206,126 +15296,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="34" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="86" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="87"/>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="87"/>
-      <c r="AE1" s="87"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="87"/>
-      <c r="AH1" s="87"/>
-      <c r="AI1" s="87"/>
-      <c r="AJ1" s="87"/>
-      <c r="AK1" s="87"/>
-      <c r="AL1" s="87"/>
-      <c r="AM1" s="87"/>
-      <c r="AN1" s="87"/>
-      <c r="AO1" s="87"/>
-      <c r="AP1" s="87"/>
-      <c r="AQ1" s="87"/>
-      <c r="AR1" s="87"/>
-      <c r="AS1" s="87"/>
-      <c r="AT1" s="87"/>
-      <c r="AU1" s="87"/>
-      <c r="AV1" s="87"/>
-      <c r="AW1" s="87"/>
-      <c r="AX1" s="88"/>
-      <c r="AY1" s="82" t="s">
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="124"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="124"/>
+      <c r="AD1" s="124"/>
+      <c r="AE1" s="124"/>
+      <c r="AF1" s="124"/>
+      <c r="AG1" s="124"/>
+      <c r="AH1" s="124"/>
+      <c r="AI1" s="124"/>
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="124"/>
+      <c r="AL1" s="124"/>
+      <c r="AM1" s="124"/>
+      <c r="AN1" s="124"/>
+      <c r="AO1" s="124"/>
+      <c r="AP1" s="124"/>
+      <c r="AQ1" s="124"/>
+      <c r="AR1" s="124"/>
+      <c r="AS1" s="124"/>
+      <c r="AT1" s="124"/>
+      <c r="AU1" s="124"/>
+      <c r="AV1" s="124"/>
+      <c r="AW1" s="124"/>
+      <c r="AX1" s="125"/>
+      <c r="AY1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="82"/>
-      <c r="BA1" s="82"/>
-      <c r="BB1" s="82"/>
-      <c r="BC1" s="83"/>
+      <c r="AZ1" s="119"/>
+      <c r="BA1" s="119"/>
+      <c r="BB1" s="119"/>
+      <c r="BC1" s="120"/>
     </row>
     <row r="2" spans="1:55" s="34" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="90"/>
-      <c r="T2" s="90"/>
-      <c r="U2" s="90"/>
-      <c r="V2" s="90"/>
-      <c r="W2" s="90"/>
-      <c r="X2" s="90"/>
-      <c r="Y2" s="90"/>
-      <c r="Z2" s="90"/>
-      <c r="AA2" s="90"/>
-      <c r="AB2" s="90"/>
-      <c r="AC2" s="90"/>
-      <c r="AD2" s="90"/>
-      <c r="AE2" s="90"/>
-      <c r="AF2" s="90"/>
-      <c r="AG2" s="90"/>
-      <c r="AH2" s="90"/>
-      <c r="AI2" s="90"/>
-      <c r="AJ2" s="90"/>
-      <c r="AK2" s="90"/>
-      <c r="AL2" s="90"/>
-      <c r="AM2" s="90"/>
-      <c r="AN2" s="90"/>
-      <c r="AO2" s="90"/>
-      <c r="AP2" s="90"/>
-      <c r="AQ2" s="90"/>
-      <c r="AR2" s="90"/>
-      <c r="AS2" s="90"/>
-      <c r="AT2" s="90"/>
-      <c r="AU2" s="90"/>
-      <c r="AV2" s="90"/>
-      <c r="AW2" s="90"/>
-      <c r="AX2" s="91"/>
-      <c r="AY2" s="84" t="s">
+      <c r="A2" s="137"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="127"/>
+      <c r="AW2" s="127"/>
+      <c r="AX2" s="128"/>
+      <c r="AY2" s="121" t="s">
         <v>1841</v>
       </c>
-      <c r="AZ2" s="84"/>
-      <c r="BA2" s="84"/>
-      <c r="BB2" s="84"/>
-      <c r="BC2" s="85"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
+      <c r="BB2" s="121"/>
+      <c r="BC2" s="122"/>
     </row>
     <row r="3" spans="1:55" s="34" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A3" s="35"/>
@@ -15377,1934 +15467,1951 @@
       <c r="A4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="92" t="s">
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102"/>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="102"/>
-      <c r="T4" s="102"/>
-      <c r="U4" s="102"/>
-      <c r="V4" s="102"/>
-      <c r="W4" s="102"/>
-      <c r="X4" s="102"/>
-      <c r="Y4" s="102"/>
-      <c r="Z4" s="102"/>
-      <c r="AA4" s="102"/>
-      <c r="AB4" s="102"/>
-      <c r="AC4" s="102"/>
-      <c r="AD4" s="102"/>
-      <c r="AE4" s="102"/>
-      <c r="AF4" s="102"/>
-      <c r="AG4" s="102"/>
-      <c r="AH4" s="102"/>
-      <c r="AI4" s="102"/>
-      <c r="AJ4" s="102"/>
-      <c r="AK4" s="103"/>
-      <c r="AL4" s="103"/>
-      <c r="AM4" s="103"/>
-      <c r="AN4" s="104"/>
-      <c r="AO4" s="95" t="s">
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="139"/>
+      <c r="O4" s="139"/>
+      <c r="P4" s="139"/>
+      <c r="Q4" s="139"/>
+      <c r="R4" s="139"/>
+      <c r="S4" s="139"/>
+      <c r="T4" s="139"/>
+      <c r="U4" s="139"/>
+      <c r="V4" s="139"/>
+      <c r="W4" s="139"/>
+      <c r="X4" s="139"/>
+      <c r="Y4" s="139"/>
+      <c r="Z4" s="139"/>
+      <c r="AA4" s="139"/>
+      <c r="AB4" s="139"/>
+      <c r="AC4" s="139"/>
+      <c r="AD4" s="139"/>
+      <c r="AE4" s="139"/>
+      <c r="AF4" s="139"/>
+      <c r="AG4" s="139"/>
+      <c r="AH4" s="139"/>
+      <c r="AI4" s="139"/>
+      <c r="AJ4" s="139"/>
+      <c r="AK4" s="140"/>
+      <c r="AL4" s="140"/>
+      <c r="AM4" s="140"/>
+      <c r="AN4" s="141"/>
+      <c r="AO4" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="AP4" s="96"/>
-      <c r="AQ4" s="96"/>
-      <c r="AR4" s="96"/>
-      <c r="AS4" s="96"/>
-      <c r="AT4" s="96"/>
-      <c r="AU4" s="96"/>
-      <c r="AV4" s="96"/>
-      <c r="AW4" s="96"/>
-      <c r="AX4" s="96"/>
-      <c r="AY4" s="96"/>
-      <c r="AZ4" s="96"/>
-      <c r="BA4" s="96"/>
-      <c r="BB4" s="96"/>
-      <c r="BC4" s="97"/>
+      <c r="AP4" s="133"/>
+      <c r="AQ4" s="133"/>
+      <c r="AR4" s="133"/>
+      <c r="AS4" s="133"/>
+      <c r="AT4" s="133"/>
+      <c r="AU4" s="133"/>
+      <c r="AV4" s="133"/>
+      <c r="AW4" s="133"/>
+      <c r="AX4" s="133"/>
+      <c r="AY4" s="133"/>
+      <c r="AZ4" s="133"/>
+      <c r="BA4" s="133"/>
+      <c r="BB4" s="133"/>
+      <c r="BC4" s="134"/>
     </row>
     <row r="5" spans="1:55" ht="15" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>1803</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="130" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="128"/>
-      <c r="X5" s="128"/>
-      <c r="Y5" s="128"/>
-      <c r="Z5" s="128"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="128"/>
-      <c r="AC5" s="128"/>
-      <c r="AD5" s="128"/>
-      <c r="AE5" s="128"/>
-      <c r="AF5" s="128"/>
-      <c r="AG5" s="128"/>
-      <c r="AH5" s="128"/>
-      <c r="AI5" s="128"/>
-      <c r="AJ5" s="128"/>
-      <c r="AK5" s="133"/>
-      <c r="AL5" s="133"/>
-      <c r="AM5" s="133"/>
-      <c r="AN5" s="134"/>
-      <c r="AO5" s="127"/>
-      <c r="AP5" s="128"/>
-      <c r="AQ5" s="128"/>
-      <c r="AR5" s="128"/>
-      <c r="AS5" s="128"/>
-      <c r="AT5" s="128"/>
-      <c r="AU5" s="128"/>
-      <c r="AV5" s="128"/>
-      <c r="AW5" s="128"/>
-      <c r="AX5" s="128"/>
-      <c r="AY5" s="128"/>
-      <c r="AZ5" s="128"/>
-      <c r="BA5" s="128"/>
-      <c r="BB5" s="128"/>
-      <c r="BC5" s="129"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="99"/>
+      <c r="AD5" s="99"/>
+      <c r="AE5" s="99"/>
+      <c r="AF5" s="99"/>
+      <c r="AG5" s="99"/>
+      <c r="AH5" s="99"/>
+      <c r="AI5" s="99"/>
+      <c r="AJ5" s="99"/>
+      <c r="AK5" s="100"/>
+      <c r="AL5" s="100"/>
+      <c r="AM5" s="100"/>
+      <c r="AN5" s="101"/>
+      <c r="AO5" s="115"/>
+      <c r="AP5" s="99"/>
+      <c r="AQ5" s="99"/>
+      <c r="AR5" s="99"/>
+      <c r="AS5" s="99"/>
+      <c r="AT5" s="99"/>
+      <c r="AU5" s="99"/>
+      <c r="AV5" s="99"/>
+      <c r="AW5" s="99"/>
+      <c r="AX5" s="99"/>
+      <c r="AY5" s="99"/>
+      <c r="AZ5" s="99"/>
+      <c r="BA5" s="99"/>
+      <c r="BB5" s="99"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
         <v>2334</v>
       </c>
-      <c r="B6" s="105"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="137" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="104" t="s">
         <v>2335</v>
       </c>
-      <c r="J6" s="138"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="138"/>
-      <c r="N6" s="138"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="138"/>
-      <c r="T6" s="138"/>
-      <c r="U6" s="138"/>
-      <c r="V6" s="138"/>
-      <c r="W6" s="138"/>
-      <c r="X6" s="138"/>
-      <c r="Y6" s="138"/>
-      <c r="Z6" s="138"/>
-      <c r="AA6" s="138"/>
-      <c r="AB6" s="138"/>
-      <c r="AC6" s="138"/>
-      <c r="AD6" s="138"/>
-      <c r="AE6" s="138"/>
-      <c r="AF6" s="138"/>
-      <c r="AG6" s="138"/>
-      <c r="AH6" s="138"/>
-      <c r="AI6" s="138"/>
-      <c r="AJ6" s="138"/>
-      <c r="AK6" s="138"/>
-      <c r="AL6" s="138"/>
-      <c r="AM6" s="138"/>
-      <c r="AN6" s="139"/>
-      <c r="AO6" s="108" t="s">
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="105"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="105"/>
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="105"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="105"/>
+      <c r="Y6" s="105"/>
+      <c r="Z6" s="105"/>
+      <c r="AA6" s="105"/>
+      <c r="AB6" s="105"/>
+      <c r="AC6" s="105"/>
+      <c r="AD6" s="105"/>
+      <c r="AE6" s="105"/>
+      <c r="AF6" s="105"/>
+      <c r="AG6" s="105"/>
+      <c r="AH6" s="105"/>
+      <c r="AI6" s="105"/>
+      <c r="AJ6" s="105"/>
+      <c r="AK6" s="105"/>
+      <c r="AL6" s="105"/>
+      <c r="AM6" s="105"/>
+      <c r="AN6" s="106"/>
+      <c r="AO6" s="142" t="s">
         <v>2336</v>
       </c>
-      <c r="AP6" s="109"/>
-      <c r="AQ6" s="109"/>
-      <c r="AR6" s="109"/>
-      <c r="AS6" s="109"/>
-      <c r="AT6" s="109"/>
-      <c r="AU6" s="109"/>
-      <c r="AV6" s="109"/>
-      <c r="AW6" s="109"/>
-      <c r="AX6" s="109"/>
-      <c r="AY6" s="109"/>
-      <c r="AZ6" s="109"/>
-      <c r="BA6" s="109"/>
-      <c r="BB6" s="109"/>
-      <c r="BC6" s="110"/>
+      <c r="AP6" s="143"/>
+      <c r="AQ6" s="143"/>
+      <c r="AR6" s="143"/>
+      <c r="AS6" s="143"/>
+      <c r="AT6" s="143"/>
+      <c r="AU6" s="143"/>
+      <c r="AV6" s="143"/>
+      <c r="AW6" s="143"/>
+      <c r="AX6" s="143"/>
+      <c r="AY6" s="143"/>
+      <c r="AZ6" s="143"/>
+      <c r="BA6" s="143"/>
+      <c r="BB6" s="143"/>
+      <c r="BC6" s="144"/>
     </row>
     <row r="7" spans="1:55" ht="15" customHeight="1">
       <c r="A7" s="40"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="112"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="112"/>
-      <c r="R7" s="112"/>
-      <c r="S7" s="112"/>
-      <c r="T7" s="112"/>
-      <c r="U7" s="112"/>
-      <c r="V7" s="112"/>
-      <c r="W7" s="112"/>
-      <c r="X7" s="112"/>
-      <c r="Y7" s="112"/>
-      <c r="Z7" s="112"/>
-      <c r="AA7" s="112"/>
-      <c r="AB7" s="112"/>
-      <c r="AC7" s="112"/>
-      <c r="AD7" s="112"/>
-      <c r="AE7" s="112"/>
-      <c r="AF7" s="112"/>
-      <c r="AG7" s="112"/>
-      <c r="AH7" s="112"/>
-      <c r="AI7" s="112"/>
-      <c r="AJ7" s="112"/>
-      <c r="AK7" s="114"/>
-      <c r="AL7" s="114"/>
-      <c r="AM7" s="114"/>
-      <c r="AN7" s="115"/>
-      <c r="AO7" s="111"/>
-      <c r="AP7" s="112"/>
-      <c r="AQ7" s="112"/>
-      <c r="AR7" s="112"/>
-      <c r="AS7" s="112"/>
-      <c r="AT7" s="112"/>
-      <c r="AU7" s="112"/>
-      <c r="AV7" s="112"/>
-      <c r="AW7" s="112"/>
-      <c r="AX7" s="112"/>
-      <c r="AY7" s="112"/>
-      <c r="AZ7" s="112"/>
-      <c r="BA7" s="112"/>
-      <c r="BB7" s="112"/>
-      <c r="BC7" s="113"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="88"/>
+      <c r="O7" s="88"/>
+      <c r="P7" s="88"/>
+      <c r="Q7" s="88"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="88"/>
+      <c r="T7" s="88"/>
+      <c r="U7" s="88"/>
+      <c r="V7" s="88"/>
+      <c r="W7" s="88"/>
+      <c r="X7" s="88"/>
+      <c r="Y7" s="88"/>
+      <c r="Z7" s="88"/>
+      <c r="AA7" s="88"/>
+      <c r="AB7" s="88"/>
+      <c r="AC7" s="88"/>
+      <c r="AD7" s="88"/>
+      <c r="AE7" s="88"/>
+      <c r="AF7" s="88"/>
+      <c r="AG7" s="88"/>
+      <c r="AH7" s="88"/>
+      <c r="AI7" s="88"/>
+      <c r="AJ7" s="88"/>
+      <c r="AK7" s="91"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="91"/>
+      <c r="AN7" s="92"/>
+      <c r="AO7" s="87"/>
+      <c r="AP7" s="88"/>
+      <c r="AQ7" s="88"/>
+      <c r="AR7" s="88"/>
+      <c r="AS7" s="88"/>
+      <c r="AT7" s="88"/>
+      <c r="AU7" s="88"/>
+      <c r="AV7" s="88"/>
+      <c r="AW7" s="88"/>
+      <c r="AX7" s="88"/>
+      <c r="AY7" s="88"/>
+      <c r="AZ7" s="88"/>
+      <c r="BA7" s="88"/>
+      <c r="BB7" s="88"/>
+      <c r="BC7" s="89"/>
     </row>
     <row r="8" spans="1:55" ht="15" customHeight="1">
       <c r="A8" s="40"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="112"/>
-      <c r="S8" s="112"/>
-      <c r="T8" s="112"/>
-      <c r="U8" s="112"/>
-      <c r="V8" s="112"/>
-      <c r="W8" s="112"/>
-      <c r="X8" s="112"/>
-      <c r="Y8" s="112"/>
-      <c r="Z8" s="112"/>
-      <c r="AA8" s="112"/>
-      <c r="AB8" s="112"/>
-      <c r="AC8" s="112"/>
-      <c r="AD8" s="112"/>
-      <c r="AE8" s="112"/>
-      <c r="AF8" s="112"/>
-      <c r="AG8" s="112"/>
-      <c r="AH8" s="112"/>
-      <c r="AI8" s="112"/>
-      <c r="AJ8" s="112"/>
-      <c r="AK8" s="114"/>
-      <c r="AL8" s="114"/>
-      <c r="AM8" s="114"/>
-      <c r="AN8" s="115"/>
-      <c r="AO8" s="111"/>
-      <c r="AP8" s="112"/>
-      <c r="AQ8" s="112"/>
-      <c r="AR8" s="112"/>
-      <c r="AS8" s="112"/>
-      <c r="AT8" s="112"/>
-      <c r="AU8" s="112"/>
-      <c r="AV8" s="112"/>
-      <c r="AW8" s="112"/>
-      <c r="AX8" s="112"/>
-      <c r="AY8" s="112"/>
-      <c r="AZ8" s="112"/>
-      <c r="BA8" s="112"/>
-      <c r="BB8" s="112"/>
-      <c r="BC8" s="113"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="88"/>
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AC8" s="88"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="88"/>
+      <c r="AG8" s="88"/>
+      <c r="AH8" s="88"/>
+      <c r="AI8" s="88"/>
+      <c r="AJ8" s="88"/>
+      <c r="AK8" s="91"/>
+      <c r="AL8" s="91"/>
+      <c r="AM8" s="91"/>
+      <c r="AN8" s="92"/>
+      <c r="AO8" s="87"/>
+      <c r="AP8" s="88"/>
+      <c r="AQ8" s="88"/>
+      <c r="AR8" s="88"/>
+      <c r="AS8" s="88"/>
+      <c r="AT8" s="88"/>
+      <c r="AU8" s="88"/>
+      <c r="AV8" s="88"/>
+      <c r="AW8" s="88"/>
+      <c r="AX8" s="88"/>
+      <c r="AY8" s="88"/>
+      <c r="AZ8" s="88"/>
+      <c r="BA8" s="88"/>
+      <c r="BB8" s="88"/>
+      <c r="BC8" s="89"/>
     </row>
     <row r="9" spans="1:55" ht="15" customHeight="1">
       <c r="A9" s="40"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
-      <c r="Q9" s="112"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="112"/>
-      <c r="T9" s="112"/>
-      <c r="U9" s="112"/>
-      <c r="V9" s="112"/>
-      <c r="W9" s="112"/>
-      <c r="X9" s="112"/>
-      <c r="Y9" s="112"/>
-      <c r="Z9" s="112"/>
-      <c r="AA9" s="112"/>
-      <c r="AB9" s="112"/>
-      <c r="AC9" s="112"/>
-      <c r="AD9" s="112"/>
-      <c r="AE9" s="112"/>
-      <c r="AF9" s="112"/>
-      <c r="AG9" s="112"/>
-      <c r="AH9" s="112"/>
-      <c r="AI9" s="112"/>
-      <c r="AJ9" s="112"/>
-      <c r="AK9" s="114"/>
-      <c r="AL9" s="114"/>
-      <c r="AM9" s="114"/>
-      <c r="AN9" s="115"/>
-      <c r="AO9" s="111"/>
-      <c r="AP9" s="112"/>
-      <c r="AQ9" s="112"/>
-      <c r="AR9" s="112"/>
-      <c r="AS9" s="112"/>
-      <c r="AT9" s="112"/>
-      <c r="AU9" s="112"/>
-      <c r="AV9" s="112"/>
-      <c r="AW9" s="112"/>
-      <c r="AX9" s="112"/>
-      <c r="AY9" s="112"/>
-      <c r="AZ9" s="112"/>
-      <c r="BA9" s="112"/>
-      <c r="BB9" s="112"/>
-      <c r="BC9" s="113"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="88"/>
+      <c r="M9" s="88"/>
+      <c r="N9" s="88"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="88"/>
+      <c r="AG9" s="88"/>
+      <c r="AH9" s="88"/>
+      <c r="AI9" s="88"/>
+      <c r="AJ9" s="88"/>
+      <c r="AK9" s="91"/>
+      <c r="AL9" s="91"/>
+      <c r="AM9" s="91"/>
+      <c r="AN9" s="92"/>
+      <c r="AO9" s="87"/>
+      <c r="AP9" s="88"/>
+      <c r="AQ9" s="88"/>
+      <c r="AR9" s="88"/>
+      <c r="AS9" s="88"/>
+      <c r="AT9" s="88"/>
+      <c r="AU9" s="88"/>
+      <c r="AV9" s="88"/>
+      <c r="AW9" s="88"/>
+      <c r="AX9" s="88"/>
+      <c r="AY9" s="88"/>
+      <c r="AZ9" s="88"/>
+      <c r="BA9" s="88"/>
+      <c r="BB9" s="88"/>
+      <c r="BC9" s="89"/>
     </row>
     <row r="10" spans="1:55" ht="15" customHeight="1">
       <c r="A10" s="40"/>
-      <c r="B10" s="105"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="112"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="112"/>
-      <c r="S10" s="112"/>
-      <c r="T10" s="112"/>
-      <c r="U10" s="112"/>
-      <c r="V10" s="112"/>
-      <c r="W10" s="112"/>
-      <c r="X10" s="112"/>
-      <c r="Y10" s="112"/>
-      <c r="Z10" s="112"/>
-      <c r="AA10" s="112"/>
-      <c r="AB10" s="112"/>
-      <c r="AC10" s="112"/>
-      <c r="AD10" s="112"/>
-      <c r="AE10" s="112"/>
-      <c r="AF10" s="112"/>
-      <c r="AG10" s="112"/>
-      <c r="AH10" s="112"/>
-      <c r="AI10" s="112"/>
-      <c r="AJ10" s="112"/>
-      <c r="AK10" s="114"/>
-      <c r="AL10" s="114"/>
-      <c r="AM10" s="114"/>
-      <c r="AN10" s="115"/>
-      <c r="AO10" s="111"/>
-      <c r="AP10" s="112"/>
-      <c r="AQ10" s="112"/>
-      <c r="AR10" s="112"/>
-      <c r="AS10" s="112"/>
-      <c r="AT10" s="112"/>
-      <c r="AU10" s="112"/>
-      <c r="AV10" s="112"/>
-      <c r="AW10" s="112"/>
-      <c r="AX10" s="112"/>
-      <c r="AY10" s="112"/>
-      <c r="AZ10" s="112"/>
-      <c r="BA10" s="112"/>
-      <c r="BB10" s="112"/>
-      <c r="BC10" s="113"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="88"/>
+      <c r="N10" s="88"/>
+      <c r="O10" s="88"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="88"/>
+      <c r="AF10" s="88"/>
+      <c r="AG10" s="88"/>
+      <c r="AH10" s="88"/>
+      <c r="AI10" s="88"/>
+      <c r="AJ10" s="88"/>
+      <c r="AK10" s="91"/>
+      <c r="AL10" s="91"/>
+      <c r="AM10" s="91"/>
+      <c r="AN10" s="92"/>
+      <c r="AO10" s="87"/>
+      <c r="AP10" s="88"/>
+      <c r="AQ10" s="88"/>
+      <c r="AR10" s="88"/>
+      <c r="AS10" s="88"/>
+      <c r="AT10" s="88"/>
+      <c r="AU10" s="88"/>
+      <c r="AV10" s="88"/>
+      <c r="AW10" s="88"/>
+      <c r="AX10" s="88"/>
+      <c r="AY10" s="88"/>
+      <c r="AZ10" s="88"/>
+      <c r="BA10" s="88"/>
+      <c r="BB10" s="88"/>
+      <c r="BC10" s="89"/>
     </row>
     <row r="11" spans="1:55" ht="15" customHeight="1">
       <c r="A11" s="40"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="112"/>
-      <c r="K11" s="112"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
-      <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
-      <c r="Q11" s="112"/>
-      <c r="R11" s="112"/>
-      <c r="S11" s="112"/>
-      <c r="T11" s="112"/>
-      <c r="U11" s="112"/>
-      <c r="V11" s="112"/>
-      <c r="W11" s="112"/>
-      <c r="X11" s="112"/>
-      <c r="Y11" s="112"/>
-      <c r="Z11" s="112"/>
-      <c r="AA11" s="112"/>
-      <c r="AB11" s="112"/>
-      <c r="AC11" s="112"/>
-      <c r="AD11" s="112"/>
-      <c r="AE11" s="112"/>
-      <c r="AF11" s="112"/>
-      <c r="AG11" s="112"/>
-      <c r="AH11" s="112"/>
-      <c r="AI11" s="112"/>
-      <c r="AJ11" s="112"/>
-      <c r="AK11" s="114"/>
-      <c r="AL11" s="114"/>
-      <c r="AM11" s="114"/>
-      <c r="AN11" s="115"/>
-      <c r="AO11" s="111"/>
-      <c r="AP11" s="112"/>
-      <c r="AQ11" s="112"/>
-      <c r="AR11" s="112"/>
-      <c r="AS11" s="112"/>
-      <c r="AT11" s="112"/>
-      <c r="AU11" s="112"/>
-      <c r="AV11" s="112"/>
-      <c r="AW11" s="112"/>
-      <c r="AX11" s="112"/>
-      <c r="AY11" s="112"/>
-      <c r="AZ11" s="112"/>
-      <c r="BA11" s="112"/>
-      <c r="BB11" s="112"/>
-      <c r="BC11" s="113"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="88"/>
+      <c r="AF11" s="88"/>
+      <c r="AG11" s="88"/>
+      <c r="AH11" s="88"/>
+      <c r="AI11" s="88"/>
+      <c r="AJ11" s="88"/>
+      <c r="AK11" s="91"/>
+      <c r="AL11" s="91"/>
+      <c r="AM11" s="91"/>
+      <c r="AN11" s="92"/>
+      <c r="AO11" s="87"/>
+      <c r="AP11" s="88"/>
+      <c r="AQ11" s="88"/>
+      <c r="AR11" s="88"/>
+      <c r="AS11" s="88"/>
+      <c r="AT11" s="88"/>
+      <c r="AU11" s="88"/>
+      <c r="AV11" s="88"/>
+      <c r="AW11" s="88"/>
+      <c r="AX11" s="88"/>
+      <c r="AY11" s="88"/>
+      <c r="AZ11" s="88"/>
+      <c r="BA11" s="88"/>
+      <c r="BB11" s="88"/>
+      <c r="BC11" s="89"/>
     </row>
     <row r="12" spans="1:55" ht="15" customHeight="1">
       <c r="A12" s="40"/>
-      <c r="B12" s="105"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="112"/>
-      <c r="L12" s="112"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="112"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="112"/>
-      <c r="R12" s="112"/>
-      <c r="S12" s="112"/>
-      <c r="T12" s="112"/>
-      <c r="U12" s="112"/>
-      <c r="V12" s="112"/>
-      <c r="W12" s="112"/>
-      <c r="X12" s="112"/>
-      <c r="Y12" s="112"/>
-      <c r="Z12" s="112"/>
-      <c r="AA12" s="112"/>
-      <c r="AB12" s="112"/>
-      <c r="AC12" s="112"/>
-      <c r="AD12" s="112"/>
-      <c r="AE12" s="112"/>
-      <c r="AF12" s="112"/>
-      <c r="AG12" s="112"/>
-      <c r="AH12" s="112"/>
-      <c r="AI12" s="112"/>
-      <c r="AJ12" s="112"/>
-      <c r="AK12" s="114"/>
-      <c r="AL12" s="114"/>
-      <c r="AM12" s="114"/>
-      <c r="AN12" s="115"/>
-      <c r="AO12" s="111"/>
-      <c r="AP12" s="112"/>
-      <c r="AQ12" s="112"/>
-      <c r="AR12" s="112"/>
-      <c r="AS12" s="112"/>
-      <c r="AT12" s="112"/>
-      <c r="AU12" s="112"/>
-      <c r="AV12" s="112"/>
-      <c r="AW12" s="112"/>
-      <c r="AX12" s="112"/>
-      <c r="AY12" s="112"/>
-      <c r="AZ12" s="112"/>
-      <c r="BA12" s="112"/>
-      <c r="BB12" s="112"/>
-      <c r="BC12" s="113"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="88"/>
+      <c r="L12" s="88"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="88"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="88"/>
+      <c r="AF12" s="88"/>
+      <c r="AG12" s="88"/>
+      <c r="AH12" s="88"/>
+      <c r="AI12" s="88"/>
+      <c r="AJ12" s="88"/>
+      <c r="AK12" s="91"/>
+      <c r="AL12" s="91"/>
+      <c r="AM12" s="91"/>
+      <c r="AN12" s="92"/>
+      <c r="AO12" s="87"/>
+      <c r="AP12" s="88"/>
+      <c r="AQ12" s="88"/>
+      <c r="AR12" s="88"/>
+      <c r="AS12" s="88"/>
+      <c r="AT12" s="88"/>
+      <c r="AU12" s="88"/>
+      <c r="AV12" s="88"/>
+      <c r="AW12" s="88"/>
+      <c r="AX12" s="88"/>
+      <c r="AY12" s="88"/>
+      <c r="AZ12" s="88"/>
+      <c r="BA12" s="88"/>
+      <c r="BB12" s="88"/>
+      <c r="BC12" s="89"/>
     </row>
     <row r="13" spans="1:55" ht="15" customHeight="1">
       <c r="A13" s="40"/>
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="112"/>
-      <c r="Q13" s="112"/>
-      <c r="R13" s="112"/>
-      <c r="S13" s="112"/>
-      <c r="T13" s="112"/>
-      <c r="U13" s="112"/>
-      <c r="V13" s="112"/>
-      <c r="W13" s="112"/>
-      <c r="X13" s="112"/>
-      <c r="Y13" s="112"/>
-      <c r="Z13" s="112"/>
-      <c r="AA13" s="112"/>
-      <c r="AB13" s="112"/>
-      <c r="AC13" s="112"/>
-      <c r="AD13" s="112"/>
-      <c r="AE13" s="112"/>
-      <c r="AF13" s="112"/>
-      <c r="AG13" s="112"/>
-      <c r="AH13" s="112"/>
-      <c r="AI13" s="112"/>
-      <c r="AJ13" s="112"/>
-      <c r="AK13" s="114"/>
-      <c r="AL13" s="114"/>
-      <c r="AM13" s="114"/>
-      <c r="AN13" s="115"/>
-      <c r="AO13" s="111"/>
-      <c r="AP13" s="112"/>
-      <c r="AQ13" s="112"/>
-      <c r="AR13" s="112"/>
-      <c r="AS13" s="112"/>
-      <c r="AT13" s="112"/>
-      <c r="AU13" s="112"/>
-      <c r="AV13" s="112"/>
-      <c r="AW13" s="112"/>
-      <c r="AX13" s="112"/>
-      <c r="AY13" s="112"/>
-      <c r="AZ13" s="112"/>
-      <c r="BA13" s="112"/>
-      <c r="BB13" s="112"/>
-      <c r="BC13" s="113"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="88"/>
+      <c r="AF13" s="88"/>
+      <c r="AG13" s="88"/>
+      <c r="AH13" s="88"/>
+      <c r="AI13" s="88"/>
+      <c r="AJ13" s="88"/>
+      <c r="AK13" s="91"/>
+      <c r="AL13" s="91"/>
+      <c r="AM13" s="91"/>
+      <c r="AN13" s="92"/>
+      <c r="AO13" s="87"/>
+      <c r="AP13" s="88"/>
+      <c r="AQ13" s="88"/>
+      <c r="AR13" s="88"/>
+      <c r="AS13" s="88"/>
+      <c r="AT13" s="88"/>
+      <c r="AU13" s="88"/>
+      <c r="AV13" s="88"/>
+      <c r="AW13" s="88"/>
+      <c r="AX13" s="88"/>
+      <c r="AY13" s="88"/>
+      <c r="AZ13" s="88"/>
+      <c r="BA13" s="88"/>
+      <c r="BB13" s="88"/>
+      <c r="BC13" s="89"/>
     </row>
     <row r="14" spans="1:55" ht="15" customHeight="1">
       <c r="A14" s="40"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
-      <c r="S14" s="112"/>
-      <c r="T14" s="112"/>
-      <c r="U14" s="112"/>
-      <c r="V14" s="112"/>
-      <c r="W14" s="112"/>
-      <c r="X14" s="112"/>
-      <c r="Y14" s="112"/>
-      <c r="Z14" s="112"/>
-      <c r="AA14" s="112"/>
-      <c r="AB14" s="112"/>
-      <c r="AC14" s="112"/>
-      <c r="AD14" s="112"/>
-      <c r="AE14" s="112"/>
-      <c r="AF14" s="112"/>
-      <c r="AG14" s="112"/>
-      <c r="AH14" s="112"/>
-      <c r="AI14" s="112"/>
-      <c r="AJ14" s="112"/>
-      <c r="AK14" s="114"/>
-      <c r="AL14" s="114"/>
-      <c r="AM14" s="114"/>
-      <c r="AN14" s="115"/>
-      <c r="AO14" s="111"/>
-      <c r="AP14" s="112"/>
-      <c r="AQ14" s="112"/>
-      <c r="AR14" s="112"/>
-      <c r="AS14" s="112"/>
-      <c r="AT14" s="112"/>
-      <c r="AU14" s="112"/>
-      <c r="AV14" s="112"/>
-      <c r="AW14" s="112"/>
-      <c r="AX14" s="112"/>
-      <c r="AY14" s="112"/>
-      <c r="AZ14" s="112"/>
-      <c r="BA14" s="112"/>
-      <c r="BB14" s="112"/>
-      <c r="BC14" s="113"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="88"/>
+      <c r="M14" s="88"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="88"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="88"/>
+      <c r="AG14" s="88"/>
+      <c r="AH14" s="88"/>
+      <c r="AI14" s="88"/>
+      <c r="AJ14" s="88"/>
+      <c r="AK14" s="91"/>
+      <c r="AL14" s="91"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="92"/>
+      <c r="AO14" s="87"/>
+      <c r="AP14" s="88"/>
+      <c r="AQ14" s="88"/>
+      <c r="AR14" s="88"/>
+      <c r="AS14" s="88"/>
+      <c r="AT14" s="88"/>
+      <c r="AU14" s="88"/>
+      <c r="AV14" s="88"/>
+      <c r="AW14" s="88"/>
+      <c r="AX14" s="88"/>
+      <c r="AY14" s="88"/>
+      <c r="AZ14" s="88"/>
+      <c r="BA14" s="88"/>
+      <c r="BB14" s="88"/>
+      <c r="BC14" s="89"/>
     </row>
     <row r="15" spans="1:55" ht="15" customHeight="1">
       <c r="A15" s="40"/>
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="112"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
-      <c r="Q15" s="112"/>
-      <c r="R15" s="112"/>
-      <c r="S15" s="112"/>
-      <c r="T15" s="112"/>
-      <c r="U15" s="112"/>
-      <c r="V15" s="112"/>
-      <c r="W15" s="112"/>
-      <c r="X15" s="112"/>
-      <c r="Y15" s="112"/>
-      <c r="Z15" s="112"/>
-      <c r="AA15" s="112"/>
-      <c r="AB15" s="112"/>
-      <c r="AC15" s="112"/>
-      <c r="AD15" s="112"/>
-      <c r="AE15" s="112"/>
-      <c r="AF15" s="112"/>
-      <c r="AG15" s="112"/>
-      <c r="AH15" s="112"/>
-      <c r="AI15" s="112"/>
-      <c r="AJ15" s="112"/>
-      <c r="AK15" s="114"/>
-      <c r="AL15" s="114"/>
-      <c r="AM15" s="114"/>
-      <c r="AN15" s="115"/>
-      <c r="AO15" s="111"/>
-      <c r="AP15" s="112"/>
-      <c r="AQ15" s="112"/>
-      <c r="AR15" s="112"/>
-      <c r="AS15" s="112"/>
-      <c r="AT15" s="112"/>
-      <c r="AU15" s="112"/>
-      <c r="AV15" s="112"/>
-      <c r="AW15" s="112"/>
-      <c r="AX15" s="112"/>
-      <c r="AY15" s="112"/>
-      <c r="AZ15" s="112"/>
-      <c r="BA15" s="112"/>
-      <c r="BB15" s="112"/>
-      <c r="BC15" s="113"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="88"/>
+      <c r="AF15" s="88"/>
+      <c r="AG15" s="88"/>
+      <c r="AH15" s="88"/>
+      <c r="AI15" s="88"/>
+      <c r="AJ15" s="88"/>
+      <c r="AK15" s="91"/>
+      <c r="AL15" s="91"/>
+      <c r="AM15" s="91"/>
+      <c r="AN15" s="92"/>
+      <c r="AO15" s="87"/>
+      <c r="AP15" s="88"/>
+      <c r="AQ15" s="88"/>
+      <c r="AR15" s="88"/>
+      <c r="AS15" s="88"/>
+      <c r="AT15" s="88"/>
+      <c r="AU15" s="88"/>
+      <c r="AV15" s="88"/>
+      <c r="AW15" s="88"/>
+      <c r="AX15" s="88"/>
+      <c r="AY15" s="88"/>
+      <c r="AZ15" s="88"/>
+      <c r="BA15" s="88"/>
+      <c r="BB15" s="88"/>
+      <c r="BC15" s="89"/>
     </row>
     <row r="16" spans="1:55" ht="15" customHeight="1">
       <c r="A16" s="40"/>
-      <c r="B16" s="105"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="112"/>
-      <c r="S16" s="112"/>
-      <c r="T16" s="112"/>
-      <c r="U16" s="112"/>
-      <c r="V16" s="112"/>
-      <c r="W16" s="112"/>
-      <c r="X16" s="112"/>
-      <c r="Y16" s="112"/>
-      <c r="Z16" s="112"/>
-      <c r="AA16" s="112"/>
-      <c r="AB16" s="112"/>
-      <c r="AC16" s="112"/>
-      <c r="AD16" s="112"/>
-      <c r="AE16" s="112"/>
-      <c r="AF16" s="112"/>
-      <c r="AG16" s="112"/>
-      <c r="AH16" s="112"/>
-      <c r="AI16" s="112"/>
-      <c r="AJ16" s="112"/>
-      <c r="AK16" s="114"/>
-      <c r="AL16" s="114"/>
-      <c r="AM16" s="114"/>
-      <c r="AN16" s="115"/>
-      <c r="AO16" s="111"/>
-      <c r="AP16" s="112"/>
-      <c r="AQ16" s="112"/>
-      <c r="AR16" s="112"/>
-      <c r="AS16" s="112"/>
-      <c r="AT16" s="112"/>
-      <c r="AU16" s="112"/>
-      <c r="AV16" s="112"/>
-      <c r="AW16" s="112"/>
-      <c r="AX16" s="112"/>
-      <c r="AY16" s="112"/>
-      <c r="AZ16" s="112"/>
-      <c r="BA16" s="112"/>
-      <c r="BB16" s="112"/>
-      <c r="BC16" s="113"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="88"/>
+      <c r="AC16" s="88"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="88"/>
+      <c r="AF16" s="88"/>
+      <c r="AG16" s="88"/>
+      <c r="AH16" s="88"/>
+      <c r="AI16" s="88"/>
+      <c r="AJ16" s="88"/>
+      <c r="AK16" s="91"/>
+      <c r="AL16" s="91"/>
+      <c r="AM16" s="91"/>
+      <c r="AN16" s="92"/>
+      <c r="AO16" s="87"/>
+      <c r="AP16" s="88"/>
+      <c r="AQ16" s="88"/>
+      <c r="AR16" s="88"/>
+      <c r="AS16" s="88"/>
+      <c r="AT16" s="88"/>
+      <c r="AU16" s="88"/>
+      <c r="AV16" s="88"/>
+      <c r="AW16" s="88"/>
+      <c r="AX16" s="88"/>
+      <c r="AY16" s="88"/>
+      <c r="AZ16" s="88"/>
+      <c r="BA16" s="88"/>
+      <c r="BB16" s="88"/>
+      <c r="BC16" s="89"/>
     </row>
     <row r="17" spans="1:55" ht="15" customHeight="1">
       <c r="A17" s="40"/>
-      <c r="B17" s="105"/>
-      <c r="C17" s="106"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
-      <c r="O17" s="112"/>
-      <c r="P17" s="112"/>
-      <c r="Q17" s="112"/>
-      <c r="R17" s="112"/>
-      <c r="S17" s="112"/>
-      <c r="T17" s="112"/>
-      <c r="U17" s="112"/>
-      <c r="V17" s="112"/>
-      <c r="W17" s="112"/>
-      <c r="X17" s="112"/>
-      <c r="Y17" s="112"/>
-      <c r="Z17" s="112"/>
-      <c r="AA17" s="112"/>
-      <c r="AB17" s="112"/>
-      <c r="AC17" s="112"/>
-      <c r="AD17" s="112"/>
-      <c r="AE17" s="112"/>
-      <c r="AF17" s="112"/>
-      <c r="AG17" s="112"/>
-      <c r="AH17" s="112"/>
-      <c r="AI17" s="112"/>
-      <c r="AJ17" s="112"/>
-      <c r="AK17" s="114"/>
-      <c r="AL17" s="114"/>
-      <c r="AM17" s="114"/>
-      <c r="AN17" s="115"/>
-      <c r="AO17" s="111"/>
-      <c r="AP17" s="112"/>
-      <c r="AQ17" s="112"/>
-      <c r="AR17" s="112"/>
-      <c r="AS17" s="112"/>
-      <c r="AT17" s="112"/>
-      <c r="AU17" s="112"/>
-      <c r="AV17" s="112"/>
-      <c r="AW17" s="112"/>
-      <c r="AX17" s="112"/>
-      <c r="AY17" s="112"/>
-      <c r="AZ17" s="112"/>
-      <c r="BA17" s="112"/>
-      <c r="BB17" s="112"/>
-      <c r="BC17" s="113"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="88"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="88"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="88"/>
+      <c r="P17" s="88"/>
+      <c r="Q17" s="88"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="88"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="88"/>
+      <c r="AC17" s="88"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="88"/>
+      <c r="AF17" s="88"/>
+      <c r="AG17" s="88"/>
+      <c r="AH17" s="88"/>
+      <c r="AI17" s="88"/>
+      <c r="AJ17" s="88"/>
+      <c r="AK17" s="91"/>
+      <c r="AL17" s="91"/>
+      <c r="AM17" s="91"/>
+      <c r="AN17" s="92"/>
+      <c r="AO17" s="87"/>
+      <c r="AP17" s="88"/>
+      <c r="AQ17" s="88"/>
+      <c r="AR17" s="88"/>
+      <c r="AS17" s="88"/>
+      <c r="AT17" s="88"/>
+      <c r="AU17" s="88"/>
+      <c r="AV17" s="88"/>
+      <c r="AW17" s="88"/>
+      <c r="AX17" s="88"/>
+      <c r="AY17" s="88"/>
+      <c r="AZ17" s="88"/>
+      <c r="BA17" s="88"/>
+      <c r="BB17" s="88"/>
+      <c r="BC17" s="89"/>
     </row>
     <row r="18" spans="1:55" ht="15" customHeight="1">
       <c r="A18" s="40"/>
-      <c r="B18" s="105"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="112"/>
-      <c r="W18" s="112"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="112"/>
-      <c r="AE18" s="112"/>
-      <c r="AF18" s="112"/>
-      <c r="AG18" s="112"/>
-      <c r="AH18" s="112"/>
-      <c r="AI18" s="112"/>
-      <c r="AJ18" s="112"/>
-      <c r="AK18" s="114"/>
-      <c r="AL18" s="114"/>
-      <c r="AM18" s="114"/>
-      <c r="AN18" s="115"/>
-      <c r="AO18" s="111"/>
-      <c r="AP18" s="112"/>
-      <c r="AQ18" s="112"/>
-      <c r="AR18" s="112"/>
-      <c r="AS18" s="112"/>
-      <c r="AT18" s="112"/>
-      <c r="AU18" s="112"/>
-      <c r="AV18" s="112"/>
-      <c r="AW18" s="112"/>
-      <c r="AX18" s="112"/>
-      <c r="AY18" s="112"/>
-      <c r="AZ18" s="112"/>
-      <c r="BA18" s="112"/>
-      <c r="BB18" s="112"/>
-      <c r="BC18" s="113"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="88"/>
+      <c r="K18" s="88"/>
+      <c r="L18" s="88"/>
+      <c r="M18" s="88"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="88"/>
+      <c r="Q18" s="88"/>
+      <c r="R18" s="88"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="88"/>
+      <c r="AC18" s="88"/>
+      <c r="AD18" s="88"/>
+      <c r="AE18" s="88"/>
+      <c r="AF18" s="88"/>
+      <c r="AG18" s="88"/>
+      <c r="AH18" s="88"/>
+      <c r="AI18" s="88"/>
+      <c r="AJ18" s="88"/>
+      <c r="AK18" s="91"/>
+      <c r="AL18" s="91"/>
+      <c r="AM18" s="91"/>
+      <c r="AN18" s="92"/>
+      <c r="AO18" s="87"/>
+      <c r="AP18" s="88"/>
+      <c r="AQ18" s="88"/>
+      <c r="AR18" s="88"/>
+      <c r="AS18" s="88"/>
+      <c r="AT18" s="88"/>
+      <c r="AU18" s="88"/>
+      <c r="AV18" s="88"/>
+      <c r="AW18" s="88"/>
+      <c r="AX18" s="88"/>
+      <c r="AY18" s="88"/>
+      <c r="AZ18" s="88"/>
+      <c r="BA18" s="88"/>
+      <c r="BB18" s="88"/>
+      <c r="BC18" s="89"/>
     </row>
     <row r="19" spans="1:55" ht="15" customHeight="1">
       <c r="A19" s="40"/>
-      <c r="B19" s="105"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="112"/>
-      <c r="AK19" s="114"/>
-      <c r="AL19" s="114"/>
-      <c r="AM19" s="114"/>
-      <c r="AN19" s="115"/>
-      <c r="AO19" s="111"/>
-      <c r="AP19" s="112"/>
-      <c r="AQ19" s="112"/>
-      <c r="AR19" s="112"/>
-      <c r="AS19" s="112"/>
-      <c r="AT19" s="112"/>
-      <c r="AU19" s="112"/>
-      <c r="AV19" s="112"/>
-      <c r="AW19" s="112"/>
-      <c r="AX19" s="112"/>
-      <c r="AY19" s="112"/>
-      <c r="AZ19" s="112"/>
-      <c r="BA19" s="112"/>
-      <c r="BB19" s="112"/>
-      <c r="BC19" s="113"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="88"/>
+      <c r="Q19" s="88"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="88"/>
+      <c r="AF19" s="88"/>
+      <c r="AG19" s="88"/>
+      <c r="AH19" s="88"/>
+      <c r="AI19" s="88"/>
+      <c r="AJ19" s="88"/>
+      <c r="AK19" s="91"/>
+      <c r="AL19" s="91"/>
+      <c r="AM19" s="91"/>
+      <c r="AN19" s="92"/>
+      <c r="AO19" s="87"/>
+      <c r="AP19" s="88"/>
+      <c r="AQ19" s="88"/>
+      <c r="AR19" s="88"/>
+      <c r="AS19" s="88"/>
+      <c r="AT19" s="88"/>
+      <c r="AU19" s="88"/>
+      <c r="AV19" s="88"/>
+      <c r="AW19" s="88"/>
+      <c r="AX19" s="88"/>
+      <c r="AY19" s="88"/>
+      <c r="AZ19" s="88"/>
+      <c r="BA19" s="88"/>
+      <c r="BB19" s="88"/>
+      <c r="BC19" s="89"/>
     </row>
     <row r="20" spans="1:55" ht="15" customHeight="1">
       <c r="A20" s="40"/>
-      <c r="B20" s="105"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="112"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="112"/>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="112"/>
-      <c r="S20" s="112"/>
-      <c r="T20" s="112"/>
-      <c r="U20" s="112"/>
-      <c r="V20" s="112"/>
-      <c r="W20" s="112"/>
-      <c r="X20" s="112"/>
-      <c r="Y20" s="112"/>
-      <c r="Z20" s="112"/>
-      <c r="AA20" s="112"/>
-      <c r="AB20" s="112"/>
-      <c r="AC20" s="112"/>
-      <c r="AD20" s="112"/>
-      <c r="AE20" s="112"/>
-      <c r="AF20" s="112"/>
-      <c r="AG20" s="112"/>
-      <c r="AH20" s="112"/>
-      <c r="AI20" s="112"/>
-      <c r="AJ20" s="112"/>
-      <c r="AK20" s="114"/>
-      <c r="AL20" s="114"/>
-      <c r="AM20" s="114"/>
-      <c r="AN20" s="115"/>
-      <c r="AO20" s="111"/>
-      <c r="AP20" s="112"/>
-      <c r="AQ20" s="112"/>
-      <c r="AR20" s="112"/>
-      <c r="AS20" s="112"/>
-      <c r="AT20" s="112"/>
-      <c r="AU20" s="112"/>
-      <c r="AV20" s="112"/>
-      <c r="AW20" s="112"/>
-      <c r="AX20" s="112"/>
-      <c r="AY20" s="112"/>
-      <c r="AZ20" s="112"/>
-      <c r="BA20" s="112"/>
-      <c r="BB20" s="112"/>
-      <c r="BC20" s="113"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+      <c r="M20" s="88"/>
+      <c r="N20" s="88"/>
+      <c r="O20" s="88"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="88"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="88"/>
+      <c r="V20" s="88"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="88"/>
+      <c r="Z20" s="88"/>
+      <c r="AA20" s="88"/>
+      <c r="AB20" s="88"/>
+      <c r="AC20" s="88"/>
+      <c r="AD20" s="88"/>
+      <c r="AE20" s="88"/>
+      <c r="AF20" s="88"/>
+      <c r="AG20" s="88"/>
+      <c r="AH20" s="88"/>
+      <c r="AI20" s="88"/>
+      <c r="AJ20" s="88"/>
+      <c r="AK20" s="91"/>
+      <c r="AL20" s="91"/>
+      <c r="AM20" s="91"/>
+      <c r="AN20" s="92"/>
+      <c r="AO20" s="87"/>
+      <c r="AP20" s="88"/>
+      <c r="AQ20" s="88"/>
+      <c r="AR20" s="88"/>
+      <c r="AS20" s="88"/>
+      <c r="AT20" s="88"/>
+      <c r="AU20" s="88"/>
+      <c r="AV20" s="88"/>
+      <c r="AW20" s="88"/>
+      <c r="AX20" s="88"/>
+      <c r="AY20" s="88"/>
+      <c r="AZ20" s="88"/>
+      <c r="BA20" s="88"/>
+      <c r="BB20" s="88"/>
+      <c r="BC20" s="89"/>
     </row>
     <row r="21" spans="1:55" ht="15" customHeight="1">
       <c r="A21" s="40"/>
-      <c r="B21" s="105"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
-      <c r="N21" s="112"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="112"/>
-      <c r="W21" s="112"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="112"/>
-      <c r="AE21" s="112"/>
-      <c r="AF21" s="112"/>
-      <c r="AG21" s="112"/>
-      <c r="AH21" s="112"/>
-      <c r="AI21" s="112"/>
-      <c r="AJ21" s="112"/>
-      <c r="AK21" s="114"/>
-      <c r="AL21" s="114"/>
-      <c r="AM21" s="114"/>
-      <c r="AN21" s="115"/>
-      <c r="AO21" s="111"/>
-      <c r="AP21" s="112"/>
-      <c r="AQ21" s="112"/>
-      <c r="AR21" s="112"/>
-      <c r="AS21" s="112"/>
-      <c r="AT21" s="112"/>
-      <c r="AU21" s="112"/>
-      <c r="AV21" s="112"/>
-      <c r="AW21" s="112"/>
-      <c r="AX21" s="112"/>
-      <c r="AY21" s="112"/>
-      <c r="AZ21" s="112"/>
-      <c r="BA21" s="112"/>
-      <c r="BB21" s="112"/>
-      <c r="BC21" s="113"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="88"/>
+      <c r="K21" s="88"/>
+      <c r="L21" s="88"/>
+      <c r="M21" s="88"/>
+      <c r="N21" s="88"/>
+      <c r="O21" s="88"/>
+      <c r="P21" s="88"/>
+      <c r="Q21" s="88"/>
+      <c r="R21" s="88"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="88"/>
+      <c r="AA21" s="88"/>
+      <c r="AB21" s="88"/>
+      <c r="AC21" s="88"/>
+      <c r="AD21" s="88"/>
+      <c r="AE21" s="88"/>
+      <c r="AF21" s="88"/>
+      <c r="AG21" s="88"/>
+      <c r="AH21" s="88"/>
+      <c r="AI21" s="88"/>
+      <c r="AJ21" s="88"/>
+      <c r="AK21" s="91"/>
+      <c r="AL21" s="91"/>
+      <c r="AM21" s="91"/>
+      <c r="AN21" s="92"/>
+      <c r="AO21" s="87"/>
+      <c r="AP21" s="88"/>
+      <c r="AQ21" s="88"/>
+      <c r="AR21" s="88"/>
+      <c r="AS21" s="88"/>
+      <c r="AT21" s="88"/>
+      <c r="AU21" s="88"/>
+      <c r="AV21" s="88"/>
+      <c r="AW21" s="88"/>
+      <c r="AX21" s="88"/>
+      <c r="AY21" s="88"/>
+      <c r="AZ21" s="88"/>
+      <c r="BA21" s="88"/>
+      <c r="BB21" s="88"/>
+      <c r="BC21" s="89"/>
     </row>
     <row r="22" spans="1:55" ht="15" customHeight="1">
       <c r="A22" s="40"/>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="106"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="112"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="112"/>
-      <c r="N22" s="112"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="112"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="112"/>
-      <c r="S22" s="112"/>
-      <c r="T22" s="112"/>
-      <c r="U22" s="112"/>
-      <c r="V22" s="112"/>
-      <c r="W22" s="112"/>
-      <c r="X22" s="112"/>
-      <c r="Y22" s="112"/>
-      <c r="Z22" s="112"/>
-      <c r="AA22" s="112"/>
-      <c r="AB22" s="112"/>
-      <c r="AC22" s="112"/>
-      <c r="AD22" s="112"/>
-      <c r="AE22" s="112"/>
-      <c r="AF22" s="112"/>
-      <c r="AG22" s="112"/>
-      <c r="AH22" s="112"/>
-      <c r="AI22" s="112"/>
-      <c r="AJ22" s="112"/>
-      <c r="AK22" s="114"/>
-      <c r="AL22" s="114"/>
-      <c r="AM22" s="114"/>
-      <c r="AN22" s="115"/>
-      <c r="AO22" s="111"/>
-      <c r="AP22" s="112"/>
-      <c r="AQ22" s="112"/>
-      <c r="AR22" s="112"/>
-      <c r="AS22" s="112"/>
-      <c r="AT22" s="112"/>
-      <c r="AU22" s="112"/>
-      <c r="AV22" s="112"/>
-      <c r="AW22" s="112"/>
-      <c r="AX22" s="112"/>
-      <c r="AY22" s="112"/>
-      <c r="AZ22" s="112"/>
-      <c r="BA22" s="112"/>
-      <c r="BB22" s="112"/>
-      <c r="BC22" s="113"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="88"/>
+      <c r="AG22" s="88"/>
+      <c r="AH22" s="88"/>
+      <c r="AI22" s="88"/>
+      <c r="AJ22" s="88"/>
+      <c r="AK22" s="91"/>
+      <c r="AL22" s="91"/>
+      <c r="AM22" s="91"/>
+      <c r="AN22" s="92"/>
+      <c r="AO22" s="87"/>
+      <c r="AP22" s="88"/>
+      <c r="AQ22" s="88"/>
+      <c r="AR22" s="88"/>
+      <c r="AS22" s="88"/>
+      <c r="AT22" s="88"/>
+      <c r="AU22" s="88"/>
+      <c r="AV22" s="88"/>
+      <c r="AW22" s="88"/>
+      <c r="AX22" s="88"/>
+      <c r="AY22" s="88"/>
+      <c r="AZ22" s="88"/>
+      <c r="BA22" s="88"/>
+      <c r="BB22" s="88"/>
+      <c r="BC22" s="89"/>
     </row>
     <row r="23" spans="1:55" ht="15" customHeight="1">
       <c r="A23" s="41"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="112"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="112"/>
-      <c r="T23" s="112"/>
-      <c r="U23" s="112"/>
-      <c r="V23" s="112"/>
-      <c r="W23" s="112"/>
-      <c r="X23" s="112"/>
-      <c r="Y23" s="112"/>
-      <c r="Z23" s="112"/>
-      <c r="AA23" s="112"/>
-      <c r="AB23" s="112"/>
-      <c r="AC23" s="112"/>
-      <c r="AD23" s="112"/>
-      <c r="AE23" s="112"/>
-      <c r="AF23" s="112"/>
-      <c r="AG23" s="112"/>
-      <c r="AH23" s="112"/>
-      <c r="AI23" s="112"/>
-      <c r="AJ23" s="112"/>
-      <c r="AK23" s="114"/>
-      <c r="AL23" s="114"/>
-      <c r="AM23" s="114"/>
-      <c r="AN23" s="115"/>
-      <c r="AO23" s="111"/>
-      <c r="AP23" s="112"/>
-      <c r="AQ23" s="112"/>
-      <c r="AR23" s="112"/>
-      <c r="AS23" s="112"/>
-      <c r="AT23" s="112"/>
-      <c r="AU23" s="112"/>
-      <c r="AV23" s="112"/>
-      <c r="AW23" s="112"/>
-      <c r="AX23" s="112"/>
-      <c r="AY23" s="112"/>
-      <c r="AZ23" s="112"/>
-      <c r="BA23" s="112"/>
-      <c r="BB23" s="112"/>
-      <c r="BC23" s="113"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="88"/>
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88"/>
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="88"/>
+      <c r="AF23" s="88"/>
+      <c r="AG23" s="88"/>
+      <c r="AH23" s="88"/>
+      <c r="AI23" s="88"/>
+      <c r="AJ23" s="88"/>
+      <c r="AK23" s="91"/>
+      <c r="AL23" s="91"/>
+      <c r="AM23" s="91"/>
+      <c r="AN23" s="92"/>
+      <c r="AO23" s="87"/>
+      <c r="AP23" s="88"/>
+      <c r="AQ23" s="88"/>
+      <c r="AR23" s="88"/>
+      <c r="AS23" s="88"/>
+      <c r="AT23" s="88"/>
+      <c r="AU23" s="88"/>
+      <c r="AV23" s="88"/>
+      <c r="AW23" s="88"/>
+      <c r="AX23" s="88"/>
+      <c r="AY23" s="88"/>
+      <c r="AZ23" s="88"/>
+      <c r="BA23" s="88"/>
+      <c r="BB23" s="88"/>
+      <c r="BC23" s="89"/>
     </row>
     <row r="24" spans="1:55" ht="15" customHeight="1">
       <c r="A24" s="41"/>
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="112"/>
-      <c r="N24" s="112"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="112"/>
-      <c r="Q24" s="112"/>
-      <c r="R24" s="112"/>
-      <c r="S24" s="112"/>
-      <c r="T24" s="112"/>
-      <c r="U24" s="112"/>
-      <c r="V24" s="112"/>
-      <c r="W24" s="112"/>
-      <c r="X24" s="112"/>
-      <c r="Y24" s="112"/>
-      <c r="Z24" s="112"/>
-      <c r="AA24" s="112"/>
-      <c r="AB24" s="112"/>
-      <c r="AC24" s="112"/>
-      <c r="AD24" s="112"/>
-      <c r="AE24" s="112"/>
-      <c r="AF24" s="112"/>
-      <c r="AG24" s="112"/>
-      <c r="AH24" s="112"/>
-      <c r="AI24" s="112"/>
-      <c r="AJ24" s="112"/>
-      <c r="AK24" s="114"/>
-      <c r="AL24" s="114"/>
-      <c r="AM24" s="114"/>
-      <c r="AN24" s="115"/>
-      <c r="AO24" s="111"/>
-      <c r="AP24" s="112"/>
-      <c r="AQ24" s="112"/>
-      <c r="AR24" s="112"/>
-      <c r="AS24" s="112"/>
-      <c r="AT24" s="112"/>
-      <c r="AU24" s="112"/>
-      <c r="AV24" s="112"/>
-      <c r="AW24" s="112"/>
-      <c r="AX24" s="112"/>
-      <c r="AY24" s="112"/>
-      <c r="AZ24" s="112"/>
-      <c r="BA24" s="112"/>
-      <c r="BB24" s="112"/>
-      <c r="BC24" s="113"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="88"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="88"/>
+      <c r="P24" s="88"/>
+      <c r="Q24" s="88"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="88"/>
+      <c r="U24" s="88"/>
+      <c r="V24" s="88"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="88"/>
+      <c r="AA24" s="88"/>
+      <c r="AB24" s="88"/>
+      <c r="AC24" s="88"/>
+      <c r="AD24" s="88"/>
+      <c r="AE24" s="88"/>
+      <c r="AF24" s="88"/>
+      <c r="AG24" s="88"/>
+      <c r="AH24" s="88"/>
+      <c r="AI24" s="88"/>
+      <c r="AJ24" s="88"/>
+      <c r="AK24" s="91"/>
+      <c r="AL24" s="91"/>
+      <c r="AM24" s="91"/>
+      <c r="AN24" s="92"/>
+      <c r="AO24" s="87"/>
+      <c r="AP24" s="88"/>
+      <c r="AQ24" s="88"/>
+      <c r="AR24" s="88"/>
+      <c r="AS24" s="88"/>
+      <c r="AT24" s="88"/>
+      <c r="AU24" s="88"/>
+      <c r="AV24" s="88"/>
+      <c r="AW24" s="88"/>
+      <c r="AX24" s="88"/>
+      <c r="AY24" s="88"/>
+      <c r="AZ24" s="88"/>
+      <c r="BA24" s="88"/>
+      <c r="BB24" s="88"/>
+      <c r="BC24" s="89"/>
     </row>
     <row r="25" spans="1:55" ht="15" customHeight="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="105"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="112"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="112"/>
-      <c r="Q25" s="112"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="112"/>
-      <c r="T25" s="112"/>
-      <c r="U25" s="112"/>
-      <c r="V25" s="112"/>
-      <c r="W25" s="112"/>
-      <c r="X25" s="112"/>
-      <c r="Y25" s="112"/>
-      <c r="Z25" s="112"/>
-      <c r="AA25" s="112"/>
-      <c r="AB25" s="112"/>
-      <c r="AC25" s="112"/>
-      <c r="AD25" s="112"/>
-      <c r="AE25" s="112"/>
-      <c r="AF25" s="112"/>
-      <c r="AG25" s="112"/>
-      <c r="AH25" s="112"/>
-      <c r="AI25" s="112"/>
-      <c r="AJ25" s="112"/>
-      <c r="AK25" s="114"/>
-      <c r="AL25" s="114"/>
-      <c r="AM25" s="114"/>
-      <c r="AN25" s="115"/>
-      <c r="AO25" s="111"/>
-      <c r="AP25" s="112"/>
-      <c r="AQ25" s="112"/>
-      <c r="AR25" s="112"/>
-      <c r="AS25" s="112"/>
-      <c r="AT25" s="112"/>
-      <c r="AU25" s="112"/>
-      <c r="AV25" s="112"/>
-      <c r="AW25" s="112"/>
-      <c r="AX25" s="112"/>
-      <c r="AY25" s="112"/>
-      <c r="AZ25" s="112"/>
-      <c r="BA25" s="112"/>
-      <c r="BB25" s="112"/>
-      <c r="BC25" s="113"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="88"/>
+      <c r="K25" s="88"/>
+      <c r="L25" s="88"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="88"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
+      <c r="V25" s="88"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="88"/>
+      <c r="AF25" s="88"/>
+      <c r="AG25" s="88"/>
+      <c r="AH25" s="88"/>
+      <c r="AI25" s="88"/>
+      <c r="AJ25" s="88"/>
+      <c r="AK25" s="91"/>
+      <c r="AL25" s="91"/>
+      <c r="AM25" s="91"/>
+      <c r="AN25" s="92"/>
+      <c r="AO25" s="87"/>
+      <c r="AP25" s="88"/>
+      <c r="AQ25" s="88"/>
+      <c r="AR25" s="88"/>
+      <c r="AS25" s="88"/>
+      <c r="AT25" s="88"/>
+      <c r="AU25" s="88"/>
+      <c r="AV25" s="88"/>
+      <c r="AW25" s="88"/>
+      <c r="AX25" s="88"/>
+      <c r="AY25" s="88"/>
+      <c r="AZ25" s="88"/>
+      <c r="BA25" s="88"/>
+      <c r="BB25" s="88"/>
+      <c r="BC25" s="89"/>
     </row>
     <row r="26" spans="1:55" ht="15" customHeight="1">
       <c r="A26" s="40"/>
-      <c r="B26" s="105"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="112"/>
-      <c r="S26" s="112"/>
-      <c r="T26" s="112"/>
-      <c r="U26" s="112"/>
-      <c r="V26" s="112"/>
-      <c r="W26" s="112"/>
-      <c r="X26" s="112"/>
-      <c r="Y26" s="112"/>
-      <c r="Z26" s="112"/>
-      <c r="AA26" s="112"/>
-      <c r="AB26" s="112"/>
-      <c r="AC26" s="112"/>
-      <c r="AD26" s="112"/>
-      <c r="AE26" s="112"/>
-      <c r="AF26" s="112"/>
-      <c r="AG26" s="112"/>
-      <c r="AH26" s="112"/>
-      <c r="AI26" s="112"/>
-      <c r="AJ26" s="112"/>
-      <c r="AK26" s="114"/>
-      <c r="AL26" s="114"/>
-      <c r="AM26" s="114"/>
-      <c r="AN26" s="115"/>
-      <c r="AO26" s="111"/>
-      <c r="AP26" s="112"/>
-      <c r="AQ26" s="112"/>
-      <c r="AR26" s="112"/>
-      <c r="AS26" s="112"/>
-      <c r="AT26" s="112"/>
-      <c r="AU26" s="112"/>
-      <c r="AV26" s="112"/>
-      <c r="AW26" s="112"/>
-      <c r="AX26" s="112"/>
-      <c r="AY26" s="112"/>
-      <c r="AZ26" s="112"/>
-      <c r="BA26" s="112"/>
-      <c r="BB26" s="112"/>
-      <c r="BC26" s="113"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="88"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="88"/>
+      <c r="P26" s="88"/>
+      <c r="Q26" s="88"/>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="88"/>
+      <c r="U26" s="88"/>
+      <c r="V26" s="88"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="88"/>
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="88"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="88"/>
+      <c r="AF26" s="88"/>
+      <c r="AG26" s="88"/>
+      <c r="AH26" s="88"/>
+      <c r="AI26" s="88"/>
+      <c r="AJ26" s="88"/>
+      <c r="AK26" s="91"/>
+      <c r="AL26" s="91"/>
+      <c r="AM26" s="91"/>
+      <c r="AN26" s="92"/>
+      <c r="AO26" s="87"/>
+      <c r="AP26" s="88"/>
+      <c r="AQ26" s="88"/>
+      <c r="AR26" s="88"/>
+      <c r="AS26" s="88"/>
+      <c r="AT26" s="88"/>
+      <c r="AU26" s="88"/>
+      <c r="AV26" s="88"/>
+      <c r="AW26" s="88"/>
+      <c r="AX26" s="88"/>
+      <c r="AY26" s="88"/>
+      <c r="AZ26" s="88"/>
+      <c r="BA26" s="88"/>
+      <c r="BB26" s="88"/>
+      <c r="BC26" s="89"/>
     </row>
     <row r="27" spans="1:55" ht="15" customHeight="1">
       <c r="A27" s="40"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
-      <c r="Q27" s="112"/>
-      <c r="R27" s="112"/>
-      <c r="S27" s="112"/>
-      <c r="T27" s="112"/>
-      <c r="U27" s="112"/>
-      <c r="V27" s="112"/>
-      <c r="W27" s="112"/>
-      <c r="X27" s="112"/>
-      <c r="Y27" s="112"/>
-      <c r="Z27" s="112"/>
-      <c r="AA27" s="112"/>
-      <c r="AB27" s="112"/>
-      <c r="AC27" s="112"/>
-      <c r="AD27" s="112"/>
-      <c r="AE27" s="112"/>
-      <c r="AF27" s="112"/>
-      <c r="AG27" s="112"/>
-      <c r="AH27" s="112"/>
-      <c r="AI27" s="112"/>
-      <c r="AJ27" s="112"/>
-      <c r="AK27" s="114"/>
-      <c r="AL27" s="114"/>
-      <c r="AM27" s="114"/>
-      <c r="AN27" s="115"/>
-      <c r="AO27" s="111"/>
-      <c r="AP27" s="112"/>
-      <c r="AQ27" s="112"/>
-      <c r="AR27" s="112"/>
-      <c r="AS27" s="112"/>
-      <c r="AT27" s="112"/>
-      <c r="AU27" s="112"/>
-      <c r="AV27" s="112"/>
-      <c r="AW27" s="112"/>
-      <c r="AX27" s="112"/>
-      <c r="AY27" s="112"/>
-      <c r="AZ27" s="112"/>
-      <c r="BA27" s="112"/>
-      <c r="BB27" s="112"/>
-      <c r="BC27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
+      <c r="L27" s="88"/>
+      <c r="M27" s="88"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="88"/>
+      <c r="P27" s="88"/>
+      <c r="Q27" s="88"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="88"/>
+      <c r="U27" s="88"/>
+      <c r="V27" s="88"/>
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+      <c r="Y27" s="88"/>
+      <c r="Z27" s="88"/>
+      <c r="AA27" s="88"/>
+      <c r="AB27" s="88"/>
+      <c r="AC27" s="88"/>
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="88"/>
+      <c r="AF27" s="88"/>
+      <c r="AG27" s="88"/>
+      <c r="AH27" s="88"/>
+      <c r="AI27" s="88"/>
+      <c r="AJ27" s="88"/>
+      <c r="AK27" s="91"/>
+      <c r="AL27" s="91"/>
+      <c r="AM27" s="91"/>
+      <c r="AN27" s="92"/>
+      <c r="AO27" s="87"/>
+      <c r="AP27" s="88"/>
+      <c r="AQ27" s="88"/>
+      <c r="AR27" s="88"/>
+      <c r="AS27" s="88"/>
+      <c r="AT27" s="88"/>
+      <c r="AU27" s="88"/>
+      <c r="AV27" s="88"/>
+      <c r="AW27" s="88"/>
+      <c r="AX27" s="88"/>
+      <c r="AY27" s="88"/>
+      <c r="AZ27" s="88"/>
+      <c r="BA27" s="88"/>
+      <c r="BB27" s="88"/>
+      <c r="BC27" s="89"/>
     </row>
     <row r="28" spans="1:55" ht="15" customHeight="1">
       <c r="A28" s="40"/>
-      <c r="B28" s="105"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="107"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="112"/>
-      <c r="K28" s="112"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="112"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="112"/>
-      <c r="R28" s="112"/>
-      <c r="S28" s="112"/>
-      <c r="T28" s="112"/>
-      <c r="U28" s="112"/>
-      <c r="V28" s="112"/>
-      <c r="W28" s="112"/>
-      <c r="X28" s="112"/>
-      <c r="Y28" s="112"/>
-      <c r="Z28" s="112"/>
-      <c r="AA28" s="112"/>
-      <c r="AB28" s="112"/>
-      <c r="AC28" s="112"/>
-      <c r="AD28" s="112"/>
-      <c r="AE28" s="112"/>
-      <c r="AF28" s="112"/>
-      <c r="AG28" s="112"/>
-      <c r="AH28" s="112"/>
-      <c r="AI28" s="112"/>
-      <c r="AJ28" s="112"/>
-      <c r="AK28" s="114"/>
-      <c r="AL28" s="114"/>
-      <c r="AM28" s="114"/>
-      <c r="AN28" s="115"/>
-      <c r="AO28" s="111"/>
-      <c r="AP28" s="112"/>
-      <c r="AQ28" s="112"/>
-      <c r="AR28" s="112"/>
-      <c r="AS28" s="112"/>
-      <c r="AT28" s="112"/>
-      <c r="AU28" s="112"/>
-      <c r="AV28" s="112"/>
-      <c r="AW28" s="112"/>
-      <c r="AX28" s="112"/>
-      <c r="AY28" s="112"/>
-      <c r="AZ28" s="112"/>
-      <c r="BA28" s="112"/>
-      <c r="BB28" s="112"/>
-      <c r="BC28" s="113"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="93"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="88"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="88"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="88"/>
+      <c r="P28" s="88"/>
+      <c r="Q28" s="88"/>
+      <c r="R28" s="88"/>
+      <c r="S28" s="88"/>
+      <c r="T28" s="88"/>
+      <c r="U28" s="88"/>
+      <c r="V28" s="88"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="88"/>
+      <c r="Y28" s="88"/>
+      <c r="Z28" s="88"/>
+      <c r="AA28" s="88"/>
+      <c r="AB28" s="88"/>
+      <c r="AC28" s="88"/>
+      <c r="AD28" s="88"/>
+      <c r="AE28" s="88"/>
+      <c r="AF28" s="88"/>
+      <c r="AG28" s="88"/>
+      <c r="AH28" s="88"/>
+      <c r="AI28" s="88"/>
+      <c r="AJ28" s="88"/>
+      <c r="AK28" s="91"/>
+      <c r="AL28" s="91"/>
+      <c r="AM28" s="91"/>
+      <c r="AN28" s="92"/>
+      <c r="AO28" s="87"/>
+      <c r="AP28" s="88"/>
+      <c r="AQ28" s="88"/>
+      <c r="AR28" s="88"/>
+      <c r="AS28" s="88"/>
+      <c r="AT28" s="88"/>
+      <c r="AU28" s="88"/>
+      <c r="AV28" s="88"/>
+      <c r="AW28" s="88"/>
+      <c r="AX28" s="88"/>
+      <c r="AY28" s="88"/>
+      <c r="AZ28" s="88"/>
+      <c r="BA28" s="88"/>
+      <c r="BB28" s="88"/>
+      <c r="BC28" s="89"/>
     </row>
     <row r="29" spans="1:55" ht="15" customHeight="1">
       <c r="A29" s="40"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="107"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="112"/>
-      <c r="K29" s="112"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="112"/>
-      <c r="R29" s="112"/>
-      <c r="S29" s="112"/>
-      <c r="T29" s="112"/>
-      <c r="U29" s="112"/>
-      <c r="V29" s="112"/>
-      <c r="W29" s="112"/>
-      <c r="X29" s="112"/>
-      <c r="Y29" s="112"/>
-      <c r="Z29" s="112"/>
-      <c r="AA29" s="112"/>
-      <c r="AB29" s="112"/>
-      <c r="AC29" s="112"/>
-      <c r="AD29" s="112"/>
-      <c r="AE29" s="112"/>
-      <c r="AF29" s="112"/>
-      <c r="AG29" s="112"/>
-      <c r="AH29" s="112"/>
-      <c r="AI29" s="112"/>
-      <c r="AJ29" s="112"/>
-      <c r="AK29" s="114"/>
-      <c r="AL29" s="114"/>
-      <c r="AM29" s="114"/>
-      <c r="AN29" s="115"/>
-      <c r="AO29" s="111"/>
-      <c r="AP29" s="112"/>
-      <c r="AQ29" s="112"/>
-      <c r="AR29" s="112"/>
-      <c r="AS29" s="112"/>
-      <c r="AT29" s="112"/>
-      <c r="AU29" s="112"/>
-      <c r="AV29" s="112"/>
-      <c r="AW29" s="112"/>
-      <c r="AX29" s="112"/>
-      <c r="AY29" s="112"/>
-      <c r="AZ29" s="112"/>
-      <c r="BA29" s="112"/>
-      <c r="BB29" s="112"/>
-      <c r="BC29" s="113"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="88"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="88"/>
+      <c r="P29" s="88"/>
+      <c r="Q29" s="88"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="88"/>
+      <c r="T29" s="88"/>
+      <c r="U29" s="88"/>
+      <c r="V29" s="88"/>
+      <c r="W29" s="88"/>
+      <c r="X29" s="88"/>
+      <c r="Y29" s="88"/>
+      <c r="Z29" s="88"/>
+      <c r="AA29" s="88"/>
+      <c r="AB29" s="88"/>
+      <c r="AC29" s="88"/>
+      <c r="AD29" s="88"/>
+      <c r="AE29" s="88"/>
+      <c r="AF29" s="88"/>
+      <c r="AG29" s="88"/>
+      <c r="AH29" s="88"/>
+      <c r="AI29" s="88"/>
+      <c r="AJ29" s="88"/>
+      <c r="AK29" s="91"/>
+      <c r="AL29" s="91"/>
+      <c r="AM29" s="91"/>
+      <c r="AN29" s="92"/>
+      <c r="AO29" s="87"/>
+      <c r="AP29" s="88"/>
+      <c r="AQ29" s="88"/>
+      <c r="AR29" s="88"/>
+      <c r="AS29" s="88"/>
+      <c r="AT29" s="88"/>
+      <c r="AU29" s="88"/>
+      <c r="AV29" s="88"/>
+      <c r="AW29" s="88"/>
+      <c r="AX29" s="88"/>
+      <c r="AY29" s="88"/>
+      <c r="AZ29" s="88"/>
+      <c r="BA29" s="88"/>
+      <c r="BB29" s="88"/>
+      <c r="BC29" s="89"/>
     </row>
     <row r="30" spans="1:55" ht="15" customHeight="1">
       <c r="A30" s="40"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="106"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="107"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="112"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="112"/>
-      <c r="R30" s="112"/>
-      <c r="S30" s="112"/>
-      <c r="T30" s="112"/>
-      <c r="U30" s="112"/>
-      <c r="V30" s="112"/>
-      <c r="W30" s="112"/>
-      <c r="X30" s="112"/>
-      <c r="Y30" s="112"/>
-      <c r="Z30" s="112"/>
-      <c r="AA30" s="112"/>
-      <c r="AB30" s="112"/>
-      <c r="AC30" s="112"/>
-      <c r="AD30" s="112"/>
-      <c r="AE30" s="112"/>
-      <c r="AF30" s="112"/>
-      <c r="AG30" s="112"/>
-      <c r="AH30" s="112"/>
-      <c r="AI30" s="112"/>
-      <c r="AJ30" s="112"/>
-      <c r="AK30" s="114"/>
-      <c r="AL30" s="114"/>
-      <c r="AM30" s="114"/>
-      <c r="AN30" s="115"/>
-      <c r="AO30" s="111"/>
-      <c r="AP30" s="112"/>
-      <c r="AQ30" s="112"/>
-      <c r="AR30" s="112"/>
-      <c r="AS30" s="112"/>
-      <c r="AT30" s="112"/>
-      <c r="AU30" s="112"/>
-      <c r="AV30" s="112"/>
-      <c r="AW30" s="112"/>
-      <c r="AX30" s="112"/>
-      <c r="AY30" s="112"/>
-      <c r="AZ30" s="112"/>
-      <c r="BA30" s="112"/>
-      <c r="BB30" s="112"/>
-      <c r="BC30" s="113"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="88"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="88"/>
+      <c r="P30" s="88"/>
+      <c r="Q30" s="88"/>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="88"/>
+      <c r="U30" s="88"/>
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88"/>
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="88"/>
+      <c r="AF30" s="88"/>
+      <c r="AG30" s="88"/>
+      <c r="AH30" s="88"/>
+      <c r="AI30" s="88"/>
+      <c r="AJ30" s="88"/>
+      <c r="AK30" s="91"/>
+      <c r="AL30" s="91"/>
+      <c r="AM30" s="91"/>
+      <c r="AN30" s="92"/>
+      <c r="AO30" s="87"/>
+      <c r="AP30" s="88"/>
+      <c r="AQ30" s="88"/>
+      <c r="AR30" s="88"/>
+      <c r="AS30" s="88"/>
+      <c r="AT30" s="88"/>
+      <c r="AU30" s="88"/>
+      <c r="AV30" s="88"/>
+      <c r="AW30" s="88"/>
+      <c r="AX30" s="88"/>
+      <c r="AY30" s="88"/>
+      <c r="AZ30" s="88"/>
+      <c r="BA30" s="88"/>
+      <c r="BB30" s="88"/>
+      <c r="BC30" s="89"/>
     </row>
     <row r="31" spans="1:55" ht="15" customHeight="1">
       <c r="A31" s="40"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="107"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="112"/>
-      <c r="S31" s="112"/>
-      <c r="T31" s="112"/>
-      <c r="U31" s="112"/>
-      <c r="V31" s="112"/>
-      <c r="W31" s="112"/>
-      <c r="X31" s="112"/>
-      <c r="Y31" s="112"/>
-      <c r="Z31" s="112"/>
-      <c r="AA31" s="112"/>
-      <c r="AB31" s="112"/>
-      <c r="AC31" s="112"/>
-      <c r="AD31" s="112"/>
-      <c r="AE31" s="112"/>
-      <c r="AF31" s="112"/>
-      <c r="AG31" s="112"/>
-      <c r="AH31" s="112"/>
-      <c r="AI31" s="112"/>
-      <c r="AJ31" s="112"/>
-      <c r="AK31" s="114"/>
-      <c r="AL31" s="114"/>
-      <c r="AM31" s="114"/>
-      <c r="AN31" s="115"/>
-      <c r="AO31" s="111"/>
-      <c r="AP31" s="112"/>
-      <c r="AQ31" s="112"/>
-      <c r="AR31" s="112"/>
-      <c r="AS31" s="112"/>
-      <c r="AT31" s="112"/>
-      <c r="AU31" s="112"/>
-      <c r="AV31" s="112"/>
-      <c r="AW31" s="112"/>
-      <c r="AX31" s="112"/>
-      <c r="AY31" s="112"/>
-      <c r="AZ31" s="112"/>
-      <c r="BA31" s="112"/>
-      <c r="BB31" s="112"/>
-      <c r="BC31" s="113"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
+      <c r="L31" s="88"/>
+      <c r="M31" s="88"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="88"/>
+      <c r="P31" s="88"/>
+      <c r="Q31" s="88"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88"/>
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="88"/>
+      <c r="AF31" s="88"/>
+      <c r="AG31" s="88"/>
+      <c r="AH31" s="88"/>
+      <c r="AI31" s="88"/>
+      <c r="AJ31" s="88"/>
+      <c r="AK31" s="91"/>
+      <c r="AL31" s="91"/>
+      <c r="AM31" s="91"/>
+      <c r="AN31" s="92"/>
+      <c r="AO31" s="87"/>
+      <c r="AP31" s="88"/>
+      <c r="AQ31" s="88"/>
+      <c r="AR31" s="88"/>
+      <c r="AS31" s="88"/>
+      <c r="AT31" s="88"/>
+      <c r="AU31" s="88"/>
+      <c r="AV31" s="88"/>
+      <c r="AW31" s="88"/>
+      <c r="AX31" s="88"/>
+      <c r="AY31" s="88"/>
+      <c r="AZ31" s="88"/>
+      <c r="BA31" s="88"/>
+      <c r="BB31" s="88"/>
+      <c r="BC31" s="89"/>
     </row>
     <row r="32" spans="1:55" ht="15" customHeight="1">
       <c r="A32" s="40"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="106"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="105"/>
-      <c r="J32" s="112"/>
-      <c r="K32" s="112"/>
-      <c r="L32" s="112"/>
-      <c r="M32" s="112"/>
-      <c r="N32" s="112"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
-      <c r="Q32" s="112"/>
-      <c r="R32" s="112"/>
-      <c r="S32" s="112"/>
-      <c r="T32" s="112"/>
-      <c r="U32" s="112"/>
-      <c r="V32" s="112"/>
-      <c r="W32" s="112"/>
-      <c r="X32" s="112"/>
-      <c r="Y32" s="112"/>
-      <c r="Z32" s="112"/>
-      <c r="AA32" s="112"/>
-      <c r="AB32" s="112"/>
-      <c r="AC32" s="112"/>
-      <c r="AD32" s="112"/>
-      <c r="AE32" s="112"/>
-      <c r="AF32" s="112"/>
-      <c r="AG32" s="112"/>
-      <c r="AH32" s="112"/>
-      <c r="AI32" s="112"/>
-      <c r="AJ32" s="112"/>
-      <c r="AK32" s="114"/>
-      <c r="AL32" s="114"/>
-      <c r="AM32" s="114"/>
-      <c r="AN32" s="115"/>
-      <c r="AO32" s="111"/>
-      <c r="AP32" s="112"/>
-      <c r="AQ32" s="112"/>
-      <c r="AR32" s="112"/>
-      <c r="AS32" s="112"/>
-      <c r="AT32" s="112"/>
-      <c r="AU32" s="112"/>
-      <c r="AV32" s="112"/>
-      <c r="AW32" s="112"/>
-      <c r="AX32" s="112"/>
-      <c r="AY32" s="112"/>
-      <c r="AZ32" s="112"/>
-      <c r="BA32" s="112"/>
-      <c r="BB32" s="112"/>
-      <c r="BC32" s="113"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="88"/>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="88"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="88"/>
+      <c r="P32" s="88"/>
+      <c r="Q32" s="88"/>
+      <c r="R32" s="88"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="88"/>
+      <c r="U32" s="88"/>
+      <c r="V32" s="88"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="88"/>
+      <c r="Z32" s="88"/>
+      <c r="AA32" s="88"/>
+      <c r="AB32" s="88"/>
+      <c r="AC32" s="88"/>
+      <c r="AD32" s="88"/>
+      <c r="AE32" s="88"/>
+      <c r="AF32" s="88"/>
+      <c r="AG32" s="88"/>
+      <c r="AH32" s="88"/>
+      <c r="AI32" s="88"/>
+      <c r="AJ32" s="88"/>
+      <c r="AK32" s="91"/>
+      <c r="AL32" s="91"/>
+      <c r="AM32" s="91"/>
+      <c r="AN32" s="92"/>
+      <c r="AO32" s="87"/>
+      <c r="AP32" s="88"/>
+      <c r="AQ32" s="88"/>
+      <c r="AR32" s="88"/>
+      <c r="AS32" s="88"/>
+      <c r="AT32" s="88"/>
+      <c r="AU32" s="88"/>
+      <c r="AV32" s="88"/>
+      <c r="AW32" s="88"/>
+      <c r="AX32" s="88"/>
+      <c r="AY32" s="88"/>
+      <c r="AZ32" s="88"/>
+      <c r="BA32" s="88"/>
+      <c r="BB32" s="88"/>
+      <c r="BC32" s="89"/>
     </row>
     <row r="33" spans="1:55" ht="15" customHeight="1">
       <c r="A33" s="40"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="105"/>
-      <c r="J33" s="112"/>
-      <c r="K33" s="112"/>
-      <c r="L33" s="112"/>
-      <c r="M33" s="112"/>
-      <c r="N33" s="112"/>
-      <c r="O33" s="112"/>
-      <c r="P33" s="112"/>
-      <c r="Q33" s="112"/>
-      <c r="R33" s="112"/>
-      <c r="S33" s="112"/>
-      <c r="T33" s="112"/>
-      <c r="U33" s="112"/>
-      <c r="V33" s="112"/>
-      <c r="W33" s="112"/>
-      <c r="X33" s="112"/>
-      <c r="Y33" s="112"/>
-      <c r="Z33" s="112"/>
-      <c r="AA33" s="112"/>
-      <c r="AB33" s="112"/>
-      <c r="AC33" s="112"/>
-      <c r="AD33" s="112"/>
-      <c r="AE33" s="112"/>
-      <c r="AF33" s="112"/>
-      <c r="AG33" s="112"/>
-      <c r="AH33" s="112"/>
-      <c r="AI33" s="112"/>
-      <c r="AJ33" s="112"/>
-      <c r="AK33" s="114"/>
-      <c r="AL33" s="114"/>
-      <c r="AM33" s="114"/>
-      <c r="AN33" s="115"/>
-      <c r="AO33" s="111"/>
-      <c r="AP33" s="112"/>
-      <c r="AQ33" s="112"/>
-      <c r="AR33" s="112"/>
-      <c r="AS33" s="112"/>
-      <c r="AT33" s="112"/>
-      <c r="AU33" s="112"/>
-      <c r="AV33" s="112"/>
-      <c r="AW33" s="112"/>
-      <c r="AX33" s="112"/>
-      <c r="AY33" s="112"/>
-      <c r="AZ33" s="112"/>
-      <c r="BA33" s="112"/>
-      <c r="BB33" s="112"/>
-      <c r="BC33" s="113"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="88"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="88"/>
+      <c r="M33" s="88"/>
+      <c r="N33" s="88"/>
+      <c r="O33" s="88"/>
+      <c r="P33" s="88"/>
+      <c r="Q33" s="88"/>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="88"/>
+      <c r="U33" s="88"/>
+      <c r="V33" s="88"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+      <c r="Y33" s="88"/>
+      <c r="Z33" s="88"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="88"/>
+      <c r="AC33" s="88"/>
+      <c r="AD33" s="88"/>
+      <c r="AE33" s="88"/>
+      <c r="AF33" s="88"/>
+      <c r="AG33" s="88"/>
+      <c r="AH33" s="88"/>
+      <c r="AI33" s="88"/>
+      <c r="AJ33" s="88"/>
+      <c r="AK33" s="91"/>
+      <c r="AL33" s="91"/>
+      <c r="AM33" s="91"/>
+      <c r="AN33" s="92"/>
+      <c r="AO33" s="87"/>
+      <c r="AP33" s="88"/>
+      <c r="AQ33" s="88"/>
+      <c r="AR33" s="88"/>
+      <c r="AS33" s="88"/>
+      <c r="AT33" s="88"/>
+      <c r="AU33" s="88"/>
+      <c r="AV33" s="88"/>
+      <c r="AW33" s="88"/>
+      <c r="AX33" s="88"/>
+      <c r="AY33" s="88"/>
+      <c r="AZ33" s="88"/>
+      <c r="BA33" s="88"/>
+      <c r="BB33" s="88"/>
+      <c r="BC33" s="89"/>
     </row>
     <row r="34" spans="1:55" ht="15" customHeight="1">
       <c r="A34" s="40"/>
-      <c r="B34" s="105"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="107"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="112"/>
-      <c r="K34" s="112"/>
-      <c r="L34" s="112"/>
-      <c r="M34" s="112"/>
-      <c r="N34" s="112"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="112"/>
-      <c r="Q34" s="112"/>
-      <c r="R34" s="112"/>
-      <c r="S34" s="112"/>
-      <c r="T34" s="112"/>
-      <c r="U34" s="112"/>
-      <c r="V34" s="112"/>
-      <c r="W34" s="112"/>
-      <c r="X34" s="112"/>
-      <c r="Y34" s="112"/>
-      <c r="Z34" s="112"/>
-      <c r="AA34" s="112"/>
-      <c r="AB34" s="112"/>
-      <c r="AC34" s="112"/>
-      <c r="AD34" s="112"/>
-      <c r="AE34" s="112"/>
-      <c r="AF34" s="112"/>
-      <c r="AG34" s="112"/>
-      <c r="AH34" s="112"/>
-      <c r="AI34" s="112"/>
-      <c r="AJ34" s="112"/>
-      <c r="AK34" s="114"/>
-      <c r="AL34" s="114"/>
-      <c r="AM34" s="114"/>
-      <c r="AN34" s="115"/>
-      <c r="AO34" s="111"/>
-      <c r="AP34" s="112"/>
-      <c r="AQ34" s="112"/>
-      <c r="AR34" s="112"/>
-      <c r="AS34" s="112"/>
-      <c r="AT34" s="112"/>
-      <c r="AU34" s="112"/>
-      <c r="AV34" s="112"/>
-      <c r="AW34" s="112"/>
-      <c r="AX34" s="112"/>
-      <c r="AY34" s="112"/>
-      <c r="AZ34" s="112"/>
-      <c r="BA34" s="112"/>
-      <c r="BB34" s="112"/>
-      <c r="BC34" s="113"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="93"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="88"/>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="M34" s="88"/>
+      <c r="N34" s="88"/>
+      <c r="O34" s="88"/>
+      <c r="P34" s="88"/>
+      <c r="Q34" s="88"/>
+      <c r="R34" s="88"/>
+      <c r="S34" s="88"/>
+      <c r="T34" s="88"/>
+      <c r="U34" s="88"/>
+      <c r="V34" s="88"/>
+      <c r="W34" s="88"/>
+      <c r="X34" s="88"/>
+      <c r="Y34" s="88"/>
+      <c r="Z34" s="88"/>
+      <c r="AA34" s="88"/>
+      <c r="AB34" s="88"/>
+      <c r="AC34" s="88"/>
+      <c r="AD34" s="88"/>
+      <c r="AE34" s="88"/>
+      <c r="AF34" s="88"/>
+      <c r="AG34" s="88"/>
+      <c r="AH34" s="88"/>
+      <c r="AI34" s="88"/>
+      <c r="AJ34" s="88"/>
+      <c r="AK34" s="91"/>
+      <c r="AL34" s="91"/>
+      <c r="AM34" s="91"/>
+      <c r="AN34" s="92"/>
+      <c r="AO34" s="87"/>
+      <c r="AP34" s="88"/>
+      <c r="AQ34" s="88"/>
+      <c r="AR34" s="88"/>
+      <c r="AS34" s="88"/>
+      <c r="AT34" s="88"/>
+      <c r="AU34" s="88"/>
+      <c r="AV34" s="88"/>
+      <c r="AW34" s="88"/>
+      <c r="AX34" s="88"/>
+      <c r="AY34" s="88"/>
+      <c r="AZ34" s="88"/>
+      <c r="BA34" s="88"/>
+      <c r="BB34" s="88"/>
+      <c r="BC34" s="89"/>
     </row>
     <row r="35" spans="1:55" ht="15" customHeight="1">
       <c r="A35" s="40"/>
-      <c r="B35" s="105"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="107"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="112"/>
-      <c r="K35" s="112"/>
-      <c r="L35" s="112"/>
-      <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
-      <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
-      <c r="Q35" s="112"/>
-      <c r="R35" s="112"/>
-      <c r="S35" s="112"/>
-      <c r="T35" s="112"/>
-      <c r="U35" s="112"/>
-      <c r="V35" s="112"/>
-      <c r="W35" s="112"/>
-      <c r="X35" s="112"/>
-      <c r="Y35" s="112"/>
-      <c r="Z35" s="112"/>
-      <c r="AA35" s="112"/>
-      <c r="AB35" s="112"/>
-      <c r="AC35" s="112"/>
-      <c r="AD35" s="112"/>
-      <c r="AE35" s="112"/>
-      <c r="AF35" s="112"/>
-      <c r="AG35" s="112"/>
-      <c r="AH35" s="112"/>
-      <c r="AI35" s="112"/>
-      <c r="AJ35" s="112"/>
-      <c r="AK35" s="114"/>
-      <c r="AL35" s="114"/>
-      <c r="AM35" s="114"/>
-      <c r="AN35" s="115"/>
-      <c r="AO35" s="111"/>
-      <c r="AP35" s="112"/>
-      <c r="AQ35" s="112"/>
-      <c r="AR35" s="112"/>
-      <c r="AS35" s="112"/>
-      <c r="AT35" s="112"/>
-      <c r="AU35" s="112"/>
-      <c r="AV35" s="112"/>
-      <c r="AW35" s="112"/>
-      <c r="AX35" s="112"/>
-      <c r="AY35" s="112"/>
-      <c r="AZ35" s="112"/>
-      <c r="BA35" s="112"/>
-      <c r="BB35" s="112"/>
-      <c r="BC35" s="113"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="93"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="88"/>
+      <c r="K35" s="88"/>
+      <c r="L35" s="88"/>
+      <c r="M35" s="88"/>
+      <c r="N35" s="88"/>
+      <c r="O35" s="88"/>
+      <c r="P35" s="88"/>
+      <c r="Q35" s="88"/>
+      <c r="R35" s="88"/>
+      <c r="S35" s="88"/>
+      <c r="T35" s="88"/>
+      <c r="U35" s="88"/>
+      <c r="V35" s="88"/>
+      <c r="W35" s="88"/>
+      <c r="X35" s="88"/>
+      <c r="Y35" s="88"/>
+      <c r="Z35" s="88"/>
+      <c r="AA35" s="88"/>
+      <c r="AB35" s="88"/>
+      <c r="AC35" s="88"/>
+      <c r="AD35" s="88"/>
+      <c r="AE35" s="88"/>
+      <c r="AF35" s="88"/>
+      <c r="AG35" s="88"/>
+      <c r="AH35" s="88"/>
+      <c r="AI35" s="88"/>
+      <c r="AJ35" s="88"/>
+      <c r="AK35" s="91"/>
+      <c r="AL35" s="91"/>
+      <c r="AM35" s="91"/>
+      <c r="AN35" s="92"/>
+      <c r="AO35" s="87"/>
+      <c r="AP35" s="88"/>
+      <c r="AQ35" s="88"/>
+      <c r="AR35" s="88"/>
+      <c r="AS35" s="88"/>
+      <c r="AT35" s="88"/>
+      <c r="AU35" s="88"/>
+      <c r="AV35" s="88"/>
+      <c r="AW35" s="88"/>
+      <c r="AX35" s="88"/>
+      <c r="AY35" s="88"/>
+      <c r="AZ35" s="88"/>
+      <c r="BA35" s="88"/>
+      <c r="BB35" s="88"/>
+      <c r="BC35" s="89"/>
     </row>
     <row r="36" spans="1:55" ht="15" customHeight="1" thickBot="1">
       <c r="A36" s="42"/>
-      <c r="B36" s="122"/>
-      <c r="C36" s="125"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="122"/>
-      <c r="J36" s="120"/>
-      <c r="K36" s="120"/>
-      <c r="L36" s="120"/>
-      <c r="M36" s="120"/>
-      <c r="N36" s="120"/>
-      <c r="O36" s="120"/>
-      <c r="P36" s="120"/>
-      <c r="Q36" s="120"/>
-      <c r="R36" s="120"/>
-      <c r="S36" s="120"/>
-      <c r="T36" s="120"/>
-      <c r="U36" s="120"/>
-      <c r="V36" s="120"/>
-      <c r="W36" s="120"/>
-      <c r="X36" s="120"/>
-      <c r="Y36" s="120"/>
-      <c r="Z36" s="120"/>
-      <c r="AA36" s="120"/>
-      <c r="AB36" s="120"/>
-      <c r="AC36" s="120"/>
-      <c r="AD36" s="120"/>
-      <c r="AE36" s="120"/>
-      <c r="AF36" s="120"/>
-      <c r="AG36" s="120"/>
-      <c r="AH36" s="120"/>
-      <c r="AI36" s="120"/>
-      <c r="AJ36" s="120"/>
-      <c r="AK36" s="123"/>
-      <c r="AL36" s="123"/>
-      <c r="AM36" s="123"/>
-      <c r="AN36" s="124"/>
-      <c r="AO36" s="119"/>
-      <c r="AP36" s="120"/>
-      <c r="AQ36" s="120"/>
-      <c r="AR36" s="120"/>
-      <c r="AS36" s="120"/>
-      <c r="AT36" s="120"/>
-      <c r="AU36" s="120"/>
-      <c r="AV36" s="120"/>
-      <c r="AW36" s="120"/>
-      <c r="AX36" s="120"/>
-      <c r="AY36" s="120"/>
-      <c r="AZ36" s="120"/>
-      <c r="BA36" s="120"/>
-      <c r="BB36" s="120"/>
-      <c r="BC36" s="121"/>
+      <c r="B36" s="110"/>
+      <c r="C36" s="113"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="114"/>
+      <c r="I36" s="110"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="108"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
+      <c r="O36" s="108"/>
+      <c r="P36" s="108"/>
+      <c r="Q36" s="108"/>
+      <c r="R36" s="108"/>
+      <c r="S36" s="108"/>
+      <c r="T36" s="108"/>
+      <c r="U36" s="108"/>
+      <c r="V36" s="108"/>
+      <c r="W36" s="108"/>
+      <c r="X36" s="108"/>
+      <c r="Y36" s="108"/>
+      <c r="Z36" s="108"/>
+      <c r="AA36" s="108"/>
+      <c r="AB36" s="108"/>
+      <c r="AC36" s="108"/>
+      <c r="AD36" s="108"/>
+      <c r="AE36" s="108"/>
+      <c r="AF36" s="108"/>
+      <c r="AG36" s="108"/>
+      <c r="AH36" s="108"/>
+      <c r="AI36" s="108"/>
+      <c r="AJ36" s="108"/>
+      <c r="AK36" s="111"/>
+      <c r="AL36" s="111"/>
+      <c r="AM36" s="111"/>
+      <c r="AN36" s="112"/>
+      <c r="AO36" s="107"/>
+      <c r="AP36" s="108"/>
+      <c r="AQ36" s="108"/>
+      <c r="AR36" s="108"/>
+      <c r="AS36" s="108"/>
+      <c r="AT36" s="108"/>
+      <c r="AU36" s="108"/>
+      <c r="AV36" s="108"/>
+      <c r="AW36" s="108"/>
+      <c r="AX36" s="108"/>
+      <c r="AY36" s="108"/>
+      <c r="AZ36" s="108"/>
+      <c r="BA36" s="108"/>
+      <c r="BB36" s="108"/>
+      <c r="BC36" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="AO24:BC24"/>
-    <mergeCell ref="I24:AN24"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I28:AN28"/>
-    <mergeCell ref="AO27:BC27"/>
-    <mergeCell ref="AO28:BC28"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I29:AN29"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:AN25"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="AO23:BC23"/>
-    <mergeCell ref="I23:AN23"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="AO13:BC13"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="I12:AN12"/>
-    <mergeCell ref="I11:AN11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="AO19:BC19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:AN21"/>
-    <mergeCell ref="AO21:BC21"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:AN20"/>
-    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="AY2:BC2"/>
+    <mergeCell ref="I1:AX2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="AO4:BC4"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I4:AN4"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="AO6:BC6"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="AO29:BC29"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="AO14:BC14"/>
+    <mergeCell ref="AO9:BC9"/>
+    <mergeCell ref="AO8:BC8"/>
+    <mergeCell ref="I10:AN10"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:AN14"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:AN32"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="AO36:BC36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AO35:BC35"/>
+    <mergeCell ref="I35:AN35"/>
+    <mergeCell ref="I36:AN36"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="I33:AN33"/>
+    <mergeCell ref="AO5:BC5"/>
+    <mergeCell ref="AO34:BC34"/>
+    <mergeCell ref="I34:AN34"/>
+    <mergeCell ref="AO33:BC33"/>
+    <mergeCell ref="I27:AN27"/>
+    <mergeCell ref="AO7:BC7"/>
+    <mergeCell ref="AO32:BC32"/>
+    <mergeCell ref="AO26:BC26"/>
+    <mergeCell ref="AO22:BC22"/>
+    <mergeCell ref="AO30:BC30"/>
+    <mergeCell ref="AO31:BC31"/>
+    <mergeCell ref="I26:AN26"/>
+    <mergeCell ref="I30:AN30"/>
+    <mergeCell ref="I31:AN31"/>
+    <mergeCell ref="AO25:BC25"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I9:AN9"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="I5:AN5"/>
@@ -17329,54 +17436,37 @@
     <mergeCell ref="AO16:BC16"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="I19:AN19"/>
-    <mergeCell ref="AO36:BC36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="AO35:BC35"/>
-    <mergeCell ref="I35:AN35"/>
-    <mergeCell ref="I36:AN36"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="I33:AN33"/>
-    <mergeCell ref="AO5:BC5"/>
-    <mergeCell ref="AO34:BC34"/>
-    <mergeCell ref="I34:AN34"/>
-    <mergeCell ref="AO33:BC33"/>
-    <mergeCell ref="I27:AN27"/>
-    <mergeCell ref="AO7:BC7"/>
-    <mergeCell ref="AO32:BC32"/>
-    <mergeCell ref="AO26:BC26"/>
-    <mergeCell ref="AO22:BC22"/>
-    <mergeCell ref="AO30:BC30"/>
-    <mergeCell ref="AO31:BC31"/>
-    <mergeCell ref="I26:AN26"/>
-    <mergeCell ref="I30:AN30"/>
-    <mergeCell ref="I31:AN31"/>
-    <mergeCell ref="AO25:BC25"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I9:AN9"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="AY2:BC2"/>
-    <mergeCell ref="I1:AX2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="AO4:BC4"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I4:AN4"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="AO6:BC6"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="AO29:BC29"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="AO14:BC14"/>
-    <mergeCell ref="AO9:BC9"/>
-    <mergeCell ref="AO8:BC8"/>
-    <mergeCell ref="I10:AN10"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:AN14"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:AN32"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="AO23:BC23"/>
+    <mergeCell ref="I23:AN23"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="I11:AN11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="AO19:BC19"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:AN21"/>
+    <mergeCell ref="AO21:BC21"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:AN20"/>
+    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="AO24:BC24"/>
+    <mergeCell ref="I24:AN24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I28:AN28"/>
+    <mergeCell ref="AO27:BC27"/>
+    <mergeCell ref="AO28:BC28"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I29:AN29"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:AN25"/>
   </mergeCells>
   <phoneticPr fontId="36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -17434,17 +17524,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:11">
@@ -17495,15 +17585,15 @@
       <c r="K6" s="47"/>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="B7" s="58"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="68"/>
       <c r="K7" s="47"/>
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1">
@@ -17593,17 +17683,17 @@
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="66" t="s">
         <v>1839</v>
       </c>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="60"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="68"/>
       <c r="K15" s="46"/>
     </row>
     <row r="16" spans="1:11" ht="36">
@@ -17731,17 +17821,17 @@
     </row>
     <row r="22" spans="1:11" ht="12" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="66" t="s">
         <v>1805</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="68"/>
       <c r="K22" s="46"/>
     </row>
     <row r="23" spans="1:11" ht="36">
@@ -17871,17 +17961,17 @@
     </row>
     <row r="29" spans="1:11" ht="12" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="66" t="s">
         <v>1806</v>
       </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="60"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="68"/>
       <c r="K29" s="46"/>
     </row>
     <row r="30" spans="1:11" ht="36">
@@ -18011,17 +18101,17 @@
     </row>
     <row r="36" spans="1:11" ht="12" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="58" t="s">
+      <c r="B36" s="66" t="s">
         <v>1808</v>
       </c>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="60"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="68"/>
       <c r="K36" s="46"/>
     </row>
     <row r="37" spans="1:11" ht="36">
@@ -18151,17 +18241,17 @@
     </row>
     <row r="43" spans="1:11" s="25" customFormat="1" ht="12" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="58" t="s">
+      <c r="B43" s="66" t="s">
         <v>1810</v>
       </c>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="60"/>
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
+      <c r="I43" s="67"/>
+      <c r="J43" s="68"/>
       <c r="K43" s="48"/>
     </row>
     <row r="44" spans="1:11" s="25" customFormat="1" ht="36">
@@ -18266,17 +18356,17 @@
     </row>
     <row r="49" spans="1:11" ht="48" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="66" t="s">
         <v>1811</v>
       </c>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="59"/>
-      <c r="J49" s="60"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="68"/>
       <c r="K49" s="46"/>
     </row>
     <row r="50" spans="1:11">
@@ -18421,17 +18511,17 @@
     </row>
     <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="66" t="s">
         <v>1813</v>
       </c>
-      <c r="C57" s="59"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="59"/>
-      <c r="F57" s="59"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="59"/>
-      <c r="J57" s="60"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="67"/>
+      <c r="J57" s="68"/>
       <c r="K57" s="46"/>
     </row>
     <row r="58" spans="1:11" ht="36">
@@ -18536,17 +18626,17 @@
     </row>
     <row r="63" spans="1:11" ht="24" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="66" t="s">
         <v>1815</v>
       </c>
-      <c r="C63" s="59"/>
-      <c r="D63" s="59"/>
-      <c r="E63" s="59"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="59"/>
-      <c r="J63" s="60"/>
+      <c r="C63" s="67"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="67"/>
+      <c r="F63" s="67"/>
+      <c r="G63" s="67"/>
+      <c r="H63" s="67"/>
+      <c r="I63" s="67"/>
+      <c r="J63" s="68"/>
       <c r="K63" s="46"/>
     </row>
     <row r="64" spans="1:11" ht="36">
@@ -18651,17 +18741,17 @@
     </row>
     <row r="69" spans="1:11" ht="24" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="58" t="s">
+      <c r="B69" s="66" t="s">
         <v>1817</v>
       </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="59"/>
-      <c r="J69" s="60"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="68"/>
       <c r="K69" s="46"/>
     </row>
     <row r="70" spans="1:11" ht="36">
@@ -18766,17 +18856,17 @@
     </row>
     <row r="75" spans="1:11" ht="12" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="58" t="s">
+      <c r="B75" s="66" t="s">
         <v>1818</v>
       </c>
-      <c r="C75" s="59"/>
-      <c r="D75" s="59"/>
-      <c r="E75" s="59"/>
-      <c r="F75" s="59"/>
-      <c r="G75" s="59"/>
-      <c r="H75" s="59"/>
-      <c r="I75" s="59"/>
-      <c r="J75" s="60"/>
+      <c r="C75" s="67"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="67"/>
+      <c r="H75" s="67"/>
+      <c r="I75" s="67"/>
+      <c r="J75" s="68"/>
       <c r="K75" s="46"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -19342,17 +19432,17 @@
     </row>
     <row r="101" spans="1:11" ht="12" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="58" t="s">
+      <c r="B101" s="66" t="s">
         <v>1819</v>
       </c>
-      <c r="C101" s="59"/>
-      <c r="D101" s="59"/>
-      <c r="E101" s="59"/>
-      <c r="F101" s="59"/>
-      <c r="G101" s="59"/>
-      <c r="H101" s="59"/>
-      <c r="I101" s="59"/>
-      <c r="J101" s="60"/>
+      <c r="C101" s="67"/>
+      <c r="D101" s="67"/>
+      <c r="E101" s="67"/>
+      <c r="F101" s="67"/>
+      <c r="G101" s="67"/>
+      <c r="H101" s="67"/>
+      <c r="I101" s="67"/>
+      <c r="J101" s="68"/>
       <c r="K101" s="46"/>
     </row>
     <row r="102" spans="1:11" ht="12" customHeight="1">
@@ -19844,7 +19934,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="24">
+    <row r="124" spans="1:11">
       <c r="A124" s="1" t="s">
         <v>36</v>
       </c>
@@ -19871,17 +19961,17 @@
     </row>
     <row r="125" spans="1:11" ht="12" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="58" t="s">
+      <c r="B125" s="66" t="s">
         <v>1820</v>
       </c>
-      <c r="C125" s="59"/>
-      <c r="D125" s="59"/>
-      <c r="E125" s="59"/>
-      <c r="F125" s="59"/>
-      <c r="G125" s="59"/>
-      <c r="H125" s="59"/>
-      <c r="I125" s="59"/>
-      <c r="J125" s="60"/>
+      <c r="C125" s="67"/>
+      <c r="D125" s="67"/>
+      <c r="E125" s="67"/>
+      <c r="F125" s="67"/>
+      <c r="G125" s="67"/>
+      <c r="H125" s="67"/>
+      <c r="I125" s="67"/>
+      <c r="J125" s="68"/>
       <c r="K125" s="46"/>
     </row>
     <row r="126" spans="1:11" ht="36">
@@ -20400,17 +20490,17 @@
     </row>
     <row r="149" spans="1:11" ht="12" customHeight="1">
       <c r="A149" s="1"/>
-      <c r="B149" s="58" t="s">
+      <c r="B149" s="66" t="s">
         <v>1822</v>
       </c>
-      <c r="C149" s="59"/>
-      <c r="D149" s="59"/>
-      <c r="E149" s="59"/>
-      <c r="F149" s="59"/>
-      <c r="G149" s="59"/>
-      <c r="H149" s="59"/>
-      <c r="I149" s="59"/>
-      <c r="J149" s="60"/>
+      <c r="C149" s="67"/>
+      <c r="D149" s="67"/>
+      <c r="E149" s="67"/>
+      <c r="F149" s="67"/>
+      <c r="G149" s="67"/>
+      <c r="H149" s="67"/>
+      <c r="I149" s="67"/>
+      <c r="J149" s="68"/>
       <c r="K149" s="46"/>
     </row>
     <row r="150" spans="1:11" ht="36">
@@ -20653,17 +20743,17 @@
     </row>
     <row r="161" spans="1:11" ht="24" customHeight="1">
       <c r="A161" s="1"/>
-      <c r="B161" s="58" t="s">
+      <c r="B161" s="66" t="s">
         <v>1824</v>
       </c>
-      <c r="C161" s="59"/>
-      <c r="D161" s="59"/>
-      <c r="E161" s="59"/>
-      <c r="F161" s="59"/>
-      <c r="G161" s="59"/>
-      <c r="H161" s="59"/>
-      <c r="I161" s="59"/>
-      <c r="J161" s="60"/>
+      <c r="C161" s="67"/>
+      <c r="D161" s="67"/>
+      <c r="E161" s="67"/>
+      <c r="F161" s="67"/>
+      <c r="G161" s="67"/>
+      <c r="H161" s="67"/>
+      <c r="I161" s="67"/>
+      <c r="J161" s="68"/>
       <c r="K161" s="46"/>
     </row>
     <row r="162" spans="1:11">
@@ -20835,17 +20925,17 @@
     </row>
     <row r="170" spans="1:11" ht="12" customHeight="1">
       <c r="A170" s="1"/>
-      <c r="B170" s="58" t="s">
+      <c r="B170" s="66" t="s">
         <v>1818</v>
       </c>
-      <c r="C170" s="59"/>
-      <c r="D170" s="59"/>
-      <c r="E170" s="59"/>
-      <c r="F170" s="59"/>
-      <c r="G170" s="59"/>
-      <c r="H170" s="59"/>
-      <c r="I170" s="59"/>
-      <c r="J170" s="60"/>
+      <c r="C170" s="67"/>
+      <c r="D170" s="67"/>
+      <c r="E170" s="67"/>
+      <c r="F170" s="67"/>
+      <c r="G170" s="67"/>
+      <c r="H170" s="67"/>
+      <c r="I170" s="67"/>
+      <c r="J170" s="68"/>
       <c r="K170" s="46"/>
     </row>
     <row r="171" spans="1:11" ht="36">
@@ -21523,17 +21613,17 @@
     </row>
     <row r="202" spans="1:11" ht="24" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="58" t="s">
+      <c r="B202" s="66" t="s">
         <v>1827</v>
       </c>
-      <c r="C202" s="59"/>
-      <c r="D202" s="59"/>
-      <c r="E202" s="59"/>
-      <c r="F202" s="59"/>
-      <c r="G202" s="59"/>
-      <c r="H202" s="59"/>
-      <c r="I202" s="59"/>
-      <c r="J202" s="60"/>
+      <c r="C202" s="67"/>
+      <c r="D202" s="67"/>
+      <c r="E202" s="67"/>
+      <c r="F202" s="67"/>
+      <c r="G202" s="67"/>
+      <c r="H202" s="67"/>
+      <c r="I202" s="67"/>
+      <c r="J202" s="68"/>
       <c r="K202" s="46"/>
     </row>
     <row r="203" spans="1:11" ht="12" customHeight="1">
@@ -30699,17 +30789,17 @@
     </row>
     <row r="620" spans="1:11" ht="24" customHeight="1">
       <c r="A620" s="1"/>
-      <c r="B620" s="58" t="s">
+      <c r="B620" s="66" t="s">
         <v>1829</v>
       </c>
-      <c r="C620" s="59"/>
-      <c r="D620" s="59"/>
-      <c r="E620" s="59"/>
-      <c r="F620" s="59"/>
-      <c r="G620" s="59"/>
-      <c r="H620" s="59"/>
-      <c r="I620" s="59"/>
-      <c r="J620" s="60"/>
+      <c r="C620" s="67"/>
+      <c r="D620" s="67"/>
+      <c r="E620" s="67"/>
+      <c r="F620" s="67"/>
+      <c r="G620" s="67"/>
+      <c r="H620" s="67"/>
+      <c r="I620" s="67"/>
+      <c r="J620" s="68"/>
       <c r="K620" s="46"/>
     </row>
     <row r="621" spans="1:11" ht="12" customHeight="1">
@@ -39897,17 +39987,17 @@
     </row>
     <row r="1039" spans="1:11" ht="24" customHeight="1">
       <c r="A1039" s="1"/>
-      <c r="B1039" s="58" t="s">
+      <c r="B1039" s="66" t="s">
         <v>1831</v>
       </c>
-      <c r="C1039" s="59"/>
-      <c r="D1039" s="59"/>
-      <c r="E1039" s="59"/>
-      <c r="F1039" s="59"/>
-      <c r="G1039" s="59"/>
-      <c r="H1039" s="59"/>
-      <c r="I1039" s="59"/>
-      <c r="J1039" s="60"/>
+      <c r="C1039" s="67"/>
+      <c r="D1039" s="67"/>
+      <c r="E1039" s="67"/>
+      <c r="F1039" s="67"/>
+      <c r="G1039" s="67"/>
+      <c r="H1039" s="67"/>
+      <c r="I1039" s="67"/>
+      <c r="J1039" s="68"/>
       <c r="K1039" s="46"/>
     </row>
     <row r="1040" spans="1:11" ht="12" customHeight="1">
@@ -49134,14 +49224,14 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="1461" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1461" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1461" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B1461" s="140" t="s">
+      <c r="B1461" s="58" t="s">
         <v>2374</v>
       </c>
-      <c r="C1461" s="141"/>
+      <c r="C1461" s="59"/>
       <c r="D1461" s="53" t="s">
         <v>2358</v>
       </c>
@@ -49149,32 +49239,32 @@
       <c r="F1461" s="52">
         <v>3</v>
       </c>
-      <c r="G1461" s="140" t="s">
+      <c r="G1461" s="58" t="s">
         <v>2359</v>
       </c>
-      <c r="H1461" s="141"/>
-      <c r="I1461" s="140"/>
-      <c r="J1461" s="141"/>
-      <c r="K1461" s="142" t="s">
+      <c r="H1461" s="59"/>
+      <c r="I1461" s="58"/>
+      <c r="J1461" s="59"/>
+      <c r="K1461" s="60" t="s">
         <v>2360</v>
       </c>
     </row>
-    <row r="1462" spans="1:11" s="143" customFormat="1" ht="57" customHeight="1">
+    <row r="1462" spans="1:11" s="61" customFormat="1" ht="57" customHeight="1">
       <c r="A1462" s="51"/>
-      <c r="B1462" s="144" t="s">
+      <c r="B1462" s="62" t="s">
         <v>2361</v>
       </c>
-      <c r="C1462" s="145"/>
-      <c r="D1462" s="145"/>
-      <c r="E1462" s="145"/>
-      <c r="F1462" s="145"/>
-      <c r="G1462" s="145"/>
-      <c r="H1462" s="145"/>
-      <c r="I1462" s="145"/>
-      <c r="J1462" s="146"/>
-      <c r="K1462" s="142"/>
-    </row>
-    <row r="1463" spans="1:11" s="143" customFormat="1" ht="42.75">
+      <c r="C1462" s="63"/>
+      <c r="D1462" s="63"/>
+      <c r="E1462" s="63"/>
+      <c r="F1462" s="63"/>
+      <c r="G1462" s="63"/>
+      <c r="H1462" s="63"/>
+      <c r="I1462" s="63"/>
+      <c r="J1462" s="64"/>
+      <c r="K1462" s="60"/>
+    </row>
+    <row r="1463" spans="1:11" s="61" customFormat="1" ht="42.75">
       <c r="A1463" s="51"/>
       <c r="B1463" s="52" t="s">
         <v>37</v>
@@ -49193,11 +49283,11 @@
       <c r="H1463" s="54"/>
       <c r="I1463" s="54"/>
       <c r="J1463" s="55"/>
-      <c r="K1463" s="142" t="s">
+      <c r="K1463" s="60" t="s">
         <v>1844</v>
       </c>
     </row>
-    <row r="1464" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1464" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1464" s="51"/>
       <c r="B1464" s="52" t="s">
         <v>37</v>
@@ -49216,11 +49306,11 @@
       <c r="H1464" s="54"/>
       <c r="I1464" s="54"/>
       <c r="J1464" s="55"/>
-      <c r="K1464" s="142" t="s">
+      <c r="K1464" s="60" t="s">
         <v>1925</v>
       </c>
     </row>
-    <row r="1465" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1465" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1465" s="51"/>
       <c r="B1465" s="52" t="s">
         <v>37</v>
@@ -49239,11 +49329,11 @@
       <c r="H1465" s="54"/>
       <c r="I1465" s="54"/>
       <c r="J1465" s="55"/>
-      <c r="K1465" s="142" t="s">
+      <c r="K1465" s="60" t="s">
         <v>2366</v>
       </c>
     </row>
-    <row r="1466" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1466" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1466" s="51"/>
       <c r="B1466" s="52" t="s">
         <v>37</v>
@@ -49262,11 +49352,11 @@
       <c r="H1466" s="54"/>
       <c r="I1466" s="54"/>
       <c r="J1466" s="55"/>
-      <c r="K1466" s="142" t="s">
+      <c r="K1466" s="60" t="s">
         <v>2376</v>
       </c>
     </row>
-    <row r="1467" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1467" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1467" s="51"/>
       <c r="B1467" s="52" t="s">
         <v>37</v>
@@ -49289,11 +49379,11 @@
       <c r="H1467" s="54"/>
       <c r="I1467" s="54"/>
       <c r="J1467" s="55"/>
-      <c r="K1467" s="142" t="s">
+      <c r="K1467" s="60" t="s">
         <v>2369</v>
       </c>
     </row>
-    <row r="1468" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1468" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1468" s="51"/>
       <c r="B1468" s="52" t="s">
         <v>37</v>
@@ -49314,11 +49404,11 @@
       <c r="H1468" s="54"/>
       <c r="I1468" s="54"/>
       <c r="J1468" s="55"/>
-      <c r="K1468" s="142" t="s">
+      <c r="K1468" s="60" t="s">
         <v>2372</v>
       </c>
     </row>
-    <row r="1469" spans="1:11" s="143" customFormat="1" ht="14.25">
+    <row r="1469" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A1469" s="51"/>
       <c r="B1469" s="52" t="s">
         <v>37</v>
@@ -49337,12 +49427,17 @@
       <c r="H1469" s="54"/>
       <c r="I1469" s="54"/>
       <c r="J1469" s="55"/>
-      <c r="K1469" s="142" t="s">
+      <c r="K1469" s="60" t="s">
         <v>1925</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B620:J620"/>
+    <mergeCell ref="B1039:J1039"/>
+    <mergeCell ref="B170:J170"/>
+    <mergeCell ref="B161:J161"/>
+    <mergeCell ref="B149:J149"/>
     <mergeCell ref="B1462:J1462"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B7:J7"/>
@@ -49359,11 +49454,6 @@
     <mergeCell ref="B101:J101"/>
     <mergeCell ref="B125:J125"/>
     <mergeCell ref="B202:J202"/>
-    <mergeCell ref="B620:J620"/>
-    <mergeCell ref="B1039:J1039"/>
-    <mergeCell ref="B170:J170"/>
-    <mergeCell ref="B161:J161"/>
-    <mergeCell ref="B149:J149"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -49422,17 +49512,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11">
@@ -49491,7 +49581,7 @@
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K623"/>
+  <dimension ref="A1:K637"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="9" customWidth="1"/>
@@ -49534,17 +49624,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:11">
@@ -49588,15 +49678,15 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="68"/>
       <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:11">
@@ -49678,17 +49768,17 @@
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="66" t="s">
         <v>1832</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="60"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="68"/>
       <c r="K14" s="46"/>
     </row>
     <row r="15" spans="1:11" ht="36">
@@ -50057,17 +50147,17 @@
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="66" t="s">
         <v>1833</v>
       </c>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="63"/>
+      <c r="C32" s="145"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="145"/>
+      <c r="G32" s="145"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="146"/>
       <c r="K32" s="46"/>
     </row>
     <row r="33" spans="1:11" ht="24">
@@ -50449,17 +50539,17 @@
     </row>
     <row r="50" spans="1:11" ht="12" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="66" t="s">
         <v>1835</v>
       </c>
-      <c r="C50" s="62"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="62"/>
-      <c r="F50" s="62"/>
-      <c r="G50" s="62"/>
-      <c r="H50" s="62"/>
-      <c r="I50" s="62"/>
-      <c r="J50" s="63"/>
+      <c r="C50" s="145"/>
+      <c r="D50" s="145"/>
+      <c r="E50" s="145"/>
+      <c r="F50" s="145"/>
+      <c r="G50" s="145"/>
+      <c r="H50" s="145"/>
+      <c r="I50" s="145"/>
+      <c r="J50" s="146"/>
       <c r="K50" s="46"/>
     </row>
     <row r="51" spans="1:11" ht="36">
@@ -51621,17 +51711,17 @@
     </row>
     <row r="102" spans="1:11" ht="24" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="58" t="s">
+      <c r="B102" s="66" t="s">
         <v>1840</v>
       </c>
-      <c r="C102" s="59"/>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
-      <c r="F102" s="59"/>
-      <c r="G102" s="59"/>
-      <c r="H102" s="59"/>
-      <c r="I102" s="59"/>
-      <c r="J102" s="60"/>
+      <c r="C102" s="67"/>
+      <c r="D102" s="67"/>
+      <c r="E102" s="67"/>
+      <c r="F102" s="67"/>
+      <c r="G102" s="67"/>
+      <c r="H102" s="67"/>
+      <c r="I102" s="67"/>
+      <c r="J102" s="68"/>
       <c r="K102" s="46"/>
     </row>
     <row r="103" spans="1:11" ht="36">
@@ -52438,17 +52528,17 @@
     </row>
     <row r="139" spans="1:11" ht="24" customHeight="1">
       <c r="A139" s="1"/>
-      <c r="B139" s="58" t="s">
+      <c r="B139" s="66" t="s">
         <v>1838</v>
       </c>
-      <c r="C139" s="59"/>
-      <c r="D139" s="59"/>
-      <c r="E139" s="59"/>
-      <c r="F139" s="59"/>
-      <c r="G139" s="59"/>
-      <c r="H139" s="59"/>
-      <c r="I139" s="59"/>
-      <c r="J139" s="60"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="67"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="67"/>
+      <c r="H139" s="67"/>
+      <c r="I139" s="67"/>
+      <c r="J139" s="68"/>
       <c r="K139" s="46"/>
     </row>
     <row r="140" spans="1:11" ht="24">
@@ -63589,8 +63679,285 @@
       <c r="J623" s="55"/>
       <c r="K623" s="56"/>
     </row>
+    <row r="626" spans="1:11" s="61" customFormat="1" ht="12" customHeight="1">
+      <c r="A626" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B626" s="58" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C626" s="59"/>
+      <c r="D626" s="53" t="s">
+        <v>2398</v>
+      </c>
+      <c r="E626" s="55"/>
+      <c r="F626" s="52">
+        <v>3</v>
+      </c>
+      <c r="G626" s="58" t="s">
+        <v>2377</v>
+      </c>
+      <c r="H626" s="59"/>
+      <c r="I626" s="58"/>
+      <c r="J626" s="59"/>
+      <c r="K626" s="60" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="627" spans="1:11" s="61" customFormat="1" ht="14.25">
+      <c r="A627" s="51"/>
+      <c r="B627" s="147" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C627" s="148"/>
+      <c r="D627" s="148"/>
+      <c r="E627" s="148"/>
+      <c r="F627" s="148"/>
+      <c r="G627" s="148"/>
+      <c r="H627" s="148"/>
+      <c r="I627" s="148"/>
+      <c r="J627" s="149"/>
+      <c r="K627" s="60"/>
+    </row>
+    <row r="628" spans="1:11" s="61" customFormat="1" ht="12" customHeight="1">
+      <c r="A628" s="51"/>
+      <c r="B628" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C628" s="52" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D628" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E628" s="52"/>
+      <c r="F628" s="52"/>
+      <c r="G628" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="H628" s="54"/>
+      <c r="I628" s="54"/>
+      <c r="J628" s="55"/>
+      <c r="K628" s="60" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="629" spans="1:11" s="61" customFormat="1" ht="12" customHeight="1">
+      <c r="A629" s="51"/>
+      <c r="B629" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C629" s="52" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D629" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E629" s="52"/>
+      <c r="F629" s="52"/>
+      <c r="G629" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="H629" s="54"/>
+      <c r="I629" s="54"/>
+      <c r="J629" s="55"/>
+      <c r="K629" s="60" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="630" spans="1:11" s="61" customFormat="1" ht="12" customHeight="1">
+      <c r="A630" s="51"/>
+      <c r="B630" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C630" s="52" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D630" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E630" s="52"/>
+      <c r="F630" s="52"/>
+      <c r="G630" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="H630" s="54"/>
+      <c r="I630" s="54"/>
+      <c r="J630" s="55"/>
+      <c r="K630" s="60" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="631" spans="1:11" s="61" customFormat="1" ht="12" customHeight="1">
+      <c r="A631" s="51"/>
+      <c r="B631" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C631" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D631" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="E631" s="52"/>
+      <c r="F631" s="52"/>
+      <c r="G631" s="53" t="s">
+        <v>2375</v>
+      </c>
+      <c r="H631" s="54"/>
+      <c r="I631" s="54"/>
+      <c r="J631" s="55"/>
+      <c r="K631" s="60" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="632" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A632" s="51"/>
+      <c r="B632" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C632" s="52" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D632" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E632" s="52">
+        <v>10</v>
+      </c>
+      <c r="F632" s="52">
+        <v>10</v>
+      </c>
+      <c r="G632" s="53" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H632" s="54"/>
+      <c r="I632" s="54"/>
+      <c r="J632" s="55"/>
+      <c r="K632" s="60" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="633" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A633" s="51"/>
+      <c r="B633" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C633" s="52" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D633" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E633" s="52">
+        <v>20</v>
+      </c>
+      <c r="F633" s="52"/>
+      <c r="G633" s="53" t="s">
+        <v>2383</v>
+      </c>
+      <c r="H633" s="54"/>
+      <c r="I633" s="54"/>
+      <c r="J633" s="55"/>
+      <c r="K633" s="60" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="634" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A634" s="51"/>
+      <c r="B634" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C634" s="52" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D634" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E634" s="52"/>
+      <c r="F634" s="52"/>
+      <c r="G634" s="53" t="s">
+        <v>2385</v>
+      </c>
+      <c r="H634" s="54"/>
+      <c r="I634" s="54"/>
+      <c r="J634" s="55"/>
+      <c r="K634" s="60" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="635" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A635" s="51"/>
+      <c r="B635" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C635" s="52" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D635" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E635" s="52"/>
+      <c r="F635" s="52"/>
+      <c r="G635" s="53" t="s">
+        <v>2388</v>
+      </c>
+      <c r="H635" s="54"/>
+      <c r="I635" s="54"/>
+      <c r="J635" s="55"/>
+      <c r="K635" s="60" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="636" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A636" s="51"/>
+      <c r="B636" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C636" s="52" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D636" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E636" s="52"/>
+      <c r="F636" s="52"/>
+      <c r="G636" s="53" t="s">
+        <v>2391</v>
+      </c>
+      <c r="H636" s="54"/>
+      <c r="I636" s="54"/>
+      <c r="J636" s="55"/>
+      <c r="K636" s="60" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="637" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A637" s="51"/>
+      <c r="B637" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C637" s="52" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D637" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E637" s="52"/>
+      <c r="F637" s="52"/>
+      <c r="G637" s="53" t="s">
+        <v>2394</v>
+      </c>
+      <c r="H637" s="54"/>
+      <c r="I637" s="54"/>
+      <c r="J637" s="55"/>
+      <c r="K637" s="60" t="s">
+        <v>2395</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B627:J627"/>
     <mergeCell ref="B139:J139"/>
     <mergeCell ref="B102:J102"/>
     <mergeCell ref="B3:J3"/>

--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118A0C4E-518D-4E30-BB48-8F4F6EF105B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB46C104-3E5F-4D9D-9077-4E76DB07C7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10239" uniqueCount="2399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10244" uniqueCount="2401">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -11163,6 +11163,12 @@
   </si>
   <si>
     <t>受注登録用の取引先</t>
+  </si>
+  <si>
+    <t>売上担当者</t>
+  </si>
+  <si>
+    <t>Sale user cd.</t>
   </si>
 </sst>
 </file>
@@ -13303,17 +13309,14 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="3" xfId="230" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -13322,6 +13325,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="3" xfId="230" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="229" applyFont="1" applyAlignment="1">
@@ -13377,102 +13389,6 @@
     </xf>
     <xf numFmtId="168" fontId="53" fillId="0" borderId="24" xfId="229" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="29" borderId="42" xfId="228" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13544,6 +13460,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13552,19 +13477,100 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="25" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="38" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="41" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="39" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="41" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="37" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="34" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="227" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="232" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14996,130 +15002,130 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:47">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="73" t="s">
         <v>390</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="73"/>
-      <c r="AF3" s="73"/>
-      <c r="AG3" s="73"/>
-      <c r="AH3" s="73"/>
-      <c r="AI3" s="74"/>
-      <c r="AJ3" s="75" t="s">
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="AD3" s="74"/>
+      <c r="AE3" s="75"/>
+      <c r="AF3" s="75"/>
+      <c r="AG3" s="75"/>
+      <c r="AH3" s="75"/>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="77" t="s">
         <v>391</v>
       </c>
-      <c r="AK3" s="75"/>
-      <c r="AL3" s="75"/>
-      <c r="AM3" s="75"/>
-      <c r="AN3" s="75"/>
-      <c r="AO3" s="75"/>
-      <c r="AP3" s="76" t="s">
+      <c r="AK3" s="77"/>
+      <c r="AL3" s="77"/>
+      <c r="AM3" s="77"/>
+      <c r="AN3" s="77"/>
+      <c r="AO3" s="77"/>
+      <c r="AP3" s="78" t="s">
         <v>392</v>
       </c>
-      <c r="AQ3" s="77"/>
-      <c r="AR3" s="77"/>
-      <c r="AS3" s="77"/>
-      <c r="AT3" s="77"/>
-      <c r="AU3" s="78"/>
+      <c r="AQ3" s="79"/>
+      <c r="AR3" s="79"/>
+      <c r="AS3" s="79"/>
+      <c r="AT3" s="79"/>
+      <c r="AU3" s="80"/>
     </row>
     <row r="4" spans="2:47">
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="AD4" s="73"/>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="73"/>
-      <c r="AH4" s="73"/>
-      <c r="AI4" s="74"/>
-      <c r="AJ4" s="75"/>
-      <c r="AK4" s="75"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
-      <c r="AN4" s="75"/>
-      <c r="AO4" s="75"/>
-      <c r="AP4" s="76"/>
-      <c r="AQ4" s="77"/>
-      <c r="AR4" s="77"/>
-      <c r="AS4" s="77"/>
-      <c r="AT4" s="77"/>
-      <c r="AU4" s="78"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="AD4" s="75"/>
+      <c r="AE4" s="75"/>
+      <c r="AF4" s="75"/>
+      <c r="AG4" s="75"/>
+      <c r="AH4" s="75"/>
+      <c r="AI4" s="76"/>
+      <c r="AJ4" s="77"/>
+      <c r="AK4" s="77"/>
+      <c r="AL4" s="77"/>
+      <c r="AM4" s="77"/>
+      <c r="AN4" s="77"/>
+      <c r="AO4" s="77"/>
+      <c r="AP4" s="78"/>
+      <c r="AQ4" s="79"/>
+      <c r="AR4" s="79"/>
+      <c r="AS4" s="79"/>
+      <c r="AT4" s="79"/>
+      <c r="AU4" s="80"/>
     </row>
     <row r="5" spans="2:47">
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="AD5" s="79"/>
-      <c r="AE5" s="80"/>
-      <c r="AF5" s="80"/>
-      <c r="AG5" s="80"/>
-      <c r="AH5" s="80"/>
-      <c r="AI5" s="81"/>
-      <c r="AJ5" s="82" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="AD5" s="81"/>
+      <c r="AE5" s="82"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82"/>
+      <c r="AH5" s="82"/>
+      <c r="AI5" s="83"/>
+      <c r="AJ5" s="84" t="s">
         <v>1841</v>
       </c>
-      <c r="AK5" s="82"/>
-      <c r="AL5" s="82"/>
-      <c r="AM5" s="82"/>
-      <c r="AN5" s="82"/>
-      <c r="AO5" s="82"/>
-      <c r="AP5" s="83" t="s">
+      <c r="AK5" s="84"/>
+      <c r="AL5" s="84"/>
+      <c r="AM5" s="84"/>
+      <c r="AN5" s="84"/>
+      <c r="AO5" s="84"/>
+      <c r="AP5" s="85" t="s">
         <v>2337</v>
       </c>
-      <c r="AQ5" s="84"/>
-      <c r="AR5" s="84"/>
-      <c r="AS5" s="84"/>
-      <c r="AT5" s="84"/>
-      <c r="AU5" s="85"/>
+      <c r="AQ5" s="86"/>
+      <c r="AR5" s="86"/>
+      <c r="AS5" s="86"/>
+      <c r="AT5" s="86"/>
+      <c r="AU5" s="87"/>
     </row>
     <row r="6" spans="2:47">
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="AD6" s="80"/>
-      <c r="AE6" s="80"/>
-      <c r="AF6" s="80"/>
-      <c r="AG6" s="80"/>
-      <c r="AH6" s="80"/>
-      <c r="AI6" s="81"/>
-      <c r="AJ6" s="82"/>
-      <c r="AK6" s="82"/>
-      <c r="AL6" s="82"/>
-      <c r="AM6" s="82"/>
-      <c r="AN6" s="82"/>
-      <c r="AO6" s="82"/>
-      <c r="AP6" s="86"/>
-      <c r="AQ6" s="84"/>
-      <c r="AR6" s="84"/>
-      <c r="AS6" s="84"/>
-      <c r="AT6" s="84"/>
-      <c r="AU6" s="85"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="AD6" s="82"/>
+      <c r="AE6" s="82"/>
+      <c r="AF6" s="82"/>
+      <c r="AG6" s="82"/>
+      <c r="AH6" s="82"/>
+      <c r="AI6" s="83"/>
+      <c r="AJ6" s="84"/>
+      <c r="AK6" s="84"/>
+      <c r="AL6" s="84"/>
+      <c r="AM6" s="84"/>
+      <c r="AN6" s="84"/>
+      <c r="AO6" s="84"/>
+      <c r="AP6" s="88"/>
+      <c r="AQ6" s="86"/>
+      <c r="AR6" s="86"/>
+      <c r="AS6" s="86"/>
+      <c r="AT6" s="86"/>
+      <c r="AU6" s="87"/>
     </row>
     <row r="7" spans="2:47" ht="24">
       <c r="B7" s="33" t="s">
@@ -15141,122 +15147,122 @@
       </c>
     </row>
     <row r="15" spans="2:47">
-      <c r="M15" s="69" t="s">
+      <c r="M15" s="71" t="s">
         <v>393</v>
       </c>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="70"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="70"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="70"/>
-      <c r="AC15" s="70"/>
-      <c r="AD15" s="70"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="70"/>
-      <c r="AL15" s="70"/>
-      <c r="AM15" s="70"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72"/>
+      <c r="X15" s="72"/>
+      <c r="Y15" s="72"/>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="72"/>
+      <c r="AB15" s="72"/>
+      <c r="AC15" s="72"/>
+      <c r="AD15" s="72"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="72"/>
+      <c r="AG15" s="72"/>
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
+      <c r="AJ15" s="72"/>
+      <c r="AK15" s="72"/>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="72"/>
     </row>
     <row r="16" spans="2:47">
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="70"/>
-      <c r="T16" s="70"/>
-      <c r="U16" s="70"/>
-      <c r="V16" s="70"/>
-      <c r="W16" s="70"/>
-      <c r="X16" s="70"/>
-      <c r="Y16" s="70"/>
-      <c r="Z16" s="70"/>
-      <c r="AA16" s="70"/>
-      <c r="AB16" s="70"/>
-      <c r="AC16" s="70"/>
-      <c r="AD16" s="70"/>
-      <c r="AE16" s="70"/>
-      <c r="AF16" s="70"/>
-      <c r="AG16" s="70"/>
-      <c r="AH16" s="70"/>
-      <c r="AI16" s="70"/>
-      <c r="AJ16" s="70"/>
-      <c r="AK16" s="70"/>
-      <c r="AL16" s="70"/>
-      <c r="AM16" s="70"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="72"/>
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="72"/>
+      <c r="AD16" s="72"/>
+      <c r="AE16" s="72"/>
+      <c r="AF16" s="72"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="72"/>
+      <c r="AL16" s="72"/>
+      <c r="AM16" s="72"/>
     </row>
     <row r="17" spans="13:39">
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
-      <c r="AC17" s="70"/>
-      <c r="AD17" s="70"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="70"/>
-      <c r="AI17" s="70"/>
-      <c r="AJ17" s="70"/>
-      <c r="AK17" s="70"/>
-      <c r="AL17" s="70"/>
-      <c r="AM17" s="70"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="72"/>
+      <c r="X17" s="72"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="72"/>
+      <c r="AB17" s="72"/>
+      <c r="AC17" s="72"/>
+      <c r="AD17" s="72"/>
+      <c r="AE17" s="72"/>
+      <c r="AF17" s="72"/>
+      <c r="AG17" s="72"/>
+      <c r="AH17" s="72"/>
+      <c r="AI17" s="72"/>
+      <c r="AJ17" s="72"/>
+      <c r="AK17" s="72"/>
+      <c r="AL17" s="72"/>
+      <c r="AM17" s="72"/>
     </row>
     <row r="18" spans="13:39">
-      <c r="M18" s="70"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
-      <c r="R18" s="70"/>
-      <c r="S18" s="70"/>
-      <c r="T18" s="70"/>
-      <c r="U18" s="70"/>
-      <c r="V18" s="70"/>
-      <c r="W18" s="70"/>
-      <c r="X18" s="70"/>
-      <c r="Y18" s="70"/>
-      <c r="Z18" s="70"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="70"/>
-      <c r="AC18" s="70"/>
-      <c r="AD18" s="70"/>
-      <c r="AE18" s="70"/>
-      <c r="AF18" s="70"/>
-      <c r="AG18" s="70"/>
-      <c r="AH18" s="70"/>
-      <c r="AI18" s="70"/>
-      <c r="AJ18" s="70"/>
-      <c r="AK18" s="70"/>
-      <c r="AL18" s="70"/>
-      <c r="AM18" s="70"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="72"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="72"/>
+      <c r="AA18" s="72"/>
+      <c r="AB18" s="72"/>
+      <c r="AC18" s="72"/>
+      <c r="AD18" s="72"/>
+      <c r="AE18" s="72"/>
+      <c r="AF18" s="72"/>
+      <c r="AG18" s="72"/>
+      <c r="AH18" s="72"/>
+      <c r="AI18" s="72"/>
+      <c r="AJ18" s="72"/>
+      <c r="AK18" s="72"/>
+      <c r="AL18" s="72"/>
+      <c r="AM18" s="72"/>
     </row>
     <row r="26" spans="13:39" ht="15.75" customHeight="1"/>
     <row r="27" spans="13:39" ht="15.75" customHeight="1"/>
@@ -15296,126 +15302,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="34" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="123" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
-      <c r="AC1" s="124"/>
-      <c r="AD1" s="124"/>
-      <c r="AE1" s="124"/>
-      <c r="AF1" s="124"/>
-      <c r="AG1" s="124"/>
-      <c r="AH1" s="124"/>
-      <c r="AI1" s="124"/>
-      <c r="AJ1" s="124"/>
-      <c r="AK1" s="124"/>
-      <c r="AL1" s="124"/>
-      <c r="AM1" s="124"/>
-      <c r="AN1" s="124"/>
-      <c r="AO1" s="124"/>
-      <c r="AP1" s="124"/>
-      <c r="AQ1" s="124"/>
-      <c r="AR1" s="124"/>
-      <c r="AS1" s="124"/>
-      <c r="AT1" s="124"/>
-      <c r="AU1" s="124"/>
-      <c r="AV1" s="124"/>
-      <c r="AW1" s="124"/>
-      <c r="AX1" s="125"/>
-      <c r="AY1" s="119" t="s">
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
+      <c r="AA1" s="94"/>
+      <c r="AB1" s="94"/>
+      <c r="AC1" s="94"/>
+      <c r="AD1" s="94"/>
+      <c r="AE1" s="94"/>
+      <c r="AF1" s="94"/>
+      <c r="AG1" s="94"/>
+      <c r="AH1" s="94"/>
+      <c r="AI1" s="94"/>
+      <c r="AJ1" s="94"/>
+      <c r="AK1" s="94"/>
+      <c r="AL1" s="94"/>
+      <c r="AM1" s="94"/>
+      <c r="AN1" s="94"/>
+      <c r="AO1" s="94"/>
+      <c r="AP1" s="94"/>
+      <c r="AQ1" s="94"/>
+      <c r="AR1" s="94"/>
+      <c r="AS1" s="94"/>
+      <c r="AT1" s="94"/>
+      <c r="AU1" s="94"/>
+      <c r="AV1" s="94"/>
+      <c r="AW1" s="94"/>
+      <c r="AX1" s="95"/>
+      <c r="AY1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="119"/>
-      <c r="BA1" s="119"/>
-      <c r="BB1" s="119"/>
-      <c r="BC1" s="120"/>
+      <c r="AZ1" s="89"/>
+      <c r="BA1" s="89"/>
+      <c r="BB1" s="89"/>
+      <c r="BC1" s="90"/>
     </row>
     <row r="2" spans="1:55" s="34" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="137"/>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="127"/>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
-      <c r="AA2" s="127"/>
-      <c r="AB2" s="127"/>
-      <c r="AC2" s="127"/>
-      <c r="AD2" s="127"/>
-      <c r="AE2" s="127"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="127"/>
-      <c r="AI2" s="127"/>
-      <c r="AJ2" s="127"/>
-      <c r="AK2" s="127"/>
-      <c r="AL2" s="127"/>
-      <c r="AM2" s="127"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="127"/>
-      <c r="AT2" s="127"/>
-      <c r="AU2" s="127"/>
-      <c r="AV2" s="127"/>
-      <c r="AW2" s="127"/>
-      <c r="AX2" s="128"/>
-      <c r="AY2" s="121" t="s">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="97"/>
+      <c r="Y2" s="97"/>
+      <c r="Z2" s="97"/>
+      <c r="AA2" s="97"/>
+      <c r="AB2" s="97"/>
+      <c r="AC2" s="97"/>
+      <c r="AD2" s="97"/>
+      <c r="AE2" s="97"/>
+      <c r="AF2" s="97"/>
+      <c r="AG2" s="97"/>
+      <c r="AH2" s="97"/>
+      <c r="AI2" s="97"/>
+      <c r="AJ2" s="97"/>
+      <c r="AK2" s="97"/>
+      <c r="AL2" s="97"/>
+      <c r="AM2" s="97"/>
+      <c r="AN2" s="97"/>
+      <c r="AO2" s="97"/>
+      <c r="AP2" s="97"/>
+      <c r="AQ2" s="97"/>
+      <c r="AR2" s="97"/>
+      <c r="AS2" s="97"/>
+      <c r="AT2" s="97"/>
+      <c r="AU2" s="97"/>
+      <c r="AV2" s="97"/>
+      <c r="AW2" s="97"/>
+      <c r="AX2" s="98"/>
+      <c r="AY2" s="91" t="s">
         <v>1841</v>
       </c>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
-      <c r="BB2" s="121"/>
-      <c r="BC2" s="122"/>
+      <c r="AZ2" s="91"/>
+      <c r="BA2" s="91"/>
+      <c r="BB2" s="91"/>
+      <c r="BC2" s="92"/>
     </row>
     <row r="3" spans="1:55" s="34" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A3" s="35"/>
@@ -15467,1903 +15473,1982 @@
       <c r="A4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="129" t="s">
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="139"/>
-      <c r="K4" s="139"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="139"/>
-      <c r="N4" s="139"/>
-      <c r="O4" s="139"/>
-      <c r="P4" s="139"/>
-      <c r="Q4" s="139"/>
-      <c r="R4" s="139"/>
-      <c r="S4" s="139"/>
-      <c r="T4" s="139"/>
-      <c r="U4" s="139"/>
-      <c r="V4" s="139"/>
-      <c r="W4" s="139"/>
-      <c r="X4" s="139"/>
-      <c r="Y4" s="139"/>
-      <c r="Z4" s="139"/>
-      <c r="AA4" s="139"/>
-      <c r="AB4" s="139"/>
-      <c r="AC4" s="139"/>
-      <c r="AD4" s="139"/>
-      <c r="AE4" s="139"/>
-      <c r="AF4" s="139"/>
-      <c r="AG4" s="139"/>
-      <c r="AH4" s="139"/>
-      <c r="AI4" s="139"/>
-      <c r="AJ4" s="139"/>
-      <c r="AK4" s="140"/>
-      <c r="AL4" s="140"/>
-      <c r="AM4" s="140"/>
-      <c r="AN4" s="141"/>
-      <c r="AO4" s="132" t="s">
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="109"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="109"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="109"/>
+      <c r="U4" s="109"/>
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109"/>
+      <c r="Z4" s="109"/>
+      <c r="AA4" s="109"/>
+      <c r="AB4" s="109"/>
+      <c r="AC4" s="109"/>
+      <c r="AD4" s="109"/>
+      <c r="AE4" s="109"/>
+      <c r="AF4" s="109"/>
+      <c r="AG4" s="109"/>
+      <c r="AH4" s="109"/>
+      <c r="AI4" s="109"/>
+      <c r="AJ4" s="109"/>
+      <c r="AK4" s="110"/>
+      <c r="AL4" s="110"/>
+      <c r="AM4" s="110"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="AP4" s="133"/>
-      <c r="AQ4" s="133"/>
-      <c r="AR4" s="133"/>
-      <c r="AS4" s="133"/>
-      <c r="AT4" s="133"/>
-      <c r="AU4" s="133"/>
-      <c r="AV4" s="133"/>
-      <c r="AW4" s="133"/>
-      <c r="AX4" s="133"/>
-      <c r="AY4" s="133"/>
-      <c r="AZ4" s="133"/>
-      <c r="BA4" s="133"/>
-      <c r="BB4" s="133"/>
-      <c r="BC4" s="134"/>
+      <c r="AP4" s="103"/>
+      <c r="AQ4" s="103"/>
+      <c r="AR4" s="103"/>
+      <c r="AS4" s="103"/>
+      <c r="AT4" s="103"/>
+      <c r="AU4" s="103"/>
+      <c r="AV4" s="103"/>
+      <c r="AW4" s="103"/>
+      <c r="AX4" s="103"/>
+      <c r="AY4" s="103"/>
+      <c r="AZ4" s="103"/>
+      <c r="BA4" s="103"/>
+      <c r="BB4" s="103"/>
+      <c r="BC4" s="104"/>
     </row>
     <row r="5" spans="1:55" ht="15" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>1803</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="98" t="s">
+      <c r="B5" s="137"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="99"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="100"/>
-      <c r="AL5" s="100"/>
-      <c r="AM5" s="100"/>
-      <c r="AN5" s="101"/>
-      <c r="AO5" s="115"/>
-      <c r="AP5" s="99"/>
-      <c r="AQ5" s="99"/>
-      <c r="AR5" s="99"/>
-      <c r="AS5" s="99"/>
-      <c r="AT5" s="99"/>
-      <c r="AU5" s="99"/>
-      <c r="AV5" s="99"/>
-      <c r="AW5" s="99"/>
-      <c r="AX5" s="99"/>
-      <c r="AY5" s="99"/>
-      <c r="AZ5" s="99"/>
-      <c r="BA5" s="99"/>
-      <c r="BB5" s="99"/>
-      <c r="BC5" s="116"/>
+      <c r="J5" s="135"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
+      <c r="M5" s="135"/>
+      <c r="N5" s="135"/>
+      <c r="O5" s="135"/>
+      <c r="P5" s="135"/>
+      <c r="Q5" s="135"/>
+      <c r="R5" s="135"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="135"/>
+      <c r="Z5" s="135"/>
+      <c r="AA5" s="135"/>
+      <c r="AB5" s="135"/>
+      <c r="AC5" s="135"/>
+      <c r="AD5" s="135"/>
+      <c r="AE5" s="135"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="140"/>
+      <c r="AL5" s="140"/>
+      <c r="AM5" s="140"/>
+      <c r="AN5" s="141"/>
+      <c r="AO5" s="134"/>
+      <c r="AP5" s="135"/>
+      <c r="AQ5" s="135"/>
+      <c r="AR5" s="135"/>
+      <c r="AS5" s="135"/>
+      <c r="AT5" s="135"/>
+      <c r="AU5" s="135"/>
+      <c r="AV5" s="135"/>
+      <c r="AW5" s="135"/>
+      <c r="AX5" s="135"/>
+      <c r="AY5" s="135"/>
+      <c r="AZ5" s="135"/>
+      <c r="BA5" s="135"/>
+      <c r="BB5" s="135"/>
+      <c r="BC5" s="136"/>
     </row>
     <row r="6" spans="1:55" ht="15" customHeight="1">
       <c r="A6" s="40" t="s">
         <v>2334</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="104" t="s">
+      <c r="B6" s="112"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="144" t="s">
         <v>2335</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="105"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="105"/>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="105"/>
-      <c r="S6" s="105"/>
-      <c r="T6" s="105"/>
-      <c r="U6" s="105"/>
-      <c r="V6" s="105"/>
-      <c r="W6" s="105"/>
-      <c r="X6" s="105"/>
-      <c r="Y6" s="105"/>
-      <c r="Z6" s="105"/>
-      <c r="AA6" s="105"/>
-      <c r="AB6" s="105"/>
-      <c r="AC6" s="105"/>
-      <c r="AD6" s="105"/>
-      <c r="AE6" s="105"/>
-      <c r="AF6" s="105"/>
-      <c r="AG6" s="105"/>
-      <c r="AH6" s="105"/>
-      <c r="AI6" s="105"/>
-      <c r="AJ6" s="105"/>
-      <c r="AK6" s="105"/>
-      <c r="AL6" s="105"/>
-      <c r="AM6" s="105"/>
-      <c r="AN6" s="106"/>
-      <c r="AO6" s="142" t="s">
+      <c r="J6" s="145"/>
+      <c r="K6" s="145"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="145"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
+      <c r="R6" s="145"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="145"/>
+      <c r="W6" s="145"/>
+      <c r="X6" s="145"/>
+      <c r="Y6" s="145"/>
+      <c r="Z6" s="145"/>
+      <c r="AA6" s="145"/>
+      <c r="AB6" s="145"/>
+      <c r="AC6" s="145"/>
+      <c r="AD6" s="145"/>
+      <c r="AE6" s="145"/>
+      <c r="AF6" s="145"/>
+      <c r="AG6" s="145"/>
+      <c r="AH6" s="145"/>
+      <c r="AI6" s="145"/>
+      <c r="AJ6" s="145"/>
+      <c r="AK6" s="145"/>
+      <c r="AL6" s="145"/>
+      <c r="AM6" s="145"/>
+      <c r="AN6" s="146"/>
+      <c r="AO6" s="115" t="s">
         <v>2336</v>
       </c>
-      <c r="AP6" s="143"/>
-      <c r="AQ6" s="143"/>
-      <c r="AR6" s="143"/>
-      <c r="AS6" s="143"/>
-      <c r="AT6" s="143"/>
-      <c r="AU6" s="143"/>
-      <c r="AV6" s="143"/>
-      <c r="AW6" s="143"/>
-      <c r="AX6" s="143"/>
-      <c r="AY6" s="143"/>
-      <c r="AZ6" s="143"/>
-      <c r="BA6" s="143"/>
-      <c r="BB6" s="143"/>
-      <c r="BC6" s="144"/>
+      <c r="AP6" s="116"/>
+      <c r="AQ6" s="116"/>
+      <c r="AR6" s="116"/>
+      <c r="AS6" s="116"/>
+      <c r="AT6" s="116"/>
+      <c r="AU6" s="116"/>
+      <c r="AV6" s="116"/>
+      <c r="AW6" s="116"/>
+      <c r="AX6" s="116"/>
+      <c r="AY6" s="116"/>
+      <c r="AZ6" s="116"/>
+      <c r="BA6" s="116"/>
+      <c r="BB6" s="116"/>
+      <c r="BC6" s="117"/>
     </row>
     <row r="7" spans="1:55" ht="15" customHeight="1">
       <c r="A7" s="40"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="88"/>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
-      <c r="S7" s="88"/>
-      <c r="T7" s="88"/>
-      <c r="U7" s="88"/>
-      <c r="V7" s="88"/>
-      <c r="W7" s="88"/>
-      <c r="X7" s="88"/>
-      <c r="Y7" s="88"/>
-      <c r="Z7" s="88"/>
-      <c r="AA7" s="88"/>
-      <c r="AB7" s="88"/>
-      <c r="AC7" s="88"/>
-      <c r="AD7" s="88"/>
-      <c r="AE7" s="88"/>
-      <c r="AF7" s="88"/>
-      <c r="AG7" s="88"/>
-      <c r="AH7" s="88"/>
-      <c r="AI7" s="88"/>
-      <c r="AJ7" s="88"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="92"/>
-      <c r="AO7" s="87"/>
-      <c r="AP7" s="88"/>
-      <c r="AQ7" s="88"/>
-      <c r="AR7" s="88"/>
-      <c r="AS7" s="88"/>
-      <c r="AT7" s="88"/>
-      <c r="AU7" s="88"/>
-      <c r="AV7" s="88"/>
-      <c r="AW7" s="88"/>
-      <c r="AX7" s="88"/>
-      <c r="AY7" s="88"/>
-      <c r="AZ7" s="88"/>
-      <c r="BA7" s="88"/>
-      <c r="BB7" s="88"/>
-      <c r="BC7" s="89"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="119"/>
+      <c r="S7" s="119"/>
+      <c r="T7" s="119"/>
+      <c r="U7" s="119"/>
+      <c r="V7" s="119"/>
+      <c r="W7" s="119"/>
+      <c r="X7" s="119"/>
+      <c r="Y7" s="119"/>
+      <c r="Z7" s="119"/>
+      <c r="AA7" s="119"/>
+      <c r="AB7" s="119"/>
+      <c r="AC7" s="119"/>
+      <c r="AD7" s="119"/>
+      <c r="AE7" s="119"/>
+      <c r="AF7" s="119"/>
+      <c r="AG7" s="119"/>
+      <c r="AH7" s="119"/>
+      <c r="AI7" s="119"/>
+      <c r="AJ7" s="119"/>
+      <c r="AK7" s="121"/>
+      <c r="AL7" s="121"/>
+      <c r="AM7" s="121"/>
+      <c r="AN7" s="122"/>
+      <c r="AO7" s="118"/>
+      <c r="AP7" s="119"/>
+      <c r="AQ7" s="119"/>
+      <c r="AR7" s="119"/>
+      <c r="AS7" s="119"/>
+      <c r="AT7" s="119"/>
+      <c r="AU7" s="119"/>
+      <c r="AV7" s="119"/>
+      <c r="AW7" s="119"/>
+      <c r="AX7" s="119"/>
+      <c r="AY7" s="119"/>
+      <c r="AZ7" s="119"/>
+      <c r="BA7" s="119"/>
+      <c r="BB7" s="119"/>
+      <c r="BC7" s="120"/>
     </row>
     <row r="8" spans="1:55" ht="15" customHeight="1">
       <c r="A8" s="40"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="88"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="88"/>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="88"/>
-      <c r="Y8" s="88"/>
-      <c r="Z8" s="88"/>
-      <c r="AA8" s="88"/>
-      <c r="AB8" s="88"/>
-      <c r="AC8" s="88"/>
-      <c r="AD8" s="88"/>
-      <c r="AE8" s="88"/>
-      <c r="AF8" s="88"/>
-      <c r="AG8" s="88"/>
-      <c r="AH8" s="88"/>
-      <c r="AI8" s="88"/>
-      <c r="AJ8" s="88"/>
-      <c r="AK8" s="91"/>
-      <c r="AL8" s="91"/>
-      <c r="AM8" s="91"/>
-      <c r="AN8" s="92"/>
-      <c r="AO8" s="87"/>
-      <c r="AP8" s="88"/>
-      <c r="AQ8" s="88"/>
-      <c r="AR8" s="88"/>
-      <c r="AS8" s="88"/>
-      <c r="AT8" s="88"/>
-      <c r="AU8" s="88"/>
-      <c r="AV8" s="88"/>
-      <c r="AW8" s="88"/>
-      <c r="AX8" s="88"/>
-      <c r="AY8" s="88"/>
-      <c r="AZ8" s="88"/>
-      <c r="BA8" s="88"/>
-      <c r="BB8" s="88"/>
-      <c r="BC8" s="89"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
+      <c r="S8" s="119"/>
+      <c r="T8" s="119"/>
+      <c r="U8" s="119"/>
+      <c r="V8" s="119"/>
+      <c r="W8" s="119"/>
+      <c r="X8" s="119"/>
+      <c r="Y8" s="119"/>
+      <c r="Z8" s="119"/>
+      <c r="AA8" s="119"/>
+      <c r="AB8" s="119"/>
+      <c r="AC8" s="119"/>
+      <c r="AD8" s="119"/>
+      <c r="AE8" s="119"/>
+      <c r="AF8" s="119"/>
+      <c r="AG8" s="119"/>
+      <c r="AH8" s="119"/>
+      <c r="AI8" s="119"/>
+      <c r="AJ8" s="119"/>
+      <c r="AK8" s="121"/>
+      <c r="AL8" s="121"/>
+      <c r="AM8" s="121"/>
+      <c r="AN8" s="122"/>
+      <c r="AO8" s="118"/>
+      <c r="AP8" s="119"/>
+      <c r="AQ8" s="119"/>
+      <c r="AR8" s="119"/>
+      <c r="AS8" s="119"/>
+      <c r="AT8" s="119"/>
+      <c r="AU8" s="119"/>
+      <c r="AV8" s="119"/>
+      <c r="AW8" s="119"/>
+      <c r="AX8" s="119"/>
+      <c r="AY8" s="119"/>
+      <c r="AZ8" s="119"/>
+      <c r="BA8" s="119"/>
+      <c r="BB8" s="119"/>
+      <c r="BC8" s="120"/>
     </row>
     <row r="9" spans="1:55" ht="15" customHeight="1">
       <c r="A9" s="40"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="88"/>
-      <c r="L9" s="88"/>
-      <c r="M9" s="88"/>
-      <c r="N9" s="88"/>
-      <c r="O9" s="88"/>
-      <c r="P9" s="88"/>
-      <c r="Q9" s="88"/>
-      <c r="R9" s="88"/>
-      <c r="S9" s="88"/>
-      <c r="T9" s="88"/>
-      <c r="U9" s="88"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="88"/>
-      <c r="Y9" s="88"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="88"/>
-      <c r="AB9" s="88"/>
-      <c r="AC9" s="88"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="88"/>
-      <c r="AF9" s="88"/>
-      <c r="AG9" s="88"/>
-      <c r="AH9" s="88"/>
-      <c r="AI9" s="88"/>
-      <c r="AJ9" s="88"/>
-      <c r="AK9" s="91"/>
-      <c r="AL9" s="91"/>
-      <c r="AM9" s="91"/>
-      <c r="AN9" s="92"/>
-      <c r="AO9" s="87"/>
-      <c r="AP9" s="88"/>
-      <c r="AQ9" s="88"/>
-      <c r="AR9" s="88"/>
-      <c r="AS9" s="88"/>
-      <c r="AT9" s="88"/>
-      <c r="AU9" s="88"/>
-      <c r="AV9" s="88"/>
-      <c r="AW9" s="88"/>
-      <c r="AX9" s="88"/>
-      <c r="AY9" s="88"/>
-      <c r="AZ9" s="88"/>
-      <c r="BA9" s="88"/>
-      <c r="BB9" s="88"/>
-      <c r="BC9" s="89"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="119"/>
+      <c r="U9" s="119"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="119"/>
+      <c r="Y9" s="119"/>
+      <c r="Z9" s="119"/>
+      <c r="AA9" s="119"/>
+      <c r="AB9" s="119"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="119"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="119"/>
+      <c r="AG9" s="119"/>
+      <c r="AH9" s="119"/>
+      <c r="AI9" s="119"/>
+      <c r="AJ9" s="119"/>
+      <c r="AK9" s="121"/>
+      <c r="AL9" s="121"/>
+      <c r="AM9" s="121"/>
+      <c r="AN9" s="122"/>
+      <c r="AO9" s="118"/>
+      <c r="AP9" s="119"/>
+      <c r="AQ9" s="119"/>
+      <c r="AR9" s="119"/>
+      <c r="AS9" s="119"/>
+      <c r="AT9" s="119"/>
+      <c r="AU9" s="119"/>
+      <c r="AV9" s="119"/>
+      <c r="AW9" s="119"/>
+      <c r="AX9" s="119"/>
+      <c r="AY9" s="119"/>
+      <c r="AZ9" s="119"/>
+      <c r="BA9" s="119"/>
+      <c r="BB9" s="119"/>
+      <c r="BC9" s="120"/>
     </row>
     <row r="10" spans="1:55" ht="15" customHeight="1">
       <c r="A10" s="40"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="88"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="88"/>
-      <c r="O10" s="88"/>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
-      <c r="R10" s="88"/>
-      <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="U10" s="88"/>
-      <c r="V10" s="88"/>
-      <c r="W10" s="88"/>
-      <c r="X10" s="88"/>
-      <c r="Y10" s="88"/>
-      <c r="Z10" s="88"/>
-      <c r="AA10" s="88"/>
-      <c r="AB10" s="88"/>
-      <c r="AC10" s="88"/>
-      <c r="AD10" s="88"/>
-      <c r="AE10" s="88"/>
-      <c r="AF10" s="88"/>
-      <c r="AG10" s="88"/>
-      <c r="AH10" s="88"/>
-      <c r="AI10" s="88"/>
-      <c r="AJ10" s="88"/>
-      <c r="AK10" s="91"/>
-      <c r="AL10" s="91"/>
-      <c r="AM10" s="91"/>
-      <c r="AN10" s="92"/>
-      <c r="AO10" s="87"/>
-      <c r="AP10" s="88"/>
-      <c r="AQ10" s="88"/>
-      <c r="AR10" s="88"/>
-      <c r="AS10" s="88"/>
-      <c r="AT10" s="88"/>
-      <c r="AU10" s="88"/>
-      <c r="AV10" s="88"/>
-      <c r="AW10" s="88"/>
-      <c r="AX10" s="88"/>
-      <c r="AY10" s="88"/>
-      <c r="AZ10" s="88"/>
-      <c r="BA10" s="88"/>
-      <c r="BB10" s="88"/>
-      <c r="BC10" s="89"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="119"/>
+      <c r="R10" s="119"/>
+      <c r="S10" s="119"/>
+      <c r="T10" s="119"/>
+      <c r="U10" s="119"/>
+      <c r="V10" s="119"/>
+      <c r="W10" s="119"/>
+      <c r="X10" s="119"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="119"/>
+      <c r="AA10" s="119"/>
+      <c r="AB10" s="119"/>
+      <c r="AC10" s="119"/>
+      <c r="AD10" s="119"/>
+      <c r="AE10" s="119"/>
+      <c r="AF10" s="119"/>
+      <c r="AG10" s="119"/>
+      <c r="AH10" s="119"/>
+      <c r="AI10" s="119"/>
+      <c r="AJ10" s="119"/>
+      <c r="AK10" s="121"/>
+      <c r="AL10" s="121"/>
+      <c r="AM10" s="121"/>
+      <c r="AN10" s="122"/>
+      <c r="AO10" s="118"/>
+      <c r="AP10" s="119"/>
+      <c r="AQ10" s="119"/>
+      <c r="AR10" s="119"/>
+      <c r="AS10" s="119"/>
+      <c r="AT10" s="119"/>
+      <c r="AU10" s="119"/>
+      <c r="AV10" s="119"/>
+      <c r="AW10" s="119"/>
+      <c r="AX10" s="119"/>
+      <c r="AY10" s="119"/>
+      <c r="AZ10" s="119"/>
+      <c r="BA10" s="119"/>
+      <c r="BB10" s="119"/>
+      <c r="BC10" s="120"/>
     </row>
     <row r="11" spans="1:55" ht="15" customHeight="1">
       <c r="A11" s="40"/>
-      <c r="B11" s="90"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="88"/>
-      <c r="AF11" s="88"/>
-      <c r="AG11" s="88"/>
-      <c r="AH11" s="88"/>
-      <c r="AI11" s="88"/>
-      <c r="AJ11" s="88"/>
-      <c r="AK11" s="91"/>
-      <c r="AL11" s="91"/>
-      <c r="AM11" s="91"/>
-      <c r="AN11" s="92"/>
-      <c r="AO11" s="87"/>
-      <c r="AP11" s="88"/>
-      <c r="AQ11" s="88"/>
-      <c r="AR11" s="88"/>
-      <c r="AS11" s="88"/>
-      <c r="AT11" s="88"/>
-      <c r="AU11" s="88"/>
-      <c r="AV11" s="88"/>
-      <c r="AW11" s="88"/>
-      <c r="AX11" s="88"/>
-      <c r="AY11" s="88"/>
-      <c r="AZ11" s="88"/>
-      <c r="BA11" s="88"/>
-      <c r="BB11" s="88"/>
-      <c r="BC11" s="89"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="119"/>
+      <c r="N11" s="119"/>
+      <c r="O11" s="119"/>
+      <c r="P11" s="119"/>
+      <c r="Q11" s="119"/>
+      <c r="R11" s="119"/>
+      <c r="S11" s="119"/>
+      <c r="T11" s="119"/>
+      <c r="U11" s="119"/>
+      <c r="V11" s="119"/>
+      <c r="W11" s="119"/>
+      <c r="X11" s="119"/>
+      <c r="Y11" s="119"/>
+      <c r="Z11" s="119"/>
+      <c r="AA11" s="119"/>
+      <c r="AB11" s="119"/>
+      <c r="AC11" s="119"/>
+      <c r="AD11" s="119"/>
+      <c r="AE11" s="119"/>
+      <c r="AF11" s="119"/>
+      <c r="AG11" s="119"/>
+      <c r="AH11" s="119"/>
+      <c r="AI11" s="119"/>
+      <c r="AJ11" s="119"/>
+      <c r="AK11" s="121"/>
+      <c r="AL11" s="121"/>
+      <c r="AM11" s="121"/>
+      <c r="AN11" s="122"/>
+      <c r="AO11" s="118"/>
+      <c r="AP11" s="119"/>
+      <c r="AQ11" s="119"/>
+      <c r="AR11" s="119"/>
+      <c r="AS11" s="119"/>
+      <c r="AT11" s="119"/>
+      <c r="AU11" s="119"/>
+      <c r="AV11" s="119"/>
+      <c r="AW11" s="119"/>
+      <c r="AX11" s="119"/>
+      <c r="AY11" s="119"/>
+      <c r="AZ11" s="119"/>
+      <c r="BA11" s="119"/>
+      <c r="BB11" s="119"/>
+      <c r="BC11" s="120"/>
     </row>
     <row r="12" spans="1:55" ht="15" customHeight="1">
       <c r="A12" s="40"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="88"/>
-      <c r="K12" s="88"/>
-      <c r="L12" s="88"/>
-      <c r="M12" s="88"/>
-      <c r="N12" s="88"/>
-      <c r="O12" s="88"/>
-      <c r="P12" s="88"/>
-      <c r="Q12" s="88"/>
-      <c r="R12" s="88"/>
-      <c r="S12" s="88"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="88"/>
-      <c r="V12" s="88"/>
-      <c r="W12" s="88"/>
-      <c r="X12" s="88"/>
-      <c r="Y12" s="88"/>
-      <c r="Z12" s="88"/>
-      <c r="AA12" s="88"/>
-      <c r="AB12" s="88"/>
-      <c r="AC12" s="88"/>
-      <c r="AD12" s="88"/>
-      <c r="AE12" s="88"/>
-      <c r="AF12" s="88"/>
-      <c r="AG12" s="88"/>
-      <c r="AH12" s="88"/>
-      <c r="AI12" s="88"/>
-      <c r="AJ12" s="88"/>
-      <c r="AK12" s="91"/>
-      <c r="AL12" s="91"/>
-      <c r="AM12" s="91"/>
-      <c r="AN12" s="92"/>
-      <c r="AO12" s="87"/>
-      <c r="AP12" s="88"/>
-      <c r="AQ12" s="88"/>
-      <c r="AR12" s="88"/>
-      <c r="AS12" s="88"/>
-      <c r="AT12" s="88"/>
-      <c r="AU12" s="88"/>
-      <c r="AV12" s="88"/>
-      <c r="AW12" s="88"/>
-      <c r="AX12" s="88"/>
-      <c r="AY12" s="88"/>
-      <c r="AZ12" s="88"/>
-      <c r="BA12" s="88"/>
-      <c r="BB12" s="88"/>
-      <c r="BC12" s="89"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="119"/>
+      <c r="Q12" s="119"/>
+      <c r="R12" s="119"/>
+      <c r="S12" s="119"/>
+      <c r="T12" s="119"/>
+      <c r="U12" s="119"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="119"/>
+      <c r="X12" s="119"/>
+      <c r="Y12" s="119"/>
+      <c r="Z12" s="119"/>
+      <c r="AA12" s="119"/>
+      <c r="AB12" s="119"/>
+      <c r="AC12" s="119"/>
+      <c r="AD12" s="119"/>
+      <c r="AE12" s="119"/>
+      <c r="AF12" s="119"/>
+      <c r="AG12" s="119"/>
+      <c r="AH12" s="119"/>
+      <c r="AI12" s="119"/>
+      <c r="AJ12" s="119"/>
+      <c r="AK12" s="121"/>
+      <c r="AL12" s="121"/>
+      <c r="AM12" s="121"/>
+      <c r="AN12" s="122"/>
+      <c r="AO12" s="118"/>
+      <c r="AP12" s="119"/>
+      <c r="AQ12" s="119"/>
+      <c r="AR12" s="119"/>
+      <c r="AS12" s="119"/>
+      <c r="AT12" s="119"/>
+      <c r="AU12" s="119"/>
+      <c r="AV12" s="119"/>
+      <c r="AW12" s="119"/>
+      <c r="AX12" s="119"/>
+      <c r="AY12" s="119"/>
+      <c r="AZ12" s="119"/>
+      <c r="BA12" s="119"/>
+      <c r="BB12" s="119"/>
+      <c r="BC12" s="120"/>
     </row>
     <row r="13" spans="1:55" ht="15" customHeight="1">
       <c r="A13" s="40"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="88"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="88"/>
-      <c r="M13" s="88"/>
-      <c r="N13" s="88"/>
-      <c r="O13" s="88"/>
-      <c r="P13" s="88"/>
-      <c r="Q13" s="88"/>
-      <c r="R13" s="88"/>
-      <c r="S13" s="88"/>
-      <c r="T13" s="88"/>
-      <c r="U13" s="88"/>
-      <c r="V13" s="88"/>
-      <c r="W13" s="88"/>
-      <c r="X13" s="88"/>
-      <c r="Y13" s="88"/>
-      <c r="Z13" s="88"/>
-      <c r="AA13" s="88"/>
-      <c r="AB13" s="88"/>
-      <c r="AC13" s="88"/>
-      <c r="AD13" s="88"/>
-      <c r="AE13" s="88"/>
-      <c r="AF13" s="88"/>
-      <c r="AG13" s="88"/>
-      <c r="AH13" s="88"/>
-      <c r="AI13" s="88"/>
-      <c r="AJ13" s="88"/>
-      <c r="AK13" s="91"/>
-      <c r="AL13" s="91"/>
-      <c r="AM13" s="91"/>
-      <c r="AN13" s="92"/>
-      <c r="AO13" s="87"/>
-      <c r="AP13" s="88"/>
-      <c r="AQ13" s="88"/>
-      <c r="AR13" s="88"/>
-      <c r="AS13" s="88"/>
-      <c r="AT13" s="88"/>
-      <c r="AU13" s="88"/>
-      <c r="AV13" s="88"/>
-      <c r="AW13" s="88"/>
-      <c r="AX13" s="88"/>
-      <c r="AY13" s="88"/>
-      <c r="AZ13" s="88"/>
-      <c r="BA13" s="88"/>
-      <c r="BB13" s="88"/>
-      <c r="BC13" s="89"/>
+      <c r="B13" s="112"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="119"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="119"/>
+      <c r="R13" s="119"/>
+      <c r="S13" s="119"/>
+      <c r="T13" s="119"/>
+      <c r="U13" s="119"/>
+      <c r="V13" s="119"/>
+      <c r="W13" s="119"/>
+      <c r="X13" s="119"/>
+      <c r="Y13" s="119"/>
+      <c r="Z13" s="119"/>
+      <c r="AA13" s="119"/>
+      <c r="AB13" s="119"/>
+      <c r="AC13" s="119"/>
+      <c r="AD13" s="119"/>
+      <c r="AE13" s="119"/>
+      <c r="AF13" s="119"/>
+      <c r="AG13" s="119"/>
+      <c r="AH13" s="119"/>
+      <c r="AI13" s="119"/>
+      <c r="AJ13" s="119"/>
+      <c r="AK13" s="121"/>
+      <c r="AL13" s="121"/>
+      <c r="AM13" s="121"/>
+      <c r="AN13" s="122"/>
+      <c r="AO13" s="118"/>
+      <c r="AP13" s="119"/>
+      <c r="AQ13" s="119"/>
+      <c r="AR13" s="119"/>
+      <c r="AS13" s="119"/>
+      <c r="AT13" s="119"/>
+      <c r="AU13" s="119"/>
+      <c r="AV13" s="119"/>
+      <c r="AW13" s="119"/>
+      <c r="AX13" s="119"/>
+      <c r="AY13" s="119"/>
+      <c r="AZ13" s="119"/>
+      <c r="BA13" s="119"/>
+      <c r="BB13" s="119"/>
+      <c r="BC13" s="120"/>
     </row>
     <row r="14" spans="1:55" ht="15" customHeight="1">
       <c r="A14" s="40"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="88"/>
-      <c r="P14" s="88"/>
-      <c r="Q14" s="88"/>
-      <c r="R14" s="88"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="88"/>
-      <c r="U14" s="88"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="88"/>
-      <c r="Y14" s="88"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="88"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="88"/>
-      <c r="AE14" s="88"/>
-      <c r="AF14" s="88"/>
-      <c r="AG14" s="88"/>
-      <c r="AH14" s="88"/>
-      <c r="AI14" s="88"/>
-      <c r="AJ14" s="88"/>
-      <c r="AK14" s="91"/>
-      <c r="AL14" s="91"/>
-      <c r="AM14" s="91"/>
-      <c r="AN14" s="92"/>
-      <c r="AO14" s="87"/>
-      <c r="AP14" s="88"/>
-      <c r="AQ14" s="88"/>
-      <c r="AR14" s="88"/>
-      <c r="AS14" s="88"/>
-      <c r="AT14" s="88"/>
-      <c r="AU14" s="88"/>
-      <c r="AV14" s="88"/>
-      <c r="AW14" s="88"/>
-      <c r="AX14" s="88"/>
-      <c r="AY14" s="88"/>
-      <c r="AZ14" s="88"/>
-      <c r="BA14" s="88"/>
-      <c r="BB14" s="88"/>
-      <c r="BC14" s="89"/>
+      <c r="B14" s="112"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="119"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="119"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="119"/>
+      <c r="R14" s="119"/>
+      <c r="S14" s="119"/>
+      <c r="T14" s="119"/>
+      <c r="U14" s="119"/>
+      <c r="V14" s="119"/>
+      <c r="W14" s="119"/>
+      <c r="X14" s="119"/>
+      <c r="Y14" s="119"/>
+      <c r="Z14" s="119"/>
+      <c r="AA14" s="119"/>
+      <c r="AB14" s="119"/>
+      <c r="AC14" s="119"/>
+      <c r="AD14" s="119"/>
+      <c r="AE14" s="119"/>
+      <c r="AF14" s="119"/>
+      <c r="AG14" s="119"/>
+      <c r="AH14" s="119"/>
+      <c r="AI14" s="119"/>
+      <c r="AJ14" s="119"/>
+      <c r="AK14" s="121"/>
+      <c r="AL14" s="121"/>
+      <c r="AM14" s="121"/>
+      <c r="AN14" s="122"/>
+      <c r="AO14" s="118"/>
+      <c r="AP14" s="119"/>
+      <c r="AQ14" s="119"/>
+      <c r="AR14" s="119"/>
+      <c r="AS14" s="119"/>
+      <c r="AT14" s="119"/>
+      <c r="AU14" s="119"/>
+      <c r="AV14" s="119"/>
+      <c r="AW14" s="119"/>
+      <c r="AX14" s="119"/>
+      <c r="AY14" s="119"/>
+      <c r="AZ14" s="119"/>
+      <c r="BA14" s="119"/>
+      <c r="BB14" s="119"/>
+      <c r="BC14" s="120"/>
     </row>
     <row r="15" spans="1:55" ht="15" customHeight="1">
       <c r="A15" s="40"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="88"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="88"/>
-      <c r="Y15" s="88"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="88"/>
-      <c r="AB15" s="88"/>
-      <c r="AC15" s="88"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="88"/>
-      <c r="AF15" s="88"/>
-      <c r="AG15" s="88"/>
-      <c r="AH15" s="88"/>
-      <c r="AI15" s="88"/>
-      <c r="AJ15" s="88"/>
-      <c r="AK15" s="91"/>
-      <c r="AL15" s="91"/>
-      <c r="AM15" s="91"/>
-      <c r="AN15" s="92"/>
-      <c r="AO15" s="87"/>
-      <c r="AP15" s="88"/>
-      <c r="AQ15" s="88"/>
-      <c r="AR15" s="88"/>
-      <c r="AS15" s="88"/>
-      <c r="AT15" s="88"/>
-      <c r="AU15" s="88"/>
-      <c r="AV15" s="88"/>
-      <c r="AW15" s="88"/>
-      <c r="AX15" s="88"/>
-      <c r="AY15" s="88"/>
-      <c r="AZ15" s="88"/>
-      <c r="BA15" s="88"/>
-      <c r="BB15" s="88"/>
-      <c r="BC15" s="89"/>
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="119"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="119"/>
+      <c r="P15" s="119"/>
+      <c r="Q15" s="119"/>
+      <c r="R15" s="119"/>
+      <c r="S15" s="119"/>
+      <c r="T15" s="119"/>
+      <c r="U15" s="119"/>
+      <c r="V15" s="119"/>
+      <c r="W15" s="119"/>
+      <c r="X15" s="119"/>
+      <c r="Y15" s="119"/>
+      <c r="Z15" s="119"/>
+      <c r="AA15" s="119"/>
+      <c r="AB15" s="119"/>
+      <c r="AC15" s="119"/>
+      <c r="AD15" s="119"/>
+      <c r="AE15" s="119"/>
+      <c r="AF15" s="119"/>
+      <c r="AG15" s="119"/>
+      <c r="AH15" s="119"/>
+      <c r="AI15" s="119"/>
+      <c r="AJ15" s="119"/>
+      <c r="AK15" s="121"/>
+      <c r="AL15" s="121"/>
+      <c r="AM15" s="121"/>
+      <c r="AN15" s="122"/>
+      <c r="AO15" s="118"/>
+      <c r="AP15" s="119"/>
+      <c r="AQ15" s="119"/>
+      <c r="AR15" s="119"/>
+      <c r="AS15" s="119"/>
+      <c r="AT15" s="119"/>
+      <c r="AU15" s="119"/>
+      <c r="AV15" s="119"/>
+      <c r="AW15" s="119"/>
+      <c r="AX15" s="119"/>
+      <c r="AY15" s="119"/>
+      <c r="AZ15" s="119"/>
+      <c r="BA15" s="119"/>
+      <c r="BB15" s="119"/>
+      <c r="BC15" s="120"/>
     </row>
     <row r="16" spans="1:55" ht="15" customHeight="1">
       <c r="A16" s="40"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="88"/>
-      <c r="O16" s="88"/>
-      <c r="P16" s="88"/>
-      <c r="Q16" s="88"/>
-      <c r="R16" s="88"/>
-      <c r="S16" s="88"/>
-      <c r="T16" s="88"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="88"/>
-      <c r="W16" s="88"/>
-      <c r="X16" s="88"/>
-      <c r="Y16" s="88"/>
-      <c r="Z16" s="88"/>
-      <c r="AA16" s="88"/>
-      <c r="AB16" s="88"/>
-      <c r="AC16" s="88"/>
-      <c r="AD16" s="88"/>
-      <c r="AE16" s="88"/>
-      <c r="AF16" s="88"/>
-      <c r="AG16" s="88"/>
-      <c r="AH16" s="88"/>
-      <c r="AI16" s="88"/>
-      <c r="AJ16" s="88"/>
-      <c r="AK16" s="91"/>
-      <c r="AL16" s="91"/>
-      <c r="AM16" s="91"/>
-      <c r="AN16" s="92"/>
-      <c r="AO16" s="87"/>
-      <c r="AP16" s="88"/>
-      <c r="AQ16" s="88"/>
-      <c r="AR16" s="88"/>
-      <c r="AS16" s="88"/>
-      <c r="AT16" s="88"/>
-      <c r="AU16" s="88"/>
-      <c r="AV16" s="88"/>
-      <c r="AW16" s="88"/>
-      <c r="AX16" s="88"/>
-      <c r="AY16" s="88"/>
-      <c r="AZ16" s="88"/>
-      <c r="BA16" s="88"/>
-      <c r="BB16" s="88"/>
-      <c r="BC16" s="89"/>
+      <c r="B16" s="112"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="119"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="119"/>
+      <c r="U16" s="119"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="119"/>
+      <c r="X16" s="119"/>
+      <c r="Y16" s="119"/>
+      <c r="Z16" s="119"/>
+      <c r="AA16" s="119"/>
+      <c r="AB16" s="119"/>
+      <c r="AC16" s="119"/>
+      <c r="AD16" s="119"/>
+      <c r="AE16" s="119"/>
+      <c r="AF16" s="119"/>
+      <c r="AG16" s="119"/>
+      <c r="AH16" s="119"/>
+      <c r="AI16" s="119"/>
+      <c r="AJ16" s="119"/>
+      <c r="AK16" s="121"/>
+      <c r="AL16" s="121"/>
+      <c r="AM16" s="121"/>
+      <c r="AN16" s="122"/>
+      <c r="AO16" s="118"/>
+      <c r="AP16" s="119"/>
+      <c r="AQ16" s="119"/>
+      <c r="AR16" s="119"/>
+      <c r="AS16" s="119"/>
+      <c r="AT16" s="119"/>
+      <c r="AU16" s="119"/>
+      <c r="AV16" s="119"/>
+      <c r="AW16" s="119"/>
+      <c r="AX16" s="119"/>
+      <c r="AY16" s="119"/>
+      <c r="AZ16" s="119"/>
+      <c r="BA16" s="119"/>
+      <c r="BB16" s="119"/>
+      <c r="BC16" s="120"/>
     </row>
     <row r="17" spans="1:55" ht="15" customHeight="1">
       <c r="A17" s="40"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="88"/>
-      <c r="O17" s="88"/>
-      <c r="P17" s="88"/>
-      <c r="Q17" s="88"/>
-      <c r="R17" s="88"/>
-      <c r="S17" s="88"/>
-      <c r="T17" s="88"/>
-      <c r="U17" s="88"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="88"/>
-      <c r="Y17" s="88"/>
-      <c r="Z17" s="88"/>
-      <c r="AA17" s="88"/>
-      <c r="AB17" s="88"/>
-      <c r="AC17" s="88"/>
-      <c r="AD17" s="88"/>
-      <c r="AE17" s="88"/>
-      <c r="AF17" s="88"/>
-      <c r="AG17" s="88"/>
-      <c r="AH17" s="88"/>
-      <c r="AI17" s="88"/>
-      <c r="AJ17" s="88"/>
-      <c r="AK17" s="91"/>
-      <c r="AL17" s="91"/>
-      <c r="AM17" s="91"/>
-      <c r="AN17" s="92"/>
-      <c r="AO17" s="87"/>
-      <c r="AP17" s="88"/>
-      <c r="AQ17" s="88"/>
-      <c r="AR17" s="88"/>
-      <c r="AS17" s="88"/>
-      <c r="AT17" s="88"/>
-      <c r="AU17" s="88"/>
-      <c r="AV17" s="88"/>
-      <c r="AW17" s="88"/>
-      <c r="AX17" s="88"/>
-      <c r="AY17" s="88"/>
-      <c r="AZ17" s="88"/>
-      <c r="BA17" s="88"/>
-      <c r="BB17" s="88"/>
-      <c r="BC17" s="89"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
+      <c r="P17" s="119"/>
+      <c r="Q17" s="119"/>
+      <c r="R17" s="119"/>
+      <c r="S17" s="119"/>
+      <c r="T17" s="119"/>
+      <c r="U17" s="119"/>
+      <c r="V17" s="119"/>
+      <c r="W17" s="119"/>
+      <c r="X17" s="119"/>
+      <c r="Y17" s="119"/>
+      <c r="Z17" s="119"/>
+      <c r="AA17" s="119"/>
+      <c r="AB17" s="119"/>
+      <c r="AC17" s="119"/>
+      <c r="AD17" s="119"/>
+      <c r="AE17" s="119"/>
+      <c r="AF17" s="119"/>
+      <c r="AG17" s="119"/>
+      <c r="AH17" s="119"/>
+      <c r="AI17" s="119"/>
+      <c r="AJ17" s="119"/>
+      <c r="AK17" s="121"/>
+      <c r="AL17" s="121"/>
+      <c r="AM17" s="121"/>
+      <c r="AN17" s="122"/>
+      <c r="AO17" s="118"/>
+      <c r="AP17" s="119"/>
+      <c r="AQ17" s="119"/>
+      <c r="AR17" s="119"/>
+      <c r="AS17" s="119"/>
+      <c r="AT17" s="119"/>
+      <c r="AU17" s="119"/>
+      <c r="AV17" s="119"/>
+      <c r="AW17" s="119"/>
+      <c r="AX17" s="119"/>
+      <c r="AY17" s="119"/>
+      <c r="AZ17" s="119"/>
+      <c r="BA17" s="119"/>
+      <c r="BB17" s="119"/>
+      <c r="BC17" s="120"/>
     </row>
     <row r="18" spans="1:55" ht="15" customHeight="1">
       <c r="A18" s="40"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="88"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="88"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="88"/>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="88"/>
-      <c r="AC18" s="88"/>
-      <c r="AD18" s="88"/>
-      <c r="AE18" s="88"/>
-      <c r="AF18" s="88"/>
-      <c r="AG18" s="88"/>
-      <c r="AH18" s="88"/>
-      <c r="AI18" s="88"/>
-      <c r="AJ18" s="88"/>
-      <c r="AK18" s="91"/>
-      <c r="AL18" s="91"/>
-      <c r="AM18" s="91"/>
-      <c r="AN18" s="92"/>
-      <c r="AO18" s="87"/>
-      <c r="AP18" s="88"/>
-      <c r="AQ18" s="88"/>
-      <c r="AR18" s="88"/>
-      <c r="AS18" s="88"/>
-      <c r="AT18" s="88"/>
-      <c r="AU18" s="88"/>
-      <c r="AV18" s="88"/>
-      <c r="AW18" s="88"/>
-      <c r="AX18" s="88"/>
-      <c r="AY18" s="88"/>
-      <c r="AZ18" s="88"/>
-      <c r="BA18" s="88"/>
-      <c r="BB18" s="88"/>
-      <c r="BC18" s="89"/>
+      <c r="B18" s="112"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
+      <c r="N18" s="119"/>
+      <c r="O18" s="119"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
+      <c r="U18" s="119"/>
+      <c r="V18" s="119"/>
+      <c r="W18" s="119"/>
+      <c r="X18" s="119"/>
+      <c r="Y18" s="119"/>
+      <c r="Z18" s="119"/>
+      <c r="AA18" s="119"/>
+      <c r="AB18" s="119"/>
+      <c r="AC18" s="119"/>
+      <c r="AD18" s="119"/>
+      <c r="AE18" s="119"/>
+      <c r="AF18" s="119"/>
+      <c r="AG18" s="119"/>
+      <c r="AH18" s="119"/>
+      <c r="AI18" s="119"/>
+      <c r="AJ18" s="119"/>
+      <c r="AK18" s="121"/>
+      <c r="AL18" s="121"/>
+      <c r="AM18" s="121"/>
+      <c r="AN18" s="122"/>
+      <c r="AO18" s="118"/>
+      <c r="AP18" s="119"/>
+      <c r="AQ18" s="119"/>
+      <c r="AR18" s="119"/>
+      <c r="AS18" s="119"/>
+      <c r="AT18" s="119"/>
+      <c r="AU18" s="119"/>
+      <c r="AV18" s="119"/>
+      <c r="AW18" s="119"/>
+      <c r="AX18" s="119"/>
+      <c r="AY18" s="119"/>
+      <c r="AZ18" s="119"/>
+      <c r="BA18" s="119"/>
+      <c r="BB18" s="119"/>
+      <c r="BC18" s="120"/>
     </row>
     <row r="19" spans="1:55" ht="15" customHeight="1">
       <c r="A19" s="40"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="88"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="88"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="88"/>
-      <c r="AE19" s="88"/>
-      <c r="AF19" s="88"/>
-      <c r="AG19" s="88"/>
-      <c r="AH19" s="88"/>
-      <c r="AI19" s="88"/>
-      <c r="AJ19" s="88"/>
-      <c r="AK19" s="91"/>
-      <c r="AL19" s="91"/>
-      <c r="AM19" s="91"/>
-      <c r="AN19" s="92"/>
-      <c r="AO19" s="87"/>
-      <c r="AP19" s="88"/>
-      <c r="AQ19" s="88"/>
-      <c r="AR19" s="88"/>
-      <c r="AS19" s="88"/>
-      <c r="AT19" s="88"/>
-      <c r="AU19" s="88"/>
-      <c r="AV19" s="88"/>
-      <c r="AW19" s="88"/>
-      <c r="AX19" s="88"/>
-      <c r="AY19" s="88"/>
-      <c r="AZ19" s="88"/>
-      <c r="BA19" s="88"/>
-      <c r="BB19" s="88"/>
-      <c r="BC19" s="89"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
+      <c r="R19" s="119"/>
+      <c r="S19" s="119"/>
+      <c r="T19" s="119"/>
+      <c r="U19" s="119"/>
+      <c r="V19" s="119"/>
+      <c r="W19" s="119"/>
+      <c r="X19" s="119"/>
+      <c r="Y19" s="119"/>
+      <c r="Z19" s="119"/>
+      <c r="AA19" s="119"/>
+      <c r="AB19" s="119"/>
+      <c r="AC19" s="119"/>
+      <c r="AD19" s="119"/>
+      <c r="AE19" s="119"/>
+      <c r="AF19" s="119"/>
+      <c r="AG19" s="119"/>
+      <c r="AH19" s="119"/>
+      <c r="AI19" s="119"/>
+      <c r="AJ19" s="119"/>
+      <c r="AK19" s="121"/>
+      <c r="AL19" s="121"/>
+      <c r="AM19" s="121"/>
+      <c r="AN19" s="122"/>
+      <c r="AO19" s="118"/>
+      <c r="AP19" s="119"/>
+      <c r="AQ19" s="119"/>
+      <c r="AR19" s="119"/>
+      <c r="AS19" s="119"/>
+      <c r="AT19" s="119"/>
+      <c r="AU19" s="119"/>
+      <c r="AV19" s="119"/>
+      <c r="AW19" s="119"/>
+      <c r="AX19" s="119"/>
+      <c r="AY19" s="119"/>
+      <c r="AZ19" s="119"/>
+      <c r="BA19" s="119"/>
+      <c r="BB19" s="119"/>
+      <c r="BC19" s="120"/>
     </row>
     <row r="20" spans="1:55" ht="15" customHeight="1">
       <c r="A20" s="40"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="88"/>
-      <c r="O20" s="88"/>
-      <c r="P20" s="88"/>
-      <c r="Q20" s="88"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="88"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="88"/>
-      <c r="X20" s="88"/>
-      <c r="Y20" s="88"/>
-      <c r="Z20" s="88"/>
-      <c r="AA20" s="88"/>
-      <c r="AB20" s="88"/>
-      <c r="AC20" s="88"/>
-      <c r="AD20" s="88"/>
-      <c r="AE20" s="88"/>
-      <c r="AF20" s="88"/>
-      <c r="AG20" s="88"/>
-      <c r="AH20" s="88"/>
-      <c r="AI20" s="88"/>
-      <c r="AJ20" s="88"/>
-      <c r="AK20" s="91"/>
-      <c r="AL20" s="91"/>
-      <c r="AM20" s="91"/>
-      <c r="AN20" s="92"/>
-      <c r="AO20" s="87"/>
-      <c r="AP20" s="88"/>
-      <c r="AQ20" s="88"/>
-      <c r="AR20" s="88"/>
-      <c r="AS20" s="88"/>
-      <c r="AT20" s="88"/>
-      <c r="AU20" s="88"/>
-      <c r="AV20" s="88"/>
-      <c r="AW20" s="88"/>
-      <c r="AX20" s="88"/>
-      <c r="AY20" s="88"/>
-      <c r="AZ20" s="88"/>
-      <c r="BA20" s="88"/>
-      <c r="BB20" s="88"/>
-      <c r="BC20" s="89"/>
+      <c r="B20" s="112"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="119"/>
+      <c r="R20" s="119"/>
+      <c r="S20" s="119"/>
+      <c r="T20" s="119"/>
+      <c r="U20" s="119"/>
+      <c r="V20" s="119"/>
+      <c r="W20" s="119"/>
+      <c r="X20" s="119"/>
+      <c r="Y20" s="119"/>
+      <c r="Z20" s="119"/>
+      <c r="AA20" s="119"/>
+      <c r="AB20" s="119"/>
+      <c r="AC20" s="119"/>
+      <c r="AD20" s="119"/>
+      <c r="AE20" s="119"/>
+      <c r="AF20" s="119"/>
+      <c r="AG20" s="119"/>
+      <c r="AH20" s="119"/>
+      <c r="AI20" s="119"/>
+      <c r="AJ20" s="119"/>
+      <c r="AK20" s="121"/>
+      <c r="AL20" s="121"/>
+      <c r="AM20" s="121"/>
+      <c r="AN20" s="122"/>
+      <c r="AO20" s="118"/>
+      <c r="AP20" s="119"/>
+      <c r="AQ20" s="119"/>
+      <c r="AR20" s="119"/>
+      <c r="AS20" s="119"/>
+      <c r="AT20" s="119"/>
+      <c r="AU20" s="119"/>
+      <c r="AV20" s="119"/>
+      <c r="AW20" s="119"/>
+      <c r="AX20" s="119"/>
+      <c r="AY20" s="119"/>
+      <c r="AZ20" s="119"/>
+      <c r="BA20" s="119"/>
+      <c r="BB20" s="119"/>
+      <c r="BC20" s="120"/>
     </row>
     <row r="21" spans="1:55" ht="15" customHeight="1">
       <c r="A21" s="40"/>
-      <c r="B21" s="90"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="88"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="88"/>
-      <c r="N21" s="88"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="88"/>
-      <c r="Q21" s="88"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="88"/>
-      <c r="U21" s="88"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="88"/>
-      <c r="X21" s="88"/>
-      <c r="Y21" s="88"/>
-      <c r="Z21" s="88"/>
-      <c r="AA21" s="88"/>
-      <c r="AB21" s="88"/>
-      <c r="AC21" s="88"/>
-      <c r="AD21" s="88"/>
-      <c r="AE21" s="88"/>
-      <c r="AF21" s="88"/>
-      <c r="AG21" s="88"/>
-      <c r="AH21" s="88"/>
-      <c r="AI21" s="88"/>
-      <c r="AJ21" s="88"/>
-      <c r="AK21" s="91"/>
-      <c r="AL21" s="91"/>
-      <c r="AM21" s="91"/>
-      <c r="AN21" s="92"/>
-      <c r="AO21" s="87"/>
-      <c r="AP21" s="88"/>
-      <c r="AQ21" s="88"/>
-      <c r="AR21" s="88"/>
-      <c r="AS21" s="88"/>
-      <c r="AT21" s="88"/>
-      <c r="AU21" s="88"/>
-      <c r="AV21" s="88"/>
-      <c r="AW21" s="88"/>
-      <c r="AX21" s="88"/>
-      <c r="AY21" s="88"/>
-      <c r="AZ21" s="88"/>
-      <c r="BA21" s="88"/>
-      <c r="BB21" s="88"/>
-      <c r="BC21" s="89"/>
+      <c r="B21" s="112"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="119"/>
+      <c r="R21" s="119"/>
+      <c r="S21" s="119"/>
+      <c r="T21" s="119"/>
+      <c r="U21" s="119"/>
+      <c r="V21" s="119"/>
+      <c r="W21" s="119"/>
+      <c r="X21" s="119"/>
+      <c r="Y21" s="119"/>
+      <c r="Z21" s="119"/>
+      <c r="AA21" s="119"/>
+      <c r="AB21" s="119"/>
+      <c r="AC21" s="119"/>
+      <c r="AD21" s="119"/>
+      <c r="AE21" s="119"/>
+      <c r="AF21" s="119"/>
+      <c r="AG21" s="119"/>
+      <c r="AH21" s="119"/>
+      <c r="AI21" s="119"/>
+      <c r="AJ21" s="119"/>
+      <c r="AK21" s="121"/>
+      <c r="AL21" s="121"/>
+      <c r="AM21" s="121"/>
+      <c r="AN21" s="122"/>
+      <c r="AO21" s="118"/>
+      <c r="AP21" s="119"/>
+      <c r="AQ21" s="119"/>
+      <c r="AR21" s="119"/>
+      <c r="AS21" s="119"/>
+      <c r="AT21" s="119"/>
+      <c r="AU21" s="119"/>
+      <c r="AV21" s="119"/>
+      <c r="AW21" s="119"/>
+      <c r="AX21" s="119"/>
+      <c r="AY21" s="119"/>
+      <c r="AZ21" s="119"/>
+      <c r="BA21" s="119"/>
+      <c r="BB21" s="119"/>
+      <c r="BC21" s="120"/>
     </row>
     <row r="22" spans="1:55" ht="15" customHeight="1">
       <c r="A22" s="40"/>
-      <c r="B22" s="90"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="88"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="88"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="88"/>
-      <c r="X22" s="88"/>
-      <c r="Y22" s="88"/>
-      <c r="Z22" s="88"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="88"/>
-      <c r="AC22" s="88"/>
-      <c r="AD22" s="88"/>
-      <c r="AE22" s="88"/>
-      <c r="AF22" s="88"/>
-      <c r="AG22" s="88"/>
-      <c r="AH22" s="88"/>
-      <c r="AI22" s="88"/>
-      <c r="AJ22" s="88"/>
-      <c r="AK22" s="91"/>
-      <c r="AL22" s="91"/>
-      <c r="AM22" s="91"/>
-      <c r="AN22" s="92"/>
-      <c r="AO22" s="87"/>
-      <c r="AP22" s="88"/>
-      <c r="AQ22" s="88"/>
-      <c r="AR22" s="88"/>
-      <c r="AS22" s="88"/>
-      <c r="AT22" s="88"/>
-      <c r="AU22" s="88"/>
-      <c r="AV22" s="88"/>
-      <c r="AW22" s="88"/>
-      <c r="AX22" s="88"/>
-      <c r="AY22" s="88"/>
-      <c r="AZ22" s="88"/>
-      <c r="BA22" s="88"/>
-      <c r="BB22" s="88"/>
-      <c r="BC22" s="89"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="119"/>
+      <c r="R22" s="119"/>
+      <c r="S22" s="119"/>
+      <c r="T22" s="119"/>
+      <c r="U22" s="119"/>
+      <c r="V22" s="119"/>
+      <c r="W22" s="119"/>
+      <c r="X22" s="119"/>
+      <c r="Y22" s="119"/>
+      <c r="Z22" s="119"/>
+      <c r="AA22" s="119"/>
+      <c r="AB22" s="119"/>
+      <c r="AC22" s="119"/>
+      <c r="AD22" s="119"/>
+      <c r="AE22" s="119"/>
+      <c r="AF22" s="119"/>
+      <c r="AG22" s="119"/>
+      <c r="AH22" s="119"/>
+      <c r="AI22" s="119"/>
+      <c r="AJ22" s="119"/>
+      <c r="AK22" s="121"/>
+      <c r="AL22" s="121"/>
+      <c r="AM22" s="121"/>
+      <c r="AN22" s="122"/>
+      <c r="AO22" s="118"/>
+      <c r="AP22" s="119"/>
+      <c r="AQ22" s="119"/>
+      <c r="AR22" s="119"/>
+      <c r="AS22" s="119"/>
+      <c r="AT22" s="119"/>
+      <c r="AU22" s="119"/>
+      <c r="AV22" s="119"/>
+      <c r="AW22" s="119"/>
+      <c r="AX22" s="119"/>
+      <c r="AY22" s="119"/>
+      <c r="AZ22" s="119"/>
+      <c r="BA22" s="119"/>
+      <c r="BB22" s="119"/>
+      <c r="BC22" s="120"/>
     </row>
     <row r="23" spans="1:55" ht="15" customHeight="1">
       <c r="A23" s="41"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="88"/>
-      <c r="Q23" s="88"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="88"/>
-      <c r="T23" s="88"/>
-      <c r="U23" s="88"/>
-      <c r="V23" s="88"/>
-      <c r="W23" s="88"/>
-      <c r="X23" s="88"/>
-      <c r="Y23" s="88"/>
-      <c r="Z23" s="88"/>
-      <c r="AA23" s="88"/>
-      <c r="AB23" s="88"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="88"/>
-      <c r="AE23" s="88"/>
-      <c r="AF23" s="88"/>
-      <c r="AG23" s="88"/>
-      <c r="AH23" s="88"/>
-      <c r="AI23" s="88"/>
-      <c r="AJ23" s="88"/>
-      <c r="AK23" s="91"/>
-      <c r="AL23" s="91"/>
-      <c r="AM23" s="91"/>
-      <c r="AN23" s="92"/>
-      <c r="AO23" s="87"/>
-      <c r="AP23" s="88"/>
-      <c r="AQ23" s="88"/>
-      <c r="AR23" s="88"/>
-      <c r="AS23" s="88"/>
-      <c r="AT23" s="88"/>
-      <c r="AU23" s="88"/>
-      <c r="AV23" s="88"/>
-      <c r="AW23" s="88"/>
-      <c r="AX23" s="88"/>
-      <c r="AY23" s="88"/>
-      <c r="AZ23" s="88"/>
-      <c r="BA23" s="88"/>
-      <c r="BB23" s="88"/>
-      <c r="BC23" s="89"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="119"/>
+      <c r="S23" s="119"/>
+      <c r="T23" s="119"/>
+      <c r="U23" s="119"/>
+      <c r="V23" s="119"/>
+      <c r="W23" s="119"/>
+      <c r="X23" s="119"/>
+      <c r="Y23" s="119"/>
+      <c r="Z23" s="119"/>
+      <c r="AA23" s="119"/>
+      <c r="AB23" s="119"/>
+      <c r="AC23" s="119"/>
+      <c r="AD23" s="119"/>
+      <c r="AE23" s="119"/>
+      <c r="AF23" s="119"/>
+      <c r="AG23" s="119"/>
+      <c r="AH23" s="119"/>
+      <c r="AI23" s="119"/>
+      <c r="AJ23" s="119"/>
+      <c r="AK23" s="121"/>
+      <c r="AL23" s="121"/>
+      <c r="AM23" s="121"/>
+      <c r="AN23" s="122"/>
+      <c r="AO23" s="118"/>
+      <c r="AP23" s="119"/>
+      <c r="AQ23" s="119"/>
+      <c r="AR23" s="119"/>
+      <c r="AS23" s="119"/>
+      <c r="AT23" s="119"/>
+      <c r="AU23" s="119"/>
+      <c r="AV23" s="119"/>
+      <c r="AW23" s="119"/>
+      <c r="AX23" s="119"/>
+      <c r="AY23" s="119"/>
+      <c r="AZ23" s="119"/>
+      <c r="BA23" s="119"/>
+      <c r="BB23" s="119"/>
+      <c r="BC23" s="120"/>
     </row>
     <row r="24" spans="1:55" ht="15" customHeight="1">
       <c r="A24" s="41"/>
-      <c r="B24" s="90"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="88"/>
-      <c r="O24" s="88"/>
-      <c r="P24" s="88"/>
-      <c r="Q24" s="88"/>
-      <c r="R24" s="88"/>
-      <c r="S24" s="88"/>
-      <c r="T24" s="88"/>
-      <c r="U24" s="88"/>
-      <c r="V24" s="88"/>
-      <c r="W24" s="88"/>
-      <c r="X24" s="88"/>
-      <c r="Y24" s="88"/>
-      <c r="Z24" s="88"/>
-      <c r="AA24" s="88"/>
-      <c r="AB24" s="88"/>
-      <c r="AC24" s="88"/>
-      <c r="AD24" s="88"/>
-      <c r="AE24" s="88"/>
-      <c r="AF24" s="88"/>
-      <c r="AG24" s="88"/>
-      <c r="AH24" s="88"/>
-      <c r="AI24" s="88"/>
-      <c r="AJ24" s="88"/>
-      <c r="AK24" s="91"/>
-      <c r="AL24" s="91"/>
-      <c r="AM24" s="91"/>
-      <c r="AN24" s="92"/>
-      <c r="AO24" s="87"/>
-      <c r="AP24" s="88"/>
-      <c r="AQ24" s="88"/>
-      <c r="AR24" s="88"/>
-      <c r="AS24" s="88"/>
-      <c r="AT24" s="88"/>
-      <c r="AU24" s="88"/>
-      <c r="AV24" s="88"/>
-      <c r="AW24" s="88"/>
-      <c r="AX24" s="88"/>
-      <c r="AY24" s="88"/>
-      <c r="AZ24" s="88"/>
-      <c r="BA24" s="88"/>
-      <c r="BB24" s="88"/>
-      <c r="BC24" s="89"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="113"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="114"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
+      <c r="S24" s="119"/>
+      <c r="T24" s="119"/>
+      <c r="U24" s="119"/>
+      <c r="V24" s="119"/>
+      <c r="W24" s="119"/>
+      <c r="X24" s="119"/>
+      <c r="Y24" s="119"/>
+      <c r="Z24" s="119"/>
+      <c r="AA24" s="119"/>
+      <c r="AB24" s="119"/>
+      <c r="AC24" s="119"/>
+      <c r="AD24" s="119"/>
+      <c r="AE24" s="119"/>
+      <c r="AF24" s="119"/>
+      <c r="AG24" s="119"/>
+      <c r="AH24" s="119"/>
+      <c r="AI24" s="119"/>
+      <c r="AJ24" s="119"/>
+      <c r="AK24" s="121"/>
+      <c r="AL24" s="121"/>
+      <c r="AM24" s="121"/>
+      <c r="AN24" s="122"/>
+      <c r="AO24" s="118"/>
+      <c r="AP24" s="119"/>
+      <c r="AQ24" s="119"/>
+      <c r="AR24" s="119"/>
+      <c r="AS24" s="119"/>
+      <c r="AT24" s="119"/>
+      <c r="AU24" s="119"/>
+      <c r="AV24" s="119"/>
+      <c r="AW24" s="119"/>
+      <c r="AX24" s="119"/>
+      <c r="AY24" s="119"/>
+      <c r="AZ24" s="119"/>
+      <c r="BA24" s="119"/>
+      <c r="BB24" s="119"/>
+      <c r="BC24" s="120"/>
     </row>
     <row r="25" spans="1:55" ht="15" customHeight="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="88"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="88"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="88"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="88"/>
-      <c r="Q25" s="88"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="88"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="88"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="88"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="88"/>
-      <c r="AE25" s="88"/>
-      <c r="AF25" s="88"/>
-      <c r="AG25" s="88"/>
-      <c r="AH25" s="88"/>
-      <c r="AI25" s="88"/>
-      <c r="AJ25" s="88"/>
-      <c r="AK25" s="91"/>
-      <c r="AL25" s="91"/>
-      <c r="AM25" s="91"/>
-      <c r="AN25" s="92"/>
-      <c r="AO25" s="87"/>
-      <c r="AP25" s="88"/>
-      <c r="AQ25" s="88"/>
-      <c r="AR25" s="88"/>
-      <c r="AS25" s="88"/>
-      <c r="AT25" s="88"/>
-      <c r="AU25" s="88"/>
-      <c r="AV25" s="88"/>
-      <c r="AW25" s="88"/>
-      <c r="AX25" s="88"/>
-      <c r="AY25" s="88"/>
-      <c r="AZ25" s="88"/>
-      <c r="BA25" s="88"/>
-      <c r="BB25" s="88"/>
-      <c r="BC25" s="89"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="114"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="119"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
+      <c r="R25" s="119"/>
+      <c r="S25" s="119"/>
+      <c r="T25" s="119"/>
+      <c r="U25" s="119"/>
+      <c r="V25" s="119"/>
+      <c r="W25" s="119"/>
+      <c r="X25" s="119"/>
+      <c r="Y25" s="119"/>
+      <c r="Z25" s="119"/>
+      <c r="AA25" s="119"/>
+      <c r="AB25" s="119"/>
+      <c r="AC25" s="119"/>
+      <c r="AD25" s="119"/>
+      <c r="AE25" s="119"/>
+      <c r="AF25" s="119"/>
+      <c r="AG25" s="119"/>
+      <c r="AH25" s="119"/>
+      <c r="AI25" s="119"/>
+      <c r="AJ25" s="119"/>
+      <c r="AK25" s="121"/>
+      <c r="AL25" s="121"/>
+      <c r="AM25" s="121"/>
+      <c r="AN25" s="122"/>
+      <c r="AO25" s="118"/>
+      <c r="AP25" s="119"/>
+      <c r="AQ25" s="119"/>
+      <c r="AR25" s="119"/>
+      <c r="AS25" s="119"/>
+      <c r="AT25" s="119"/>
+      <c r="AU25" s="119"/>
+      <c r="AV25" s="119"/>
+      <c r="AW25" s="119"/>
+      <c r="AX25" s="119"/>
+      <c r="AY25" s="119"/>
+      <c r="AZ25" s="119"/>
+      <c r="BA25" s="119"/>
+      <c r="BB25" s="119"/>
+      <c r="BC25" s="120"/>
     </row>
     <row r="26" spans="1:55" ht="15" customHeight="1">
       <c r="A26" s="40"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="88"/>
-      <c r="O26" s="88"/>
-      <c r="P26" s="88"/>
-      <c r="Q26" s="88"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="88"/>
-      <c r="T26" s="88"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="88"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="88"/>
-      <c r="Z26" s="88"/>
-      <c r="AA26" s="88"/>
-      <c r="AB26" s="88"/>
-      <c r="AC26" s="88"/>
-      <c r="AD26" s="88"/>
-      <c r="AE26" s="88"/>
-      <c r="AF26" s="88"/>
-      <c r="AG26" s="88"/>
-      <c r="AH26" s="88"/>
-      <c r="AI26" s="88"/>
-      <c r="AJ26" s="88"/>
-      <c r="AK26" s="91"/>
-      <c r="AL26" s="91"/>
-      <c r="AM26" s="91"/>
-      <c r="AN26" s="92"/>
-      <c r="AO26" s="87"/>
-      <c r="AP26" s="88"/>
-      <c r="AQ26" s="88"/>
-      <c r="AR26" s="88"/>
-      <c r="AS26" s="88"/>
-      <c r="AT26" s="88"/>
-      <c r="AU26" s="88"/>
-      <c r="AV26" s="88"/>
-      <c r="AW26" s="88"/>
-      <c r="AX26" s="88"/>
-      <c r="AY26" s="88"/>
-      <c r="AZ26" s="88"/>
-      <c r="BA26" s="88"/>
-      <c r="BB26" s="88"/>
-      <c r="BC26" s="89"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="114"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="119"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
+      <c r="R26" s="119"/>
+      <c r="S26" s="119"/>
+      <c r="T26" s="119"/>
+      <c r="U26" s="119"/>
+      <c r="V26" s="119"/>
+      <c r="W26" s="119"/>
+      <c r="X26" s="119"/>
+      <c r="Y26" s="119"/>
+      <c r="Z26" s="119"/>
+      <c r="AA26" s="119"/>
+      <c r="AB26" s="119"/>
+      <c r="AC26" s="119"/>
+      <c r="AD26" s="119"/>
+      <c r="AE26" s="119"/>
+      <c r="AF26" s="119"/>
+      <c r="AG26" s="119"/>
+      <c r="AH26" s="119"/>
+      <c r="AI26" s="119"/>
+      <c r="AJ26" s="119"/>
+      <c r="AK26" s="121"/>
+      <c r="AL26" s="121"/>
+      <c r="AM26" s="121"/>
+      <c r="AN26" s="122"/>
+      <c r="AO26" s="118"/>
+      <c r="AP26" s="119"/>
+      <c r="AQ26" s="119"/>
+      <c r="AR26" s="119"/>
+      <c r="AS26" s="119"/>
+      <c r="AT26" s="119"/>
+      <c r="AU26" s="119"/>
+      <c r="AV26" s="119"/>
+      <c r="AW26" s="119"/>
+      <c r="AX26" s="119"/>
+      <c r="AY26" s="119"/>
+      <c r="AZ26" s="119"/>
+      <c r="BA26" s="119"/>
+      <c r="BB26" s="119"/>
+      <c r="BC26" s="120"/>
     </row>
     <row r="27" spans="1:55" ht="15" customHeight="1">
       <c r="A27" s="40"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="88"/>
-      <c r="O27" s="88"/>
-      <c r="P27" s="88"/>
-      <c r="Q27" s="88"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="88"/>
-      <c r="U27" s="88"/>
-      <c r="V27" s="88"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="88"/>
-      <c r="Y27" s="88"/>
-      <c r="Z27" s="88"/>
-      <c r="AA27" s="88"/>
-      <c r="AB27" s="88"/>
-      <c r="AC27" s="88"/>
-      <c r="AD27" s="88"/>
-      <c r="AE27" s="88"/>
-      <c r="AF27" s="88"/>
-      <c r="AG27" s="88"/>
-      <c r="AH27" s="88"/>
-      <c r="AI27" s="88"/>
-      <c r="AJ27" s="88"/>
-      <c r="AK27" s="91"/>
-      <c r="AL27" s="91"/>
-      <c r="AM27" s="91"/>
-      <c r="AN27" s="92"/>
-      <c r="AO27" s="87"/>
-      <c r="AP27" s="88"/>
-      <c r="AQ27" s="88"/>
-      <c r="AR27" s="88"/>
-      <c r="AS27" s="88"/>
-      <c r="AT27" s="88"/>
-      <c r="AU27" s="88"/>
-      <c r="AV27" s="88"/>
-      <c r="AW27" s="88"/>
-      <c r="AX27" s="88"/>
-      <c r="AY27" s="88"/>
-      <c r="AZ27" s="88"/>
-      <c r="BA27" s="88"/>
-      <c r="BB27" s="88"/>
-      <c r="BC27" s="89"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="119"/>
+      <c r="N27" s="119"/>
+      <c r="O27" s="119"/>
+      <c r="P27" s="119"/>
+      <c r="Q27" s="119"/>
+      <c r="R27" s="119"/>
+      <c r="S27" s="119"/>
+      <c r="T27" s="119"/>
+      <c r="U27" s="119"/>
+      <c r="V27" s="119"/>
+      <c r="W27" s="119"/>
+      <c r="X27" s="119"/>
+      <c r="Y27" s="119"/>
+      <c r="Z27" s="119"/>
+      <c r="AA27" s="119"/>
+      <c r="AB27" s="119"/>
+      <c r="AC27" s="119"/>
+      <c r="AD27" s="119"/>
+      <c r="AE27" s="119"/>
+      <c r="AF27" s="119"/>
+      <c r="AG27" s="119"/>
+      <c r="AH27" s="119"/>
+      <c r="AI27" s="119"/>
+      <c r="AJ27" s="119"/>
+      <c r="AK27" s="121"/>
+      <c r="AL27" s="121"/>
+      <c r="AM27" s="121"/>
+      <c r="AN27" s="122"/>
+      <c r="AO27" s="118"/>
+      <c r="AP27" s="119"/>
+      <c r="AQ27" s="119"/>
+      <c r="AR27" s="119"/>
+      <c r="AS27" s="119"/>
+      <c r="AT27" s="119"/>
+      <c r="AU27" s="119"/>
+      <c r="AV27" s="119"/>
+      <c r="AW27" s="119"/>
+      <c r="AX27" s="119"/>
+      <c r="AY27" s="119"/>
+      <c r="AZ27" s="119"/>
+      <c r="BA27" s="119"/>
+      <c r="BB27" s="119"/>
+      <c r="BC27" s="120"/>
     </row>
     <row r="28" spans="1:55" ht="15" customHeight="1">
       <c r="A28" s="40"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="88"/>
-      <c r="O28" s="88"/>
-      <c r="P28" s="88"/>
-      <c r="Q28" s="88"/>
-      <c r="R28" s="88"/>
-      <c r="S28" s="88"/>
-      <c r="T28" s="88"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="88"/>
-      <c r="W28" s="88"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="88"/>
-      <c r="Z28" s="88"/>
-      <c r="AA28" s="88"/>
-      <c r="AB28" s="88"/>
-      <c r="AC28" s="88"/>
-      <c r="AD28" s="88"/>
-      <c r="AE28" s="88"/>
-      <c r="AF28" s="88"/>
-      <c r="AG28" s="88"/>
-      <c r="AH28" s="88"/>
-      <c r="AI28" s="88"/>
-      <c r="AJ28" s="88"/>
-      <c r="AK28" s="91"/>
-      <c r="AL28" s="91"/>
-      <c r="AM28" s="91"/>
-      <c r="AN28" s="92"/>
-      <c r="AO28" s="87"/>
-      <c r="AP28" s="88"/>
-      <c r="AQ28" s="88"/>
-      <c r="AR28" s="88"/>
-      <c r="AS28" s="88"/>
-      <c r="AT28" s="88"/>
-      <c r="AU28" s="88"/>
-      <c r="AV28" s="88"/>
-      <c r="AW28" s="88"/>
-      <c r="AX28" s="88"/>
-      <c r="AY28" s="88"/>
-      <c r="AZ28" s="88"/>
-      <c r="BA28" s="88"/>
-      <c r="BB28" s="88"/>
-      <c r="BC28" s="89"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="119"/>
+      <c r="N28" s="119"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="119"/>
+      <c r="Q28" s="119"/>
+      <c r="R28" s="119"/>
+      <c r="S28" s="119"/>
+      <c r="T28" s="119"/>
+      <c r="U28" s="119"/>
+      <c r="V28" s="119"/>
+      <c r="W28" s="119"/>
+      <c r="X28" s="119"/>
+      <c r="Y28" s="119"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="119"/>
+      <c r="AB28" s="119"/>
+      <c r="AC28" s="119"/>
+      <c r="AD28" s="119"/>
+      <c r="AE28" s="119"/>
+      <c r="AF28" s="119"/>
+      <c r="AG28" s="119"/>
+      <c r="AH28" s="119"/>
+      <c r="AI28" s="119"/>
+      <c r="AJ28" s="119"/>
+      <c r="AK28" s="121"/>
+      <c r="AL28" s="121"/>
+      <c r="AM28" s="121"/>
+      <c r="AN28" s="122"/>
+      <c r="AO28" s="118"/>
+      <c r="AP28" s="119"/>
+      <c r="AQ28" s="119"/>
+      <c r="AR28" s="119"/>
+      <c r="AS28" s="119"/>
+      <c r="AT28" s="119"/>
+      <c r="AU28" s="119"/>
+      <c r="AV28" s="119"/>
+      <c r="AW28" s="119"/>
+      <c r="AX28" s="119"/>
+      <c r="AY28" s="119"/>
+      <c r="AZ28" s="119"/>
+      <c r="BA28" s="119"/>
+      <c r="BB28" s="119"/>
+      <c r="BC28" s="120"/>
     </row>
     <row r="29" spans="1:55" ht="15" customHeight="1">
       <c r="A29" s="40"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="88"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="88"/>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="88"/>
-      <c r="T29" s="88"/>
-      <c r="U29" s="88"/>
-      <c r="V29" s="88"/>
-      <c r="W29" s="88"/>
-      <c r="X29" s="88"/>
-      <c r="Y29" s="88"/>
-      <c r="Z29" s="88"/>
-      <c r="AA29" s="88"/>
-      <c r="AB29" s="88"/>
-      <c r="AC29" s="88"/>
-      <c r="AD29" s="88"/>
-      <c r="AE29" s="88"/>
-      <c r="AF29" s="88"/>
-      <c r="AG29" s="88"/>
-      <c r="AH29" s="88"/>
-      <c r="AI29" s="88"/>
-      <c r="AJ29" s="88"/>
-      <c r="AK29" s="91"/>
-      <c r="AL29" s="91"/>
-      <c r="AM29" s="91"/>
-      <c r="AN29" s="92"/>
-      <c r="AO29" s="87"/>
-      <c r="AP29" s="88"/>
-      <c r="AQ29" s="88"/>
-      <c r="AR29" s="88"/>
-      <c r="AS29" s="88"/>
-      <c r="AT29" s="88"/>
-      <c r="AU29" s="88"/>
-      <c r="AV29" s="88"/>
-      <c r="AW29" s="88"/>
-      <c r="AX29" s="88"/>
-      <c r="AY29" s="88"/>
-      <c r="AZ29" s="88"/>
-      <c r="BA29" s="88"/>
-      <c r="BB29" s="88"/>
-      <c r="BC29" s="89"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="114"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="119"/>
+      <c r="N29" s="119"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="119"/>
+      <c r="Q29" s="119"/>
+      <c r="R29" s="119"/>
+      <c r="S29" s="119"/>
+      <c r="T29" s="119"/>
+      <c r="U29" s="119"/>
+      <c r="V29" s="119"/>
+      <c r="W29" s="119"/>
+      <c r="X29" s="119"/>
+      <c r="Y29" s="119"/>
+      <c r="Z29" s="119"/>
+      <c r="AA29" s="119"/>
+      <c r="AB29" s="119"/>
+      <c r="AC29" s="119"/>
+      <c r="AD29" s="119"/>
+      <c r="AE29" s="119"/>
+      <c r="AF29" s="119"/>
+      <c r="AG29" s="119"/>
+      <c r="AH29" s="119"/>
+      <c r="AI29" s="119"/>
+      <c r="AJ29" s="119"/>
+      <c r="AK29" s="121"/>
+      <c r="AL29" s="121"/>
+      <c r="AM29" s="121"/>
+      <c r="AN29" s="122"/>
+      <c r="AO29" s="118"/>
+      <c r="AP29" s="119"/>
+      <c r="AQ29" s="119"/>
+      <c r="AR29" s="119"/>
+      <c r="AS29" s="119"/>
+      <c r="AT29" s="119"/>
+      <c r="AU29" s="119"/>
+      <c r="AV29" s="119"/>
+      <c r="AW29" s="119"/>
+      <c r="AX29" s="119"/>
+      <c r="AY29" s="119"/>
+      <c r="AZ29" s="119"/>
+      <c r="BA29" s="119"/>
+      <c r="BB29" s="119"/>
+      <c r="BC29" s="120"/>
     </row>
     <row r="30" spans="1:55" ht="15" customHeight="1">
       <c r="A30" s="40"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
-      <c r="O30" s="88"/>
-      <c r="P30" s="88"/>
-      <c r="Q30" s="88"/>
-      <c r="R30" s="88"/>
-      <c r="S30" s="88"/>
-      <c r="T30" s="88"/>
-      <c r="U30" s="88"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="88"/>
-      <c r="X30" s="88"/>
-      <c r="Y30" s="88"/>
-      <c r="Z30" s="88"/>
-      <c r="AA30" s="88"/>
-      <c r="AB30" s="88"/>
-      <c r="AC30" s="88"/>
-      <c r="AD30" s="88"/>
-      <c r="AE30" s="88"/>
-      <c r="AF30" s="88"/>
-      <c r="AG30" s="88"/>
-      <c r="AH30" s="88"/>
-      <c r="AI30" s="88"/>
-      <c r="AJ30" s="88"/>
-      <c r="AK30" s="91"/>
-      <c r="AL30" s="91"/>
-      <c r="AM30" s="91"/>
-      <c r="AN30" s="92"/>
-      <c r="AO30" s="87"/>
-      <c r="AP30" s="88"/>
-      <c r="AQ30" s="88"/>
-      <c r="AR30" s="88"/>
-      <c r="AS30" s="88"/>
-      <c r="AT30" s="88"/>
-      <c r="AU30" s="88"/>
-      <c r="AV30" s="88"/>
-      <c r="AW30" s="88"/>
-      <c r="AX30" s="88"/>
-      <c r="AY30" s="88"/>
-      <c r="AZ30" s="88"/>
-      <c r="BA30" s="88"/>
-      <c r="BB30" s="88"/>
-      <c r="BC30" s="89"/>
+      <c r="B30" s="112"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="112"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="119"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="119"/>
+      <c r="Q30" s="119"/>
+      <c r="R30" s="119"/>
+      <c r="S30" s="119"/>
+      <c r="T30" s="119"/>
+      <c r="U30" s="119"/>
+      <c r="V30" s="119"/>
+      <c r="W30" s="119"/>
+      <c r="X30" s="119"/>
+      <c r="Y30" s="119"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="119"/>
+      <c r="AB30" s="119"/>
+      <c r="AC30" s="119"/>
+      <c r="AD30" s="119"/>
+      <c r="AE30" s="119"/>
+      <c r="AF30" s="119"/>
+      <c r="AG30" s="119"/>
+      <c r="AH30" s="119"/>
+      <c r="AI30" s="119"/>
+      <c r="AJ30" s="119"/>
+      <c r="AK30" s="121"/>
+      <c r="AL30" s="121"/>
+      <c r="AM30" s="121"/>
+      <c r="AN30" s="122"/>
+      <c r="AO30" s="118"/>
+      <c r="AP30" s="119"/>
+      <c r="AQ30" s="119"/>
+      <c r="AR30" s="119"/>
+      <c r="AS30" s="119"/>
+      <c r="AT30" s="119"/>
+      <c r="AU30" s="119"/>
+      <c r="AV30" s="119"/>
+      <c r="AW30" s="119"/>
+      <c r="AX30" s="119"/>
+      <c r="AY30" s="119"/>
+      <c r="AZ30" s="119"/>
+      <c r="BA30" s="119"/>
+      <c r="BB30" s="119"/>
+      <c r="BC30" s="120"/>
     </row>
     <row r="31" spans="1:55" ht="15" customHeight="1">
       <c r="A31" s="40"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="90"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="88"/>
-      <c r="N31" s="88"/>
-      <c r="O31" s="88"/>
-      <c r="P31" s="88"/>
-      <c r="Q31" s="88"/>
-      <c r="R31" s="88"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="88"/>
-      <c r="U31" s="88"/>
-      <c r="V31" s="88"/>
-      <c r="W31" s="88"/>
-      <c r="X31" s="88"/>
-      <c r="Y31" s="88"/>
-      <c r="Z31" s="88"/>
-      <c r="AA31" s="88"/>
-      <c r="AB31" s="88"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="88"/>
-      <c r="AE31" s="88"/>
-      <c r="AF31" s="88"/>
-      <c r="AG31" s="88"/>
-      <c r="AH31" s="88"/>
-      <c r="AI31" s="88"/>
-      <c r="AJ31" s="88"/>
-      <c r="AK31" s="91"/>
-      <c r="AL31" s="91"/>
-      <c r="AM31" s="91"/>
-      <c r="AN31" s="92"/>
-      <c r="AO31" s="87"/>
-      <c r="AP31" s="88"/>
-      <c r="AQ31" s="88"/>
-      <c r="AR31" s="88"/>
-      <c r="AS31" s="88"/>
-      <c r="AT31" s="88"/>
-      <c r="AU31" s="88"/>
-      <c r="AV31" s="88"/>
-      <c r="AW31" s="88"/>
-      <c r="AX31" s="88"/>
-      <c r="AY31" s="88"/>
-      <c r="AZ31" s="88"/>
-      <c r="BA31" s="88"/>
-      <c r="BB31" s="88"/>
-      <c r="BC31" s="89"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="114"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="119"/>
+      <c r="N31" s="119"/>
+      <c r="O31" s="119"/>
+      <c r="P31" s="119"/>
+      <c r="Q31" s="119"/>
+      <c r="R31" s="119"/>
+      <c r="S31" s="119"/>
+      <c r="T31" s="119"/>
+      <c r="U31" s="119"/>
+      <c r="V31" s="119"/>
+      <c r="W31" s="119"/>
+      <c r="X31" s="119"/>
+      <c r="Y31" s="119"/>
+      <c r="Z31" s="119"/>
+      <c r="AA31" s="119"/>
+      <c r="AB31" s="119"/>
+      <c r="AC31" s="119"/>
+      <c r="AD31" s="119"/>
+      <c r="AE31" s="119"/>
+      <c r="AF31" s="119"/>
+      <c r="AG31" s="119"/>
+      <c r="AH31" s="119"/>
+      <c r="AI31" s="119"/>
+      <c r="AJ31" s="119"/>
+      <c r="AK31" s="121"/>
+      <c r="AL31" s="121"/>
+      <c r="AM31" s="121"/>
+      <c r="AN31" s="122"/>
+      <c r="AO31" s="118"/>
+      <c r="AP31" s="119"/>
+      <c r="AQ31" s="119"/>
+      <c r="AR31" s="119"/>
+      <c r="AS31" s="119"/>
+      <c r="AT31" s="119"/>
+      <c r="AU31" s="119"/>
+      <c r="AV31" s="119"/>
+      <c r="AW31" s="119"/>
+      <c r="AX31" s="119"/>
+      <c r="AY31" s="119"/>
+      <c r="AZ31" s="119"/>
+      <c r="BA31" s="119"/>
+      <c r="BB31" s="119"/>
+      <c r="BC31" s="120"/>
     </row>
     <row r="32" spans="1:55" ht="15" customHeight="1">
       <c r="A32" s="40"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="88"/>
-      <c r="O32" s="88"/>
-      <c r="P32" s="88"/>
-      <c r="Q32" s="88"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="88"/>
-      <c r="T32" s="88"/>
-      <c r="U32" s="88"/>
-      <c r="V32" s="88"/>
-      <c r="W32" s="88"/>
-      <c r="X32" s="88"/>
-      <c r="Y32" s="88"/>
-      <c r="Z32" s="88"/>
-      <c r="AA32" s="88"/>
-      <c r="AB32" s="88"/>
-      <c r="AC32" s="88"/>
-      <c r="AD32" s="88"/>
-      <c r="AE32" s="88"/>
-      <c r="AF32" s="88"/>
-      <c r="AG32" s="88"/>
-      <c r="AH32" s="88"/>
-      <c r="AI32" s="88"/>
-      <c r="AJ32" s="88"/>
-      <c r="AK32" s="91"/>
-      <c r="AL32" s="91"/>
-      <c r="AM32" s="91"/>
-      <c r="AN32" s="92"/>
-      <c r="AO32" s="87"/>
-      <c r="AP32" s="88"/>
-      <c r="AQ32" s="88"/>
-      <c r="AR32" s="88"/>
-      <c r="AS32" s="88"/>
-      <c r="AT32" s="88"/>
-      <c r="AU32" s="88"/>
-      <c r="AV32" s="88"/>
-      <c r="AW32" s="88"/>
-      <c r="AX32" s="88"/>
-      <c r="AY32" s="88"/>
-      <c r="AZ32" s="88"/>
-      <c r="BA32" s="88"/>
-      <c r="BB32" s="88"/>
-      <c r="BC32" s="89"/>
+      <c r="B32" s="112"/>
+      <c r="C32" s="113"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="114"/>
+      <c r="I32" s="112"/>
+      <c r="J32" s="119"/>
+      <c r="K32" s="119"/>
+      <c r="L32" s="119"/>
+      <c r="M32" s="119"/>
+      <c r="N32" s="119"/>
+      <c r="O32" s="119"/>
+      <c r="P32" s="119"/>
+      <c r="Q32" s="119"/>
+      <c r="R32" s="119"/>
+      <c r="S32" s="119"/>
+      <c r="T32" s="119"/>
+      <c r="U32" s="119"/>
+      <c r="V32" s="119"/>
+      <c r="W32" s="119"/>
+      <c r="X32" s="119"/>
+      <c r="Y32" s="119"/>
+      <c r="Z32" s="119"/>
+      <c r="AA32" s="119"/>
+      <c r="AB32" s="119"/>
+      <c r="AC32" s="119"/>
+      <c r="AD32" s="119"/>
+      <c r="AE32" s="119"/>
+      <c r="AF32" s="119"/>
+      <c r="AG32" s="119"/>
+      <c r="AH32" s="119"/>
+      <c r="AI32" s="119"/>
+      <c r="AJ32" s="119"/>
+      <c r="AK32" s="121"/>
+      <c r="AL32" s="121"/>
+      <c r="AM32" s="121"/>
+      <c r="AN32" s="122"/>
+      <c r="AO32" s="118"/>
+      <c r="AP32" s="119"/>
+      <c r="AQ32" s="119"/>
+      <c r="AR32" s="119"/>
+      <c r="AS32" s="119"/>
+      <c r="AT32" s="119"/>
+      <c r="AU32" s="119"/>
+      <c r="AV32" s="119"/>
+      <c r="AW32" s="119"/>
+      <c r="AX32" s="119"/>
+      <c r="AY32" s="119"/>
+      <c r="AZ32" s="119"/>
+      <c r="BA32" s="119"/>
+      <c r="BB32" s="119"/>
+      <c r="BC32" s="120"/>
     </row>
     <row r="33" spans="1:55" ht="15" customHeight="1">
       <c r="A33" s="40"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="90"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="88"/>
-      <c r="O33" s="88"/>
-      <c r="P33" s="88"/>
-      <c r="Q33" s="88"/>
-      <c r="R33" s="88"/>
-      <c r="S33" s="88"/>
-      <c r="T33" s="88"/>
-      <c r="U33" s="88"/>
-      <c r="V33" s="88"/>
-      <c r="W33" s="88"/>
-      <c r="X33" s="88"/>
-      <c r="Y33" s="88"/>
-      <c r="Z33" s="88"/>
-      <c r="AA33" s="88"/>
-      <c r="AB33" s="88"/>
-      <c r="AC33" s="88"/>
-      <c r="AD33" s="88"/>
-      <c r="AE33" s="88"/>
-      <c r="AF33" s="88"/>
-      <c r="AG33" s="88"/>
-      <c r="AH33" s="88"/>
-      <c r="AI33" s="88"/>
-      <c r="AJ33" s="88"/>
-      <c r="AK33" s="91"/>
-      <c r="AL33" s="91"/>
-      <c r="AM33" s="91"/>
-      <c r="AN33" s="92"/>
-      <c r="AO33" s="87"/>
-      <c r="AP33" s="88"/>
-      <c r="AQ33" s="88"/>
-      <c r="AR33" s="88"/>
-      <c r="AS33" s="88"/>
-      <c r="AT33" s="88"/>
-      <c r="AU33" s="88"/>
-      <c r="AV33" s="88"/>
-      <c r="AW33" s="88"/>
-      <c r="AX33" s="88"/>
-      <c r="AY33" s="88"/>
-      <c r="AZ33" s="88"/>
-      <c r="BA33" s="88"/>
-      <c r="BB33" s="88"/>
-      <c r="BC33" s="89"/>
+      <c r="B33" s="112"/>
+      <c r="C33" s="113"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="114"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="119"/>
+      <c r="L33" s="119"/>
+      <c r="M33" s="119"/>
+      <c r="N33" s="119"/>
+      <c r="O33" s="119"/>
+      <c r="P33" s="119"/>
+      <c r="Q33" s="119"/>
+      <c r="R33" s="119"/>
+      <c r="S33" s="119"/>
+      <c r="T33" s="119"/>
+      <c r="U33" s="119"/>
+      <c r="V33" s="119"/>
+      <c r="W33" s="119"/>
+      <c r="X33" s="119"/>
+      <c r="Y33" s="119"/>
+      <c r="Z33" s="119"/>
+      <c r="AA33" s="119"/>
+      <c r="AB33" s="119"/>
+      <c r="AC33" s="119"/>
+      <c r="AD33" s="119"/>
+      <c r="AE33" s="119"/>
+      <c r="AF33" s="119"/>
+      <c r="AG33" s="119"/>
+      <c r="AH33" s="119"/>
+      <c r="AI33" s="119"/>
+      <c r="AJ33" s="119"/>
+      <c r="AK33" s="121"/>
+      <c r="AL33" s="121"/>
+      <c r="AM33" s="121"/>
+      <c r="AN33" s="122"/>
+      <c r="AO33" s="118"/>
+      <c r="AP33" s="119"/>
+      <c r="AQ33" s="119"/>
+      <c r="AR33" s="119"/>
+      <c r="AS33" s="119"/>
+      <c r="AT33" s="119"/>
+      <c r="AU33" s="119"/>
+      <c r="AV33" s="119"/>
+      <c r="AW33" s="119"/>
+      <c r="AX33" s="119"/>
+      <c r="AY33" s="119"/>
+      <c r="AZ33" s="119"/>
+      <c r="BA33" s="119"/>
+      <c r="BB33" s="119"/>
+      <c r="BC33" s="120"/>
     </row>
     <row r="34" spans="1:55" ht="15" customHeight="1">
       <c r="A34" s="40"/>
-      <c r="B34" s="90"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="90"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="88"/>
-      <c r="P34" s="88"/>
-      <c r="Q34" s="88"/>
-      <c r="R34" s="88"/>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="88"/>
-      <c r="V34" s="88"/>
-      <c r="W34" s="88"/>
-      <c r="X34" s="88"/>
-      <c r="Y34" s="88"/>
-      <c r="Z34" s="88"/>
-      <c r="AA34" s="88"/>
-      <c r="AB34" s="88"/>
-      <c r="AC34" s="88"/>
-      <c r="AD34" s="88"/>
-      <c r="AE34" s="88"/>
-      <c r="AF34" s="88"/>
-      <c r="AG34" s="88"/>
-      <c r="AH34" s="88"/>
-      <c r="AI34" s="88"/>
-      <c r="AJ34" s="88"/>
-      <c r="AK34" s="91"/>
-      <c r="AL34" s="91"/>
-      <c r="AM34" s="91"/>
-      <c r="AN34" s="92"/>
-      <c r="AO34" s="87"/>
-      <c r="AP34" s="88"/>
-      <c r="AQ34" s="88"/>
-      <c r="AR34" s="88"/>
-      <c r="AS34" s="88"/>
-      <c r="AT34" s="88"/>
-      <c r="AU34" s="88"/>
-      <c r="AV34" s="88"/>
-      <c r="AW34" s="88"/>
-      <c r="AX34" s="88"/>
-      <c r="AY34" s="88"/>
-      <c r="AZ34" s="88"/>
-      <c r="BA34" s="88"/>
-      <c r="BB34" s="88"/>
-      <c r="BC34" s="89"/>
+      <c r="B34" s="112"/>
+      <c r="C34" s="113"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="112"/>
+      <c r="J34" s="119"/>
+      <c r="K34" s="119"/>
+      <c r="L34" s="119"/>
+      <c r="M34" s="119"/>
+      <c r="N34" s="119"/>
+      <c r="O34" s="119"/>
+      <c r="P34" s="119"/>
+      <c r="Q34" s="119"/>
+      <c r="R34" s="119"/>
+      <c r="S34" s="119"/>
+      <c r="T34" s="119"/>
+      <c r="U34" s="119"/>
+      <c r="V34" s="119"/>
+      <c r="W34" s="119"/>
+      <c r="X34" s="119"/>
+      <c r="Y34" s="119"/>
+      <c r="Z34" s="119"/>
+      <c r="AA34" s="119"/>
+      <c r="AB34" s="119"/>
+      <c r="AC34" s="119"/>
+      <c r="AD34" s="119"/>
+      <c r="AE34" s="119"/>
+      <c r="AF34" s="119"/>
+      <c r="AG34" s="119"/>
+      <c r="AH34" s="119"/>
+      <c r="AI34" s="119"/>
+      <c r="AJ34" s="119"/>
+      <c r="AK34" s="121"/>
+      <c r="AL34" s="121"/>
+      <c r="AM34" s="121"/>
+      <c r="AN34" s="122"/>
+      <c r="AO34" s="118"/>
+      <c r="AP34" s="119"/>
+      <c r="AQ34" s="119"/>
+      <c r="AR34" s="119"/>
+      <c r="AS34" s="119"/>
+      <c r="AT34" s="119"/>
+      <c r="AU34" s="119"/>
+      <c r="AV34" s="119"/>
+      <c r="AW34" s="119"/>
+      <c r="AX34" s="119"/>
+      <c r="AY34" s="119"/>
+      <c r="AZ34" s="119"/>
+      <c r="BA34" s="119"/>
+      <c r="BB34" s="119"/>
+      <c r="BC34" s="120"/>
     </row>
     <row r="35" spans="1:55" ht="15" customHeight="1">
       <c r="A35" s="40"/>
-      <c r="B35" s="90"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="90"/>
-      <c r="J35" s="88"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="88"/>
-      <c r="M35" s="88"/>
-      <c r="N35" s="88"/>
-      <c r="O35" s="88"/>
-      <c r="P35" s="88"/>
-      <c r="Q35" s="88"/>
-      <c r="R35" s="88"/>
-      <c r="S35" s="88"/>
-      <c r="T35" s="88"/>
-      <c r="U35" s="88"/>
-      <c r="V35" s="88"/>
-      <c r="W35" s="88"/>
-      <c r="X35" s="88"/>
-      <c r="Y35" s="88"/>
-      <c r="Z35" s="88"/>
-      <c r="AA35" s="88"/>
-      <c r="AB35" s="88"/>
-      <c r="AC35" s="88"/>
-      <c r="AD35" s="88"/>
-      <c r="AE35" s="88"/>
-      <c r="AF35" s="88"/>
-      <c r="AG35" s="88"/>
-      <c r="AH35" s="88"/>
-      <c r="AI35" s="88"/>
-      <c r="AJ35" s="88"/>
-      <c r="AK35" s="91"/>
-      <c r="AL35" s="91"/>
-      <c r="AM35" s="91"/>
-      <c r="AN35" s="92"/>
-      <c r="AO35" s="87"/>
-      <c r="AP35" s="88"/>
-      <c r="AQ35" s="88"/>
-      <c r="AR35" s="88"/>
-      <c r="AS35" s="88"/>
-      <c r="AT35" s="88"/>
-      <c r="AU35" s="88"/>
-      <c r="AV35" s="88"/>
-      <c r="AW35" s="88"/>
-      <c r="AX35" s="88"/>
-      <c r="AY35" s="88"/>
-      <c r="AZ35" s="88"/>
-      <c r="BA35" s="88"/>
-      <c r="BB35" s="88"/>
-      <c r="BC35" s="89"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="113"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="113"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="112"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="119"/>
+      <c r="L35" s="119"/>
+      <c r="M35" s="119"/>
+      <c r="N35" s="119"/>
+      <c r="O35" s="119"/>
+      <c r="P35" s="119"/>
+      <c r="Q35" s="119"/>
+      <c r="R35" s="119"/>
+      <c r="S35" s="119"/>
+      <c r="T35" s="119"/>
+      <c r="U35" s="119"/>
+      <c r="V35" s="119"/>
+      <c r="W35" s="119"/>
+      <c r="X35" s="119"/>
+      <c r="Y35" s="119"/>
+      <c r="Z35" s="119"/>
+      <c r="AA35" s="119"/>
+      <c r="AB35" s="119"/>
+      <c r="AC35" s="119"/>
+      <c r="AD35" s="119"/>
+      <c r="AE35" s="119"/>
+      <c r="AF35" s="119"/>
+      <c r="AG35" s="119"/>
+      <c r="AH35" s="119"/>
+      <c r="AI35" s="119"/>
+      <c r="AJ35" s="119"/>
+      <c r="AK35" s="121"/>
+      <c r="AL35" s="121"/>
+      <c r="AM35" s="121"/>
+      <c r="AN35" s="122"/>
+      <c r="AO35" s="118"/>
+      <c r="AP35" s="119"/>
+      <c r="AQ35" s="119"/>
+      <c r="AR35" s="119"/>
+      <c r="AS35" s="119"/>
+      <c r="AT35" s="119"/>
+      <c r="AU35" s="119"/>
+      <c r="AV35" s="119"/>
+      <c r="AW35" s="119"/>
+      <c r="AX35" s="119"/>
+      <c r="AY35" s="119"/>
+      <c r="AZ35" s="119"/>
+      <c r="BA35" s="119"/>
+      <c r="BB35" s="119"/>
+      <c r="BC35" s="120"/>
     </row>
     <row r="36" spans="1:55" ht="15" customHeight="1" thickBot="1">
       <c r="A36" s="42"/>
-      <c r="B36" s="110"/>
-      <c r="C36" s="113"/>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="113"/>
-      <c r="G36" s="113"/>
-      <c r="H36" s="114"/>
-      <c r="I36" s="110"/>
-      <c r="J36" s="108"/>
-      <c r="K36" s="108"/>
-      <c r="L36" s="108"/>
-      <c r="M36" s="108"/>
-      <c r="N36" s="108"/>
-      <c r="O36" s="108"/>
-      <c r="P36" s="108"/>
-      <c r="Q36" s="108"/>
-      <c r="R36" s="108"/>
-      <c r="S36" s="108"/>
-      <c r="T36" s="108"/>
-      <c r="U36" s="108"/>
-      <c r="V36" s="108"/>
-      <c r="W36" s="108"/>
-      <c r="X36" s="108"/>
-      <c r="Y36" s="108"/>
-      <c r="Z36" s="108"/>
-      <c r="AA36" s="108"/>
-      <c r="AB36" s="108"/>
-      <c r="AC36" s="108"/>
-      <c r="AD36" s="108"/>
-      <c r="AE36" s="108"/>
-      <c r="AF36" s="108"/>
-      <c r="AG36" s="108"/>
-      <c r="AH36" s="108"/>
-      <c r="AI36" s="108"/>
-      <c r="AJ36" s="108"/>
-      <c r="AK36" s="111"/>
-      <c r="AL36" s="111"/>
-      <c r="AM36" s="111"/>
-      <c r="AN36" s="112"/>
-      <c r="AO36" s="107"/>
-      <c r="AP36" s="108"/>
-      <c r="AQ36" s="108"/>
-      <c r="AR36" s="108"/>
-      <c r="AS36" s="108"/>
-      <c r="AT36" s="108"/>
-      <c r="AU36" s="108"/>
-      <c r="AV36" s="108"/>
-      <c r="AW36" s="108"/>
-      <c r="AX36" s="108"/>
-      <c r="AY36" s="108"/>
-      <c r="AZ36" s="108"/>
-      <c r="BA36" s="108"/>
-      <c r="BB36" s="108"/>
-      <c r="BC36" s="109"/>
+      <c r="B36" s="129"/>
+      <c r="C36" s="132"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="132"/>
+      <c r="H36" s="133"/>
+      <c r="I36" s="129"/>
+      <c r="J36" s="127"/>
+      <c r="K36" s="127"/>
+      <c r="L36" s="127"/>
+      <c r="M36" s="127"/>
+      <c r="N36" s="127"/>
+      <c r="O36" s="127"/>
+      <c r="P36" s="127"/>
+      <c r="Q36" s="127"/>
+      <c r="R36" s="127"/>
+      <c r="S36" s="127"/>
+      <c r="T36" s="127"/>
+      <c r="U36" s="127"/>
+      <c r="V36" s="127"/>
+      <c r="W36" s="127"/>
+      <c r="X36" s="127"/>
+      <c r="Y36" s="127"/>
+      <c r="Z36" s="127"/>
+      <c r="AA36" s="127"/>
+      <c r="AB36" s="127"/>
+      <c r="AC36" s="127"/>
+      <c r="AD36" s="127"/>
+      <c r="AE36" s="127"/>
+      <c r="AF36" s="127"/>
+      <c r="AG36" s="127"/>
+      <c r="AH36" s="127"/>
+      <c r="AI36" s="127"/>
+      <c r="AJ36" s="127"/>
+      <c r="AK36" s="130"/>
+      <c r="AL36" s="130"/>
+      <c r="AM36" s="130"/>
+      <c r="AN36" s="131"/>
+      <c r="AO36" s="126"/>
+      <c r="AP36" s="127"/>
+      <c r="AQ36" s="127"/>
+      <c r="AR36" s="127"/>
+      <c r="AS36" s="127"/>
+      <c r="AT36" s="127"/>
+      <c r="AU36" s="127"/>
+      <c r="AV36" s="127"/>
+      <c r="AW36" s="127"/>
+      <c r="AX36" s="127"/>
+      <c r="AY36" s="127"/>
+      <c r="AZ36" s="127"/>
+      <c r="BA36" s="127"/>
+      <c r="BB36" s="127"/>
+      <c r="BC36" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="103">
+    <mergeCell ref="AO24:BC24"/>
+    <mergeCell ref="I24:AN24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I28:AN28"/>
+    <mergeCell ref="AO27:BC27"/>
+    <mergeCell ref="AO28:BC28"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I29:AN29"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:AN25"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="AO23:BC23"/>
+    <mergeCell ref="I23:AN23"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="I11:AN11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="AO19:BC19"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:AN21"/>
+    <mergeCell ref="AO21:BC21"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:AN20"/>
+    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I5:AN5"/>
+    <mergeCell ref="I7:AN7"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:AN6"/>
+    <mergeCell ref="I22:AN22"/>
+    <mergeCell ref="I13:AN13"/>
+    <mergeCell ref="AO11:BC11"/>
+    <mergeCell ref="I8:AN8"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="I17:AN17"/>
+    <mergeCell ref="AO17:BC17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="I18:AN18"/>
+    <mergeCell ref="AO18:BC18"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:AN15"/>
+    <mergeCell ref="AO15:BC15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:AN16"/>
+    <mergeCell ref="AO16:BC16"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="I19:AN19"/>
+    <mergeCell ref="AO36:BC36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AO35:BC35"/>
+    <mergeCell ref="I35:AN35"/>
+    <mergeCell ref="I36:AN36"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="I33:AN33"/>
+    <mergeCell ref="AO5:BC5"/>
+    <mergeCell ref="AO34:BC34"/>
+    <mergeCell ref="I34:AN34"/>
+    <mergeCell ref="AO33:BC33"/>
+    <mergeCell ref="I27:AN27"/>
+    <mergeCell ref="AO7:BC7"/>
+    <mergeCell ref="AO32:BC32"/>
+    <mergeCell ref="AO26:BC26"/>
+    <mergeCell ref="AO22:BC22"/>
+    <mergeCell ref="AO30:BC30"/>
+    <mergeCell ref="AO31:BC31"/>
+    <mergeCell ref="I26:AN26"/>
+    <mergeCell ref="I30:AN30"/>
+    <mergeCell ref="I31:AN31"/>
+    <mergeCell ref="AO25:BC25"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I9:AN9"/>
     <mergeCell ref="AY1:BC1"/>
     <mergeCell ref="AY2:BC2"/>
     <mergeCell ref="I1:AX2"/>
@@ -17388,85 +17473,6 @@
     <mergeCell ref="I32:AN32"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="AO36:BC36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="AO35:BC35"/>
-    <mergeCell ref="I35:AN35"/>
-    <mergeCell ref="I36:AN36"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="I33:AN33"/>
-    <mergeCell ref="AO5:BC5"/>
-    <mergeCell ref="AO34:BC34"/>
-    <mergeCell ref="I34:AN34"/>
-    <mergeCell ref="AO33:BC33"/>
-    <mergeCell ref="I27:AN27"/>
-    <mergeCell ref="AO7:BC7"/>
-    <mergeCell ref="AO32:BC32"/>
-    <mergeCell ref="AO26:BC26"/>
-    <mergeCell ref="AO22:BC22"/>
-    <mergeCell ref="AO30:BC30"/>
-    <mergeCell ref="AO31:BC31"/>
-    <mergeCell ref="I26:AN26"/>
-    <mergeCell ref="I30:AN30"/>
-    <mergeCell ref="I31:AN31"/>
-    <mergeCell ref="AO25:BC25"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I9:AN9"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I5:AN5"/>
-    <mergeCell ref="I7:AN7"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:AN6"/>
-    <mergeCell ref="I22:AN22"/>
-    <mergeCell ref="I13:AN13"/>
-    <mergeCell ref="AO11:BC11"/>
-    <mergeCell ref="I8:AN8"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="I17:AN17"/>
-    <mergeCell ref="AO17:BC17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="I18:AN18"/>
-    <mergeCell ref="AO18:BC18"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:AN15"/>
-    <mergeCell ref="AO15:BC15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:AN16"/>
-    <mergeCell ref="AO16:BC16"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I19:AN19"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="AO23:BC23"/>
-    <mergeCell ref="I23:AN23"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="AO13:BC13"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="I12:AN12"/>
-    <mergeCell ref="I11:AN11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="AO19:BC19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:AN21"/>
-    <mergeCell ref="AO21:BC21"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:AN20"/>
-    <mergeCell ref="AO20:BC20"/>
-    <mergeCell ref="AO24:BC24"/>
-    <mergeCell ref="I24:AN24"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I28:AN28"/>
-    <mergeCell ref="AO27:BC27"/>
-    <mergeCell ref="AO28:BC28"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I29:AN29"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:AN25"/>
   </mergeCells>
   <phoneticPr fontId="36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -17524,17 +17530,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
       <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:11">
@@ -17585,15 +17591,15 @@
       <c r="K6" s="47"/>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="68"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
       <c r="K7" s="47"/>
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1">
@@ -17683,17 +17689,17 @@
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="65" t="s">
         <v>1839</v>
       </c>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="68"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="67"/>
       <c r="K15" s="46"/>
     </row>
     <row r="16" spans="1:11" ht="36">
@@ -17821,17 +17827,17 @@
     </row>
     <row r="22" spans="1:11" ht="12" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="65" t="s">
         <v>1805</v>
       </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="68"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
       <c r="K22" s="46"/>
     </row>
     <row r="23" spans="1:11" ht="36">
@@ -17961,17 +17967,17 @@
     </row>
     <row r="29" spans="1:11" ht="12" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="65" t="s">
         <v>1806</v>
       </c>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="68"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="67"/>
       <c r="K29" s="46"/>
     </row>
     <row r="30" spans="1:11" ht="36">
@@ -18101,17 +18107,17 @@
     </row>
     <row r="36" spans="1:11" ht="12" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="66" t="s">
+      <c r="B36" s="65" t="s">
         <v>1808</v>
       </c>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="68"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="66"/>
+      <c r="J36" s="67"/>
       <c r="K36" s="46"/>
     </row>
     <row r="37" spans="1:11" ht="36">
@@ -18241,17 +18247,17 @@
     </row>
     <row r="43" spans="1:11" s="25" customFormat="1" ht="12" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="66" t="s">
+      <c r="B43" s="65" t="s">
         <v>1810</v>
       </c>
-      <c r="C43" s="67"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
-      <c r="I43" s="67"/>
-      <c r="J43" s="68"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
       <c r="K43" s="48"/>
     </row>
     <row r="44" spans="1:11" s="25" customFormat="1" ht="36">
@@ -18356,17 +18362,17 @@
     </row>
     <row r="49" spans="1:11" ht="48" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="66" t="s">
+      <c r="B49" s="65" t="s">
         <v>1811</v>
       </c>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="68"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="67"/>
       <c r="K49" s="46"/>
     </row>
     <row r="50" spans="1:11">
@@ -18511,17 +18517,17 @@
     </row>
     <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="66" t="s">
+      <c r="B57" s="65" t="s">
         <v>1813</v>
       </c>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="68"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="66"/>
+      <c r="I57" s="66"/>
+      <c r="J57" s="67"/>
       <c r="K57" s="46"/>
     </row>
     <row r="58" spans="1:11" ht="36">
@@ -18626,17 +18632,17 @@
     </row>
     <row r="63" spans="1:11" ht="24" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="66" t="s">
+      <c r="B63" s="65" t="s">
         <v>1815</v>
       </c>
-      <c r="C63" s="67"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="67"/>
-      <c r="H63" s="67"/>
-      <c r="I63" s="67"/>
-      <c r="J63" s="68"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="66"/>
+      <c r="E63" s="66"/>
+      <c r="F63" s="66"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="66"/>
+      <c r="I63" s="66"/>
+      <c r="J63" s="67"/>
       <c r="K63" s="46"/>
     </row>
     <row r="64" spans="1:11" ht="36">
@@ -18741,17 +18747,17 @@
     </row>
     <row r="69" spans="1:11" ht="24" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="66" t="s">
+      <c r="B69" s="65" t="s">
         <v>1817</v>
       </c>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="67"/>
-      <c r="I69" s="67"/>
-      <c r="J69" s="68"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="66"/>
+      <c r="I69" s="66"/>
+      <c r="J69" s="67"/>
       <c r="K69" s="46"/>
     </row>
     <row r="70" spans="1:11" ht="36">
@@ -18856,17 +18862,17 @@
     </row>
     <row r="75" spans="1:11" ht="12" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="66" t="s">
+      <c r="B75" s="65" t="s">
         <v>1818</v>
       </c>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="68"/>
+      <c r="C75" s="66"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="66"/>
+      <c r="F75" s="66"/>
+      <c r="G75" s="66"/>
+      <c r="H75" s="66"/>
+      <c r="I75" s="66"/>
+      <c r="J75" s="67"/>
       <c r="K75" s="46"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -19432,17 +19438,17 @@
     </row>
     <row r="101" spans="1:11" ht="12" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="66" t="s">
+      <c r="B101" s="65" t="s">
         <v>1819</v>
       </c>
-      <c r="C101" s="67"/>
-      <c r="D101" s="67"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="67"/>
-      <c r="G101" s="67"/>
-      <c r="H101" s="67"/>
-      <c r="I101" s="67"/>
-      <c r="J101" s="68"/>
+      <c r="C101" s="66"/>
+      <c r="D101" s="66"/>
+      <c r="E101" s="66"/>
+      <c r="F101" s="66"/>
+      <c r="G101" s="66"/>
+      <c r="H101" s="66"/>
+      <c r="I101" s="66"/>
+      <c r="J101" s="67"/>
       <c r="K101" s="46"/>
     </row>
     <row r="102" spans="1:11" ht="12" customHeight="1">
@@ -19961,17 +19967,17 @@
     </row>
     <row r="125" spans="1:11" ht="12" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="66" t="s">
+      <c r="B125" s="65" t="s">
         <v>1820</v>
       </c>
-      <c r="C125" s="67"/>
-      <c r="D125" s="67"/>
-      <c r="E125" s="67"/>
-      <c r="F125" s="67"/>
-      <c r="G125" s="67"/>
-      <c r="H125" s="67"/>
-      <c r="I125" s="67"/>
-      <c r="J125" s="68"/>
+      <c r="C125" s="66"/>
+      <c r="D125" s="66"/>
+      <c r="E125" s="66"/>
+      <c r="F125" s="66"/>
+      <c r="G125" s="66"/>
+      <c r="H125" s="66"/>
+      <c r="I125" s="66"/>
+      <c r="J125" s="67"/>
       <c r="K125" s="46"/>
     </row>
     <row r="126" spans="1:11" ht="36">
@@ -20490,17 +20496,17 @@
     </row>
     <row r="149" spans="1:11" ht="12" customHeight="1">
       <c r="A149" s="1"/>
-      <c r="B149" s="66" t="s">
+      <c r="B149" s="65" t="s">
         <v>1822</v>
       </c>
-      <c r="C149" s="67"/>
-      <c r="D149" s="67"/>
-      <c r="E149" s="67"/>
-      <c r="F149" s="67"/>
-      <c r="G149" s="67"/>
-      <c r="H149" s="67"/>
-      <c r="I149" s="67"/>
-      <c r="J149" s="68"/>
+      <c r="C149" s="66"/>
+      <c r="D149" s="66"/>
+      <c r="E149" s="66"/>
+      <c r="F149" s="66"/>
+      <c r="G149" s="66"/>
+      <c r="H149" s="66"/>
+      <c r="I149" s="66"/>
+      <c r="J149" s="67"/>
       <c r="K149" s="46"/>
     </row>
     <row r="150" spans="1:11" ht="36">
@@ -20743,17 +20749,17 @@
     </row>
     <row r="161" spans="1:11" ht="24" customHeight="1">
       <c r="A161" s="1"/>
-      <c r="B161" s="66" t="s">
+      <c r="B161" s="65" t="s">
         <v>1824</v>
       </c>
-      <c r="C161" s="67"/>
-      <c r="D161" s="67"/>
-      <c r="E161" s="67"/>
-      <c r="F161" s="67"/>
-      <c r="G161" s="67"/>
-      <c r="H161" s="67"/>
-      <c r="I161" s="67"/>
-      <c r="J161" s="68"/>
+      <c r="C161" s="66"/>
+      <c r="D161" s="66"/>
+      <c r="E161" s="66"/>
+      <c r="F161" s="66"/>
+      <c r="G161" s="66"/>
+      <c r="H161" s="66"/>
+      <c r="I161" s="66"/>
+      <c r="J161" s="67"/>
       <c r="K161" s="46"/>
     </row>
     <row r="162" spans="1:11">
@@ -20925,17 +20931,17 @@
     </row>
     <row r="170" spans="1:11" ht="12" customHeight="1">
       <c r="A170" s="1"/>
-      <c r="B170" s="66" t="s">
+      <c r="B170" s="65" t="s">
         <v>1818</v>
       </c>
-      <c r="C170" s="67"/>
-      <c r="D170" s="67"/>
-      <c r="E170" s="67"/>
-      <c r="F170" s="67"/>
-      <c r="G170" s="67"/>
-      <c r="H170" s="67"/>
-      <c r="I170" s="67"/>
-      <c r="J170" s="68"/>
+      <c r="C170" s="66"/>
+      <c r="D170" s="66"/>
+      <c r="E170" s="66"/>
+      <c r="F170" s="66"/>
+      <c r="G170" s="66"/>
+      <c r="H170" s="66"/>
+      <c r="I170" s="66"/>
+      <c r="J170" s="67"/>
       <c r="K170" s="46"/>
     </row>
     <row r="171" spans="1:11" ht="36">
@@ -21613,17 +21619,17 @@
     </row>
     <row r="202" spans="1:11" ht="24" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="66" t="s">
+      <c r="B202" s="65" t="s">
         <v>1827</v>
       </c>
-      <c r="C202" s="67"/>
-      <c r="D202" s="67"/>
-      <c r="E202" s="67"/>
-      <c r="F202" s="67"/>
-      <c r="G202" s="67"/>
-      <c r="H202" s="67"/>
-      <c r="I202" s="67"/>
-      <c r="J202" s="68"/>
+      <c r="C202" s="66"/>
+      <c r="D202" s="66"/>
+      <c r="E202" s="66"/>
+      <c r="F202" s="66"/>
+      <c r="G202" s="66"/>
+      <c r="H202" s="66"/>
+      <c r="I202" s="66"/>
+      <c r="J202" s="67"/>
       <c r="K202" s="46"/>
     </row>
     <row r="203" spans="1:11" ht="12" customHeight="1">
@@ -30789,17 +30795,17 @@
     </row>
     <row r="620" spans="1:11" ht="24" customHeight="1">
       <c r="A620" s="1"/>
-      <c r="B620" s="66" t="s">
+      <c r="B620" s="65" t="s">
         <v>1829</v>
       </c>
-      <c r="C620" s="67"/>
-      <c r="D620" s="67"/>
-      <c r="E620" s="67"/>
-      <c r="F620" s="67"/>
-      <c r="G620" s="67"/>
-      <c r="H620" s="67"/>
-      <c r="I620" s="67"/>
-      <c r="J620" s="68"/>
+      <c r="C620" s="66"/>
+      <c r="D620" s="66"/>
+      <c r="E620" s="66"/>
+      <c r="F620" s="66"/>
+      <c r="G620" s="66"/>
+      <c r="H620" s="66"/>
+      <c r="I620" s="66"/>
+      <c r="J620" s="67"/>
       <c r="K620" s="46"/>
     </row>
     <row r="621" spans="1:11" ht="12" customHeight="1">
@@ -39987,17 +39993,17 @@
     </row>
     <row r="1039" spans="1:11" ht="24" customHeight="1">
       <c r="A1039" s="1"/>
-      <c r="B1039" s="66" t="s">
+      <c r="B1039" s="65" t="s">
         <v>1831</v>
       </c>
-      <c r="C1039" s="67"/>
-      <c r="D1039" s="67"/>
-      <c r="E1039" s="67"/>
-      <c r="F1039" s="67"/>
-      <c r="G1039" s="67"/>
-      <c r="H1039" s="67"/>
-      <c r="I1039" s="67"/>
-      <c r="J1039" s="68"/>
+      <c r="C1039" s="66"/>
+      <c r="D1039" s="66"/>
+      <c r="E1039" s="66"/>
+      <c r="F1039" s="66"/>
+      <c r="G1039" s="66"/>
+      <c r="H1039" s="66"/>
+      <c r="I1039" s="66"/>
+      <c r="J1039" s="67"/>
       <c r="K1039" s="46"/>
     </row>
     <row r="1040" spans="1:11" ht="12" customHeight="1">
@@ -49251,17 +49257,17 @@
     </row>
     <row r="1462" spans="1:11" s="61" customFormat="1" ht="57" customHeight="1">
       <c r="A1462" s="51"/>
-      <c r="B1462" s="62" t="s">
+      <c r="B1462" s="147" t="s">
         <v>2361</v>
       </c>
-      <c r="C1462" s="63"/>
-      <c r="D1462" s="63"/>
-      <c r="E1462" s="63"/>
-      <c r="F1462" s="63"/>
-      <c r="G1462" s="63"/>
-      <c r="H1462" s="63"/>
-      <c r="I1462" s="63"/>
-      <c r="J1462" s="64"/>
+      <c r="C1462" s="148"/>
+      <c r="D1462" s="148"/>
+      <c r="E1462" s="148"/>
+      <c r="F1462" s="148"/>
+      <c r="G1462" s="148"/>
+      <c r="H1462" s="148"/>
+      <c r="I1462" s="148"/>
+      <c r="J1462" s="149"/>
       <c r="K1462" s="60"/>
     </row>
     <row r="1463" spans="1:11" s="61" customFormat="1" ht="42.75">
@@ -49433,11 +49439,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B620:J620"/>
-    <mergeCell ref="B1039:J1039"/>
-    <mergeCell ref="B170:J170"/>
-    <mergeCell ref="B161:J161"/>
-    <mergeCell ref="B149:J149"/>
     <mergeCell ref="B1462:J1462"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B7:J7"/>
@@ -49454,6 +49455,11 @@
     <mergeCell ref="B101:J101"/>
     <mergeCell ref="B125:J125"/>
     <mergeCell ref="B202:J202"/>
+    <mergeCell ref="B620:J620"/>
+    <mergeCell ref="B1039:J1039"/>
+    <mergeCell ref="B170:J170"/>
+    <mergeCell ref="B161:J161"/>
+    <mergeCell ref="B149:J149"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -49512,17 +49518,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
       <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11">
@@ -49581,7 +49587,7 @@
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K637"/>
+  <dimension ref="A1:K638"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="9" customWidth="1"/>
@@ -49624,17 +49630,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8"/>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
       <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:11">
@@ -49678,15 +49684,15 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="68"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
       <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:11">
@@ -49768,17 +49774,17 @@
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="65" t="s">
         <v>1832</v>
       </c>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="68"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="46"/>
     </row>
     <row r="15" spans="1:11" ht="36">
@@ -50147,17 +50153,17 @@
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="66" t="s">
+      <c r="B32" s="65" t="s">
         <v>1833</v>
       </c>
-      <c r="C32" s="145"/>
-      <c r="D32" s="145"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="145"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="145"/>
-      <c r="J32" s="146"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="70"/>
       <c r="K32" s="46"/>
     </row>
     <row r="33" spans="1:11" ht="24">
@@ -50539,17 +50545,17 @@
     </row>
     <row r="50" spans="1:11" ht="12" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="66" t="s">
+      <c r="B50" s="65" t="s">
         <v>1835</v>
       </c>
-      <c r="C50" s="145"/>
-      <c r="D50" s="145"/>
-      <c r="E50" s="145"/>
-      <c r="F50" s="145"/>
-      <c r="G50" s="145"/>
-      <c r="H50" s="145"/>
-      <c r="I50" s="145"/>
-      <c r="J50" s="146"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="70"/>
       <c r="K50" s="46"/>
     </row>
     <row r="51" spans="1:11" ht="36">
@@ -51711,17 +51717,17 @@
     </row>
     <row r="102" spans="1:11" ht="24" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="66" t="s">
+      <c r="B102" s="65" t="s">
         <v>1840</v>
       </c>
-      <c r="C102" s="67"/>
-      <c r="D102" s="67"/>
-      <c r="E102" s="67"/>
-      <c r="F102" s="67"/>
-      <c r="G102" s="67"/>
-      <c r="H102" s="67"/>
-      <c r="I102" s="67"/>
-      <c r="J102" s="68"/>
+      <c r="C102" s="66"/>
+      <c r="D102" s="66"/>
+      <c r="E102" s="66"/>
+      <c r="F102" s="66"/>
+      <c r="G102" s="66"/>
+      <c r="H102" s="66"/>
+      <c r="I102" s="66"/>
+      <c r="J102" s="67"/>
       <c r="K102" s="46"/>
     </row>
     <row r="103" spans="1:11" ht="36">
@@ -52528,17 +52534,17 @@
     </row>
     <row r="139" spans="1:11" ht="24" customHeight="1">
       <c r="A139" s="1"/>
-      <c r="B139" s="66" t="s">
+      <c r="B139" s="65" t="s">
         <v>1838</v>
       </c>
-      <c r="C139" s="67"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="67"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="67"/>
-      <c r="H139" s="67"/>
-      <c r="I139" s="67"/>
-      <c r="J139" s="68"/>
+      <c r="C139" s="66"/>
+      <c r="D139" s="66"/>
+      <c r="E139" s="66"/>
+      <c r="F139" s="66"/>
+      <c r="G139" s="66"/>
+      <c r="H139" s="66"/>
+      <c r="I139" s="66"/>
+      <c r="J139" s="67"/>
       <c r="K139" s="46"/>
     </row>
     <row r="140" spans="1:11" ht="24">
@@ -63706,17 +63712,17 @@
     </row>
     <row r="627" spans="1:11" s="61" customFormat="1" ht="14.25">
       <c r="A627" s="51"/>
-      <c r="B627" s="147" t="s">
+      <c r="B627" s="62" t="s">
         <v>2397</v>
       </c>
-      <c r="C627" s="148"/>
-      <c r="D627" s="148"/>
-      <c r="E627" s="148"/>
-      <c r="F627" s="148"/>
-      <c r="G627" s="148"/>
-      <c r="H627" s="148"/>
-      <c r="I627" s="148"/>
-      <c r="J627" s="149"/>
+      <c r="C627" s="63"/>
+      <c r="D627" s="63"/>
+      <c r="E627" s="63"/>
+      <c r="F627" s="63"/>
+      <c r="G627" s="63"/>
+      <c r="H627" s="63"/>
+      <c r="I627" s="63"/>
+      <c r="J627" s="64"/>
       <c r="K627" s="60"/>
     </row>
     <row r="628" spans="1:11" s="61" customFormat="1" ht="12" customHeight="1">
@@ -63953,6 +63959,29 @@
       <c r="J637" s="55"/>
       <c r="K637" s="60" t="s">
         <v>2395</v>
+      </c>
+    </row>
+    <row r="638" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A638" s="51"/>
+      <c r="B638" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C638" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="D638" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E638" s="52"/>
+      <c r="F638" s="52"/>
+      <c r="G638" s="53" t="s">
+        <v>2399</v>
+      </c>
+      <c r="H638" s="54"/>
+      <c r="I638" s="54"/>
+      <c r="J638" s="55"/>
+      <c r="K638" s="60" t="s">
+        <v>2400</v>
       </c>
     </row>
   </sheetData>

--- a/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MSBB/MSBBListLogicDef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MSBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB46C104-3E5F-4D9D-9077-4E76DB07C7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1E6A79-C718-45EA-8BE5-4AADFFFA1EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="814" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="22" r:id="rId1"/>
@@ -647,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10244" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10249" uniqueCount="2403">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -11162,13 +11162,19 @@
     <t>引数の検索区分（取引先入力補助検索区分）に対応する取引先情報を、取引先マスタから取得する&lt;br&gt;</t>
   </si>
   <si>
-    <t>受注登録用の取引先</t>
-  </si>
-  <si>
     <t>売上担当者</t>
   </si>
   <si>
     <t>Sale user cd.</t>
+  </si>
+  <si>
+    <t>納品先CD</t>
+  </si>
+  <si>
+    <t>Delivery cd.</t>
+  </si>
+  <si>
+    <t>受注登録用の得意先</t>
   </si>
 </sst>
 </file>
@@ -49587,7 +49593,7 @@
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K638"/>
+  <dimension ref="A1:K639"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="9" customWidth="1"/>
@@ -63694,7 +63700,7 @@
       </c>
       <c r="C626" s="59"/>
       <c r="D626" s="53" t="s">
-        <v>2398</v>
+        <v>2402</v>
       </c>
       <c r="E626" s="55"/>
       <c r="F626" s="52">
@@ -63975,13 +63981,36 @@
       <c r="E638" s="52"/>
       <c r="F638" s="52"/>
       <c r="G638" s="53" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="H638" s="54"/>
       <c r="I638" s="54"/>
       <c r="J638" s="55"/>
       <c r="K638" s="60" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="639" spans="1:11" s="61" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A639" s="51"/>
+      <c r="B639" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C639" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="D639" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E639" s="52"/>
+      <c r="F639" s="52"/>
+      <c r="G639" s="53" t="s">
         <v>2400</v>
+      </c>
+      <c r="H639" s="54"/>
+      <c r="I639" s="54"/>
+      <c r="J639" s="55"/>
+      <c r="K639" s="60" t="s">
+        <v>2401</v>
       </c>
     </row>
   </sheetData>
